--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-1</v>
+        <v>25-서초구-2</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -533,13 +533,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q5" t="str">
-        <v>서초동 1318-4</v>
+        <v>서초동 1319-1</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>강남역 #10번출구 앞 도로</v>
+        <v>강남역 #8번출구 앞 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-서초구-2</v>
+        <v>25-서초구-3</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -595,13 +595,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q6" t="str">
-        <v>서초동 1319-1</v>
+        <v>서초동 1319-11</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>강남역 #8번출구 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="str">
         <v>강남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-서초구-3</v>
+        <v>25-서초구-4</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -654,16 +654,16 @@
         <v>일반</v>
       </c>
       <c r="P7" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q7" t="str">
-        <v>서초동 1319-11</v>
+        <v>서초동 1319-13</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>강남역 #6번출구 뒤 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-서초구-4</v>
+        <v>25-서초구-5</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -719,13 +719,13 @@
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v>서초동 1319-13</v>
+        <v>서초동 1328-3</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>강남역 #6번출구 뒤 도로</v>
+        <v>우리은행 서초금융센터 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-서초구-5</v>
+        <v>25-서초구-6</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -778,16 +778,16 @@
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>포장 복구개소</v>
       </c>
       <c r="Q9" t="str">
-        <v>서초동 1328-3</v>
+        <v>서초동 1328-10</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>우리은행 서초금융센터 앞 도로</v>
+        <v>강남역 #5번출구 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-서초구-6</v>
+        <v>25-서초구-7</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -840,16 +840,16 @@
         <v>일반</v>
       </c>
       <c r="P10" t="str">
-        <v>포장 복구개소</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q10" t="str">
-        <v>서초동 1328-10</v>
+        <v>서초동 1328-11</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>강남역 #5번출구 앞 도로</v>
+        <v>도씨의 빛Ⅱ 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-서초구-7</v>
+        <v>25-서초구-8</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -902,16 +902,16 @@
         <v>일반</v>
       </c>
       <c r="P11" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q11" t="str">
-        <v>서초동 1328-11</v>
+        <v>서초동 1329</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>도씨의 빛Ⅱ 앞 도로</v>
+        <v>삼성화제 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-서초구-8</v>
+        <v>25-서초구-9</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -964,16 +964,16 @@
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q12" t="str">
-        <v>서초동 1329</v>
+        <v>서초동 1329-7</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>삼성화제 앞 도로</v>
+        <v>신한투자증권 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-서초구-9</v>
+        <v>25-서초구-10</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1029,13 +1029,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q13" t="str">
-        <v>서초동 1329-7</v>
+        <v>서초동 1329-8</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>신한투자증권 앞 도로</v>
+        <v>모닝글로리 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-서초구-10</v>
+        <v>25-서초구-11</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1088,16 +1088,16 @@
         <v>일반</v>
       </c>
       <c r="P14" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q14" t="str">
-        <v>서초동 1329-8</v>
+        <v>서초동 1329-10</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>모닝글로리 앞 도로</v>
+        <v>우성아파트 사거리 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-서초구-11</v>
+        <v>25-서초구-12</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1150,16 +1150,16 @@
         <v>일반</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q15" t="str">
-        <v>서초동 1329-10</v>
+        <v>서초동 1337-32</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>우성아파트 사거리 도로</v>
+        <v>한국투자증권 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-서초구-12</v>
+        <v>25-서초구-13</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1212,16 +1212,16 @@
         <v>일반</v>
       </c>
       <c r="P16" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q16" t="str">
-        <v>서초동 1337-32</v>
+        <v>서초동 1337-22</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>한국투자증권 앞 도로</v>
+        <v>디오빌프라임 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-서초구-13</v>
+        <v>25-서초구-14</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1277,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>서초동 1337-22</v>
+        <v>서초동 1338-23</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>디오빌프라임 앞 도로</v>
+        <v>투썸플레이스 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-서초구-14</v>
+        <v>25-서초구-15</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1339,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>서초동 1338-23</v>
+        <v>서초동 1338-20</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>투썸플레이스 도로</v>
+        <v>현대렉시온 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-서초구-15</v>
+        <v>25-서초구-16</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1368,7 +1368,7 @@
         <v>거북등</v>
       </c>
       <c r="F19" t="str">
-        <v>양호</v>
+        <v>건조</v>
       </c>
       <c r="G19" t="str">
         <v>13.5</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>서초동 1338-20</v>
+        <v>서초동 1339-9</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>현대렉시온 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-서초구-16</v>
+        <v>25-서초구-17</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1463,13 +1463,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>서초동 1339-9</v>
+        <v>서초동 1340-6</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>KIA 서초지점 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1522,7 +1522,7 @@
         <v>일반</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q21" t="str">
         <v>서초동 1340-6</v>
@@ -1531,7 +1531,7 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>KIA 서초지점 앞 도로</v>
+        <v>남강매점 앞 횡단보도</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,13 +1539,13 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="str">
         <v>강남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-서초구-18</v>
+        <v>25-서초구-19</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
@@ -1584,16 +1584,16 @@
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q22" t="str">
-        <v>서초동 1340-6</v>
+        <v>서초동 1357-33</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>남강매점 앞 횡단보도</v>
+        <v>한국디지털 평생교육원 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" t="str">
         <v>강남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-서초구-19</v>
+        <v>25-서초구-20</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
@@ -1646,16 +1646,16 @@
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q23" t="str">
-        <v>서초동 1357-33</v>
+        <v>서초동 1357-35</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>한국디지털 평생교육원 앞 도로</v>
+        <v>부산은행 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,13 +1663,13 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="str">
         <v>강남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-서초구-20</v>
+        <v>25-서초구-21</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
@@ -1711,13 +1711,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q24" t="str">
-        <v>서초동 1357-35</v>
+        <v>서초동 1358-6</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>부산은행 앞 도로</v>
+        <v>송남빌딩 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" t="str">
         <v>강남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-서초구-21</v>
+        <v>25-서초구-22</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
       </c>
       <c r="E25" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F25" t="str">
         <v>건조</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1764,22 +1764,22 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O25" t="str">
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q25" t="str">
-        <v>서초동 1358-6</v>
+        <v>서초동 1361-1</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>송남빌딩 앞 도로</v>
+        <v>보들설곰탕 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="str">
         <v>강남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-서초구-22</v>
+        <v>25-서초구-23</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1835,13 +1835,13 @@
         <v/>
       </c>
       <c r="Q26" t="str">
-        <v>서초동 1361-1</v>
+        <v>서초동 1361-5</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>보들설곰탕 앞 도로</v>
+        <v>새움빌딩 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,19 +1849,19 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" t="str">
         <v>강남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-서초구-23</v>
+        <v>25-서초구-24</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
       </c>
       <c r="E27" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F27" t="str">
         <v>건조</v>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O27" t="str">
         <v>일반</v>
@@ -1897,13 +1897,13 @@
         <v/>
       </c>
       <c r="Q27" t="str">
-        <v>서초동 1361-5</v>
+        <v>서초동 1361-10</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>새움빌딩 앞 도로</v>
+        <v>호텔 페이토 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" t="str">
         <v>강남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-서초구-24</v>
+        <v>25-서초구-25</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q28" t="str">
-        <v>서초동 1361-10</v>
+        <v>서초동 1362</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>호텔 페이토 앞 도로</v>
+        <v>e마트24 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" t="str">
         <v>강남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-서초구-25</v>
+        <v>25-서초구-26</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2018,16 +2018,16 @@
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q29" t="str">
-        <v>서초동 1362</v>
+        <v>서초동 1362-26</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>e마트24 앞 도로</v>
+        <v>힐든가든인 서울강남 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="str">
         <v>강남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-서초구-26</v>
+        <v>25-서초구-27</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2080,16 +2080,16 @@
         <v>일반</v>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q30" t="str">
-        <v>서초동 1362-26</v>
+        <v>서초동 1362-27</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>힐든가든인 서울강남 앞 도로</v>
+        <v>니드오피스텔 앞 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" t="str">
         <v>강남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-서초구-27</v>
+        <v>25-서초구-28</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
@@ -2142,16 +2142,16 @@
         <v>일반</v>
       </c>
       <c r="P31" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q31" t="str">
-        <v>서초동 1362-27</v>
+        <v>서초동 1366-7</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>니드오피스텔 앞 도로</v>
+        <v>깐부치킨 앞 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,13 +2159,13 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-서초구-28</v>
+        <v>25-서초구-29</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
@@ -2204,16 +2204,16 @@
         <v>일반</v>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q32" t="str">
-        <v>서초동 1366-7</v>
+        <v>서초동 1366-9</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>깐부치킨 앞 도로</v>
+        <v>양재역 교차로 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,13 +2221,13 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-서초구-29</v>
+        <v>25-서초구-30</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
@@ -2266,16 +2266,16 @@
         <v>일반</v>
       </c>
       <c r="P33" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q33" t="str">
-        <v>서초동 1366-9</v>
+        <v>양재동 23</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>양재역 교차로 도로</v>
+        <v>바나프레소 앞 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,13 +2283,13 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-서초구-30</v>
+        <v>25-서초구-31</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
@@ -2331,13 +2331,13 @@
         <v/>
       </c>
       <c r="Q34" t="str">
-        <v>양재동 23</v>
+        <v>양재동 25</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>바나프레소 앞 도로</v>
+        <v>서초문화 예술회관 앞 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,13 +2345,13 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" t="str">
         <v>강남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-서초구-31</v>
+        <v>25-서초구-32</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
@@ -2393,13 +2393,13 @@
         <v/>
       </c>
       <c r="Q35" t="str">
-        <v>양재동 25</v>
+        <v>양재동 14-4</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>서초문화 예술회관 앞 도로</v>
+        <v>모산빌딩 앞 횡단보도</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,19 +2407,19 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" t="str">
         <v>강남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-서초구-32</v>
+        <v>25-서초구-33</v>
       </c>
       <c r="D36" t="str">
-        <v>양호</v>
+        <v>50</v>
       </c>
       <c r="E36" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F36" t="str">
         <v>건조</v>
@@ -2430,11 +2430,11 @@
       <c r="H36" t="str">
         <v>-</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -2446,22 +2446,22 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O36" t="str">
         <v>일반</v>
       </c>
       <c r="P36" t="str">
-        <v/>
+        <v>보도침하5cm</v>
       </c>
       <c r="Q36" t="str">
-        <v>양재동 14-4</v>
+        <v>양재동 67-7</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>모산빌딩 앞 횡단보도</v>
+        <v>바나프레스 앞 보도</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,19 +2469,19 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="str">
         <v>강남대로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-서초구-33</v>
+        <v>25-서초구-34</v>
       </c>
       <c r="D37" t="str">
-        <v>50</v>
+        <v>양호</v>
       </c>
       <c r="E37" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F37" t="str">
         <v>건조</v>
@@ -2492,11 +2492,11 @@
       <c r="H37" t="str">
         <v>-</v>
       </c>
-      <c r="I37" t="b">
+      <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -2508,22 +2508,22 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O37" t="str">
         <v>일반</v>
       </c>
       <c r="P37" t="str">
-        <v>보도침하5cm</v>
+        <v/>
       </c>
       <c r="Q37" t="str">
-        <v>양재동 67-7</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>바나프레스 앞 보도</v>
+        <v>교육개발원 사거리 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,19 +2531,19 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" t="str">
         <v>강남대로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-서초구-34</v>
+        <v>25-서초구-35</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
       </c>
       <c r="E38" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F38" t="str">
         <v>건조</v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O38" t="str">
         <v>일반</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동 109</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>교육개발원 사거리 도로</v>
+        <v>카페 릴리블랑 앞 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,19 +2593,19 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" t="str">
         <v>강남대로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-서초구-35</v>
+        <v>25-서초구-36</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
       </c>
       <c r="E39" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F39" t="str">
         <v>건조</v>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O39" t="str">
         <v>일반</v>
@@ -2641,13 +2641,13 @@
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>양재동 109</v>
+        <v>양재동 125</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>카페 릴리블랑 앞 도로</v>
+        <v>넥스팜 코리아 앞 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" t="str">
         <v>강남대로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-서초구-36</v>
+        <v>25-서초구-37</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2703,13 +2703,13 @@
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>양재동 125</v>
+        <v>양재동 80-3</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>넥스팜 코리아 앞 도로</v>
+        <v>도야짬뽕 앞 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-서초구-37</v>
+        <v>25-서초구-38</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2765,13 +2765,13 @@
         <v/>
       </c>
       <c r="Q41" t="str">
-        <v>양재동 80-3</v>
+        <v>양재동 237-1</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>도야짬뽕 앞 도로</v>
+        <v>공영주차장 앞 도로</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,13 +2779,13 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-서초구-38</v>
+        <v>25-서초구-39</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
@@ -2827,13 +2827,13 @@
         <v/>
       </c>
       <c r="Q42" t="str">
-        <v>양재동 237-1</v>
+        <v>신원동 308-1</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>공영주차장 앞 도로</v>
+        <v>가로등(청계산로145) 양차선 도로</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B43" t="str">
         <v>청계산로</v>
       </c>
       <c r="C43" t="str">
-        <v>25-서초구-39</v>
+        <v>25-서초구-40</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
@@ -2889,13 +2889,13 @@
         <v/>
       </c>
       <c r="Q43" t="str">
-        <v>신원동 308-1</v>
+        <v>원지동 294-3</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>가로등(청계산로145) 양차선 도로</v>
+        <v>전봇대(원지간37H1) 양차선 도로</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,13 +2903,13 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" t="str">
         <v>청계산로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-서초구-40</v>
+        <v>25-서초구-41</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
@@ -2948,16 +2948,16 @@
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>거북등 맨홀침하4cm</v>
       </c>
       <c r="Q44" t="str">
-        <v>원지동 294-3</v>
+        <v>원지동 594-1</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>전봇대(원지간37H1) 양차선 도로</v>
+        <v>도로교통표지판 앞 상수도맨홀 도로</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B45" t="str">
         <v>청계산로</v>
       </c>
       <c r="C45" t="str">
-        <v>25-서초구-41</v>
+        <v>25-서초구-42</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
@@ -3010,16 +3010,16 @@
         <v>일반</v>
       </c>
       <c r="P45" t="str">
-        <v>거북등 맨홀침하4cm</v>
+        <v/>
       </c>
       <c r="Q45" t="str">
-        <v>원지동 594-1</v>
+        <v>신원동 280</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>도로교통표지판 앞 상수도맨홀 도로</v>
+        <v>공영주차장 앞 T 교차로 양차선 도로</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,13 +3027,13 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" t="str">
         <v>청계산로</v>
       </c>
       <c r="C46" t="str">
-        <v>25-서초구-42</v>
+        <v>25-서초구-43</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
@@ -3075,13 +3075,13 @@
         <v/>
       </c>
       <c r="Q46" t="str">
-        <v>신원동 280</v>
+        <v>신원동 278-6</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>공영주차장 앞 T 교차로 양차선 도로</v>
+        <v>공영주차장 앞 양차선 도로</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,13 +3089,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B47" t="str">
         <v>청계산로</v>
       </c>
       <c r="C47" t="str">
-        <v>25-서초구-43</v>
+        <v>25-서초구-44</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
@@ -3134,16 +3134,16 @@
         <v>일반</v>
       </c>
       <c r="P47" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q47" t="str">
-        <v>신원동 278-6</v>
+        <v>신원동 611</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>공영주차장 앞 양차선 도로</v>
+        <v>투썸플레이스 앞 보도</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,19 +3151,19 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B48" t="str">
         <v>청계산로</v>
       </c>
       <c r="C48" t="str">
-        <v>25-서초구-44</v>
+        <v>25-서초구-45</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F48" t="str">
         <v>건조</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3190,22 +3190,22 @@
         <v>0</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O48" t="str">
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v>보도침하4cm</v>
+        <v/>
       </c>
       <c r="Q48" t="str">
-        <v>신원동 611</v>
+        <v>신원동 612</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>투썸플레이스 앞 보도</v>
+        <v>LAB 앞 도로</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49" t="str">
         <v>청계산로</v>
       </c>
       <c r="C49" t="str">
-        <v>25-서초구-45</v>
+        <v>25-서초구-46</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
       </c>
       <c r="E49" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F49" t="str">
         <v>건조</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -3252,22 +3252,22 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O49" t="str">
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q49" t="str">
-        <v>신원동 612</v>
+        <v>신원동 660</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>LAB 앞 도로</v>
+        <v>심플리시티 앞 보도</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,13 +3275,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" t="str">
         <v>청계산로</v>
       </c>
       <c r="C50" t="str">
-        <v>25-서초구-46</v>
+        <v>25-서초구-47</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3320,16 +3320,16 @@
         <v>일반</v>
       </c>
       <c r="P50" t="str">
-        <v>보도침하4cm</v>
+        <v>보도침하3cm</v>
       </c>
       <c r="Q50" t="str">
-        <v>신원동 660</v>
+        <v>신원동 197-1</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>심플리시티 앞 보도</v>
+        <v>부안애서 맞음편 보도</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B51" t="str">
         <v>청계산로</v>
       </c>
       <c r="C51" t="str">
-        <v>25-서초구-47</v>
+        <v>25-서초구-48</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3382,16 +3382,16 @@
         <v>일반</v>
       </c>
       <c r="P51" t="str">
-        <v>보도침하3cm</v>
+        <v/>
       </c>
       <c r="Q51" t="str">
-        <v>신원동 197-1</v>
+        <v>원지동 384-1</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>부안애서 맞음편 보도</v>
+        <v>커피플라워 앞 양차선 도로</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B52" t="str">
         <v>청계산로</v>
       </c>
       <c r="C52" t="str">
-        <v>25-서초구-48</v>
+        <v>25-서초구-49</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3447,13 +3447,13 @@
         <v/>
       </c>
       <c r="Q52" t="str">
-        <v>원지동 384-1</v>
+        <v>신원동 192-73</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>커피플라워 앞 양차선 도로</v>
+        <v>봉평막국수 앞 양차선 도로</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B53" t="str">
         <v>청계산로</v>
       </c>
       <c r="C53" t="str">
-        <v>25-서초구-49</v>
+        <v>25-서초구-50</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3509,13 +3509,13 @@
         <v/>
       </c>
       <c r="Q53" t="str">
-        <v>신원동 192-73</v>
+        <v>신원동 172-1</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>봉평막국수 앞 양차선 도로</v>
+        <v>향린조경 앞 양차선 도로</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3523,13 +3523,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" t="str">
         <v>청계산로</v>
       </c>
       <c r="C54" t="str">
-        <v>25-서초구-50</v>
+        <v>25-서초구-51</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3571,13 +3571,13 @@
         <v/>
       </c>
       <c r="Q54" t="str">
-        <v>신원동 172-1</v>
+        <v>신원동 153</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>향린조경 앞 양차선 도로</v>
+        <v>삼석원 앞 양차선 도로</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B55" t="str">
         <v>청계산로</v>
       </c>
       <c r="C55" t="str">
-        <v>25-서초구-51</v>
+        <v>25-서초구-52</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3633,13 +3633,13 @@
         <v/>
       </c>
       <c r="Q55" t="str">
-        <v>신원동 153</v>
+        <v>신원동 150-1</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>삼석원 앞 양차선 도로</v>
+        <v>성심조경 앞 양차선 도로</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3647,13 +3647,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B56" t="str">
         <v>청계산로</v>
       </c>
       <c r="C56" t="str">
-        <v>25-서초구-52</v>
+        <v>25-서초구-53</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3692,16 +3692,16 @@
         <v>일반</v>
       </c>
       <c r="P56" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q56" t="str">
-        <v>신원동 150-1</v>
+        <v>원지동 470-1</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>성심조경 앞 양차선 도로</v>
+        <v>가로등(청계산로154) 앞 보도</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3709,13 +3709,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B57" t="str">
         <v>청계산로</v>
       </c>
       <c r="C57" t="str">
-        <v>25-서초구-53</v>
+        <v>25-서초구-54</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3754,16 +3754,16 @@
         <v>일반</v>
       </c>
       <c r="P57" t="str">
-        <v>5cm이하 침하</v>
+        <v>보도침하</v>
       </c>
       <c r="Q57" t="str">
-        <v>원지동 470-1</v>
+        <v>원지동 491-6</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>가로등(청계산로154) 앞 보도</v>
+        <v>가로등(청계산로156) 맞음편 보도</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3771,13 +3771,13 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B58" t="str">
         <v>청계산로</v>
       </c>
       <c r="C58" t="str">
-        <v>25-서초구-54</v>
+        <v>25-서초구-55</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3816,16 +3816,16 @@
         <v>일반</v>
       </c>
       <c r="P58" t="str">
-        <v>보도침하</v>
+        <v/>
       </c>
       <c r="Q58" t="str">
-        <v>원지동 491-6</v>
+        <v>원지동 493</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>가로등(청계산로156) 맞음편 보도</v>
+        <v>양재조경 앞 양차선 도로</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3833,13 +3833,13 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B59" t="str">
         <v>청계산로</v>
       </c>
       <c r="C59" t="str">
-        <v>25-서초구-55</v>
+        <v>25-서초구-56</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3881,13 +3881,13 @@
         <v/>
       </c>
       <c r="Q59" t="str">
-        <v>원지동 493</v>
+        <v>원지동 497-3</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>양재조경 앞 양차선 도로</v>
+        <v>가로등(청계산로168) 앞 양차선 도로</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3895,13 +3895,13 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B60" t="str">
         <v>청계산로</v>
       </c>
       <c r="C60" t="str">
-        <v>25-서초구-56</v>
+        <v>25-서초구-57</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
@@ -3943,13 +3943,13 @@
         <v/>
       </c>
       <c r="Q60" t="str">
-        <v>원지동 497-3</v>
+        <v>신원동 산 60-2</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>가로등(청계산로168) 앞 양차선 도로</v>
+        <v>대원조경 앞 양차선 도로</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3957,13 +3957,13 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B61" t="str">
         <v>청계산로</v>
       </c>
       <c r="C61" t="str">
-        <v>25-서초구-57</v>
+        <v>25-서초구-58</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
@@ -4005,13 +4005,13 @@
         <v/>
       </c>
       <c r="Q61" t="str">
-        <v>신원동 산 60-2</v>
+        <v>신원동 105-4</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>대원조경 앞 양차선 도로</v>
+        <v>둥지조경 제2농장 앞 양차선 도로</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4019,13 +4019,13 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B62" t="str">
         <v>청계산로</v>
       </c>
       <c r="C62" t="str">
-        <v>25-서초구-58</v>
+        <v>25-서초구-59</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
@@ -4067,13 +4067,13 @@
         <v/>
       </c>
       <c r="Q62" t="str">
-        <v>신원동 105-4</v>
+        <v>신원동 105-33</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>둥지조경 제2농장 앞 양차선 도로</v>
+        <v>한백자생식물원 앞 양차선 도로</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4081,13 +4081,13 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B63" t="str">
         <v>청계산로</v>
       </c>
       <c r="C63" t="str">
-        <v>25-서초구-59</v>
+        <v>25-서초구-60</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
@@ -4126,16 +4126,16 @@
         <v>일반</v>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q63" t="str">
-        <v>신원동 105-33</v>
+        <v>신원동 105-19</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>한백자생식물원 앞 양차선 도로</v>
+        <v>가로등(청계산로190) 앞 양차선 도로</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4143,19 +4143,19 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B64" t="str">
         <v>청계산로</v>
       </c>
       <c r="C64" t="str">
-        <v>25-서초구-60</v>
+        <v>25-서초구-61</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
       </c>
       <c r="E64" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F64" t="str">
         <v>건조</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -4182,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O64" t="str">
         <v>일반</v>
@@ -4191,13 +4191,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q64" t="str">
-        <v>신원동 105-19</v>
+        <v>신원동 44-1</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>가로등(청계산로190) 앞 양차선 도로</v>
+        <v>새정이마을 입구 교차로</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4205,19 +4205,19 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B65" t="str">
         <v>청계산로</v>
       </c>
       <c r="C65" t="str">
-        <v>25-서초구-61</v>
+        <v>25-서초구-62</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
       </c>
       <c r="E65" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F65" t="str">
         <v>건조</v>
@@ -4250,16 +4250,16 @@
         <v>일반</v>
       </c>
       <c r="P65" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q65" t="str">
-        <v>신원동 44-1</v>
+        <v>신원동 44-5</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>새정이마을 입구 교차로</v>
+        <v>은하조경 앞 양차선 도로</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4267,13 +4267,13 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B66" t="str">
         <v>청계산로</v>
       </c>
       <c r="C66" t="str">
-        <v>25-서초구-62</v>
+        <v>25-서초구-63</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4315,13 +4315,13 @@
         <v/>
       </c>
       <c r="Q66" t="str">
-        <v>신원동 44-5</v>
+        <v>신원동 57</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>은하조경 앞 양차선 도로</v>
+        <v>서림원예종묘 앞 양차선 도로</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4329,19 +4329,19 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B67" t="str">
         <v>청계산로</v>
       </c>
       <c r="C67" t="str">
-        <v>25-서초구-63</v>
+        <v>25-서초구-64</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
       </c>
       <c r="E67" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F67" t="str">
         <v>건조</v>
@@ -4356,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O67" t="str">
         <v>일반</v>
@@ -4377,27 +4377,27 @@
         <v/>
       </c>
       <c r="Q67" t="str">
-        <v>신원동 57</v>
+        <v>신원동 64-1</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>서림원예종묘 앞 양차선 도로</v>
+        <v>옥천조경 앞 양차선 도로</v>
       </c>
       <c r="T67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68">
-        <v>64</v>
+      <c r="A68" t="str">
+        <v>26-01</v>
       </c>
       <c r="B68" t="str">
-        <v>청계산로</v>
+        <v>강남대로</v>
       </c>
       <c r="C68" t="str">
-        <v>25-서초구-64</v>
+        <v>26-서초구-01</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
@@ -4406,46 +4406,46 @@
         <v>거북등</v>
       </c>
       <c r="F68" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G68" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H68" t="str">
         <v>-</v>
       </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>3</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>1</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
+      <c r="I68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J68" t="str">
+        <v>3</v>
+      </c>
+      <c r="K68" t="str">
+        <v>0</v>
+      </c>
+      <c r="L68" t="str">
+        <v>1</v>
+      </c>
+      <c r="M68" t="str">
+        <v>0</v>
+      </c>
+      <c r="N68" t="str">
         <v>4</v>
       </c>
       <c r="O68" t="str">
         <v>일반</v>
       </c>
       <c r="P68" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q68" t="str">
-        <v>신원동 64-1</v>
+        <v>서초동1318-4</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>옥천조경 앞 양차선 도로</v>
+        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4453,13 +4453,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B69" t="str">
         <v>강남대로</v>
       </c>
       <c r="C69" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D69" t="str">
         <v>양호</v>
@@ -4501,27 +4501,27 @@
         <v>-</v>
       </c>
       <c r="Q69" t="str">
-        <v>서초동1318-4</v>
+        <v>강남역사거리</v>
       </c>
       <c r="R69" t="str">
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
+        <v>강남역사거리(강남대로396)</v>
       </c>
       <c r="T69" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B70" t="str">
         <v>강남대로</v>
       </c>
       <c r="C70" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D70" t="str">
         <v>양호</v>
@@ -4563,21 +4563,83 @@
         <v>-</v>
       </c>
       <c r="Q70" t="str">
-        <v>강남역사거리</v>
+        <v>서초동1319-5</v>
       </c>
       <c r="R70" t="str">
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>강남역사거리(강남대로396)</v>
+        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
       </c>
       <c r="T70" t="str">
-        <v>현장확인필요</v>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>26-04</v>
+      </c>
+      <c r="B71" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C71" t="str">
+        <v>26-서초구-04</v>
+      </c>
+      <c r="D71" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E71" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F71" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G71" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H71" t="str">
+        <v>-</v>
+      </c>
+      <c r="I71" t="str">
+        <v>0</v>
+      </c>
+      <c r="J71" t="str">
+        <v>3</v>
+      </c>
+      <c r="K71" t="str">
+        <v>0</v>
+      </c>
+      <c r="L71" t="str">
+        <v>1</v>
+      </c>
+      <c r="M71" t="str">
+        <v>0</v>
+      </c>
+      <c r="N71" t="str">
+        <v>4</v>
+      </c>
+      <c r="O71" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P71" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>서초동1319-11</v>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
+      </c>
+      <c r="T71" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T71"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T71"/>
+  <dimension ref="A1:T78"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4637,9 +4637,443 @@
         <v/>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>26-05</v>
+      </c>
+      <c r="B72" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C72" t="str">
+        <v>26-서초구-05</v>
+      </c>
+      <c r="D72" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E72" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F72" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G72" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H72" t="str">
+        <v>-</v>
+      </c>
+      <c r="I72" t="str">
+        <v>0</v>
+      </c>
+      <c r="J72" t="str">
+        <v>3</v>
+      </c>
+      <c r="K72" t="str">
+        <v>0</v>
+      </c>
+      <c r="L72" t="str">
+        <v>1</v>
+      </c>
+      <c r="M72" t="str">
+        <v>0</v>
+      </c>
+      <c r="N72" t="str">
+        <v>4</v>
+      </c>
+      <c r="O72" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P72" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q72" t="str">
+        <v>서초동1328-3</v>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
+      </c>
+      <c r="T72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>26-06</v>
+      </c>
+      <c r="B73" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C73" t="str">
+        <v>26-서초구-06</v>
+      </c>
+      <c r="D73" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E73" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F73" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G73" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H73" t="str">
+        <v>-</v>
+      </c>
+      <c r="I73" t="str">
+        <v>0</v>
+      </c>
+      <c r="J73" t="str">
+        <v>3</v>
+      </c>
+      <c r="K73" t="str">
+        <v>0</v>
+      </c>
+      <c r="L73" t="str">
+        <v>1</v>
+      </c>
+      <c r="M73" t="str">
+        <v>0</v>
+      </c>
+      <c r="N73" t="str">
+        <v>4</v>
+      </c>
+      <c r="O73" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P73" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q73" t="str">
+        <v>서초동1328-11</v>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
+      </c>
+      <c r="T73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>26-07</v>
+      </c>
+      <c r="B74" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C74" t="str">
+        <v>26-서초구-07</v>
+      </c>
+      <c r="D74" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E74" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F74" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G74" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H74" t="str">
+        <v>-</v>
+      </c>
+      <c r="I74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J74" t="str">
+        <v>3</v>
+      </c>
+      <c r="K74" t="str">
+        <v>0</v>
+      </c>
+      <c r="L74" t="str">
+        <v>1</v>
+      </c>
+      <c r="M74" t="str">
+        <v>0</v>
+      </c>
+      <c r="N74" t="str">
+        <v>4</v>
+      </c>
+      <c r="O74" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P74" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q74" t="str">
+        <v>서초동1329</v>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
+      </c>
+      <c r="T74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>26-08</v>
+      </c>
+      <c r="B75" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C75" t="str">
+        <v>26-서초구-08</v>
+      </c>
+      <c r="D75" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E75" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F75" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G75" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H75" t="str">
+        <v>-</v>
+      </c>
+      <c r="I75" t="str">
+        <v>0</v>
+      </c>
+      <c r="J75" t="str">
+        <v>3</v>
+      </c>
+      <c r="K75" t="str">
+        <v>0</v>
+      </c>
+      <c r="L75" t="str">
+        <v>1</v>
+      </c>
+      <c r="M75" t="str">
+        <v>0</v>
+      </c>
+      <c r="N75" t="str">
+        <v>4</v>
+      </c>
+      <c r="O75" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P75" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>서초동1329-4</v>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v>우남빌딩 앞 도로(강남대로349)</v>
+      </c>
+      <c r="T75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>26-09</v>
+      </c>
+      <c r="B76" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C76" t="str">
+        <v>26-서초구-09</v>
+      </c>
+      <c r="D76" t="str">
+        <v>불량</v>
+      </c>
+      <c r="E76" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F76" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G76" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H76" t="str">
+        <v>-</v>
+      </c>
+      <c r="I76" t="str">
+        <v>9</v>
+      </c>
+      <c r="J76" t="str">
+        <v>3</v>
+      </c>
+      <c r="K76" t="str">
+        <v>0</v>
+      </c>
+      <c r="L76" t="str">
+        <v>1</v>
+      </c>
+      <c r="M76" t="str">
+        <v>0</v>
+      </c>
+      <c r="N76" t="str">
+        <v>13</v>
+      </c>
+      <c r="O76" t="str">
+        <v>긴급</v>
+      </c>
+      <c r="P76" t="str">
+        <v>복구부 밑 빈공간있음(80cm)</v>
+      </c>
+      <c r="Q76" t="str">
+        <v>서초동1329-7</v>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
+      </c>
+      <c r="T76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>26-10</v>
+      </c>
+      <c r="B77" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C77" t="str">
+        <v>26-서초구-10</v>
+      </c>
+      <c r="D77" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E77" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F77" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G77" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H77" t="str">
+        <v>-</v>
+      </c>
+      <c r="I77" t="str">
+        <v>0</v>
+      </c>
+      <c r="J77" t="str">
+        <v>3</v>
+      </c>
+      <c r="K77" t="str">
+        <v>0</v>
+      </c>
+      <c r="L77" t="str">
+        <v>1</v>
+      </c>
+      <c r="M77" t="str">
+        <v>0</v>
+      </c>
+      <c r="N77" t="str">
+        <v>4</v>
+      </c>
+      <c r="O77" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P77" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q77" t="str">
+        <v>서초동1329-8</v>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
+      </c>
+      <c r="T77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>26-11</v>
+      </c>
+      <c r="B78" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C78" t="str">
+        <v>26-서초구-11</v>
+      </c>
+      <c r="D78" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E78" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F78" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G78" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H78" t="str">
+        <v>-</v>
+      </c>
+      <c r="I78" t="str">
+        <v>0</v>
+      </c>
+      <c r="J78" t="str">
+        <v>3</v>
+      </c>
+      <c r="K78" t="str">
+        <v>0</v>
+      </c>
+      <c r="L78" t="str">
+        <v>1</v>
+      </c>
+      <c r="M78" t="str">
+        <v>0</v>
+      </c>
+      <c r="N78" t="str">
+        <v>4</v>
+      </c>
+      <c r="O78" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v>우성아파트앞 사거리</v>
+      </c>
+      <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v>교차로(강남대로346-2)</v>
+      </c>
+      <c r="T78" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T78"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -4944,7 +4944,7 @@
         <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
       </c>
       <c r="T76" t="str">
-        <v/>
+        <v>현장확인필요</v>
       </c>
     </row>
     <row r="77">

--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -5023,7 +5023,7 @@
         <v>양호</v>
       </c>
       <c r="E78" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F78" t="str">
         <v>양호</v>

--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T89"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-2</v>
+        <v>25-서초구-3</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -533,13 +533,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q5" t="str">
-        <v>서초동 1319-1</v>
+        <v>서초동 1319-11</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>강남역 #8번출구 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-서초구-3</v>
+        <v>25-서초구-4</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -592,16 +592,16 @@
         <v>일반</v>
       </c>
       <c r="P6" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
-        <v>서초동 1319-11</v>
+        <v>서초동 1319-13</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>강남역 #6번출구 뒤 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="str">
         <v>강남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-서초구-4</v>
+        <v>25-서초구-5</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -657,13 +657,13 @@
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v>서초동 1319-13</v>
+        <v>서초동 1328-3</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>강남역 #6번출구 뒤 도로</v>
+        <v>우리은행 서초금융센터 앞 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-서초구-5</v>
+        <v>25-서초구-6</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -716,16 +716,16 @@
         <v>일반</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>포장 복구개소</v>
       </c>
       <c r="Q8" t="str">
-        <v>서초동 1328-3</v>
+        <v>서초동 1328-10</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>우리은행 서초금융센터 앞 도로</v>
+        <v>강남역 #5번출구 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-서초구-6</v>
+        <v>25-서초구-7</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -778,16 +778,16 @@
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v>포장 복구개소</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q9" t="str">
-        <v>서초동 1328-10</v>
+        <v>서초동 1328-11</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>강남역 #5번출구 앞 도로</v>
+        <v>도씨의 빛Ⅱ 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-서초구-7</v>
+        <v>25-서초구-8</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -840,16 +840,16 @@
         <v>일반</v>
       </c>
       <c r="P10" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q10" t="str">
-        <v>서초동 1328-11</v>
+        <v>서초동 1329</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>도씨의 빛Ⅱ 앞 도로</v>
+        <v>삼성화제 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-서초구-8</v>
+        <v>25-서초구-9</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -902,16 +902,16 @@
         <v>일반</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q11" t="str">
-        <v>서초동 1329</v>
+        <v>서초동 1329-7</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>삼성화제 앞 도로</v>
+        <v>신한투자증권 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-서초구-9</v>
+        <v>25-서초구-10</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -967,13 +967,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q12" t="str">
-        <v>서초동 1329-7</v>
+        <v>서초동 1329-8</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>신한투자증권 앞 도로</v>
+        <v>모닝글로리 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-서초구-10</v>
+        <v>25-서초구-11</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1026,16 +1026,16 @@
         <v>일반</v>
       </c>
       <c r="P13" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
-        <v>서초동 1329-8</v>
+        <v>서초동 1329-10</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>모닝글로리 앞 도로</v>
+        <v>우성아파트 사거리 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-서초구-11</v>
+        <v>25-서초구-12</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1088,16 +1088,16 @@
         <v>일반</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q14" t="str">
-        <v>서초동 1329-10</v>
+        <v>서초동 1337-32</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>우성아파트 사거리 도로</v>
+        <v>한국투자증권 앞 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-서초구-12</v>
+        <v>25-서초구-13</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1150,16 +1150,16 @@
         <v>일반</v>
       </c>
       <c r="P15" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q15" t="str">
-        <v>서초동 1337-32</v>
+        <v>서초동 1337-22</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>한국투자증권 앞 도로</v>
+        <v>디오빌프라임 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-서초구-13</v>
+        <v>25-서초구-14</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1215,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>서초동 1337-22</v>
+        <v>서초동 1338-23</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>디오빌프라임 앞 도로</v>
+        <v>투썸플레이스 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-서초구-14</v>
+        <v>25-서초구-15</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1277,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>서초동 1338-23</v>
+        <v>서초동 1338-20</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>투썸플레이스 도로</v>
+        <v>현대렉시온 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-서초구-15</v>
+        <v>25-서초구-16</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1306,7 +1306,7 @@
         <v>거북등</v>
       </c>
       <c r="F18" t="str">
-        <v>양호</v>
+        <v>건조</v>
       </c>
       <c r="G18" t="str">
         <v>13.5</v>
@@ -1339,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>서초동 1338-20</v>
+        <v>서초동 1339-9</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>현대렉시온 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-서초구-16</v>
+        <v>25-서초구-17</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>서초동 1339-9</v>
+        <v>서초동 1340-6</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>KIA 서초지점 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1460,7 +1460,7 @@
         <v>일반</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q20" t="str">
         <v>서초동 1340-6</v>
@@ -1469,7 +1469,7 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>KIA 서초지점 앞 도로</v>
+        <v>남강매점 앞 횡단보도</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-서초구-18</v>
+        <v>25-서초구-19</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1522,16 +1522,16 @@
         <v>일반</v>
       </c>
       <c r="P21" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q21" t="str">
-        <v>서초동 1340-6</v>
+        <v>서초동 1357-33</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>남강매점 앞 횡단보도</v>
+        <v>한국디지털 평생교육원 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,13 +1539,13 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" t="str">
         <v>강남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-서초구-19</v>
+        <v>25-서초구-20</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
@@ -1584,16 +1584,16 @@
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q22" t="str">
-        <v>서초동 1357-33</v>
+        <v>서초동 1357-35</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>한국디지털 평생교육원 앞 도로</v>
+        <v>부산은행 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="str">
         <v>강남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-서초구-20</v>
+        <v>25-서초구-21</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
@@ -1649,13 +1649,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q23" t="str">
-        <v>서초동 1357-35</v>
+        <v>서초동 1358-6</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>부산은행 앞 도로</v>
+        <v>송남빌딩 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,19 +1663,19 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="str">
         <v>강남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-서초구-21</v>
+        <v>25-서초구-22</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
       </c>
       <c r="E24" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F24" t="str">
         <v>건조</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1702,22 +1702,22 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O24" t="str">
         <v>일반</v>
       </c>
       <c r="P24" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q24" t="str">
-        <v>서초동 1358-6</v>
+        <v>서초동 1361-1</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>송남빌딩 앞 도로</v>
+        <v>보들설곰탕 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="str">
         <v>강남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-서초구-22</v>
+        <v>25-서초구-23</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
@@ -1773,13 +1773,13 @@
         <v/>
       </c>
       <c r="Q25" t="str">
-        <v>서초동 1361-1</v>
+        <v>서초동 1361-5</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>보들설곰탕 앞 도로</v>
+        <v>새움빌딩 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,19 +1787,19 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" t="str">
         <v>강남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-서초구-23</v>
+        <v>25-서초구-24</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
       </c>
       <c r="E26" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F26" t="str">
         <v>건조</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O26" t="str">
         <v>일반</v>
@@ -1835,13 +1835,13 @@
         <v/>
       </c>
       <c r="Q26" t="str">
-        <v>서초동 1361-5</v>
+        <v>서초동 1361-10</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>새움빌딩 앞 도로</v>
+        <v>호텔 페이토 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="str">
         <v>강남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-서초구-24</v>
+        <v>25-서초구-25</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1894,16 +1894,16 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q27" t="str">
-        <v>서초동 1361-10</v>
+        <v>서초동 1362</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>호텔 페이토 앞 도로</v>
+        <v>e마트24 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" t="str">
         <v>강남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-서초구-25</v>
+        <v>25-서초구-26</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q28" t="str">
-        <v>서초동 1362</v>
+        <v>서초동 1362-26</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>e마트24 앞 도로</v>
+        <v>힐든가든인 서울강남 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="str">
         <v>강남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-서초구-26</v>
+        <v>25-서초구-27</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2018,16 +2018,16 @@
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q29" t="str">
-        <v>서초동 1362-26</v>
+        <v>서초동 1362-27</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>힐든가든인 서울강남 앞 도로</v>
+        <v>니드오피스텔 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" t="str">
         <v>강남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-서초구-27</v>
+        <v>25-서초구-28</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2080,16 +2080,16 @@
         <v>일반</v>
       </c>
       <c r="P30" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q30" t="str">
-        <v>서초동 1362-27</v>
+        <v>서초동 1366-7</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>니드오피스텔 앞 도로</v>
+        <v>깐부치킨 앞 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" t="str">
         <v>강남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-서초구-28</v>
+        <v>25-서초구-29</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
@@ -2142,16 +2142,16 @@
         <v>일반</v>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q31" t="str">
-        <v>서초동 1366-7</v>
+        <v>서초동 1366-9</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>깐부치킨 앞 도로</v>
+        <v>양재역 교차로 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,13 +2159,13 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-서초구-29</v>
+        <v>25-서초구-30</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
@@ -2204,16 +2204,16 @@
         <v>일반</v>
       </c>
       <c r="P32" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q32" t="str">
-        <v>서초동 1366-9</v>
+        <v>양재동 23</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>양재역 교차로 도로</v>
+        <v>바나프레소 앞 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,13 +2221,13 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-서초구-30</v>
+        <v>25-서초구-31</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
@@ -2269,13 +2269,13 @@
         <v/>
       </c>
       <c r="Q33" t="str">
-        <v>양재동 23</v>
+        <v>양재동 25</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>바나프레소 앞 도로</v>
+        <v>서초문화 예술회관 앞 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,13 +2283,13 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-서초구-31</v>
+        <v>25-서초구-32</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
@@ -2331,13 +2331,13 @@
         <v/>
       </c>
       <c r="Q34" t="str">
-        <v>양재동 25</v>
+        <v>양재동 14-4</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>서초문화 예술회관 앞 도로</v>
+        <v>모산빌딩 앞 횡단보도</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,19 +2345,19 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="str">
         <v>강남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-서초구-32</v>
+        <v>25-서초구-33</v>
       </c>
       <c r="D35" t="str">
-        <v>양호</v>
+        <v>50</v>
       </c>
       <c r="E35" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F35" t="str">
         <v>건조</v>
@@ -2368,11 +2368,11 @@
       <c r="H35" t="str">
         <v>-</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2384,22 +2384,22 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O35" t="str">
         <v>일반</v>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>보도침하5cm</v>
       </c>
       <c r="Q35" t="str">
-        <v>양재동 14-4</v>
+        <v>양재동 67-7</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>모산빌딩 앞 횡단보도</v>
+        <v>바나프레스 앞 보도</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,19 +2407,19 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="str">
         <v>강남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-서초구-33</v>
+        <v>25-서초구-34</v>
       </c>
       <c r="D36" t="str">
-        <v>50</v>
+        <v>양호</v>
       </c>
       <c r="E36" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F36" t="str">
         <v>건조</v>
@@ -2430,11 +2430,11 @@
       <c r="H36" t="str">
         <v>-</v>
       </c>
-      <c r="I36" t="b">
+      <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -2446,22 +2446,22 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O36" t="str">
         <v>일반</v>
       </c>
       <c r="P36" t="str">
-        <v>보도침하5cm</v>
+        <v/>
       </c>
       <c r="Q36" t="str">
-        <v>양재동 67-7</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>바나프레스 앞 보도</v>
+        <v>교육개발원 사거리 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,19 +2469,19 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" t="str">
         <v>강남대로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-서초구-34</v>
+        <v>25-서초구-35</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
       </c>
       <c r="E37" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F37" t="str">
         <v>건조</v>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O37" t="str">
         <v>일반</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동 109</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>교육개발원 사거리 도로</v>
+        <v>카페 릴리블랑 앞 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,19 +2531,19 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" t="str">
         <v>강남대로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-서초구-35</v>
+        <v>25-서초구-36</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
       </c>
       <c r="E38" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F38" t="str">
         <v>건조</v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O38" t="str">
         <v>일반</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>양재동 109</v>
+        <v>양재동 125</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>카페 릴리블랑 앞 도로</v>
+        <v>넥스팜 코리아 앞 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" t="str">
         <v>강남대로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-서초구-36</v>
+        <v>25-서초구-37</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2641,13 +2641,13 @@
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>양재동 125</v>
+        <v>양재동 80-3</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>넥스팜 코리아 앞 도로</v>
+        <v>도야짬뽕 앞 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-서초구-37</v>
+        <v>25-서초구-38</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2703,13 +2703,13 @@
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>양재동 80-3</v>
+        <v>양재동 237-1</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>도야짬뽕 앞 도로</v>
+        <v>공영주차장 앞 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-서초구-38</v>
+        <v>25-서초구-39</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2765,13 +2765,13 @@
         <v/>
       </c>
       <c r="Q41" t="str">
-        <v>양재동 237-1</v>
+        <v>신원동 308-1</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>공영주차장 앞 도로</v>
+        <v>가로등(청계산로145) 양차선 도로</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,13 +2779,13 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" t="str">
         <v>청계산로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-서초구-39</v>
+        <v>25-서초구-40</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
@@ -2827,13 +2827,13 @@
         <v/>
       </c>
       <c r="Q42" t="str">
-        <v>신원동 308-1</v>
+        <v>원지동 294-3</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>가로등(청계산로145) 양차선 도로</v>
+        <v>전봇대(원지간37H1) 양차선 도로</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" t="str">
         <v>청계산로</v>
       </c>
       <c r="C43" t="str">
-        <v>25-서초구-40</v>
+        <v>25-서초구-41</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
@@ -2886,16 +2886,16 @@
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v/>
+        <v>거북등 맨홀침하4cm</v>
       </c>
       <c r="Q43" t="str">
-        <v>원지동 294-3</v>
+        <v>원지동 594-1</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>전봇대(원지간37H1) 양차선 도로</v>
+        <v>도로교통표지판 앞 상수도맨홀 도로</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,13 +2903,13 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" t="str">
         <v>청계산로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-서초구-41</v>
+        <v>25-서초구-42</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
@@ -2948,16 +2948,16 @@
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v>거북등 맨홀침하4cm</v>
+        <v/>
       </c>
       <c r="Q44" t="str">
-        <v>원지동 594-1</v>
+        <v>신원동 280</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>도로교통표지판 앞 상수도맨홀 도로</v>
+        <v>공영주차장 앞 T 교차로 양차선 도로</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" t="str">
         <v>청계산로</v>
       </c>
       <c r="C45" t="str">
-        <v>25-서초구-42</v>
+        <v>25-서초구-43</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
@@ -3013,13 +3013,13 @@
         <v/>
       </c>
       <c r="Q45" t="str">
-        <v>신원동 280</v>
+        <v>신원동 278-6</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>공영주차장 앞 T 교차로 양차선 도로</v>
+        <v>공영주차장 앞 양차선 도로</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,13 +3027,13 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" t="str">
         <v>청계산로</v>
       </c>
       <c r="C46" t="str">
-        <v>25-서초구-43</v>
+        <v>25-서초구-44</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
@@ -3072,16 +3072,16 @@
         <v>일반</v>
       </c>
       <c r="P46" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q46" t="str">
-        <v>신원동 278-6</v>
+        <v>신원동 611</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>공영주차장 앞 양차선 도로</v>
+        <v>투썸플레이스 앞 보도</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,19 +3089,19 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" t="str">
         <v>청계산로</v>
       </c>
       <c r="C47" t="str">
-        <v>25-서초구-44</v>
+        <v>25-서초구-45</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F47" t="str">
         <v>건조</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -3128,22 +3128,22 @@
         <v>0</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O47" t="str">
         <v>일반</v>
       </c>
       <c r="P47" t="str">
-        <v>보도침하4cm</v>
+        <v/>
       </c>
       <c r="Q47" t="str">
-        <v>신원동 611</v>
+        <v>신원동 612</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>투썸플레이스 앞 보도</v>
+        <v>LAB 앞 도로</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,19 +3151,19 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" t="str">
         <v>청계산로</v>
       </c>
       <c r="C48" t="str">
-        <v>25-서초구-45</v>
+        <v>25-서초구-46</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F48" t="str">
         <v>건조</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -3190,22 +3190,22 @@
         <v>0</v>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O48" t="str">
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q48" t="str">
-        <v>신원동 612</v>
+        <v>신원동 660</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>LAB 앞 도로</v>
+        <v>심플리시티 앞 보도</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,13 +3213,13 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" t="str">
         <v>청계산로</v>
       </c>
       <c r="C49" t="str">
-        <v>25-서초구-46</v>
+        <v>25-서초구-47</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3258,16 +3258,16 @@
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v>보도침하4cm</v>
+        <v>보도침하3cm</v>
       </c>
       <c r="Q49" t="str">
-        <v>신원동 660</v>
+        <v>신원동 197-1</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>심플리시티 앞 보도</v>
+        <v>부안애서 맞음편 보도</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,13 +3275,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" t="str">
         <v>청계산로</v>
       </c>
       <c r="C50" t="str">
-        <v>25-서초구-47</v>
+        <v>25-서초구-48</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3320,16 +3320,16 @@
         <v>일반</v>
       </c>
       <c r="P50" t="str">
-        <v>보도침하3cm</v>
+        <v/>
       </c>
       <c r="Q50" t="str">
-        <v>신원동 197-1</v>
+        <v>원지동 384-1</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>부안애서 맞음편 보도</v>
+        <v>커피플라워 앞 양차선 도로</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" t="str">
         <v>청계산로</v>
       </c>
       <c r="C51" t="str">
-        <v>25-서초구-48</v>
+        <v>25-서초구-49</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3385,13 +3385,13 @@
         <v/>
       </c>
       <c r="Q51" t="str">
-        <v>원지동 384-1</v>
+        <v>신원동 192-73</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>커피플라워 앞 양차선 도로</v>
+        <v>봉평막국수 앞 양차선 도로</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" t="str">
         <v>청계산로</v>
       </c>
       <c r="C52" t="str">
-        <v>25-서초구-49</v>
+        <v>25-서초구-50</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3447,13 +3447,13 @@
         <v/>
       </c>
       <c r="Q52" t="str">
-        <v>신원동 192-73</v>
+        <v>신원동 172-1</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>봉평막국수 앞 양차선 도로</v>
+        <v>향린조경 앞 양차선 도로</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53" t="str">
         <v>청계산로</v>
       </c>
       <c r="C53" t="str">
-        <v>25-서초구-50</v>
+        <v>25-서초구-51</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3509,13 +3509,13 @@
         <v/>
       </c>
       <c r="Q53" t="str">
-        <v>신원동 172-1</v>
+        <v>신원동 153</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>향린조경 앞 양차선 도로</v>
+        <v>삼석원 앞 양차선 도로</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3523,13 +3523,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" t="str">
         <v>청계산로</v>
       </c>
       <c r="C54" t="str">
-        <v>25-서초구-51</v>
+        <v>25-서초구-52</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3571,13 +3571,13 @@
         <v/>
       </c>
       <c r="Q54" t="str">
-        <v>신원동 153</v>
+        <v>신원동 150-1</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>삼석원 앞 양차선 도로</v>
+        <v>성심조경 앞 양차선 도로</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" t="str">
         <v>청계산로</v>
       </c>
       <c r="C55" t="str">
-        <v>25-서초구-52</v>
+        <v>25-서초구-53</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3630,16 +3630,16 @@
         <v>일반</v>
       </c>
       <c r="P55" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q55" t="str">
-        <v>신원동 150-1</v>
+        <v>원지동 470-1</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>성심조경 앞 양차선 도로</v>
+        <v>가로등(청계산로154) 앞 보도</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3647,13 +3647,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" t="str">
         <v>청계산로</v>
       </c>
       <c r="C56" t="str">
-        <v>25-서초구-53</v>
+        <v>25-서초구-54</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3692,16 +3692,16 @@
         <v>일반</v>
       </c>
       <c r="P56" t="str">
-        <v>5cm이하 침하</v>
+        <v>보도침하</v>
       </c>
       <c r="Q56" t="str">
-        <v>원지동 470-1</v>
+        <v>원지동 491-6</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>가로등(청계산로154) 앞 보도</v>
+        <v>가로등(청계산로156) 맞음편 보도</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3709,13 +3709,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" t="str">
         <v>청계산로</v>
       </c>
       <c r="C57" t="str">
-        <v>25-서초구-54</v>
+        <v>25-서초구-55</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3754,16 +3754,16 @@
         <v>일반</v>
       </c>
       <c r="P57" t="str">
-        <v>보도침하</v>
+        <v/>
       </c>
       <c r="Q57" t="str">
-        <v>원지동 491-6</v>
+        <v>원지동 493</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>가로등(청계산로156) 맞음편 보도</v>
+        <v>양재조경 앞 양차선 도로</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3771,13 +3771,13 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B58" t="str">
         <v>청계산로</v>
       </c>
       <c r="C58" t="str">
-        <v>25-서초구-55</v>
+        <v>25-서초구-56</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3819,13 +3819,13 @@
         <v/>
       </c>
       <c r="Q58" t="str">
-        <v>원지동 493</v>
+        <v>원지동 497-3</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>양재조경 앞 양차선 도로</v>
+        <v>가로등(청계산로168) 앞 양차선 도로</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3833,13 +3833,13 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59" t="str">
         <v>청계산로</v>
       </c>
       <c r="C59" t="str">
-        <v>25-서초구-56</v>
+        <v>25-서초구-57</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3881,13 +3881,13 @@
         <v/>
       </c>
       <c r="Q59" t="str">
-        <v>원지동 497-3</v>
+        <v>신원동 산 60-2</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>가로등(청계산로168) 앞 양차선 도로</v>
+        <v>대원조경 앞 양차선 도로</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3895,13 +3895,13 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60" t="str">
         <v>청계산로</v>
       </c>
       <c r="C60" t="str">
-        <v>25-서초구-57</v>
+        <v>25-서초구-58</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
@@ -3943,13 +3943,13 @@
         <v/>
       </c>
       <c r="Q60" t="str">
-        <v>신원동 산 60-2</v>
+        <v>신원동 105-4</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>대원조경 앞 양차선 도로</v>
+        <v>둥지조경 제2농장 앞 양차선 도로</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3957,13 +3957,13 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61" t="str">
         <v>청계산로</v>
       </c>
       <c r="C61" t="str">
-        <v>25-서초구-58</v>
+        <v>25-서초구-59</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
@@ -4005,13 +4005,13 @@
         <v/>
       </c>
       <c r="Q61" t="str">
-        <v>신원동 105-4</v>
+        <v>신원동 105-33</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>둥지조경 제2농장 앞 양차선 도로</v>
+        <v>한백자생식물원 앞 양차선 도로</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4019,13 +4019,13 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62" t="str">
         <v>청계산로</v>
       </c>
       <c r="C62" t="str">
-        <v>25-서초구-59</v>
+        <v>25-서초구-60</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
@@ -4064,16 +4064,16 @@
         <v>일반</v>
       </c>
       <c r="P62" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q62" t="str">
-        <v>신원동 105-33</v>
+        <v>신원동 105-19</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>한백자생식물원 앞 양차선 도로</v>
+        <v>가로등(청계산로190) 앞 양차선 도로</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4081,19 +4081,19 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63" t="str">
         <v>청계산로</v>
       </c>
       <c r="C63" t="str">
-        <v>25-서초구-60</v>
+        <v>25-서초구-61</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
       </c>
       <c r="E63" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F63" t="str">
         <v>건조</v>
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O63" t="str">
         <v>일반</v>
@@ -4129,13 +4129,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q63" t="str">
-        <v>신원동 105-19</v>
+        <v>신원동 44-1</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>가로등(청계산로190) 앞 양차선 도로</v>
+        <v>새정이마을 입구 교차로</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4143,19 +4143,19 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64" t="str">
         <v>청계산로</v>
       </c>
       <c r="C64" t="str">
-        <v>25-서초구-61</v>
+        <v>25-서초구-62</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
       </c>
       <c r="E64" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F64" t="str">
         <v>건조</v>
@@ -4188,16 +4188,16 @@
         <v>일반</v>
       </c>
       <c r="P64" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q64" t="str">
-        <v>신원동 44-1</v>
+        <v>신원동 44-5</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>새정이마을 입구 교차로</v>
+        <v>은하조경 앞 양차선 도로</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4205,13 +4205,13 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B65" t="str">
         <v>청계산로</v>
       </c>
       <c r="C65" t="str">
-        <v>25-서초구-62</v>
+        <v>25-서초구-63</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
@@ -4253,13 +4253,13 @@
         <v/>
       </c>
       <c r="Q65" t="str">
-        <v>신원동 44-5</v>
+        <v>신원동 57</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>은하조경 앞 양차선 도로</v>
+        <v>서림원예종묘 앞 양차선 도로</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4267,19 +4267,19 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66" t="str">
         <v>청계산로</v>
       </c>
       <c r="C66" t="str">
-        <v>25-서초구-63</v>
+        <v>25-서초구-64</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
       </c>
       <c r="E66" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F66" t="str">
         <v>건조</v>
@@ -4294,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O66" t="str">
         <v>일반</v>
@@ -4315,27 +4315,27 @@
         <v/>
       </c>
       <c r="Q66" t="str">
-        <v>신원동 57</v>
+        <v>신원동 64-1</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>서림원예종묘 앞 양차선 도로</v>
+        <v>옥천조경 앞 양차선 도로</v>
       </c>
       <c r="T66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67">
-        <v>64</v>
+      <c r="A67" t="str">
+        <v>26-01</v>
       </c>
       <c r="B67" t="str">
-        <v>청계산로</v>
+        <v>강남대로</v>
       </c>
       <c r="C67" t="str">
-        <v>25-서초구-64</v>
+        <v>26-서초구-01</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
@@ -4344,46 +4344,46 @@
         <v>거북등</v>
       </c>
       <c r="F67" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G67" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H67" t="str">
         <v>-</v>
       </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>3</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>1</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
+      <c r="I67" t="str">
+        <v>0</v>
+      </c>
+      <c r="J67" t="str">
+        <v>3</v>
+      </c>
+      <c r="K67" t="str">
+        <v>0</v>
+      </c>
+      <c r="L67" t="str">
+        <v>1</v>
+      </c>
+      <c r="M67" t="str">
+        <v>0</v>
+      </c>
+      <c r="N67" t="str">
         <v>4</v>
       </c>
       <c r="O67" t="str">
         <v>일반</v>
       </c>
       <c r="P67" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q67" t="str">
-        <v>신원동 64-1</v>
+        <v>서초동1318-4</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>옥천조경 앞 양차선 도로</v>
+        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4391,13 +4391,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B68" t="str">
         <v>강남대로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
@@ -4439,13 +4439,13 @@
         <v>-</v>
       </c>
       <c r="Q68" t="str">
-        <v>서초동1318-4</v>
+        <v>강남역사거리</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
+        <v>강남역사거리(강남대로396)</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4453,13 +4453,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B69" t="str">
         <v>강남대로</v>
       </c>
       <c r="C69" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D69" t="str">
         <v>양호</v>
@@ -4501,13 +4501,13 @@
         <v>-</v>
       </c>
       <c r="Q69" t="str">
-        <v>강남역사거리</v>
+        <v>서초동1319-5</v>
       </c>
       <c r="R69" t="str">
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>강남역사거리(강남대로396)</v>
+        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4515,13 +4515,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B70" t="str">
         <v>강남대로</v>
       </c>
       <c r="C70" t="str">
-        <v>26-서초구-03</v>
+        <v>26-서초구-04</v>
       </c>
       <c r="D70" t="str">
         <v>양호</v>
@@ -4563,13 +4563,13 @@
         <v>-</v>
       </c>
       <c r="Q70" t="str">
-        <v>서초동1319-5</v>
+        <v>서초동1319-11</v>
       </c>
       <c r="R70" t="str">
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
+        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4577,13 +4577,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B71" t="str">
         <v>강남대로</v>
       </c>
       <c r="C71" t="str">
-        <v>26-서초구-04</v>
+        <v>26-서초구-05</v>
       </c>
       <c r="D71" t="str">
         <v>양호</v>
@@ -4625,13 +4625,13 @@
         <v>-</v>
       </c>
       <c r="Q71" t="str">
-        <v>서초동1319-11</v>
+        <v>서초동1328-3</v>
       </c>
       <c r="R71" t="str">
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
+        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
       </c>
       <c r="T71" t="str">
         <v/>
@@ -4639,13 +4639,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B72" t="str">
         <v>강남대로</v>
       </c>
       <c r="C72" t="str">
-        <v>26-서초구-05</v>
+        <v>26-서초구-06</v>
       </c>
       <c r="D72" t="str">
         <v>양호</v>
@@ -4684,16 +4684,16 @@
         <v>일반</v>
       </c>
       <c r="P72" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q72" t="str">
-        <v>서초동1328-3</v>
+        <v>서초동1328-11</v>
       </c>
       <c r="R72" t="str">
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
+        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
       </c>
       <c r="T72" t="str">
         <v/>
@@ -4701,13 +4701,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B73" t="str">
         <v>강남대로</v>
       </c>
       <c r="C73" t="str">
-        <v>26-서초구-06</v>
+        <v>26-서초구-07</v>
       </c>
       <c r="D73" t="str">
         <v>양호</v>
@@ -4749,13 +4749,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q73" t="str">
-        <v>서초동1328-11</v>
+        <v>서초동1329</v>
       </c>
       <c r="R73" t="str">
         <v/>
       </c>
       <c r="S73" t="str">
-        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
+        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
       </c>
       <c r="T73" t="str">
         <v/>
@@ -4763,13 +4763,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B74" t="str">
         <v>강남대로</v>
       </c>
       <c r="C74" t="str">
-        <v>26-서초구-07</v>
+        <v>26-서초구-08</v>
       </c>
       <c r="D74" t="str">
         <v>양호</v>
@@ -4808,16 +4808,16 @@
         <v>일반</v>
       </c>
       <c r="P74" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q74" t="str">
-        <v>서초동1329</v>
+        <v>서초동1329-4</v>
       </c>
       <c r="R74" t="str">
         <v/>
       </c>
       <c r="S74" t="str">
-        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
+        <v>우남빌딩 앞 도로(강남대로349)</v>
       </c>
       <c r="T74" t="str">
         <v/>
@@ -4825,16 +4825,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B75" t="str">
         <v>강남대로</v>
       </c>
       <c r="C75" t="str">
-        <v>26-서초구-08</v>
+        <v>26-서초구-09</v>
       </c>
       <c r="D75" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E75" t="str">
         <v>거북등</v>
@@ -4849,7 +4849,7 @@
         <v>-</v>
       </c>
       <c r="I75" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J75" t="str">
         <v>3</v>
@@ -4864,39 +4864,39 @@
         <v>0</v>
       </c>
       <c r="N75" t="str">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O75" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P75" t="str">
-        <v>-</v>
+        <v>복구부 밑 빈공간있음(80cm)</v>
       </c>
       <c r="Q75" t="str">
-        <v>서초동1329-4</v>
+        <v>서초동1329-7</v>
       </c>
       <c r="R75" t="str">
         <v/>
       </c>
       <c r="S75" t="str">
-        <v>우남빌딩 앞 도로(강남대로349)</v>
+        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
       </c>
       <c r="T75" t="str">
-        <v/>
+        <v>현장확인필요</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B76" t="str">
         <v>강남대로</v>
       </c>
       <c r="C76" t="str">
-        <v>26-서초구-09</v>
+        <v>26-서초구-10</v>
       </c>
       <c r="D76" t="str">
-        <v>불량</v>
+        <v>양호</v>
       </c>
       <c r="E76" t="str">
         <v>거북등</v>
@@ -4911,7 +4911,7 @@
         <v>-</v>
       </c>
       <c r="I76" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J76" t="str">
         <v>3</v>
@@ -4926,36 +4926,36 @@
         <v>0</v>
       </c>
       <c r="N76" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O76" t="str">
-        <v>긴급</v>
+        <v>일반</v>
       </c>
       <c r="P76" t="str">
-        <v>복구부 밑 빈공간있음(80cm)</v>
+        <v>-</v>
       </c>
       <c r="Q76" t="str">
-        <v>서초동1329-7</v>
+        <v>서초동1329-8</v>
       </c>
       <c r="R76" t="str">
         <v/>
       </c>
       <c r="S76" t="str">
-        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
+        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
       </c>
       <c r="T76" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B77" t="str">
         <v>강남대로</v>
       </c>
       <c r="C77" t="str">
-        <v>26-서초구-10</v>
+        <v>26-서초구-11</v>
       </c>
       <c r="D77" t="str">
         <v>양호</v>
@@ -4994,16 +4994,16 @@
         <v>일반</v>
       </c>
       <c r="P77" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="Q77" t="str">
-        <v>서초동1329-8</v>
+        <v>우성아파트앞 사거리</v>
       </c>
       <c r="R77" t="str">
         <v/>
       </c>
       <c r="S77" t="str">
-        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
+        <v>교차로(강남대로346-2)</v>
       </c>
       <c r="T77" t="str">
         <v/>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B78" t="str">
         <v>강남대로</v>
       </c>
       <c r="C78" t="str">
-        <v>26-서초구-11</v>
+        <v>26-서초구-12</v>
       </c>
       <c r="D78" t="str">
         <v>양호</v>
@@ -5056,24 +5056,706 @@
         <v>일반</v>
       </c>
       <c r="P78" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q78" t="str">
-        <v>우성아파트앞 사거리</v>
+        <v>서초동1337-32</v>
       </c>
       <c r="R78" t="str">
         <v/>
       </c>
       <c r="S78" t="str">
-        <v>교차로(강남대로346-2)</v>
+        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
       </c>
       <c r="T78" t="str">
-        <v/>
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>26-13</v>
+      </c>
+      <c r="B79" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C79" t="str">
+        <v>26-서초구-13</v>
+      </c>
+      <c r="D79" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E79" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F79" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G79" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H79" t="str">
+        <v>-</v>
+      </c>
+      <c r="I79" t="str">
+        <v>0</v>
+      </c>
+      <c r="J79" t="str">
+        <v>3</v>
+      </c>
+      <c r="K79" t="str">
+        <v>0</v>
+      </c>
+      <c r="L79" t="str">
+        <v>1</v>
+      </c>
+      <c r="M79" t="str">
+        <v>0</v>
+      </c>
+      <c r="N79" t="str">
+        <v>4</v>
+      </c>
+      <c r="O79" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P79" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q79" t="str">
+        <v>서초동1337-31</v>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
+      </c>
+      <c r="T79" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>26-14</v>
+      </c>
+      <c r="B80" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C80" t="str">
+        <v>26-서초구-14</v>
+      </c>
+      <c r="D80" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E80" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F80" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G80" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H80" t="str">
+        <v>-</v>
+      </c>
+      <c r="I80" t="str">
+        <v>0</v>
+      </c>
+      <c r="J80" t="str">
+        <v>3</v>
+      </c>
+      <c r="K80" t="str">
+        <v>0</v>
+      </c>
+      <c r="L80" t="str">
+        <v>1</v>
+      </c>
+      <c r="M80" t="str">
+        <v>0</v>
+      </c>
+      <c r="N80" t="str">
+        <v>4</v>
+      </c>
+      <c r="O80" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P80" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q80" t="str">
+        <v>서초동1337-20</v>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v>대륭서초타워 앞 도로(강남대로327)</v>
+      </c>
+      <c r="T80" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>26-15</v>
+      </c>
+      <c r="B81" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C81" t="str">
+        <v>26-서초구-15</v>
+      </c>
+      <c r="D81" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E81" t="str">
+        <v>거북이</v>
+      </c>
+      <c r="F81" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G81" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H81" t="str">
+        <v>-</v>
+      </c>
+      <c r="I81" t="str">
+        <v>0</v>
+      </c>
+      <c r="J81" t="str">
+        <v>3</v>
+      </c>
+      <c r="K81" t="str">
+        <v>0</v>
+      </c>
+      <c r="L81" t="str">
+        <v>1</v>
+      </c>
+      <c r="M81" t="str">
+        <v>0</v>
+      </c>
+      <c r="N81" t="str">
+        <v>4</v>
+      </c>
+      <c r="O81" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P81" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q81" t="str">
+        <v>서초동1337-22</v>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
+      </c>
+      <c r="T81" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>26-16</v>
+      </c>
+      <c r="B82" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C82" t="str">
+        <v>26-서초구-16</v>
+      </c>
+      <c r="D82" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E82" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F82" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G82" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H82" t="str">
+        <v>-</v>
+      </c>
+      <c r="I82" t="str">
+        <v>0</v>
+      </c>
+      <c r="J82" t="str">
+        <v>3</v>
+      </c>
+      <c r="K82" t="str">
+        <v>0</v>
+      </c>
+      <c r="L82" t="str">
+        <v>1</v>
+      </c>
+      <c r="M82" t="str">
+        <v>0</v>
+      </c>
+      <c r="N82" t="str">
+        <v>4</v>
+      </c>
+      <c r="O82" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P82" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q82" t="str">
+        <v>서초동1338-23</v>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
+      </c>
+      <c r="T82" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>26-17</v>
+      </c>
+      <c r="B83" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C83" t="str">
+        <v>26-서초구-17</v>
+      </c>
+      <c r="D83" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E83" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F83" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G83" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H83" t="str">
+        <v>-</v>
+      </c>
+      <c r="I83" t="str">
+        <v>0</v>
+      </c>
+      <c r="J83" t="str">
+        <v>3</v>
+      </c>
+      <c r="K83" t="str">
+        <v>0</v>
+      </c>
+      <c r="L83" t="str">
+        <v>1</v>
+      </c>
+      <c r="M83" t="str">
+        <v>0</v>
+      </c>
+      <c r="N83" t="str">
+        <v>4</v>
+      </c>
+      <c r="O83" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P83" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q83" t="str">
+        <v>서초동1338-12</v>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v>코인노트 앞 도로(강남대로311)</v>
+      </c>
+      <c r="T83" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>26-18</v>
+      </c>
+      <c r="B84" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C84" t="str">
+        <v>26-서초구-18</v>
+      </c>
+      <c r="D84" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E84" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F84" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G84" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H84" t="str">
+        <v>-</v>
+      </c>
+      <c r="I84" t="str">
+        <v>0</v>
+      </c>
+      <c r="J84" t="str">
+        <v>3</v>
+      </c>
+      <c r="K84" t="str">
+        <v>0</v>
+      </c>
+      <c r="L84" t="str">
+        <v>1</v>
+      </c>
+      <c r="M84" t="str">
+        <v>0</v>
+      </c>
+      <c r="N84" t="str">
+        <v>4</v>
+      </c>
+      <c r="O84" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P84" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q84" t="str">
+        <v>서초동1338-21</v>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
+      </c>
+      <c r="T84" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>26-19</v>
+      </c>
+      <c r="B85" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C85" t="str">
+        <v>26-서초구-19</v>
+      </c>
+      <c r="D85" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E85" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F85" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G85" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H85" t="str">
+        <v>-</v>
+      </c>
+      <c r="I85" t="str">
+        <v>0</v>
+      </c>
+      <c r="J85" t="str">
+        <v>3</v>
+      </c>
+      <c r="K85" t="str">
+        <v>0</v>
+      </c>
+      <c r="L85" t="str">
+        <v>1</v>
+      </c>
+      <c r="M85" t="str">
+        <v>0</v>
+      </c>
+      <c r="N85" t="str">
+        <v>4</v>
+      </c>
+      <c r="O85" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P85" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q85" t="str">
+        <v>서초동1338-20</v>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+      <c r="S85" t="str">
+        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
+      </c>
+      <c r="T85" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>26-20</v>
+      </c>
+      <c r="B86" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C86" t="str">
+        <v>26-서초구-20</v>
+      </c>
+      <c r="D86" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E86" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F86" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G86" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H86" t="str">
+        <v>-</v>
+      </c>
+      <c r="I86" t="str">
+        <v>0</v>
+      </c>
+      <c r="J86" t="str">
+        <v>3</v>
+      </c>
+      <c r="K86" t="str">
+        <v>0</v>
+      </c>
+      <c r="L86" t="str">
+        <v>1</v>
+      </c>
+      <c r="M86" t="str">
+        <v>0</v>
+      </c>
+      <c r="N86" t="str">
+        <v>4</v>
+      </c>
+      <c r="O86" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P86" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>서초동1339-9</v>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+      <c r="S86" t="str">
+        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
+      </c>
+      <c r="T86" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>26-21</v>
+      </c>
+      <c r="B87" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C87" t="str">
+        <v>26-서초구-21</v>
+      </c>
+      <c r="D87" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E87" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F87" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G87" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H87" t="str">
+        <v>-</v>
+      </c>
+      <c r="I87" t="str">
+        <v>0</v>
+      </c>
+      <c r="J87" t="str">
+        <v>3</v>
+      </c>
+      <c r="K87" t="str">
+        <v>0</v>
+      </c>
+      <c r="L87" t="str">
+        <v>1</v>
+      </c>
+      <c r="M87" t="str">
+        <v>0</v>
+      </c>
+      <c r="N87" t="str">
+        <v>4</v>
+      </c>
+      <c r="O87" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P87" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>서초동1340-6</v>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+      <c r="S87" t="str">
+        <v>남강빌딩 앞 도로(강남대로291)</v>
+      </c>
+      <c r="T87" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>26-22</v>
+      </c>
+      <c r="B88" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C88" t="str">
+        <v>26-서초구-22</v>
+      </c>
+      <c r="D88" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E88" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F88" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G88" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H88" t="str">
+        <v>-</v>
+      </c>
+      <c r="I88" t="str">
+        <v>0</v>
+      </c>
+      <c r="J88" t="str">
+        <v>3</v>
+      </c>
+      <c r="K88" t="str">
+        <v>0</v>
+      </c>
+      <c r="L88" t="str">
+        <v>1</v>
+      </c>
+      <c r="M88" t="str">
+        <v>0</v>
+      </c>
+      <c r="N88" t="str">
+        <v>4</v>
+      </c>
+      <c r="O88" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P88" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>서초동1357-10</v>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
+      </c>
+      <c r="T88" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>26-23</v>
+      </c>
+      <c r="B89" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C89" t="str">
+        <v>26-서초구-23</v>
+      </c>
+      <c r="D89" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E89" t="str">
+        <v>횡균열</v>
+      </c>
+      <c r="F89" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G89" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H89" t="str">
+        <v>-</v>
+      </c>
+      <c r="I89" t="str">
+        <v>0</v>
+      </c>
+      <c r="J89" t="str">
+        <v>1</v>
+      </c>
+      <c r="K89" t="str">
+        <v>0</v>
+      </c>
+      <c r="L89" t="str">
+        <v>1</v>
+      </c>
+      <c r="M89" t="str">
+        <v>0</v>
+      </c>
+      <c r="N89" t="str">
+        <v>2</v>
+      </c>
+      <c r="O89" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P89" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>서초동1357-66</v>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v>메인타워 CU 앞 도로(강남대로275)</v>
+      </c>
+      <c r="T89" t="str">
+        <v>현장확인필요</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T89"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T89"/>
+  <dimension ref="A1:T97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-3</v>
+        <v>25-서초구-4</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -530,16 +530,16 @@
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
-        <v>서초동 1319-11</v>
+        <v>서초동 1319-13</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>강남역 #6번출구 뒤 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-서초구-4</v>
+        <v>25-서초구-5</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -595,13 +595,13 @@
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v>서초동 1319-13</v>
+        <v>서초동 1328-3</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>강남역 #6번출구 뒤 도로</v>
+        <v>우리은행 서초금융센터 앞 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="str">
         <v>강남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-서초구-5</v>
+        <v>25-서초구-6</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -654,16 +654,16 @@
         <v>일반</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>포장 복구개소</v>
       </c>
       <c r="Q7" t="str">
-        <v>서초동 1328-3</v>
+        <v>서초동 1328-10</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>우리은행 서초금융센터 앞 도로</v>
+        <v>강남역 #5번출구 앞 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-서초구-6</v>
+        <v>25-서초구-7</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -716,16 +716,16 @@
         <v>일반</v>
       </c>
       <c r="P8" t="str">
-        <v>포장 복구개소</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q8" t="str">
-        <v>서초동 1328-10</v>
+        <v>서초동 1328-11</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>강남역 #5번출구 앞 도로</v>
+        <v>도씨의 빛Ⅱ 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-서초구-7</v>
+        <v>25-서초구-8</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -778,16 +778,16 @@
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q9" t="str">
-        <v>서초동 1328-11</v>
+        <v>서초동 1329</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>도씨의 빛Ⅱ 앞 도로</v>
+        <v>삼성화제 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-서초구-8</v>
+        <v>25-서초구-9</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -840,16 +840,16 @@
         <v>일반</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q10" t="str">
-        <v>서초동 1329</v>
+        <v>서초동 1329-7</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>삼성화제 앞 도로</v>
+        <v>신한투자증권 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-서초구-9</v>
+        <v>25-서초구-10</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -905,13 +905,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q11" t="str">
-        <v>서초동 1329-7</v>
+        <v>서초동 1329-8</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>신한투자증권 앞 도로</v>
+        <v>모닝글로리 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-서초구-10</v>
+        <v>25-서초구-11</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -964,16 +964,16 @@
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q12" t="str">
-        <v>서초동 1329-8</v>
+        <v>서초동 1329-10</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>모닝글로리 앞 도로</v>
+        <v>우성아파트 사거리 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-서초구-11</v>
+        <v>25-서초구-12</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1026,16 +1026,16 @@
         <v>일반</v>
       </c>
       <c r="P13" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q13" t="str">
-        <v>서초동 1329-10</v>
+        <v>서초동 1337-32</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>우성아파트 사거리 도로</v>
+        <v>한국투자증권 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-서초구-12</v>
+        <v>25-서초구-13</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1088,16 +1088,16 @@
         <v>일반</v>
       </c>
       <c r="P14" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q14" t="str">
-        <v>서초동 1337-32</v>
+        <v>서초동 1337-22</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>한국투자증권 앞 도로</v>
+        <v>디오빌프라임 앞 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-서초구-13</v>
+        <v>25-서초구-14</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>서초동 1337-22</v>
+        <v>서초동 1338-23</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>디오빌프라임 앞 도로</v>
+        <v>투썸플레이스 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-서초구-14</v>
+        <v>25-서초구-15</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1215,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>서초동 1338-23</v>
+        <v>서초동 1338-20</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>투썸플레이스 도로</v>
+        <v>현대렉시온 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-서초구-15</v>
+        <v>25-서초구-16</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1244,7 +1244,7 @@
         <v>거북등</v>
       </c>
       <c r="F17" t="str">
-        <v>양호</v>
+        <v>건조</v>
       </c>
       <c r="G17" t="str">
         <v>13.5</v>
@@ -1277,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>서초동 1338-20</v>
+        <v>서초동 1339-9</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>현대렉시온 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-서초구-16</v>
+        <v>25-서초구-17</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1339,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>서초동 1339-9</v>
+        <v>서초동 1340-6</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>KIA 서초지점 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1398,7 +1398,7 @@
         <v>일반</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q19" t="str">
         <v>서초동 1340-6</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>KIA 서초지점 앞 도로</v>
+        <v>남강매점 앞 횡단보도</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-서초구-18</v>
+        <v>25-서초구-19</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1460,16 +1460,16 @@
         <v>일반</v>
       </c>
       <c r="P20" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q20" t="str">
-        <v>서초동 1340-6</v>
+        <v>서초동 1357-33</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>남강매점 앞 횡단보도</v>
+        <v>한국디지털 평생교육원 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-서초구-19</v>
+        <v>25-서초구-20</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1522,16 +1522,16 @@
         <v>일반</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q21" t="str">
-        <v>서초동 1357-33</v>
+        <v>서초동 1357-35</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>한국디지털 평생교육원 앞 도로</v>
+        <v>부산은행 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,13 +1539,13 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="str">
         <v>강남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-서초구-20</v>
+        <v>25-서초구-21</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
@@ -1587,13 +1587,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q22" t="str">
-        <v>서초동 1357-35</v>
+        <v>서초동 1358-6</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>부산은행 앞 도로</v>
+        <v>송남빌딩 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="str">
         <v>강남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-서초구-21</v>
+        <v>25-서초구-22</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
       </c>
       <c r="E23" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F23" t="str">
         <v>건조</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1640,22 +1640,22 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O23" t="str">
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q23" t="str">
-        <v>서초동 1358-6</v>
+        <v>서초동 1361-1</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>송남빌딩 앞 도로</v>
+        <v>보들설곰탕 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,13 +1663,13 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="str">
         <v>강남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-서초구-22</v>
+        <v>25-서초구-23</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
@@ -1711,13 +1711,13 @@
         <v/>
       </c>
       <c r="Q24" t="str">
-        <v>서초동 1361-1</v>
+        <v>서초동 1361-5</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>보들설곰탕 앞 도로</v>
+        <v>새움빌딩 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="str">
         <v>강남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-서초구-23</v>
+        <v>25-서초구-24</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
       </c>
       <c r="E25" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F25" t="str">
         <v>건조</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O25" t="str">
         <v>일반</v>
@@ -1773,13 +1773,13 @@
         <v/>
       </c>
       <c r="Q25" t="str">
-        <v>서초동 1361-5</v>
+        <v>서초동 1361-10</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>새움빌딩 앞 도로</v>
+        <v>호텔 페이토 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="str">
         <v>강남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-서초구-24</v>
+        <v>25-서초구-25</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1832,16 +1832,16 @@
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q26" t="str">
-        <v>서초동 1361-10</v>
+        <v>서초동 1362</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>호텔 페이토 앞 도로</v>
+        <v>e마트24 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="str">
         <v>강남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-서초구-25</v>
+        <v>25-서초구-26</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1894,16 +1894,16 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q27" t="str">
-        <v>서초동 1362</v>
+        <v>서초동 1362-26</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>e마트24 앞 도로</v>
+        <v>힐든가든인 서울강남 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="str">
         <v>강남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-서초구-26</v>
+        <v>25-서초구-27</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q28" t="str">
-        <v>서초동 1362-26</v>
+        <v>서초동 1362-27</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>힐든가든인 서울강남 앞 도로</v>
+        <v>니드오피스텔 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="str">
         <v>강남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-서초구-27</v>
+        <v>25-서초구-28</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2018,16 +2018,16 @@
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q29" t="str">
-        <v>서초동 1362-27</v>
+        <v>서초동 1366-7</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>니드오피스텔 앞 도로</v>
+        <v>깐부치킨 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="str">
         <v>강남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-서초구-28</v>
+        <v>25-서초구-29</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2080,16 +2080,16 @@
         <v>일반</v>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q30" t="str">
-        <v>서초동 1366-7</v>
+        <v>서초동 1366-9</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>깐부치킨 앞 도로</v>
+        <v>양재역 교차로 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="str">
         <v>강남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-서초구-29</v>
+        <v>25-서초구-30</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
@@ -2142,16 +2142,16 @@
         <v>일반</v>
       </c>
       <c r="P31" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q31" t="str">
-        <v>서초동 1366-9</v>
+        <v>양재동 23</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>양재역 교차로 도로</v>
+        <v>바나프레소 앞 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,13 +2159,13 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-서초구-30</v>
+        <v>25-서초구-31</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
@@ -2207,13 +2207,13 @@
         <v/>
       </c>
       <c r="Q32" t="str">
-        <v>양재동 23</v>
+        <v>양재동 25</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>바나프레소 앞 도로</v>
+        <v>서초문화 예술회관 앞 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,13 +2221,13 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-서초구-31</v>
+        <v>25-서초구-32</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
@@ -2269,13 +2269,13 @@
         <v/>
       </c>
       <c r="Q33" t="str">
-        <v>양재동 25</v>
+        <v>양재동 14-4</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>서초문화 예술회관 앞 도로</v>
+        <v>모산빌딩 앞 횡단보도</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,19 +2283,19 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-서초구-32</v>
+        <v>25-서초구-33</v>
       </c>
       <c r="D34" t="str">
-        <v>양호</v>
+        <v>50</v>
       </c>
       <c r="E34" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F34" t="str">
         <v>건조</v>
@@ -2306,11 +2306,11 @@
       <c r="H34" t="str">
         <v>-</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2322,22 +2322,22 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O34" t="str">
         <v>일반</v>
       </c>
       <c r="P34" t="str">
-        <v/>
+        <v>보도침하5cm</v>
       </c>
       <c r="Q34" t="str">
-        <v>양재동 14-4</v>
+        <v>양재동 67-7</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>모산빌딩 앞 횡단보도</v>
+        <v>바나프레스 앞 보도</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,19 +2345,19 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="str">
         <v>강남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-서초구-33</v>
+        <v>25-서초구-34</v>
       </c>
       <c r="D35" t="str">
-        <v>50</v>
+        <v>양호</v>
       </c>
       <c r="E35" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F35" t="str">
         <v>건조</v>
@@ -2368,11 +2368,11 @@
       <c r="H35" t="str">
         <v>-</v>
       </c>
-      <c r="I35" t="b">
+      <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2384,22 +2384,22 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O35" t="str">
         <v>일반</v>
       </c>
       <c r="P35" t="str">
-        <v>보도침하5cm</v>
+        <v/>
       </c>
       <c r="Q35" t="str">
-        <v>양재동 67-7</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>바나프레스 앞 보도</v>
+        <v>교육개발원 사거리 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,19 +2407,19 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="str">
         <v>강남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-서초구-34</v>
+        <v>25-서초구-35</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
       </c>
       <c r="E36" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F36" t="str">
         <v>건조</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O36" t="str">
         <v>일반</v>
@@ -2455,13 +2455,13 @@
         <v/>
       </c>
       <c r="Q36" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동 109</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>교육개발원 사거리 도로</v>
+        <v>카페 릴리블랑 앞 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,19 +2469,19 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" t="str">
         <v>강남대로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-서초구-35</v>
+        <v>25-서초구-36</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
       </c>
       <c r="E37" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F37" t="str">
         <v>건조</v>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O37" t="str">
         <v>일반</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>양재동 109</v>
+        <v>양재동 125</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>카페 릴리블랑 앞 도로</v>
+        <v>넥스팜 코리아 앞 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" t="str">
         <v>강남대로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-서초구-36</v>
+        <v>25-서초구-37</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>양재동 125</v>
+        <v>양재동 80-3</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>넥스팜 코리아 앞 도로</v>
+        <v>도야짬뽕 앞 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-서초구-37</v>
+        <v>25-서초구-38</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2641,13 +2641,13 @@
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>양재동 80-3</v>
+        <v>양재동 237-1</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>도야짬뽕 앞 도로</v>
+        <v>공영주차장 앞 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-서초구-38</v>
+        <v>25-서초구-39</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2703,13 +2703,13 @@
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>양재동 237-1</v>
+        <v>신원동 308-1</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>공영주차장 앞 도로</v>
+        <v>가로등(청계산로145) 양차선 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" t="str">
         <v>청계산로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-서초구-39</v>
+        <v>25-서초구-40</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2765,13 +2765,13 @@
         <v/>
       </c>
       <c r="Q41" t="str">
-        <v>신원동 308-1</v>
+        <v>원지동 294-3</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>가로등(청계산로145) 양차선 도로</v>
+        <v>전봇대(원지간37H1) 양차선 도로</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,13 +2779,13 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" t="str">
         <v>청계산로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-서초구-40</v>
+        <v>25-서초구-41</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
@@ -2824,16 +2824,16 @@
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>거북등 맨홀침하4cm</v>
       </c>
       <c r="Q42" t="str">
-        <v>원지동 294-3</v>
+        <v>원지동 594-1</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>전봇대(원지간37H1) 양차선 도로</v>
+        <v>도로교통표지판 앞 상수도맨홀 도로</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" t="str">
         <v>청계산로</v>
       </c>
       <c r="C43" t="str">
-        <v>25-서초구-41</v>
+        <v>25-서초구-42</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
@@ -2886,16 +2886,16 @@
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v>거북등 맨홀침하4cm</v>
+        <v/>
       </c>
       <c r="Q43" t="str">
-        <v>원지동 594-1</v>
+        <v>신원동 280</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>도로교통표지판 앞 상수도맨홀 도로</v>
+        <v>공영주차장 앞 T 교차로 양차선 도로</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,13 +2903,13 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" t="str">
         <v>청계산로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-서초구-42</v>
+        <v>25-서초구-43</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
@@ -2951,13 +2951,13 @@
         <v/>
       </c>
       <c r="Q44" t="str">
-        <v>신원동 280</v>
+        <v>신원동 278-6</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>공영주차장 앞 T 교차로 양차선 도로</v>
+        <v>공영주차장 앞 양차선 도로</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" t="str">
         <v>청계산로</v>
       </c>
       <c r="C45" t="str">
-        <v>25-서초구-43</v>
+        <v>25-서초구-44</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
@@ -3010,16 +3010,16 @@
         <v>일반</v>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q45" t="str">
-        <v>신원동 278-6</v>
+        <v>신원동 611</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>공영주차장 앞 양차선 도로</v>
+        <v>투썸플레이스 앞 보도</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,19 +3027,19 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" t="str">
         <v>청계산로</v>
       </c>
       <c r="C46" t="str">
-        <v>25-서초구-44</v>
+        <v>25-서초구-45</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F46" t="str">
         <v>건조</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3066,22 +3066,22 @@
         <v>0</v>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O46" t="str">
         <v>일반</v>
       </c>
       <c r="P46" t="str">
-        <v>보도침하4cm</v>
+        <v/>
       </c>
       <c r="Q46" t="str">
-        <v>신원동 611</v>
+        <v>신원동 612</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>투썸플레이스 앞 보도</v>
+        <v>LAB 앞 도로</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,19 +3089,19 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" t="str">
         <v>청계산로</v>
       </c>
       <c r="C47" t="str">
-        <v>25-서초구-45</v>
+        <v>25-서초구-46</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F47" t="str">
         <v>건조</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -3128,22 +3128,22 @@
         <v>0</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O47" t="str">
         <v>일반</v>
       </c>
       <c r="P47" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q47" t="str">
-        <v>신원동 612</v>
+        <v>신원동 660</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>LAB 앞 도로</v>
+        <v>심플리시티 앞 보도</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,13 +3151,13 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" t="str">
         <v>청계산로</v>
       </c>
       <c r="C48" t="str">
-        <v>25-서초구-46</v>
+        <v>25-서초구-47</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
@@ -3196,16 +3196,16 @@
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v>보도침하4cm</v>
+        <v>보도침하3cm</v>
       </c>
       <c r="Q48" t="str">
-        <v>신원동 660</v>
+        <v>신원동 197-1</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>심플리시티 앞 보도</v>
+        <v>부안애서 맞음편 보도</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,13 +3213,13 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" t="str">
         <v>청계산로</v>
       </c>
       <c r="C49" t="str">
-        <v>25-서초구-47</v>
+        <v>25-서초구-48</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3258,16 +3258,16 @@
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v>보도침하3cm</v>
+        <v/>
       </c>
       <c r="Q49" t="str">
-        <v>신원동 197-1</v>
+        <v>원지동 384-1</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>부안애서 맞음편 보도</v>
+        <v>커피플라워 앞 양차선 도로</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,13 +3275,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" t="str">
         <v>청계산로</v>
       </c>
       <c r="C50" t="str">
-        <v>25-서초구-48</v>
+        <v>25-서초구-49</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3323,13 +3323,13 @@
         <v/>
       </c>
       <c r="Q50" t="str">
-        <v>원지동 384-1</v>
+        <v>신원동 192-73</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>커피플라워 앞 양차선 도로</v>
+        <v>봉평막국수 앞 양차선 도로</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" t="str">
         <v>청계산로</v>
       </c>
       <c r="C51" t="str">
-        <v>25-서초구-49</v>
+        <v>25-서초구-50</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3385,13 +3385,13 @@
         <v/>
       </c>
       <c r="Q51" t="str">
-        <v>신원동 192-73</v>
+        <v>신원동 172-1</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>봉평막국수 앞 양차선 도로</v>
+        <v>향린조경 앞 양차선 도로</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" t="str">
         <v>청계산로</v>
       </c>
       <c r="C52" t="str">
-        <v>25-서초구-50</v>
+        <v>25-서초구-51</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3447,13 +3447,13 @@
         <v/>
       </c>
       <c r="Q52" t="str">
-        <v>신원동 172-1</v>
+        <v>신원동 153</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>향린조경 앞 양차선 도로</v>
+        <v>삼석원 앞 양차선 도로</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="str">
         <v>청계산로</v>
       </c>
       <c r="C53" t="str">
-        <v>25-서초구-51</v>
+        <v>25-서초구-52</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3509,13 +3509,13 @@
         <v/>
       </c>
       <c r="Q53" t="str">
-        <v>신원동 153</v>
+        <v>신원동 150-1</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>삼석원 앞 양차선 도로</v>
+        <v>성심조경 앞 양차선 도로</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3523,13 +3523,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" t="str">
         <v>청계산로</v>
       </c>
       <c r="C54" t="str">
-        <v>25-서초구-52</v>
+        <v>25-서초구-53</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3568,16 +3568,16 @@
         <v>일반</v>
       </c>
       <c r="P54" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q54" t="str">
-        <v>신원동 150-1</v>
+        <v>원지동 470-1</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>성심조경 앞 양차선 도로</v>
+        <v>가로등(청계산로154) 앞 보도</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" t="str">
         <v>청계산로</v>
       </c>
       <c r="C55" t="str">
-        <v>25-서초구-53</v>
+        <v>25-서초구-54</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3630,16 +3630,16 @@
         <v>일반</v>
       </c>
       <c r="P55" t="str">
-        <v>5cm이하 침하</v>
+        <v>보도침하</v>
       </c>
       <c r="Q55" t="str">
-        <v>원지동 470-1</v>
+        <v>원지동 491-6</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>가로등(청계산로154) 앞 보도</v>
+        <v>가로등(청계산로156) 맞음편 보도</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3647,13 +3647,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" t="str">
         <v>청계산로</v>
       </c>
       <c r="C56" t="str">
-        <v>25-서초구-54</v>
+        <v>25-서초구-55</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3692,16 +3692,16 @@
         <v>일반</v>
       </c>
       <c r="P56" t="str">
-        <v>보도침하</v>
+        <v/>
       </c>
       <c r="Q56" t="str">
-        <v>원지동 491-6</v>
+        <v>원지동 493</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>가로등(청계산로156) 맞음편 보도</v>
+        <v>양재조경 앞 양차선 도로</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3709,13 +3709,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" t="str">
         <v>청계산로</v>
       </c>
       <c r="C57" t="str">
-        <v>25-서초구-55</v>
+        <v>25-서초구-56</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="Q57" t="str">
-        <v>원지동 493</v>
+        <v>원지동 497-3</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>양재조경 앞 양차선 도로</v>
+        <v>가로등(청계산로168) 앞 양차선 도로</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3771,13 +3771,13 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" t="str">
         <v>청계산로</v>
       </c>
       <c r="C58" t="str">
-        <v>25-서초구-56</v>
+        <v>25-서초구-57</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3819,13 +3819,13 @@
         <v/>
       </c>
       <c r="Q58" t="str">
-        <v>원지동 497-3</v>
+        <v>신원동 산 60-2</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>가로등(청계산로168) 앞 양차선 도로</v>
+        <v>대원조경 앞 양차선 도로</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3833,13 +3833,13 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59" t="str">
         <v>청계산로</v>
       </c>
       <c r="C59" t="str">
-        <v>25-서초구-57</v>
+        <v>25-서초구-58</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3881,13 +3881,13 @@
         <v/>
       </c>
       <c r="Q59" t="str">
-        <v>신원동 산 60-2</v>
+        <v>신원동 105-4</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>대원조경 앞 양차선 도로</v>
+        <v>둥지조경 제2농장 앞 양차선 도로</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3895,13 +3895,13 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60" t="str">
         <v>청계산로</v>
       </c>
       <c r="C60" t="str">
-        <v>25-서초구-58</v>
+        <v>25-서초구-59</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
@@ -3943,13 +3943,13 @@
         <v/>
       </c>
       <c r="Q60" t="str">
-        <v>신원동 105-4</v>
+        <v>신원동 105-33</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>둥지조경 제2농장 앞 양차선 도로</v>
+        <v>한백자생식물원 앞 양차선 도로</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3957,13 +3957,13 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" t="str">
         <v>청계산로</v>
       </c>
       <c r="C61" t="str">
-        <v>25-서초구-59</v>
+        <v>25-서초구-60</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
@@ -4002,16 +4002,16 @@
         <v>일반</v>
       </c>
       <c r="P61" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q61" t="str">
-        <v>신원동 105-33</v>
+        <v>신원동 105-19</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>한백자생식물원 앞 양차선 도로</v>
+        <v>가로등(청계산로190) 앞 양차선 도로</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4019,19 +4019,19 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62" t="str">
         <v>청계산로</v>
       </c>
       <c r="C62" t="str">
-        <v>25-서초구-60</v>
+        <v>25-서초구-61</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
       </c>
       <c r="E62" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F62" t="str">
         <v>건조</v>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O62" t="str">
         <v>일반</v>
@@ -4067,13 +4067,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q62" t="str">
-        <v>신원동 105-19</v>
+        <v>신원동 44-1</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>가로등(청계산로190) 앞 양차선 도로</v>
+        <v>새정이마을 입구 교차로</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4081,19 +4081,19 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63" t="str">
         <v>청계산로</v>
       </c>
       <c r="C63" t="str">
-        <v>25-서초구-61</v>
+        <v>25-서초구-62</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
       </c>
       <c r="E63" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F63" t="str">
         <v>건조</v>
@@ -4126,16 +4126,16 @@
         <v>일반</v>
       </c>
       <c r="P63" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q63" t="str">
-        <v>신원동 44-1</v>
+        <v>신원동 44-5</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>새정이마을 입구 교차로</v>
+        <v>은하조경 앞 양차선 도로</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4143,13 +4143,13 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B64" t="str">
         <v>청계산로</v>
       </c>
       <c r="C64" t="str">
-        <v>25-서초구-62</v>
+        <v>25-서초구-63</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
@@ -4191,13 +4191,13 @@
         <v/>
       </c>
       <c r="Q64" t="str">
-        <v>신원동 44-5</v>
+        <v>신원동 57</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>은하조경 앞 양차선 도로</v>
+        <v>서림원예종묘 앞 양차선 도로</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4205,19 +4205,19 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" t="str">
         <v>청계산로</v>
       </c>
       <c r="C65" t="str">
-        <v>25-서초구-63</v>
+        <v>25-서초구-64</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
       </c>
       <c r="E65" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F65" t="str">
         <v>건조</v>
@@ -4232,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O65" t="str">
         <v>일반</v>
@@ -4253,27 +4253,27 @@
         <v/>
       </c>
       <c r="Q65" t="str">
-        <v>신원동 57</v>
+        <v>신원동 64-1</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>서림원예종묘 앞 양차선 도로</v>
+        <v>옥천조경 앞 양차선 도로</v>
       </c>
       <c r="T65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66">
-        <v>64</v>
+      <c r="A66" t="str">
+        <v>26-01</v>
       </c>
       <c r="B66" t="str">
-        <v>청계산로</v>
+        <v>강남대로</v>
       </c>
       <c r="C66" t="str">
-        <v>25-서초구-64</v>
+        <v>26-서초구-01</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4282,46 +4282,46 @@
         <v>거북등</v>
       </c>
       <c r="F66" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G66" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H66" t="str">
         <v>-</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>3</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>1</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
+      <c r="I66" t="str">
+        <v>0</v>
+      </c>
+      <c r="J66" t="str">
+        <v>3</v>
+      </c>
+      <c r="K66" t="str">
+        <v>0</v>
+      </c>
+      <c r="L66" t="str">
+        <v>1</v>
+      </c>
+      <c r="M66" t="str">
+        <v>0</v>
+      </c>
+      <c r="N66" t="str">
         <v>4</v>
       </c>
       <c r="O66" t="str">
         <v>일반</v>
       </c>
       <c r="P66" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q66" t="str">
-        <v>신원동 64-1</v>
+        <v>서초동1318-4</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>옥천조경 앞 양차선 도로</v>
+        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4329,13 +4329,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B67" t="str">
         <v>강남대로</v>
       </c>
       <c r="C67" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
@@ -4377,13 +4377,13 @@
         <v>-</v>
       </c>
       <c r="Q67" t="str">
-        <v>서초동1318-4</v>
+        <v>강남역사거리</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
+        <v>강남역사거리(강남대로396)</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4391,13 +4391,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B68" t="str">
         <v>강남대로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
@@ -4439,13 +4439,13 @@
         <v>-</v>
       </c>
       <c r="Q68" t="str">
-        <v>강남역사거리</v>
+        <v>서초동1319-5</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>강남역사거리(강남대로396)</v>
+        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4453,13 +4453,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B69" t="str">
         <v>강남대로</v>
       </c>
       <c r="C69" t="str">
-        <v>26-서초구-03</v>
+        <v>26-서초구-04</v>
       </c>
       <c r="D69" t="str">
         <v>양호</v>
@@ -4501,13 +4501,13 @@
         <v>-</v>
       </c>
       <c r="Q69" t="str">
-        <v>서초동1319-5</v>
+        <v>서초동1319-11</v>
       </c>
       <c r="R69" t="str">
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
+        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4515,13 +4515,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B70" t="str">
         <v>강남대로</v>
       </c>
       <c r="C70" t="str">
-        <v>26-서초구-04</v>
+        <v>26-서초구-05</v>
       </c>
       <c r="D70" t="str">
         <v>양호</v>
@@ -4563,13 +4563,13 @@
         <v>-</v>
       </c>
       <c r="Q70" t="str">
-        <v>서초동1319-11</v>
+        <v>서초동1328-3</v>
       </c>
       <c r="R70" t="str">
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
+        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4577,13 +4577,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B71" t="str">
         <v>강남대로</v>
       </c>
       <c r="C71" t="str">
-        <v>26-서초구-05</v>
+        <v>26-서초구-06</v>
       </c>
       <c r="D71" t="str">
         <v>양호</v>
@@ -4622,16 +4622,16 @@
         <v>일반</v>
       </c>
       <c r="P71" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q71" t="str">
-        <v>서초동1328-3</v>
+        <v>서초동1328-11</v>
       </c>
       <c r="R71" t="str">
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
+        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
       </c>
       <c r="T71" t="str">
         <v/>
@@ -4639,13 +4639,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B72" t="str">
         <v>강남대로</v>
       </c>
       <c r="C72" t="str">
-        <v>26-서초구-06</v>
+        <v>26-서초구-07</v>
       </c>
       <c r="D72" t="str">
         <v>양호</v>
@@ -4687,13 +4687,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q72" t="str">
-        <v>서초동1328-11</v>
+        <v>서초동1329</v>
       </c>
       <c r="R72" t="str">
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
+        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
       </c>
       <c r="T72" t="str">
         <v/>
@@ -4701,13 +4701,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B73" t="str">
         <v>강남대로</v>
       </c>
       <c r="C73" t="str">
-        <v>26-서초구-07</v>
+        <v>26-서초구-08</v>
       </c>
       <c r="D73" t="str">
         <v>양호</v>
@@ -4746,16 +4746,16 @@
         <v>일반</v>
       </c>
       <c r="P73" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q73" t="str">
-        <v>서초동1329</v>
+        <v>서초동1329-4</v>
       </c>
       <c r="R73" t="str">
         <v/>
       </c>
       <c r="S73" t="str">
-        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
+        <v>우남빌딩 앞 도로(강남대로349)</v>
       </c>
       <c r="T73" t="str">
         <v/>
@@ -4763,16 +4763,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B74" t="str">
         <v>강남대로</v>
       </c>
       <c r="C74" t="str">
-        <v>26-서초구-08</v>
+        <v>26-서초구-09</v>
       </c>
       <c r="D74" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E74" t="str">
         <v>거북등</v>
@@ -4787,7 +4787,7 @@
         <v>-</v>
       </c>
       <c r="I74" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J74" t="str">
         <v>3</v>
@@ -4802,39 +4802,39 @@
         <v>0</v>
       </c>
       <c r="N74" t="str">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O74" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P74" t="str">
-        <v>-</v>
+        <v>복구부 밑 빈공간있음(80cm)</v>
       </c>
       <c r="Q74" t="str">
-        <v>서초동1329-4</v>
+        <v>서초동1329-7</v>
       </c>
       <c r="R74" t="str">
         <v/>
       </c>
       <c r="S74" t="str">
-        <v>우남빌딩 앞 도로(강남대로349)</v>
+        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
       </c>
       <c r="T74" t="str">
-        <v/>
+        <v>현장확인필요</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B75" t="str">
         <v>강남대로</v>
       </c>
       <c r="C75" t="str">
-        <v>26-서초구-09</v>
+        <v>26-서초구-10</v>
       </c>
       <c r="D75" t="str">
-        <v>불량</v>
+        <v>양호</v>
       </c>
       <c r="E75" t="str">
         <v>거북등</v>
@@ -4849,7 +4849,7 @@
         <v>-</v>
       </c>
       <c r="I75" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J75" t="str">
         <v>3</v>
@@ -4864,36 +4864,36 @@
         <v>0</v>
       </c>
       <c r="N75" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O75" t="str">
-        <v>긴급</v>
+        <v>일반</v>
       </c>
       <c r="P75" t="str">
-        <v>복구부 밑 빈공간있음(80cm)</v>
+        <v>-</v>
       </c>
       <c r="Q75" t="str">
-        <v>서초동1329-7</v>
+        <v>서초동1329-8</v>
       </c>
       <c r="R75" t="str">
         <v/>
       </c>
       <c r="S75" t="str">
-        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
+        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
       </c>
       <c r="T75" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B76" t="str">
         <v>강남대로</v>
       </c>
       <c r="C76" t="str">
-        <v>26-서초구-10</v>
+        <v>26-서초구-11</v>
       </c>
       <c r="D76" t="str">
         <v>양호</v>
@@ -4932,16 +4932,16 @@
         <v>일반</v>
       </c>
       <c r="P76" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="Q76" t="str">
-        <v>서초동1329-8</v>
+        <v>우성아파트앞 사거리</v>
       </c>
       <c r="R76" t="str">
         <v/>
       </c>
       <c r="S76" t="str">
-        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
+        <v>교차로(강남대로346-2)</v>
       </c>
       <c r="T76" t="str">
         <v/>
@@ -4949,13 +4949,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B77" t="str">
         <v>강남대로</v>
       </c>
       <c r="C77" t="str">
-        <v>26-서초구-11</v>
+        <v>26-서초구-12</v>
       </c>
       <c r="D77" t="str">
         <v>양호</v>
@@ -4994,30 +4994,30 @@
         <v>일반</v>
       </c>
       <c r="P77" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q77" t="str">
-        <v>우성아파트앞 사거리</v>
+        <v>서초동1337-32</v>
       </c>
       <c r="R77" t="str">
         <v/>
       </c>
       <c r="S77" t="str">
-        <v>교차로(강남대로346-2)</v>
+        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
       </c>
       <c r="T77" t="str">
-        <v/>
+        <v>현장확인필요</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B78" t="str">
         <v>강남대로</v>
       </c>
       <c r="C78" t="str">
-        <v>26-서초구-12</v>
+        <v>26-서초구-13</v>
       </c>
       <c r="D78" t="str">
         <v>양호</v>
@@ -5056,16 +5056,16 @@
         <v>일반</v>
       </c>
       <c r="P78" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q78" t="str">
-        <v>서초동1337-32</v>
+        <v>서초동1337-31</v>
       </c>
       <c r="R78" t="str">
         <v/>
       </c>
       <c r="S78" t="str">
-        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
+        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
       </c>
       <c r="T78" t="str">
         <v>현장확인필요</v>
@@ -5073,13 +5073,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B79" t="str">
         <v>강남대로</v>
       </c>
       <c r="C79" t="str">
-        <v>26-서초구-13</v>
+        <v>26-서초구-14</v>
       </c>
       <c r="D79" t="str">
         <v>양호</v>
@@ -5121,13 +5121,13 @@
         <v>-</v>
       </c>
       <c r="Q79" t="str">
-        <v>서초동1337-31</v>
+        <v>서초동1337-20</v>
       </c>
       <c r="R79" t="str">
         <v/>
       </c>
       <c r="S79" t="str">
-        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
+        <v>대륭서초타워 앞 도로(강남대로327)</v>
       </c>
       <c r="T79" t="str">
         <v>현장확인필요</v>
@@ -5135,19 +5135,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B80" t="str">
         <v>강남대로</v>
       </c>
       <c r="C80" t="str">
-        <v>26-서초구-14</v>
+        <v>26-서초구-15</v>
       </c>
       <c r="D80" t="str">
         <v>양호</v>
       </c>
       <c r="E80" t="str">
-        <v>거북등</v>
+        <v>거북이</v>
       </c>
       <c r="F80" t="str">
         <v>양호</v>
@@ -5183,13 +5183,13 @@
         <v>-</v>
       </c>
       <c r="Q80" t="str">
-        <v>서초동1337-20</v>
+        <v>서초동1337-22</v>
       </c>
       <c r="R80" t="str">
         <v/>
       </c>
       <c r="S80" t="str">
-        <v>대륭서초타워 앞 도로(강남대로327)</v>
+        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
       </c>
       <c r="T80" t="str">
         <v>현장확인필요</v>
@@ -5197,19 +5197,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B81" t="str">
         <v>강남대로</v>
       </c>
       <c r="C81" t="str">
-        <v>26-서초구-15</v>
+        <v>26-서초구-16</v>
       </c>
       <c r="D81" t="str">
         <v>양호</v>
       </c>
       <c r="E81" t="str">
-        <v>거북이</v>
+        <v>거북등</v>
       </c>
       <c r="F81" t="str">
         <v>양호</v>
@@ -5245,13 +5245,13 @@
         <v>-</v>
       </c>
       <c r="Q81" t="str">
-        <v>서초동1337-22</v>
+        <v>서초동1338-23</v>
       </c>
       <c r="R81" t="str">
         <v/>
       </c>
       <c r="S81" t="str">
-        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
+        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
       </c>
       <c r="T81" t="str">
         <v>현장확인필요</v>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B82" t="str">
         <v>강남대로</v>
       </c>
       <c r="C82" t="str">
-        <v>26-서초구-16</v>
+        <v>26-서초구-17</v>
       </c>
       <c r="D82" t="str">
         <v>양호</v>
@@ -5307,13 +5307,13 @@
         <v>-</v>
       </c>
       <c r="Q82" t="str">
-        <v>서초동1338-23</v>
+        <v>서초동1338-12</v>
       </c>
       <c r="R82" t="str">
         <v/>
       </c>
       <c r="S82" t="str">
-        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
+        <v>코인노트 앞 도로(강남대로311)</v>
       </c>
       <c r="T82" t="str">
         <v>현장확인필요</v>
@@ -5321,13 +5321,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B83" t="str">
         <v>강남대로</v>
       </c>
       <c r="C83" t="str">
-        <v>26-서초구-17</v>
+        <v>26-서초구-18</v>
       </c>
       <c r="D83" t="str">
         <v>양호</v>
@@ -5369,13 +5369,13 @@
         <v>-</v>
       </c>
       <c r="Q83" t="str">
-        <v>서초동1338-12</v>
+        <v>서초동1338-21</v>
       </c>
       <c r="R83" t="str">
         <v/>
       </c>
       <c r="S83" t="str">
-        <v>코인노트 앞 도로(강남대로311)</v>
+        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
       </c>
       <c r="T83" t="str">
         <v>현장확인필요</v>
@@ -5383,13 +5383,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B84" t="str">
         <v>강남대로</v>
       </c>
       <c r="C84" t="str">
-        <v>26-서초구-18</v>
+        <v>26-서초구-19</v>
       </c>
       <c r="D84" t="str">
         <v>양호</v>
@@ -5431,13 +5431,13 @@
         <v>-</v>
       </c>
       <c r="Q84" t="str">
-        <v>서초동1338-21</v>
+        <v>서초동1338-20</v>
       </c>
       <c r="R84" t="str">
         <v/>
       </c>
       <c r="S84" t="str">
-        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
+        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
       </c>
       <c r="T84" t="str">
         <v>현장확인필요</v>
@@ -5445,13 +5445,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B85" t="str">
         <v>강남대로</v>
       </c>
       <c r="C85" t="str">
-        <v>26-서초구-19</v>
+        <v>26-서초구-20</v>
       </c>
       <c r="D85" t="str">
         <v>양호</v>
@@ -5493,13 +5493,13 @@
         <v>-</v>
       </c>
       <c r="Q85" t="str">
-        <v>서초동1338-20</v>
+        <v>서초동1339-9</v>
       </c>
       <c r="R85" t="str">
         <v/>
       </c>
       <c r="S85" t="str">
-        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
+        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
       </c>
       <c r="T85" t="str">
         <v>현장확인필요</v>
@@ -5507,13 +5507,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B86" t="str">
         <v>강남대로</v>
       </c>
       <c r="C86" t="str">
-        <v>26-서초구-20</v>
+        <v>26-서초구-21</v>
       </c>
       <c r="D86" t="str">
         <v>양호</v>
@@ -5555,13 +5555,13 @@
         <v>-</v>
       </c>
       <c r="Q86" t="str">
-        <v>서초동1339-9</v>
+        <v>서초동1340-6</v>
       </c>
       <c r="R86" t="str">
         <v/>
       </c>
       <c r="S86" t="str">
-        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
+        <v>남강빌딩 앞 도로(강남대로291)</v>
       </c>
       <c r="T86" t="str">
         <v>현장확인필요</v>
@@ -5569,13 +5569,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B87" t="str">
         <v>강남대로</v>
       </c>
       <c r="C87" t="str">
-        <v>26-서초구-21</v>
+        <v>26-서초구-22</v>
       </c>
       <c r="D87" t="str">
         <v>양호</v>
@@ -5617,13 +5617,13 @@
         <v>-</v>
       </c>
       <c r="Q87" t="str">
-        <v>서초동1340-6</v>
+        <v>서초동1357-10</v>
       </c>
       <c r="R87" t="str">
         <v/>
       </c>
       <c r="S87" t="str">
-        <v>남강빌딩 앞 도로(강남대로291)</v>
+        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
       </c>
       <c r="T87" t="str">
         <v>현장확인필요</v>
@@ -5631,19 +5631,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B88" t="str">
         <v>강남대로</v>
       </c>
       <c r="C88" t="str">
-        <v>26-서초구-22</v>
+        <v>26-서초구-23</v>
       </c>
       <c r="D88" t="str">
         <v>양호</v>
       </c>
       <c r="E88" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F88" t="str">
         <v>양호</v>
@@ -5658,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K88" t="str">
         <v>0</v>
@@ -5670,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="N88" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O88" t="str">
         <v>일반</v>
@@ -5679,13 +5679,13 @@
         <v>-</v>
       </c>
       <c r="Q88" t="str">
-        <v>서초동1357-10</v>
+        <v>서초동1357-66</v>
       </c>
       <c r="R88" t="str">
         <v/>
       </c>
       <c r="S88" t="str">
-        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
+        <v>메인타워 CU 앞 도로(강남대로275)</v>
       </c>
       <c r="T88" t="str">
         <v>현장확인필요</v>
@@ -5693,19 +5693,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B89" t="str">
         <v>강남대로</v>
       </c>
       <c r="C89" t="str">
-        <v>26-서초구-23</v>
+        <v>26-서초구-24</v>
       </c>
       <c r="D89" t="str">
         <v>양호</v>
       </c>
       <c r="E89" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F89" t="str">
         <v>양호</v>
@@ -5741,21 +5741,517 @@
         <v>-</v>
       </c>
       <c r="Q89" t="str">
-        <v>서초동1357-66</v>
+        <v>서초동1358-7</v>
       </c>
       <c r="R89" t="str">
         <v/>
       </c>
       <c r="S89" t="str">
-        <v>메인타워 CU 앞 도로(강남대로275)</v>
+        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
       </c>
       <c r="T89" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>26-25</v>
+      </c>
+      <c r="B90" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C90" t="str">
+        <v>26-서초구-25</v>
+      </c>
+      <c r="D90" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E90" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F90" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G90" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H90" t="str">
+        <v>-</v>
+      </c>
+      <c r="I90" t="str">
+        <v>0</v>
+      </c>
+      <c r="J90" t="str">
+        <v>3</v>
+      </c>
+      <c r="K90" t="str">
+        <v>0</v>
+      </c>
+      <c r="L90" t="str">
+        <v>1</v>
+      </c>
+      <c r="M90" t="str">
+        <v>0</v>
+      </c>
+      <c r="N90" t="str">
+        <v>4</v>
+      </c>
+      <c r="O90" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P90" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>양재역사거리</v>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v>양재역 교차로(강남대로266-2)</v>
+      </c>
+      <c r="T90" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>26-26</v>
+      </c>
+      <c r="B91" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C91" t="str">
+        <v>26-서초구-26</v>
+      </c>
+      <c r="D91" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E91" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F91" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G91" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H91" t="str">
+        <v>-</v>
+      </c>
+      <c r="I91" t="str">
+        <v>0</v>
+      </c>
+      <c r="J91" t="str">
+        <v>3</v>
+      </c>
+      <c r="K91" t="str">
+        <v>0</v>
+      </c>
+      <c r="L91" t="str">
+        <v>1</v>
+      </c>
+      <c r="M91" t="str">
+        <v>0</v>
+      </c>
+      <c r="N91" t="str">
+        <v>4</v>
+      </c>
+      <c r="O91" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P91" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>양재동23</v>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
+      </c>
+      <c r="T91" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="B92" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C92" t="str">
+        <v>26-서초구-27</v>
+      </c>
+      <c r="D92" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E92" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F92" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G92" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H92" t="str">
+        <v>-</v>
+      </c>
+      <c r="I92" t="str">
+        <v>0</v>
+      </c>
+      <c r="J92" t="str">
+        <v>3</v>
+      </c>
+      <c r="K92" t="str">
+        <v>0</v>
+      </c>
+      <c r="L92" t="str">
+        <v>1</v>
+      </c>
+      <c r="M92" t="str">
+        <v>0</v>
+      </c>
+      <c r="N92" t="str">
+        <v>4</v>
+      </c>
+      <c r="O92" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P92" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>양재동24</v>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
+      </c>
+      <c r="T92" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>26-28</v>
+      </c>
+      <c r="B93" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C93" t="str">
+        <v>26-서초구-28</v>
+      </c>
+      <c r="D93" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E93" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F93" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G93" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H93" t="str">
+        <v>-</v>
+      </c>
+      <c r="I93" t="str">
+        <v>0</v>
+      </c>
+      <c r="J93" t="str">
+        <v>3</v>
+      </c>
+      <c r="K93" t="str">
+        <v>0</v>
+      </c>
+      <c r="L93" t="str">
+        <v>1</v>
+      </c>
+      <c r="M93" t="str">
+        <v>0</v>
+      </c>
+      <c r="N93" t="str">
+        <v>4</v>
+      </c>
+      <c r="O93" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P93" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>양재동24</v>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
+      </c>
+      <c r="T93" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>26-29</v>
+      </c>
+      <c r="B94" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C94" t="str">
+        <v>26-서초구-29</v>
+      </c>
+      <c r="D94" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E94" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F94" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G94" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H94" t="str">
+        <v>-</v>
+      </c>
+      <c r="I94" t="str">
+        <v>0</v>
+      </c>
+      <c r="J94" t="str">
+        <v>3</v>
+      </c>
+      <c r="K94" t="str">
+        <v>0</v>
+      </c>
+      <c r="L94" t="str">
+        <v>1</v>
+      </c>
+      <c r="M94" t="str">
+        <v>0</v>
+      </c>
+      <c r="N94" t="str">
+        <v>4</v>
+      </c>
+      <c r="O94" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P94" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q94" t="str">
+        <v>양재동 산20-2</v>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v>말죽거리공원 앞 도로(강남대로167)</v>
+      </c>
+      <c r="T94" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>26-30</v>
+      </c>
+      <c r="B95" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C95" t="str">
+        <v>26-서초구-30</v>
+      </c>
+      <c r="D95" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E95" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F95" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G95" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H95" t="str">
+        <v>-</v>
+      </c>
+      <c r="I95" t="str">
+        <v>0</v>
+      </c>
+      <c r="J95" t="str">
+        <v>1</v>
+      </c>
+      <c r="K95" t="str">
+        <v>0</v>
+      </c>
+      <c r="L95" t="str">
+        <v>1</v>
+      </c>
+      <c r="M95" t="str">
+        <v>0</v>
+      </c>
+      <c r="N95" t="str">
+        <v>2</v>
+      </c>
+      <c r="O95" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P95" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q95" t="str">
+        <v>양재동67</v>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v>혜인빌딩 앞 도로(163)</v>
+      </c>
+      <c r="T95" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>26-31</v>
+      </c>
+      <c r="B96" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C96" t="str">
+        <v>26-서초구-31</v>
+      </c>
+      <c r="D96" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E96" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F96" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G96" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H96" t="str">
+        <v>-</v>
+      </c>
+      <c r="I96" t="str">
+        <v>0</v>
+      </c>
+      <c r="J96" t="str">
+        <v>3</v>
+      </c>
+      <c r="K96" t="str">
+        <v>0</v>
+      </c>
+      <c r="L96" t="str">
+        <v>1</v>
+      </c>
+      <c r="M96" t="str">
+        <v>0</v>
+      </c>
+      <c r="N96" t="str">
+        <v>4</v>
+      </c>
+      <c r="O96" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P96" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q96" t="str">
+        <v>말죽거리공원사거리</v>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v>말죽거리공원 교차로(양재동20-40)</v>
+      </c>
+      <c r="T96" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>26-32</v>
+      </c>
+      <c r="B97" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C97" t="str">
+        <v>26-서초구-32</v>
+      </c>
+      <c r="D97" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E97" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F97" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G97" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H97" t="str">
+        <v>-</v>
+      </c>
+      <c r="I97" t="str">
+        <v>0</v>
+      </c>
+      <c r="J97" t="str">
+        <v>1</v>
+      </c>
+      <c r="K97" t="str">
+        <v>0</v>
+      </c>
+      <c r="L97" t="str">
+        <v>1</v>
+      </c>
+      <c r="M97" t="str">
+        <v>0</v>
+      </c>
+      <c r="N97" t="str">
+        <v>2</v>
+      </c>
+      <c r="O97" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P97" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v>직접입력</v>
+      </c>
+      <c r="T97" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T97"/>
+  <dimension ref="A1:T106"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4820,7 +4820,7 @@
         <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
       </c>
       <c r="T74" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -5006,7 +5006,7 @@
         <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
       </c>
       <c r="T77" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -5068,7 +5068,7 @@
         <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
       </c>
       <c r="T78" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -5130,7 +5130,7 @@
         <v>대륭서초타워 앞 도로(강남대로327)</v>
       </c>
       <c r="T79" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -5192,7 +5192,7 @@
         <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
       </c>
       <c r="T80" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -5254,7 +5254,7 @@
         <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
       </c>
       <c r="T81" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -5316,7 +5316,7 @@
         <v>코인노트 앞 도로(강남대로311)</v>
       </c>
       <c r="T82" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -5378,7 +5378,7 @@
         <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
       </c>
       <c r="T83" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -5440,7 +5440,7 @@
         <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
       </c>
       <c r="T84" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -5502,7 +5502,7 @@
         <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
       </c>
       <c r="T85" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -5564,7 +5564,7 @@
         <v>남강빌딩 앞 도로(강남대로291)</v>
       </c>
       <c r="T86" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -5626,7 +5626,7 @@
         <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
       </c>
       <c r="T87" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -5688,7 +5688,7 @@
         <v>메인타워 CU 앞 도로(강남대로275)</v>
       </c>
       <c r="T88" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -5750,7 +5750,7 @@
         <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
       </c>
       <c r="T89" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -5812,7 +5812,7 @@
         <v>양재역 교차로(강남대로266-2)</v>
       </c>
       <c r="T90" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -5874,7 +5874,7 @@
         <v>양재역 #10번출구 앞 도로(강남대로221)</v>
       </c>
       <c r="T91" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -5936,7 +5936,7 @@
         <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
       </c>
       <c r="T92" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -5998,7 +5998,7 @@
         <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
       </c>
       <c r="T93" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -6060,7 +6060,7 @@
         <v>말죽거리공원 앞 도로(강남대로167)</v>
       </c>
       <c r="T94" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -6122,7 +6122,7 @@
         <v>혜인빌딩 앞 도로(163)</v>
       </c>
       <c r="T95" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -6184,7 +6184,7 @@
         <v>말죽거리공원 교차로(양재동20-40)</v>
       </c>
       <c r="T96" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -6237,21 +6237,579 @@
         <v>-</v>
       </c>
       <c r="Q97" t="str">
-        <v/>
+        <v>양재동125</v>
       </c>
       <c r="R97" t="str">
         <v/>
       </c>
       <c r="S97" t="str">
-        <v>직접입력</v>
+        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
       </c>
       <c r="T97" t="str">
-        <v>현장확인필요</v>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>26-33</v>
+      </c>
+      <c r="B98" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C98" t="str">
+        <v>26-서초구-33</v>
+      </c>
+      <c r="D98" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E98" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F98" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G98" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H98" t="str">
+        <v>-</v>
+      </c>
+      <c r="I98" t="str">
+        <v>0</v>
+      </c>
+      <c r="J98" t="str">
+        <v>3</v>
+      </c>
+      <c r="K98" t="str">
+        <v>0</v>
+      </c>
+      <c r="L98" t="str">
+        <v>1</v>
+      </c>
+      <c r="M98" t="str">
+        <v>0</v>
+      </c>
+      <c r="N98" t="str">
+        <v>4</v>
+      </c>
+      <c r="O98" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P98" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q98" t="str">
+        <v>양재동80-3</v>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
+      </c>
+      <c r="T98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>26-34</v>
+      </c>
+      <c r="B99" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C99" t="str">
+        <v>26-서초구-34</v>
+      </c>
+      <c r="D99" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E99" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F99" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G99" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H99" t="str">
+        <v>-</v>
+      </c>
+      <c r="I99" t="str">
+        <v>0</v>
+      </c>
+      <c r="J99" t="str">
+        <v>3</v>
+      </c>
+      <c r="K99" t="str">
+        <v>0</v>
+      </c>
+      <c r="L99" t="str">
+        <v>1</v>
+      </c>
+      <c r="M99" t="str">
+        <v>0</v>
+      </c>
+      <c r="N99" t="str">
+        <v>4</v>
+      </c>
+      <c r="O99" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P99" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q99" t="str">
+        <v>매헌시민의숲사거리</v>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>26-35</v>
+      </c>
+      <c r="B100" t="str">
+        <v>강남대로</v>
+      </c>
+      <c r="C100" t="str">
+        <v>26-서초구-35</v>
+      </c>
+      <c r="D100" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E100" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F100" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G100" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H100" t="str">
+        <v>-</v>
+      </c>
+      <c r="I100" t="str">
+        <v>0</v>
+      </c>
+      <c r="J100" t="str">
+        <v>3</v>
+      </c>
+      <c r="K100" t="str">
+        <v>0</v>
+      </c>
+      <c r="L100" t="str">
+        <v>1</v>
+      </c>
+      <c r="M100" t="str">
+        <v>0</v>
+      </c>
+      <c r="N100" t="str">
+        <v>4</v>
+      </c>
+      <c r="O100" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P100" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q100" t="str">
+        <v>양재동237</v>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>26-36</v>
+      </c>
+      <c r="B101" t="str">
+        <v>매헌로</v>
+      </c>
+      <c r="C101" t="str">
+        <v>26-서초구-36</v>
+      </c>
+      <c r="D101" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E101" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F101" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G101" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H101" t="str">
+        <v>-</v>
+      </c>
+      <c r="I101" t="str">
+        <v>0</v>
+      </c>
+      <c r="J101" t="str">
+        <v>3</v>
+      </c>
+      <c r="K101" t="str">
+        <v>0</v>
+      </c>
+      <c r="L101" t="str">
+        <v>1</v>
+      </c>
+      <c r="M101" t="str">
+        <v>0</v>
+      </c>
+      <c r="N101" t="str">
+        <v>4</v>
+      </c>
+      <c r="O101" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P101" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>양재동237-2</v>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v>매헌역 공영주차장 입구 앞 도로</v>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>26-37</v>
+      </c>
+      <c r="B102" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C102" t="str">
+        <v>26-서초구-37</v>
+      </c>
+      <c r="D102" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E102" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F102" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G102" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H102" t="str">
+        <v>-</v>
+      </c>
+      <c r="I102" t="str">
+        <v>0</v>
+      </c>
+      <c r="J102" t="str">
+        <v>3</v>
+      </c>
+      <c r="K102" t="str">
+        <v>0</v>
+      </c>
+      <c r="L102" t="str">
+        <v>1</v>
+      </c>
+      <c r="M102" t="str">
+        <v>0</v>
+      </c>
+      <c r="N102" t="str">
+        <v>4</v>
+      </c>
+      <c r="O102" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P102" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>신원동308-1</v>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v>가로등(청계산로69)_양차선</v>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>26-38</v>
+      </c>
+      <c r="B103" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C103" t="str">
+        <v>26-서초구-38</v>
+      </c>
+      <c r="D103" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E103" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F103" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G103" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H103" t="str">
+        <v>-</v>
+      </c>
+      <c r="I103" t="str">
+        <v>0</v>
+      </c>
+      <c r="J103" t="str">
+        <v>3</v>
+      </c>
+      <c r="K103" t="str">
+        <v>0</v>
+      </c>
+      <c r="L103" t="str">
+        <v>1</v>
+      </c>
+      <c r="M103" t="str">
+        <v>0</v>
+      </c>
+      <c r="N103" t="str">
+        <v>4</v>
+      </c>
+      <c r="O103" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P103" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q103" t="str">
+        <v>신원동298-16</v>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v>청계산 수변공원 앞 도로_양차선</v>
+      </c>
+      <c r="T103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>26-39</v>
+      </c>
+      <c r="B104" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C104" t="str">
+        <v>26-서초구-39</v>
+      </c>
+      <c r="D104" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E104" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F104" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G104" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H104" t="str">
+        <v>-</v>
+      </c>
+      <c r="I104" t="str">
+        <v>0</v>
+      </c>
+      <c r="J104" t="str">
+        <v>3</v>
+      </c>
+      <c r="K104" t="str">
+        <v>0</v>
+      </c>
+      <c r="L104" t="str">
+        <v>1</v>
+      </c>
+      <c r="M104" t="str">
+        <v>0</v>
+      </c>
+      <c r="N104" t="str">
+        <v>4</v>
+      </c>
+      <c r="O104" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P104" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q104" t="str">
+        <v>신원동298-16</v>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v>가로등(청계산로81)앞도로_양차선</v>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>26-40</v>
+      </c>
+      <c r="B105" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C105" t="str">
+        <v>26-서초구-40</v>
+      </c>
+      <c r="D105" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E105" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F105" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G105" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H105" t="str">
+        <v>-</v>
+      </c>
+      <c r="I105" t="str">
+        <v>0</v>
+      </c>
+      <c r="J105" t="str">
+        <v>3</v>
+      </c>
+      <c r="K105" t="str">
+        <v>0</v>
+      </c>
+      <c r="L105" t="str">
+        <v>1</v>
+      </c>
+      <c r="M105" t="str">
+        <v>0</v>
+      </c>
+      <c r="N105" t="str">
+        <v>4</v>
+      </c>
+      <c r="O105" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P105" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>원지동595</v>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>26-41</v>
+      </c>
+      <c r="B106" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C106" t="str">
+        <v>26-서초구-41</v>
+      </c>
+      <c r="D106" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E106" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F106" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G106" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H106" t="str">
+        <v>-</v>
+      </c>
+      <c r="I106" t="str">
+        <v>0</v>
+      </c>
+      <c r="J106" t="str">
+        <v>3</v>
+      </c>
+      <c r="K106" t="str">
+        <v>0</v>
+      </c>
+      <c r="L106" t="str">
+        <v>1</v>
+      </c>
+      <c r="M106" t="str">
+        <v>0</v>
+      </c>
+      <c r="N106" t="str">
+        <v>4</v>
+      </c>
+      <c r="O106" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P106" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>신원동280-1</v>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v>교차로(T)_양차선</v>
+      </c>
+      <c r="T106" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T106"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T106"/>
+  <dimension ref="A1:T118"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-4</v>
+        <v>25-서초구-5</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -533,13 +533,13 @@
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v>서초동 1319-13</v>
+        <v>서초동 1328-3</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>강남역 #6번출구 뒤 도로</v>
+        <v>우리은행 서초금융센터 앞 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-서초구-5</v>
+        <v>25-서초구-6</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -592,16 +592,16 @@
         <v>일반</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>포장 복구개소</v>
       </c>
       <c r="Q6" t="str">
-        <v>서초동 1328-3</v>
+        <v>서초동 1328-10</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>우리은행 서초금융센터 앞 도로</v>
+        <v>강남역 #5번출구 앞 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="str">
         <v>강남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-서초구-6</v>
+        <v>25-서초구-7</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -654,16 +654,16 @@
         <v>일반</v>
       </c>
       <c r="P7" t="str">
-        <v>포장 복구개소</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q7" t="str">
-        <v>서초동 1328-10</v>
+        <v>서초동 1328-11</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>강남역 #5번출구 앞 도로</v>
+        <v>도씨의 빛Ⅱ 앞 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-서초구-7</v>
+        <v>25-서초구-8</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -716,16 +716,16 @@
         <v>일반</v>
       </c>
       <c r="P8" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q8" t="str">
-        <v>서초동 1328-11</v>
+        <v>서초동 1329</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>도씨의 빛Ⅱ 앞 도로</v>
+        <v>삼성화제 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-서초구-8</v>
+        <v>25-서초구-9</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -778,16 +778,16 @@
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q9" t="str">
-        <v>서초동 1329</v>
+        <v>서초동 1329-7</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>삼성화제 앞 도로</v>
+        <v>신한투자증권 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-서초구-9</v>
+        <v>25-서초구-10</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -843,13 +843,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q10" t="str">
-        <v>서초동 1329-7</v>
+        <v>서초동 1329-8</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>신한투자증권 앞 도로</v>
+        <v>모닝글로리 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-서초구-10</v>
+        <v>25-서초구-11</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -902,16 +902,16 @@
         <v>일반</v>
       </c>
       <c r="P11" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q11" t="str">
-        <v>서초동 1329-8</v>
+        <v>서초동 1329-10</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>모닝글로리 앞 도로</v>
+        <v>우성아파트 사거리 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-서초구-11</v>
+        <v>25-서초구-12</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -964,16 +964,16 @@
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q12" t="str">
-        <v>서초동 1329-10</v>
+        <v>서초동 1337-32</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>우성아파트 사거리 도로</v>
+        <v>한국투자증권 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-서초구-12</v>
+        <v>25-서초구-13</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1026,16 +1026,16 @@
         <v>일반</v>
       </c>
       <c r="P13" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
-        <v>서초동 1337-32</v>
+        <v>서초동 1337-22</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>한국투자증권 앞 도로</v>
+        <v>디오빌프라임 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-서초구-13</v>
+        <v>25-서초구-14</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1091,13 +1091,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>서초동 1337-22</v>
+        <v>서초동 1338-23</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>디오빌프라임 앞 도로</v>
+        <v>투썸플레이스 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-서초구-14</v>
+        <v>25-서초구-15</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>서초동 1338-23</v>
+        <v>서초동 1338-20</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>투썸플레이스 도로</v>
+        <v>현대렉시온 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-서초구-15</v>
+        <v>25-서초구-16</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1182,7 +1182,7 @@
         <v>거북등</v>
       </c>
       <c r="F16" t="str">
-        <v>양호</v>
+        <v>건조</v>
       </c>
       <c r="G16" t="str">
         <v>13.5</v>
@@ -1215,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>서초동 1338-20</v>
+        <v>서초동 1339-9</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>현대렉시온 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-서초구-16</v>
+        <v>25-서초구-17</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1277,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>서초동 1339-9</v>
+        <v>서초동 1340-6</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>KIA 서초지점 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1336,7 +1336,7 @@
         <v>일반</v>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q18" t="str">
         <v>서초동 1340-6</v>
@@ -1345,7 +1345,7 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>KIA 서초지점 앞 도로</v>
+        <v>남강매점 앞 횡단보도</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-서초구-18</v>
+        <v>25-서초구-19</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1398,16 +1398,16 @@
         <v>일반</v>
       </c>
       <c r="P19" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q19" t="str">
-        <v>서초동 1340-6</v>
+        <v>서초동 1357-33</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>남강매점 앞 횡단보도</v>
+        <v>한국디지털 평생교육원 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-서초구-19</v>
+        <v>25-서초구-20</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1460,16 +1460,16 @@
         <v>일반</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q20" t="str">
-        <v>서초동 1357-33</v>
+        <v>서초동 1357-35</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>한국디지털 평생교육원 앞 도로</v>
+        <v>부산은행 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-서초구-20</v>
+        <v>25-서초구-21</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1525,13 +1525,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q21" t="str">
-        <v>서초동 1357-35</v>
+        <v>서초동 1358-6</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>부산은행 앞 도로</v>
+        <v>송남빌딩 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,19 +1539,19 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="str">
         <v>강남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-서초구-21</v>
+        <v>25-서초구-22</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
       </c>
       <c r="E22" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F22" t="str">
         <v>건조</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1578,22 +1578,22 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O22" t="str">
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q22" t="str">
-        <v>서초동 1358-6</v>
+        <v>서초동 1361-1</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>송남빌딩 앞 도로</v>
+        <v>보들설곰탕 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="str">
         <v>강남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-서초구-22</v>
+        <v>25-서초구-23</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
@@ -1649,13 +1649,13 @@
         <v/>
       </c>
       <c r="Q23" t="str">
-        <v>서초동 1361-1</v>
+        <v>서초동 1361-5</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>보들설곰탕 앞 도로</v>
+        <v>새움빌딩 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,19 +1663,19 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="str">
         <v>강남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-서초구-23</v>
+        <v>25-서초구-24</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
       </c>
       <c r="E24" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F24" t="str">
         <v>건조</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O24" t="str">
         <v>일반</v>
@@ -1711,13 +1711,13 @@
         <v/>
       </c>
       <c r="Q24" t="str">
-        <v>서초동 1361-5</v>
+        <v>서초동 1361-10</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>새움빌딩 앞 도로</v>
+        <v>호텔 페이토 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="str">
         <v>강남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-서초구-24</v>
+        <v>25-서초구-25</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
@@ -1770,16 +1770,16 @@
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q25" t="str">
-        <v>서초동 1361-10</v>
+        <v>서초동 1362</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>호텔 페이토 앞 도로</v>
+        <v>e마트24 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="str">
         <v>강남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-서초구-25</v>
+        <v>25-서초구-26</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1832,16 +1832,16 @@
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q26" t="str">
-        <v>서초동 1362</v>
+        <v>서초동 1362-26</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>e마트24 앞 도로</v>
+        <v>힐든가든인 서울강남 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="str">
         <v>강남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-서초구-26</v>
+        <v>25-서초구-27</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1894,16 +1894,16 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q27" t="str">
-        <v>서초동 1362-26</v>
+        <v>서초동 1362-27</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>힐든가든인 서울강남 앞 도로</v>
+        <v>니드오피스텔 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="str">
         <v>강남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-서초구-27</v>
+        <v>25-서초구-28</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q28" t="str">
-        <v>서초동 1362-27</v>
+        <v>서초동 1366-7</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>니드오피스텔 앞 도로</v>
+        <v>깐부치킨 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="str">
         <v>강남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-서초구-28</v>
+        <v>25-서초구-29</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2018,16 +2018,16 @@
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q29" t="str">
-        <v>서초동 1366-7</v>
+        <v>서초동 1366-9</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>깐부치킨 앞 도로</v>
+        <v>양재역 교차로 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="str">
         <v>강남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-서초구-29</v>
+        <v>25-서초구-30</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2080,16 +2080,16 @@
         <v>일반</v>
       </c>
       <c r="P30" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q30" t="str">
-        <v>서초동 1366-9</v>
+        <v>양재동 23</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>양재역 교차로 도로</v>
+        <v>바나프레소 앞 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="str">
         <v>강남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-서초구-30</v>
+        <v>25-서초구-31</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
@@ -2145,13 +2145,13 @@
         <v/>
       </c>
       <c r="Q31" t="str">
-        <v>양재동 23</v>
+        <v>양재동 25</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>바나프레소 앞 도로</v>
+        <v>서초문화 예술회관 앞 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,13 +2159,13 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-서초구-31</v>
+        <v>25-서초구-32</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
@@ -2207,13 +2207,13 @@
         <v/>
       </c>
       <c r="Q32" t="str">
-        <v>양재동 25</v>
+        <v>양재동 14-4</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>서초문화 예술회관 앞 도로</v>
+        <v>모산빌딩 앞 횡단보도</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-서초구-32</v>
+        <v>25-서초구-33</v>
       </c>
       <c r="D33" t="str">
-        <v>양호</v>
+        <v>50</v>
       </c>
       <c r="E33" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F33" t="str">
         <v>건조</v>
@@ -2244,11 +2244,11 @@
       <c r="H33" t="str">
         <v>-</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="b">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2260,22 +2260,22 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O33" t="str">
         <v>일반</v>
       </c>
       <c r="P33" t="str">
-        <v/>
+        <v>보도침하5cm</v>
       </c>
       <c r="Q33" t="str">
-        <v>양재동 14-4</v>
+        <v>양재동 67-7</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>모산빌딩 앞 횡단보도</v>
+        <v>바나프레스 앞 보도</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,19 +2283,19 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-서초구-33</v>
+        <v>25-서초구-34</v>
       </c>
       <c r="D34" t="str">
-        <v>50</v>
+        <v>양호</v>
       </c>
       <c r="E34" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F34" t="str">
         <v>건조</v>
@@ -2306,11 +2306,11 @@
       <c r="H34" t="str">
         <v>-</v>
       </c>
-      <c r="I34" t="b">
+      <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2322,22 +2322,22 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O34" t="str">
         <v>일반</v>
       </c>
       <c r="P34" t="str">
-        <v>보도침하5cm</v>
+        <v/>
       </c>
       <c r="Q34" t="str">
-        <v>양재동 67-7</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>바나프레스 앞 보도</v>
+        <v>교육개발원 사거리 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,19 +2345,19 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="str">
         <v>강남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-서초구-34</v>
+        <v>25-서초구-35</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
       </c>
       <c r="E35" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F35" t="str">
         <v>건조</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O35" t="str">
         <v>일반</v>
@@ -2393,13 +2393,13 @@
         <v/>
       </c>
       <c r="Q35" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동 109</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>교육개발원 사거리 도로</v>
+        <v>카페 릴리블랑 앞 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,19 +2407,19 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="str">
         <v>강남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-서초구-35</v>
+        <v>25-서초구-36</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
       </c>
       <c r="E36" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F36" t="str">
         <v>건조</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O36" t="str">
         <v>일반</v>
@@ -2455,13 +2455,13 @@
         <v/>
       </c>
       <c r="Q36" t="str">
-        <v>양재동 109</v>
+        <v>양재동 125</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>카페 릴리블랑 앞 도로</v>
+        <v>넥스팜 코리아 앞 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" t="str">
         <v>강남대로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-서초구-36</v>
+        <v>25-서초구-37</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>양재동 125</v>
+        <v>양재동 80-3</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>넥스팜 코리아 앞 도로</v>
+        <v>도야짬뽕 앞 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-서초구-37</v>
+        <v>25-서초구-38</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>양재동 80-3</v>
+        <v>양재동 237-1</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>도야짬뽕 앞 도로</v>
+        <v>공영주차장 앞 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-서초구-38</v>
+        <v>25-서초구-39</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2641,13 +2641,13 @@
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>양재동 237-1</v>
+        <v>신원동 308-1</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>공영주차장 앞 도로</v>
+        <v>가로등(청계산로145) 양차선 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" t="str">
         <v>청계산로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-서초구-39</v>
+        <v>25-서초구-40</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2703,13 +2703,13 @@
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>신원동 308-1</v>
+        <v>원지동 294-3</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>가로등(청계산로145) 양차선 도로</v>
+        <v>전봇대(원지간37H1) 양차선 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="str">
         <v>청계산로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-서초구-40</v>
+        <v>25-서초구-41</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2762,16 +2762,16 @@
         <v>일반</v>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>거북등 맨홀침하4cm</v>
       </c>
       <c r="Q41" t="str">
-        <v>원지동 294-3</v>
+        <v>원지동 594-1</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>전봇대(원지간37H1) 양차선 도로</v>
+        <v>도로교통표지판 앞 상수도맨홀 도로</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,13 +2779,13 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" t="str">
         <v>청계산로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-서초구-41</v>
+        <v>25-서초구-42</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
@@ -2824,16 +2824,16 @@
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v>거북등 맨홀침하4cm</v>
+        <v/>
       </c>
       <c r="Q42" t="str">
-        <v>원지동 594-1</v>
+        <v>신원동 280</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>도로교통표지판 앞 상수도맨홀 도로</v>
+        <v>공영주차장 앞 T 교차로 양차선 도로</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="str">
         <v>청계산로</v>
       </c>
       <c r="C43" t="str">
-        <v>25-서초구-42</v>
+        <v>25-서초구-43</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
@@ -2889,13 +2889,13 @@
         <v/>
       </c>
       <c r="Q43" t="str">
-        <v>신원동 280</v>
+        <v>신원동 278-6</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>공영주차장 앞 T 교차로 양차선 도로</v>
+        <v>공영주차장 앞 양차선 도로</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,13 +2903,13 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="str">
         <v>청계산로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-서초구-43</v>
+        <v>25-서초구-44</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
@@ -2948,16 +2948,16 @@
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q44" t="str">
-        <v>신원동 278-6</v>
+        <v>신원동 611</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>공영주차장 앞 양차선 도로</v>
+        <v>투썸플레이스 앞 보도</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,19 +2965,19 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" t="str">
         <v>청계산로</v>
       </c>
       <c r="C45" t="str">
-        <v>25-서초구-44</v>
+        <v>25-서초구-45</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F45" t="str">
         <v>건조</v>
@@ -2992,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3004,22 +3004,22 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O45" t="str">
         <v>일반</v>
       </c>
       <c r="P45" t="str">
-        <v>보도침하4cm</v>
+        <v/>
       </c>
       <c r="Q45" t="str">
-        <v>신원동 611</v>
+        <v>신원동 612</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>투썸플레이스 앞 보도</v>
+        <v>LAB 앞 도로</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,19 +3027,19 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" t="str">
         <v>청계산로</v>
       </c>
       <c r="C46" t="str">
-        <v>25-서초구-45</v>
+        <v>25-서초구-46</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F46" t="str">
         <v>건조</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -3066,22 +3066,22 @@
         <v>0</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O46" t="str">
         <v>일반</v>
       </c>
       <c r="P46" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q46" t="str">
-        <v>신원동 612</v>
+        <v>신원동 660</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>LAB 앞 도로</v>
+        <v>심플리시티 앞 보도</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,13 +3089,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" t="str">
         <v>청계산로</v>
       </c>
       <c r="C47" t="str">
-        <v>25-서초구-46</v>
+        <v>25-서초구-47</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
@@ -3134,16 +3134,16 @@
         <v>일반</v>
       </c>
       <c r="P47" t="str">
-        <v>보도침하4cm</v>
+        <v>보도침하3cm</v>
       </c>
       <c r="Q47" t="str">
-        <v>신원동 660</v>
+        <v>신원동 197-1</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>심플리시티 앞 보도</v>
+        <v>부안애서 맞음편 보도</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,13 +3151,13 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" t="str">
         <v>청계산로</v>
       </c>
       <c r="C48" t="str">
-        <v>25-서초구-47</v>
+        <v>25-서초구-48</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
@@ -3196,16 +3196,16 @@
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v>보도침하3cm</v>
+        <v/>
       </c>
       <c r="Q48" t="str">
-        <v>신원동 197-1</v>
+        <v>원지동 384-1</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>부안애서 맞음편 보도</v>
+        <v>커피플라워 앞 양차선 도로</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,13 +3213,13 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" t="str">
         <v>청계산로</v>
       </c>
       <c r="C49" t="str">
-        <v>25-서초구-48</v>
+        <v>25-서초구-49</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3261,13 +3261,13 @@
         <v/>
       </c>
       <c r="Q49" t="str">
-        <v>원지동 384-1</v>
+        <v>신원동 192-73</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>커피플라워 앞 양차선 도로</v>
+        <v>봉평막국수 앞 양차선 도로</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,13 +3275,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" t="str">
         <v>청계산로</v>
       </c>
       <c r="C50" t="str">
-        <v>25-서초구-49</v>
+        <v>25-서초구-50</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3323,13 +3323,13 @@
         <v/>
       </c>
       <c r="Q50" t="str">
-        <v>신원동 192-73</v>
+        <v>신원동 172-1</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>봉평막국수 앞 양차선 도로</v>
+        <v>향린조경 앞 양차선 도로</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" t="str">
         <v>청계산로</v>
       </c>
       <c r="C51" t="str">
-        <v>25-서초구-50</v>
+        <v>25-서초구-51</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3385,13 +3385,13 @@
         <v/>
       </c>
       <c r="Q51" t="str">
-        <v>신원동 172-1</v>
+        <v>신원동 153</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>향린조경 앞 양차선 도로</v>
+        <v>삼석원 앞 양차선 도로</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" t="str">
         <v>청계산로</v>
       </c>
       <c r="C52" t="str">
-        <v>25-서초구-51</v>
+        <v>25-서초구-52</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3447,13 +3447,13 @@
         <v/>
       </c>
       <c r="Q52" t="str">
-        <v>신원동 153</v>
+        <v>신원동 150-1</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>삼석원 앞 양차선 도로</v>
+        <v>성심조경 앞 양차선 도로</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" t="str">
         <v>청계산로</v>
       </c>
       <c r="C53" t="str">
-        <v>25-서초구-52</v>
+        <v>25-서초구-53</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3506,16 +3506,16 @@
         <v>일반</v>
       </c>
       <c r="P53" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q53" t="str">
-        <v>신원동 150-1</v>
+        <v>원지동 470-1</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>성심조경 앞 양차선 도로</v>
+        <v>가로등(청계산로154) 앞 보도</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3523,13 +3523,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" t="str">
         <v>청계산로</v>
       </c>
       <c r="C54" t="str">
-        <v>25-서초구-53</v>
+        <v>25-서초구-54</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3568,16 +3568,16 @@
         <v>일반</v>
       </c>
       <c r="P54" t="str">
-        <v>5cm이하 침하</v>
+        <v>보도침하</v>
       </c>
       <c r="Q54" t="str">
-        <v>원지동 470-1</v>
+        <v>원지동 491-6</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>가로등(청계산로154) 앞 보도</v>
+        <v>가로등(청계산로156) 맞음편 보도</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" t="str">
         <v>청계산로</v>
       </c>
       <c r="C55" t="str">
-        <v>25-서초구-54</v>
+        <v>25-서초구-55</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3630,16 +3630,16 @@
         <v>일반</v>
       </c>
       <c r="P55" t="str">
-        <v>보도침하</v>
+        <v/>
       </c>
       <c r="Q55" t="str">
-        <v>원지동 491-6</v>
+        <v>원지동 493</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>가로등(청계산로156) 맞음편 보도</v>
+        <v>양재조경 앞 양차선 도로</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3647,13 +3647,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" t="str">
         <v>청계산로</v>
       </c>
       <c r="C56" t="str">
-        <v>25-서초구-55</v>
+        <v>25-서초구-56</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3695,13 +3695,13 @@
         <v/>
       </c>
       <c r="Q56" t="str">
-        <v>원지동 493</v>
+        <v>원지동 497-3</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>양재조경 앞 양차선 도로</v>
+        <v>가로등(청계산로168) 앞 양차선 도로</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3709,13 +3709,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" t="str">
         <v>청계산로</v>
       </c>
       <c r="C57" t="str">
-        <v>25-서초구-56</v>
+        <v>25-서초구-57</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="Q57" t="str">
-        <v>원지동 497-3</v>
+        <v>신원동 산 60-2</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>가로등(청계산로168) 앞 양차선 도로</v>
+        <v>대원조경 앞 양차선 도로</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3771,13 +3771,13 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" t="str">
         <v>청계산로</v>
       </c>
       <c r="C58" t="str">
-        <v>25-서초구-57</v>
+        <v>25-서초구-58</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3819,13 +3819,13 @@
         <v/>
       </c>
       <c r="Q58" t="str">
-        <v>신원동 산 60-2</v>
+        <v>신원동 105-4</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>대원조경 앞 양차선 도로</v>
+        <v>둥지조경 제2농장 앞 양차선 도로</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3833,13 +3833,13 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" t="str">
         <v>청계산로</v>
       </c>
       <c r="C59" t="str">
-        <v>25-서초구-58</v>
+        <v>25-서초구-59</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3881,13 +3881,13 @@
         <v/>
       </c>
       <c r="Q59" t="str">
-        <v>신원동 105-4</v>
+        <v>신원동 105-33</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>둥지조경 제2농장 앞 양차선 도로</v>
+        <v>한백자생식물원 앞 양차선 도로</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3895,13 +3895,13 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" t="str">
         <v>청계산로</v>
       </c>
       <c r="C60" t="str">
-        <v>25-서초구-59</v>
+        <v>25-서초구-60</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
@@ -3940,16 +3940,16 @@
         <v>일반</v>
       </c>
       <c r="P60" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q60" t="str">
-        <v>신원동 105-33</v>
+        <v>신원동 105-19</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>한백자생식물원 앞 양차선 도로</v>
+        <v>가로등(청계산로190) 앞 양차선 도로</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3957,19 +3957,19 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" t="str">
         <v>청계산로</v>
       </c>
       <c r="C61" t="str">
-        <v>25-서초구-60</v>
+        <v>25-서초구-61</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
       </c>
       <c r="E61" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F61" t="str">
         <v>건조</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O61" t="str">
         <v>일반</v>
@@ -4005,13 +4005,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q61" t="str">
-        <v>신원동 105-19</v>
+        <v>신원동 44-1</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>가로등(청계산로190) 앞 양차선 도로</v>
+        <v>새정이마을 입구 교차로</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4019,19 +4019,19 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" t="str">
         <v>청계산로</v>
       </c>
       <c r="C62" t="str">
-        <v>25-서초구-61</v>
+        <v>25-서초구-62</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
       </c>
       <c r="E62" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F62" t="str">
         <v>건조</v>
@@ -4064,16 +4064,16 @@
         <v>일반</v>
       </c>
       <c r="P62" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q62" t="str">
-        <v>신원동 44-1</v>
+        <v>신원동 44-5</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>새정이마을 입구 교차로</v>
+        <v>은하조경 앞 양차선 도로</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4081,13 +4081,13 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" t="str">
         <v>청계산로</v>
       </c>
       <c r="C63" t="str">
-        <v>25-서초구-62</v>
+        <v>25-서초구-63</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
@@ -4129,13 +4129,13 @@
         <v/>
       </c>
       <c r="Q63" t="str">
-        <v>신원동 44-5</v>
+        <v>신원동 57</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>은하조경 앞 양차선 도로</v>
+        <v>서림원예종묘 앞 양차선 도로</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4143,19 +4143,19 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" t="str">
         <v>청계산로</v>
       </c>
       <c r="C64" t="str">
-        <v>25-서초구-63</v>
+        <v>25-서초구-64</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
       </c>
       <c r="E64" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F64" t="str">
         <v>건조</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -4182,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="N64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O64" t="str">
         <v>일반</v>
@@ -4191,27 +4191,27 @@
         <v/>
       </c>
       <c r="Q64" t="str">
-        <v>신원동 57</v>
+        <v>신원동 64-1</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>서림원예종묘 앞 양차선 도로</v>
+        <v>옥천조경 앞 양차선 도로</v>
       </c>
       <c r="T64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65">
-        <v>64</v>
+      <c r="A65" t="str">
+        <v>26-01</v>
       </c>
       <c r="B65" t="str">
-        <v>청계산로</v>
+        <v>강남대로</v>
       </c>
       <c r="C65" t="str">
-        <v>25-서초구-64</v>
+        <v>26-서초구-01</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
@@ -4220,46 +4220,46 @@
         <v>거북등</v>
       </c>
       <c r="F65" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G65" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H65" t="str">
         <v>-</v>
       </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>3</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>1</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
+      <c r="I65" t="str">
+        <v>0</v>
+      </c>
+      <c r="J65" t="str">
+        <v>3</v>
+      </c>
+      <c r="K65" t="str">
+        <v>0</v>
+      </c>
+      <c r="L65" t="str">
+        <v>1</v>
+      </c>
+      <c r="M65" t="str">
+        <v>0</v>
+      </c>
+      <c r="N65" t="str">
         <v>4</v>
       </c>
       <c r="O65" t="str">
         <v>일반</v>
       </c>
       <c r="P65" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q65" t="str">
-        <v>신원동 64-1</v>
+        <v>서초동1318-4</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>옥천조경 앞 양차선 도로</v>
+        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4267,13 +4267,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B66" t="str">
         <v>강남대로</v>
       </c>
       <c r="C66" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4315,13 +4315,13 @@
         <v>-</v>
       </c>
       <c r="Q66" t="str">
-        <v>서초동1318-4</v>
+        <v>강남역사거리</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
+        <v>강남역사거리(강남대로396)</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4329,13 +4329,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B67" t="str">
         <v>강남대로</v>
       </c>
       <c r="C67" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
@@ -4377,13 +4377,13 @@
         <v>-</v>
       </c>
       <c r="Q67" t="str">
-        <v>강남역사거리</v>
+        <v>서초동1319-5</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>강남역사거리(강남대로396)</v>
+        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4391,13 +4391,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B68" t="str">
         <v>강남대로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-서초구-03</v>
+        <v>26-서초구-04</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
@@ -4439,13 +4439,13 @@
         <v>-</v>
       </c>
       <c r="Q68" t="str">
-        <v>서초동1319-5</v>
+        <v>서초동1319-11</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
+        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4453,13 +4453,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B69" t="str">
         <v>강남대로</v>
       </c>
       <c r="C69" t="str">
-        <v>26-서초구-04</v>
+        <v>26-서초구-05</v>
       </c>
       <c r="D69" t="str">
         <v>양호</v>
@@ -4501,13 +4501,13 @@
         <v>-</v>
       </c>
       <c r="Q69" t="str">
-        <v>서초동1319-11</v>
+        <v>서초동1328-3</v>
       </c>
       <c r="R69" t="str">
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
+        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4515,13 +4515,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B70" t="str">
         <v>강남대로</v>
       </c>
       <c r="C70" t="str">
-        <v>26-서초구-05</v>
+        <v>26-서초구-06</v>
       </c>
       <c r="D70" t="str">
         <v>양호</v>
@@ -4560,16 +4560,16 @@
         <v>일반</v>
       </c>
       <c r="P70" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q70" t="str">
-        <v>서초동1328-3</v>
+        <v>서초동1328-11</v>
       </c>
       <c r="R70" t="str">
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
+        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4577,13 +4577,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B71" t="str">
         <v>강남대로</v>
       </c>
       <c r="C71" t="str">
-        <v>26-서초구-06</v>
+        <v>26-서초구-07</v>
       </c>
       <c r="D71" t="str">
         <v>양호</v>
@@ -4625,13 +4625,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q71" t="str">
-        <v>서초동1328-11</v>
+        <v>서초동1329</v>
       </c>
       <c r="R71" t="str">
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
+        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
       </c>
       <c r="T71" t="str">
         <v/>
@@ -4639,13 +4639,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B72" t="str">
         <v>강남대로</v>
       </c>
       <c r="C72" t="str">
-        <v>26-서초구-07</v>
+        <v>26-서초구-08</v>
       </c>
       <c r="D72" t="str">
         <v>양호</v>
@@ -4684,16 +4684,16 @@
         <v>일반</v>
       </c>
       <c r="P72" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q72" t="str">
-        <v>서초동1329</v>
+        <v>서초동1329-4</v>
       </c>
       <c r="R72" t="str">
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
+        <v>우남빌딩 앞 도로(강남대로349)</v>
       </c>
       <c r="T72" t="str">
         <v/>
@@ -4701,16 +4701,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B73" t="str">
         <v>강남대로</v>
       </c>
       <c r="C73" t="str">
-        <v>26-서초구-08</v>
+        <v>26-서초구-09</v>
       </c>
       <c r="D73" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E73" t="str">
         <v>거북등</v>
@@ -4725,7 +4725,7 @@
         <v>-</v>
       </c>
       <c r="I73" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J73" t="str">
         <v>3</v>
@@ -4740,22 +4740,22 @@
         <v>0</v>
       </c>
       <c r="N73" t="str">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O73" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P73" t="str">
-        <v>-</v>
+        <v>복구부 밑 빈공간있음(80cm)</v>
       </c>
       <c r="Q73" t="str">
-        <v>서초동1329-4</v>
+        <v>서초동1329-7</v>
       </c>
       <c r="R73" t="str">
         <v/>
       </c>
       <c r="S73" t="str">
-        <v>우남빌딩 앞 도로(강남대로349)</v>
+        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
       </c>
       <c r="T73" t="str">
         <v/>
@@ -4763,16 +4763,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B74" t="str">
         <v>강남대로</v>
       </c>
       <c r="C74" t="str">
-        <v>26-서초구-09</v>
+        <v>26-서초구-10</v>
       </c>
       <c r="D74" t="str">
-        <v>불량</v>
+        <v>양호</v>
       </c>
       <c r="E74" t="str">
         <v>거북등</v>
@@ -4787,7 +4787,7 @@
         <v>-</v>
       </c>
       <c r="I74" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J74" t="str">
         <v>3</v>
@@ -4802,22 +4802,22 @@
         <v>0</v>
       </c>
       <c r="N74" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O74" t="str">
-        <v>긴급</v>
+        <v>일반</v>
       </c>
       <c r="P74" t="str">
-        <v>복구부 밑 빈공간있음(80cm)</v>
+        <v>-</v>
       </c>
       <c r="Q74" t="str">
-        <v>서초동1329-7</v>
+        <v>서초동1329-8</v>
       </c>
       <c r="R74" t="str">
         <v/>
       </c>
       <c r="S74" t="str">
-        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
+        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
       </c>
       <c r="T74" t="str">
         <v/>
@@ -4825,13 +4825,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B75" t="str">
         <v>강남대로</v>
       </c>
       <c r="C75" t="str">
-        <v>26-서초구-10</v>
+        <v>26-서초구-11</v>
       </c>
       <c r="D75" t="str">
         <v>양호</v>
@@ -4870,16 +4870,16 @@
         <v>일반</v>
       </c>
       <c r="P75" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="Q75" t="str">
-        <v>서초동1329-8</v>
+        <v>우성아파트앞 사거리</v>
       </c>
       <c r="R75" t="str">
         <v/>
       </c>
       <c r="S75" t="str">
-        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
+        <v>교차로(강남대로346-2)</v>
       </c>
       <c r="T75" t="str">
         <v/>
@@ -4887,13 +4887,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B76" t="str">
         <v>강남대로</v>
       </c>
       <c r="C76" t="str">
-        <v>26-서초구-11</v>
+        <v>26-서초구-12</v>
       </c>
       <c r="D76" t="str">
         <v>양호</v>
@@ -4932,16 +4932,16 @@
         <v>일반</v>
       </c>
       <c r="P76" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q76" t="str">
-        <v>우성아파트앞 사거리</v>
+        <v>서초동1337-32</v>
       </c>
       <c r="R76" t="str">
         <v/>
       </c>
       <c r="S76" t="str">
-        <v>교차로(강남대로346-2)</v>
+        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
       </c>
       <c r="T76" t="str">
         <v/>
@@ -4949,13 +4949,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B77" t="str">
         <v>강남대로</v>
       </c>
       <c r="C77" t="str">
-        <v>26-서초구-12</v>
+        <v>26-서초구-13</v>
       </c>
       <c r="D77" t="str">
         <v>양호</v>
@@ -4994,16 +4994,16 @@
         <v>일반</v>
       </c>
       <c r="P77" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q77" t="str">
-        <v>서초동1337-32</v>
+        <v>서초동1337-31</v>
       </c>
       <c r="R77" t="str">
         <v/>
       </c>
       <c r="S77" t="str">
-        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
+        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
       </c>
       <c r="T77" t="str">
         <v/>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B78" t="str">
         <v>강남대로</v>
       </c>
       <c r="C78" t="str">
-        <v>26-서초구-13</v>
+        <v>26-서초구-14</v>
       </c>
       <c r="D78" t="str">
         <v>양호</v>
@@ -5059,13 +5059,13 @@
         <v>-</v>
       </c>
       <c r="Q78" t="str">
-        <v>서초동1337-31</v>
+        <v>서초동1337-20</v>
       </c>
       <c r="R78" t="str">
         <v/>
       </c>
       <c r="S78" t="str">
-        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
+        <v>대륭서초타워 앞 도로(강남대로327)</v>
       </c>
       <c r="T78" t="str">
         <v/>
@@ -5073,19 +5073,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B79" t="str">
         <v>강남대로</v>
       </c>
       <c r="C79" t="str">
-        <v>26-서초구-14</v>
+        <v>26-서초구-15</v>
       </c>
       <c r="D79" t="str">
         <v>양호</v>
       </c>
       <c r="E79" t="str">
-        <v>거북등</v>
+        <v>거북이</v>
       </c>
       <c r="F79" t="str">
         <v>양호</v>
@@ -5121,13 +5121,13 @@
         <v>-</v>
       </c>
       <c r="Q79" t="str">
-        <v>서초동1337-20</v>
+        <v>서초동1337-22</v>
       </c>
       <c r="R79" t="str">
         <v/>
       </c>
       <c r="S79" t="str">
-        <v>대륭서초타워 앞 도로(강남대로327)</v>
+        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
       </c>
       <c r="T79" t="str">
         <v/>
@@ -5135,19 +5135,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B80" t="str">
         <v>강남대로</v>
       </c>
       <c r="C80" t="str">
-        <v>26-서초구-15</v>
+        <v>26-서초구-16</v>
       </c>
       <c r="D80" t="str">
         <v>양호</v>
       </c>
       <c r="E80" t="str">
-        <v>거북이</v>
+        <v>거북등</v>
       </c>
       <c r="F80" t="str">
         <v>양호</v>
@@ -5183,13 +5183,13 @@
         <v>-</v>
       </c>
       <c r="Q80" t="str">
-        <v>서초동1337-22</v>
+        <v>서초동1338-23</v>
       </c>
       <c r="R80" t="str">
         <v/>
       </c>
       <c r="S80" t="str">
-        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
+        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
       </c>
       <c r="T80" t="str">
         <v/>
@@ -5197,13 +5197,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B81" t="str">
         <v>강남대로</v>
       </c>
       <c r="C81" t="str">
-        <v>26-서초구-16</v>
+        <v>26-서초구-17</v>
       </c>
       <c r="D81" t="str">
         <v>양호</v>
@@ -5245,13 +5245,13 @@
         <v>-</v>
       </c>
       <c r="Q81" t="str">
-        <v>서초동1338-23</v>
+        <v>서초동1338-12</v>
       </c>
       <c r="R81" t="str">
         <v/>
       </c>
       <c r="S81" t="str">
-        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
+        <v>코인노트 앞 도로(강남대로311)</v>
       </c>
       <c r="T81" t="str">
         <v/>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B82" t="str">
         <v>강남대로</v>
       </c>
       <c r="C82" t="str">
-        <v>26-서초구-17</v>
+        <v>26-서초구-18</v>
       </c>
       <c r="D82" t="str">
         <v>양호</v>
@@ -5307,13 +5307,13 @@
         <v>-</v>
       </c>
       <c r="Q82" t="str">
-        <v>서초동1338-12</v>
+        <v>서초동1338-21</v>
       </c>
       <c r="R82" t="str">
         <v/>
       </c>
       <c r="S82" t="str">
-        <v>코인노트 앞 도로(강남대로311)</v>
+        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
       </c>
       <c r="T82" t="str">
         <v/>
@@ -5321,13 +5321,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B83" t="str">
         <v>강남대로</v>
       </c>
       <c r="C83" t="str">
-        <v>26-서초구-18</v>
+        <v>26-서초구-19</v>
       </c>
       <c r="D83" t="str">
         <v>양호</v>
@@ -5369,13 +5369,13 @@
         <v>-</v>
       </c>
       <c r="Q83" t="str">
-        <v>서초동1338-21</v>
+        <v>서초동1338-20</v>
       </c>
       <c r="R83" t="str">
         <v/>
       </c>
       <c r="S83" t="str">
-        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
+        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
       </c>
       <c r="T83" t="str">
         <v/>
@@ -5383,13 +5383,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B84" t="str">
         <v>강남대로</v>
       </c>
       <c r="C84" t="str">
-        <v>26-서초구-19</v>
+        <v>26-서초구-20</v>
       </c>
       <c r="D84" t="str">
         <v>양호</v>
@@ -5431,13 +5431,13 @@
         <v>-</v>
       </c>
       <c r="Q84" t="str">
-        <v>서초동1338-20</v>
+        <v>서초동1339-9</v>
       </c>
       <c r="R84" t="str">
         <v/>
       </c>
       <c r="S84" t="str">
-        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
+        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
       </c>
       <c r="T84" t="str">
         <v/>
@@ -5445,13 +5445,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B85" t="str">
         <v>강남대로</v>
       </c>
       <c r="C85" t="str">
-        <v>26-서초구-20</v>
+        <v>26-서초구-21</v>
       </c>
       <c r="D85" t="str">
         <v>양호</v>
@@ -5493,13 +5493,13 @@
         <v>-</v>
       </c>
       <c r="Q85" t="str">
-        <v>서초동1339-9</v>
+        <v>서초동1340-6</v>
       </c>
       <c r="R85" t="str">
         <v/>
       </c>
       <c r="S85" t="str">
-        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
+        <v>남강빌딩 앞 도로(강남대로291)</v>
       </c>
       <c r="T85" t="str">
         <v/>
@@ -5507,13 +5507,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B86" t="str">
         <v>강남대로</v>
       </c>
       <c r="C86" t="str">
-        <v>26-서초구-21</v>
+        <v>26-서초구-22</v>
       </c>
       <c r="D86" t="str">
         <v>양호</v>
@@ -5555,13 +5555,13 @@
         <v>-</v>
       </c>
       <c r="Q86" t="str">
-        <v>서초동1340-6</v>
+        <v>서초동1357-10</v>
       </c>
       <c r="R86" t="str">
         <v/>
       </c>
       <c r="S86" t="str">
-        <v>남강빌딩 앞 도로(강남대로291)</v>
+        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
       </c>
       <c r="T86" t="str">
         <v/>
@@ -5569,19 +5569,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B87" t="str">
         <v>강남대로</v>
       </c>
       <c r="C87" t="str">
-        <v>26-서초구-22</v>
+        <v>26-서초구-23</v>
       </c>
       <c r="D87" t="str">
         <v>양호</v>
       </c>
       <c r="E87" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F87" t="str">
         <v>양호</v>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K87" t="str">
         <v>0</v>
@@ -5608,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="N87" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O87" t="str">
         <v>일반</v>
@@ -5617,13 +5617,13 @@
         <v>-</v>
       </c>
       <c r="Q87" t="str">
-        <v>서초동1357-10</v>
+        <v>서초동1357-66</v>
       </c>
       <c r="R87" t="str">
         <v/>
       </c>
       <c r="S87" t="str">
-        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
+        <v>메인타워 CU 앞 도로(강남대로275)</v>
       </c>
       <c r="T87" t="str">
         <v/>
@@ -5631,19 +5631,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B88" t="str">
         <v>강남대로</v>
       </c>
       <c r="C88" t="str">
-        <v>26-서초구-23</v>
+        <v>26-서초구-24</v>
       </c>
       <c r="D88" t="str">
         <v>양호</v>
       </c>
       <c r="E88" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F88" t="str">
         <v>양호</v>
@@ -5679,13 +5679,13 @@
         <v>-</v>
       </c>
       <c r="Q88" t="str">
-        <v>서초동1357-66</v>
+        <v>서초동1358-7</v>
       </c>
       <c r="R88" t="str">
         <v/>
       </c>
       <c r="S88" t="str">
-        <v>메인타워 CU 앞 도로(강남대로275)</v>
+        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
       </c>
       <c r="T88" t="str">
         <v/>
@@ -5693,19 +5693,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>26-24</v>
+        <v>26-25</v>
       </c>
       <c r="B89" t="str">
         <v>강남대로</v>
       </c>
       <c r="C89" t="str">
-        <v>26-서초구-24</v>
+        <v>26-서초구-25</v>
       </c>
       <c r="D89" t="str">
         <v>양호</v>
       </c>
       <c r="E89" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F89" t="str">
         <v>양호</v>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K89" t="str">
         <v>0</v>
@@ -5732,7 +5732,7 @@
         <v>0</v>
       </c>
       <c r="N89" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O89" t="str">
         <v>일반</v>
@@ -5741,13 +5741,13 @@
         <v>-</v>
       </c>
       <c r="Q89" t="str">
-        <v>서초동1358-7</v>
+        <v>양재역사거리</v>
       </c>
       <c r="R89" t="str">
         <v/>
       </c>
       <c r="S89" t="str">
-        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
+        <v>양재역 교차로(강남대로266-2)</v>
       </c>
       <c r="T89" t="str">
         <v/>
@@ -5755,13 +5755,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>26-25</v>
+        <v>26-26</v>
       </c>
       <c r="B90" t="str">
         <v>강남대로</v>
       </c>
       <c r="C90" t="str">
-        <v>26-서초구-25</v>
+        <v>26-서초구-26</v>
       </c>
       <c r="D90" t="str">
         <v>양호</v>
@@ -5803,13 +5803,13 @@
         <v>-</v>
       </c>
       <c r="Q90" t="str">
-        <v>양재역사거리</v>
+        <v>양재동23</v>
       </c>
       <c r="R90" t="str">
         <v/>
       </c>
       <c r="S90" t="str">
-        <v>양재역 교차로(강남대로266-2)</v>
+        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
       </c>
       <c r="T90" t="str">
         <v/>
@@ -5817,13 +5817,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>26-26</v>
+        <v>26-27</v>
       </c>
       <c r="B91" t="str">
         <v>강남대로</v>
       </c>
       <c r="C91" t="str">
-        <v>26-서초구-26</v>
+        <v>26-서초구-27</v>
       </c>
       <c r="D91" t="str">
         <v>양호</v>
@@ -5865,13 +5865,13 @@
         <v>-</v>
       </c>
       <c r="Q91" t="str">
-        <v>양재동23</v>
+        <v>양재동24</v>
       </c>
       <c r="R91" t="str">
         <v/>
       </c>
       <c r="S91" t="str">
-        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
+        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
       </c>
       <c r="T91" t="str">
         <v/>
@@ -5879,13 +5879,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>26-27</v>
+        <v>26-28</v>
       </c>
       <c r="B92" t="str">
         <v>강남대로</v>
       </c>
       <c r="C92" t="str">
-        <v>26-서초구-27</v>
+        <v>26-서초구-28</v>
       </c>
       <c r="D92" t="str">
         <v>양호</v>
@@ -5933,7 +5933,7 @@
         <v/>
       </c>
       <c r="S92" t="str">
-        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
+        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
       </c>
       <c r="T92" t="str">
         <v/>
@@ -5941,13 +5941,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>26-28</v>
+        <v>26-29</v>
       </c>
       <c r="B93" t="str">
         <v>강남대로</v>
       </c>
       <c r="C93" t="str">
-        <v>26-서초구-28</v>
+        <v>26-서초구-29</v>
       </c>
       <c r="D93" t="str">
         <v>양호</v>
@@ -5989,13 +5989,13 @@
         <v>-</v>
       </c>
       <c r="Q93" t="str">
-        <v>양재동24</v>
+        <v>양재동 산20-2</v>
       </c>
       <c r="R93" t="str">
         <v/>
       </c>
       <c r="S93" t="str">
-        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
+        <v>말죽거리공원 앞 도로(강남대로167)</v>
       </c>
       <c r="T93" t="str">
         <v/>
@@ -6003,19 +6003,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>26-29</v>
+        <v>26-30</v>
       </c>
       <c r="B94" t="str">
         <v>강남대로</v>
       </c>
       <c r="C94" t="str">
-        <v>26-서초구-29</v>
+        <v>26-서초구-30</v>
       </c>
       <c r="D94" t="str">
         <v>양호</v>
       </c>
       <c r="E94" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F94" t="str">
         <v>양호</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K94" t="str">
         <v>0</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="N94" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O94" t="str">
         <v>일반</v>
@@ -6051,13 +6051,13 @@
         <v>-</v>
       </c>
       <c r="Q94" t="str">
-        <v>양재동 산20-2</v>
+        <v>양재동67</v>
       </c>
       <c r="R94" t="str">
         <v/>
       </c>
       <c r="S94" t="str">
-        <v>말죽거리공원 앞 도로(강남대로167)</v>
+        <v>혜인빌딩 앞 도로(163)</v>
       </c>
       <c r="T94" t="str">
         <v/>
@@ -6065,19 +6065,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>26-30</v>
+        <v>26-31</v>
       </c>
       <c r="B95" t="str">
         <v>강남대로</v>
       </c>
       <c r="C95" t="str">
-        <v>26-서초구-30</v>
+        <v>26-서초구-31</v>
       </c>
       <c r="D95" t="str">
         <v>양호</v>
       </c>
       <c r="E95" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F95" t="str">
         <v>양호</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K95" t="str">
         <v>0</v>
@@ -6104,7 +6104,7 @@
         <v>0</v>
       </c>
       <c r="N95" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O95" t="str">
         <v>일반</v>
@@ -6113,13 +6113,13 @@
         <v>-</v>
       </c>
       <c r="Q95" t="str">
-        <v>양재동67</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R95" t="str">
         <v/>
       </c>
       <c r="S95" t="str">
-        <v>혜인빌딩 앞 도로(163)</v>
+        <v>말죽거리공원 교차로(양재동20-40)</v>
       </c>
       <c r="T95" t="str">
         <v/>
@@ -6127,19 +6127,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>26-31</v>
+        <v>26-32</v>
       </c>
       <c r="B96" t="str">
         <v>강남대로</v>
       </c>
       <c r="C96" t="str">
-        <v>26-서초구-31</v>
+        <v>26-서초구-32</v>
       </c>
       <c r="D96" t="str">
         <v>양호</v>
       </c>
       <c r="E96" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F96" t="str">
         <v>양호</v>
@@ -6154,7 +6154,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K96" t="str">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="N96" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O96" t="str">
         <v>일반</v>
@@ -6175,13 +6175,13 @@
         <v>-</v>
       </c>
       <c r="Q96" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동125</v>
       </c>
       <c r="R96" t="str">
         <v/>
       </c>
       <c r="S96" t="str">
-        <v>말죽거리공원 교차로(양재동20-40)</v>
+        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
       </c>
       <c r="T96" t="str">
         <v/>
@@ -6189,19 +6189,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>26-32</v>
+        <v>26-33</v>
       </c>
       <c r="B97" t="str">
         <v>강남대로</v>
       </c>
       <c r="C97" t="str">
-        <v>26-서초구-32</v>
+        <v>26-서초구-33</v>
       </c>
       <c r="D97" t="str">
         <v>양호</v>
       </c>
       <c r="E97" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F97" t="str">
         <v>양호</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K97" t="str">
         <v>0</v>
@@ -6228,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="N97" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O97" t="str">
         <v>일반</v>
@@ -6237,13 +6237,13 @@
         <v>-</v>
       </c>
       <c r="Q97" t="str">
-        <v>양재동125</v>
+        <v>양재동80-3</v>
       </c>
       <c r="R97" t="str">
         <v/>
       </c>
       <c r="S97" t="str">
-        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
+        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
       </c>
       <c r="T97" t="str">
         <v/>
@@ -6251,13 +6251,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>26-33</v>
+        <v>26-34</v>
       </c>
       <c r="B98" t="str">
         <v>강남대로</v>
       </c>
       <c r="C98" t="str">
-        <v>26-서초구-33</v>
+        <v>26-서초구-34</v>
       </c>
       <c r="D98" t="str">
         <v>양호</v>
@@ -6299,13 +6299,13 @@
         <v>-</v>
       </c>
       <c r="Q98" t="str">
-        <v>양재동80-3</v>
+        <v>매헌시민의숲사거리</v>
       </c>
       <c r="R98" t="str">
         <v/>
       </c>
       <c r="S98" t="str">
-        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
+        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
       </c>
       <c r="T98" t="str">
         <v/>
@@ -6313,13 +6313,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>26-34</v>
+        <v>26-35</v>
       </c>
       <c r="B99" t="str">
         <v>강남대로</v>
       </c>
       <c r="C99" t="str">
-        <v>26-서초구-34</v>
+        <v>26-서초구-35</v>
       </c>
       <c r="D99" t="str">
         <v>양호</v>
@@ -6361,13 +6361,13 @@
         <v>-</v>
       </c>
       <c r="Q99" t="str">
-        <v>매헌시민의숲사거리</v>
+        <v>양재동237</v>
       </c>
       <c r="R99" t="str">
         <v/>
       </c>
       <c r="S99" t="str">
-        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
+        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
       </c>
       <c r="T99" t="str">
         <v/>
@@ -6375,13 +6375,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>26-35</v>
+        <v>26-36</v>
       </c>
       <c r="B100" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C100" t="str">
-        <v>26-서초구-35</v>
+        <v>26-서초구-36</v>
       </c>
       <c r="D100" t="str">
         <v>양호</v>
@@ -6423,13 +6423,13 @@
         <v>-</v>
       </c>
       <c r="Q100" t="str">
-        <v>양재동237</v>
+        <v>양재동237-2</v>
       </c>
       <c r="R100" t="str">
         <v/>
       </c>
       <c r="S100" t="str">
-        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
+        <v>매헌역 공영주차장 입구 앞 도로</v>
       </c>
       <c r="T100" t="str">
         <v/>
@@ -6437,13 +6437,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>26-36</v>
+        <v>26-37</v>
       </c>
       <c r="B101" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C101" t="str">
-        <v>26-서초구-36</v>
+        <v>26-서초구-37</v>
       </c>
       <c r="D101" t="str">
         <v>양호</v>
@@ -6485,13 +6485,13 @@
         <v>-</v>
       </c>
       <c r="Q101" t="str">
-        <v>양재동237-2</v>
+        <v>신원동308-1</v>
       </c>
       <c r="R101" t="str">
         <v/>
       </c>
       <c r="S101" t="str">
-        <v>매헌역 공영주차장 입구 앞 도로</v>
+        <v>가로등(청계산로69)_양차선</v>
       </c>
       <c r="T101" t="str">
         <v/>
@@ -6499,13 +6499,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>26-37</v>
+        <v>26-38</v>
       </c>
       <c r="B102" t="str">
         <v>청계산로</v>
       </c>
       <c r="C102" t="str">
-        <v>26-서초구-37</v>
+        <v>26-서초구-38</v>
       </c>
       <c r="D102" t="str">
         <v>양호</v>
@@ -6547,13 +6547,13 @@
         <v>-</v>
       </c>
       <c r="Q102" t="str">
-        <v>신원동308-1</v>
+        <v>신원동298-16</v>
       </c>
       <c r="R102" t="str">
         <v/>
       </c>
       <c r="S102" t="str">
-        <v>가로등(청계산로69)_양차선</v>
+        <v>청계산 수변공원 앞 도로_양차선</v>
       </c>
       <c r="T102" t="str">
         <v/>
@@ -6561,13 +6561,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>26-38</v>
+        <v>26-39</v>
       </c>
       <c r="B103" t="str">
         <v>청계산로</v>
       </c>
       <c r="C103" t="str">
-        <v>26-서초구-38</v>
+        <v>26-서초구-39</v>
       </c>
       <c r="D103" t="str">
         <v>양호</v>
@@ -6615,7 +6615,7 @@
         <v/>
       </c>
       <c r="S103" t="str">
-        <v>청계산 수변공원 앞 도로_양차선</v>
+        <v>가로등(청계산로81)앞도로_양차선</v>
       </c>
       <c r="T103" t="str">
         <v/>
@@ -6623,13 +6623,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>26-39</v>
+        <v>26-40</v>
       </c>
       <c r="B104" t="str">
         <v>청계산로</v>
       </c>
       <c r="C104" t="str">
-        <v>26-서초구-39</v>
+        <v>26-서초구-40</v>
       </c>
       <c r="D104" t="str">
         <v>양호</v>
@@ -6668,16 +6668,16 @@
         <v>일반</v>
       </c>
       <c r="P104" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q104" t="str">
-        <v>신원동298-16</v>
+        <v>원지동595</v>
       </c>
       <c r="R104" t="str">
         <v/>
       </c>
       <c r="S104" t="str">
-        <v>가로등(청계산로81)앞도로_양차선</v>
+        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
       </c>
       <c r="T104" t="str">
         <v/>
@@ -6685,13 +6685,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>26-40</v>
+        <v>26-41</v>
       </c>
       <c r="B105" t="str">
         <v>청계산로</v>
       </c>
       <c r="C105" t="str">
-        <v>26-서초구-40</v>
+        <v>26-서초구-41</v>
       </c>
       <c r="D105" t="str">
         <v>양호</v>
@@ -6730,16 +6730,16 @@
         <v>일반</v>
       </c>
       <c r="P105" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q105" t="str">
-        <v>원지동595</v>
+        <v>신원동280-1</v>
       </c>
       <c r="R105" t="str">
         <v/>
       </c>
       <c r="S105" t="str">
-        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
+        <v>교차로(T)_양차선</v>
       </c>
       <c r="T105" t="str">
         <v/>
@@ -6747,13 +6747,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>26-41</v>
+        <v>26-42</v>
       </c>
       <c r="B106" t="str">
         <v>청계산로</v>
       </c>
       <c r="C106" t="str">
-        <v>26-서초구-41</v>
+        <v>26-서초구-42</v>
       </c>
       <c r="D106" t="str">
         <v>양호</v>
@@ -6795,21 +6795,765 @@
         <v>-</v>
       </c>
       <c r="Q106" t="str">
-        <v>신원동280-1</v>
+        <v>신원동278-6</v>
       </c>
       <c r="R106" t="str">
         <v/>
       </c>
       <c r="S106" t="str">
-        <v>교차로(T)_양차선</v>
+        <v>버스정류장 앞 양차선</v>
       </c>
       <c r="T106" t="str">
         <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>26-43</v>
+      </c>
+      <c r="B107" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C107" t="str">
+        <v>26-서초구-43</v>
+      </c>
+      <c r="D107" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E107" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F107" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G107" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H107" t="str">
+        <v>-</v>
+      </c>
+      <c r="I107" t="str">
+        <v>0</v>
+      </c>
+      <c r="J107" t="str">
+        <v>3</v>
+      </c>
+      <c r="K107" t="str">
+        <v>0</v>
+      </c>
+      <c r="L107" t="str">
+        <v>1</v>
+      </c>
+      <c r="M107" t="str">
+        <v>0</v>
+      </c>
+      <c r="N107" t="str">
+        <v>4</v>
+      </c>
+      <c r="O107" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P107" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q107" t="str">
+        <v>신원동604</v>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v>오라카이 호텔 맞음편 도로 우수,전기맨홀(청계산로9길1-7)</v>
+      </c>
+      <c r="T107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>26-44</v>
+      </c>
+      <c r="B108" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C108" t="str">
+        <v>26-서초구-44</v>
+      </c>
+      <c r="D108" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E108" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F108" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G108" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H108" t="str">
+        <v>-</v>
+      </c>
+      <c r="I108" t="str">
+        <v>0</v>
+      </c>
+      <c r="J108" t="str">
+        <v>3</v>
+      </c>
+      <c r="K108" t="str">
+        <v>0</v>
+      </c>
+      <c r="L108" t="str">
+        <v>1</v>
+      </c>
+      <c r="M108" t="str">
+        <v>0</v>
+      </c>
+      <c r="N108" t="str">
+        <v>4</v>
+      </c>
+      <c r="O108" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P108" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q108" t="str">
+        <v>신원동607</v>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v>내곡드림시티2 펀비어킹 앞 도로(청계산로189)</v>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>26-45</v>
+      </c>
+      <c r="B109" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C109" t="str">
+        <v>26-서초구-45</v>
+      </c>
+      <c r="D109" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E109" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F109" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G109" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H109" t="str">
+        <v>-</v>
+      </c>
+      <c r="I109" t="str">
+        <v>0</v>
+      </c>
+      <c r="J109" t="str">
+        <v>3</v>
+      </c>
+      <c r="K109" t="str">
+        <v>0</v>
+      </c>
+      <c r="L109" t="str">
+        <v>1</v>
+      </c>
+      <c r="M109" t="str">
+        <v>0</v>
+      </c>
+      <c r="N109" t="str">
+        <v>4</v>
+      </c>
+      <c r="O109" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P109" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q109" t="str">
+        <v>신원동609</v>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v>내곡프라임시티 앞도로(청계산로195)</v>
+      </c>
+      <c r="T109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>26-46</v>
+      </c>
+      <c r="B110" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C110" t="str">
+        <v>26-서초구-46</v>
+      </c>
+      <c r="D110" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E110" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F110" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G110" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H110" t="str">
+        <v>-</v>
+      </c>
+      <c r="I110" t="str">
+        <v>0</v>
+      </c>
+      <c r="J110" t="str">
+        <v>3</v>
+      </c>
+      <c r="K110" t="str">
+        <v>0</v>
+      </c>
+      <c r="L110" t="str">
+        <v>1</v>
+      </c>
+      <c r="M110" t="str">
+        <v>0</v>
+      </c>
+      <c r="N110" t="str">
+        <v>4</v>
+      </c>
+      <c r="O110" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P110" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q110" t="str">
+        <v>신원동611</v>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v>서초포레지움 투썸플레이스 앞 양차선(청계산로201)</v>
+      </c>
+      <c r="T110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>26-47</v>
+      </c>
+      <c r="B111" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C111" t="str">
+        <v>26-서초구-47</v>
+      </c>
+      <c r="D111" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E111" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F111" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G111" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H111" t="str">
+        <v>-</v>
+      </c>
+      <c r="I111" t="str">
+        <v>0</v>
+      </c>
+      <c r="J111" t="str">
+        <v>3</v>
+      </c>
+      <c r="K111" t="str">
+        <v>0</v>
+      </c>
+      <c r="L111" t="str">
+        <v>1</v>
+      </c>
+      <c r="M111" t="str">
+        <v>0</v>
+      </c>
+      <c r="N111" t="str">
+        <v>4</v>
+      </c>
+      <c r="O111" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P111" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q111" t="str">
+        <v>원지동362-1</v>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v>청계쉼터 앞 도로</v>
+      </c>
+      <c r="T111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>26-48</v>
+      </c>
+      <c r="B112" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C112" t="str">
+        <v>26-서초구-48</v>
+      </c>
+      <c r="D112" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E112" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F112" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G112" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H112" t="str">
+        <v>-</v>
+      </c>
+      <c r="I112" t="str">
+        <v>0</v>
+      </c>
+      <c r="J112" t="str">
+        <v>3</v>
+      </c>
+      <c r="K112" t="str">
+        <v>0</v>
+      </c>
+      <c r="L112" t="str">
+        <v>1</v>
+      </c>
+      <c r="M112" t="str">
+        <v>0</v>
+      </c>
+      <c r="N112" t="str">
+        <v>4</v>
+      </c>
+      <c r="O112" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P112" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q112" t="str">
+        <v>원지동384-1</v>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v>청계산커피 앞 양차선</v>
+      </c>
+      <c r="T112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>26-49</v>
+      </c>
+      <c r="B113" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C113" t="str">
+        <v>26-서초구-49</v>
+      </c>
+      <c r="D113" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E113" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F113" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G113" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H113" t="str">
+        <v>-</v>
+      </c>
+      <c r="I113" t="str">
+        <v>0</v>
+      </c>
+      <c r="J113" t="str">
+        <v>3</v>
+      </c>
+      <c r="K113" t="str">
+        <v>0</v>
+      </c>
+      <c r="L113" t="str">
+        <v>1</v>
+      </c>
+      <c r="M113" t="str">
+        <v>0</v>
+      </c>
+      <c r="N113" t="str">
+        <v>4</v>
+      </c>
+      <c r="O113" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P113" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q113" t="str">
+        <v>신원동192-75</v>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v>강경불고기_청계 앞 양차선(청계산로245)</v>
+      </c>
+      <c r="T113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>26-50</v>
+      </c>
+      <c r="B114" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C114" t="str">
+        <v>26-서초구-50</v>
+      </c>
+      <c r="D114" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E114" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F114" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G114" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H114" t="str">
+        <v>-</v>
+      </c>
+      <c r="I114" t="str">
+        <v>0</v>
+      </c>
+      <c r="J114" t="str">
+        <v>3</v>
+      </c>
+      <c r="K114" t="str">
+        <v>0</v>
+      </c>
+      <c r="L114" t="str">
+        <v>1</v>
+      </c>
+      <c r="M114" t="str">
+        <v>0</v>
+      </c>
+      <c r="N114" t="str">
+        <v>4</v>
+      </c>
+      <c r="O114" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P114" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q114" t="str">
+        <v>신원동173-1</v>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v>향린조경 앞 양차선(고속도로방면침하)</v>
+      </c>
+      <c r="T114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>26-51</v>
+      </c>
+      <c r="B115" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C115" t="str">
+        <v>26-서초구-51</v>
+      </c>
+      <c r="D115" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E115" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F115" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G115" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H115" t="str">
+        <v>-</v>
+      </c>
+      <c r="I115" t="str">
+        <v>0</v>
+      </c>
+      <c r="J115" t="str">
+        <v>3</v>
+      </c>
+      <c r="K115" t="str">
+        <v>0</v>
+      </c>
+      <c r="L115" t="str">
+        <v>1</v>
+      </c>
+      <c r="M115" t="str">
+        <v>0</v>
+      </c>
+      <c r="N115" t="str">
+        <v>4</v>
+      </c>
+      <c r="O115" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P115" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q115" t="str">
+        <v>신원동152-12</v>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v>삼석원 앞 양차선(고속도로방면 침하)</v>
+      </c>
+      <c r="T115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>26-52</v>
+      </c>
+      <c r="B116" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C116" t="str">
+        <v>26-서초구-52</v>
+      </c>
+      <c r="D116" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E116" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F116" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G116" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H116" t="str">
+        <v>-</v>
+      </c>
+      <c r="I116" t="str">
+        <v>0</v>
+      </c>
+      <c r="J116" t="str">
+        <v>3</v>
+      </c>
+      <c r="K116" t="str">
+        <v>0</v>
+      </c>
+      <c r="L116" t="str">
+        <v>1</v>
+      </c>
+      <c r="M116" t="str">
+        <v>0</v>
+      </c>
+      <c r="N116" t="str">
+        <v>4</v>
+      </c>
+      <c r="O116" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P116" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q116" t="str">
+        <v>신원동148-3</v>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+      <c r="S116" t="str">
+        <v>은평조경 앞 양차선(고속도로방면 침하)(청계산로283-8)</v>
+      </c>
+      <c r="T116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>26-53</v>
+      </c>
+      <c r="B117" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C117" t="str">
+        <v>26-서초구-53</v>
+      </c>
+      <c r="D117" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E117" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F117" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G117" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H117" t="str">
+        <v>-</v>
+      </c>
+      <c r="I117" t="str">
+        <v>0</v>
+      </c>
+      <c r="J117" t="str">
+        <v>3</v>
+      </c>
+      <c r="K117" t="str">
+        <v>0</v>
+      </c>
+      <c r="L117" t="str">
+        <v>1</v>
+      </c>
+      <c r="M117" t="str">
+        <v>0</v>
+      </c>
+      <c r="N117" t="str">
+        <v>4</v>
+      </c>
+      <c r="O117" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P117" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q117" t="str">
+        <v>원지동491-2</v>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+      <c r="S117" t="str">
+        <v>인화원 앞 양차선(고속도로방면 침하)(가로등_청계산로161)</v>
+      </c>
+      <c r="T117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>26-54</v>
+      </c>
+      <c r="B118" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C118" t="str">
+        <v>26-서초구-54</v>
+      </c>
+      <c r="D118" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E118" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F118" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G118" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H118" t="str">
+        <v>-</v>
+      </c>
+      <c r="I118" t="str">
+        <v>0</v>
+      </c>
+      <c r="J118" t="str">
+        <v>3</v>
+      </c>
+      <c r="K118" t="str">
+        <v>0</v>
+      </c>
+      <c r="L118" t="str">
+        <v>1</v>
+      </c>
+      <c r="M118" t="str">
+        <v>0</v>
+      </c>
+      <c r="N118" t="str">
+        <v>4</v>
+      </c>
+      <c r="O118" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P118" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q118" t="str">
+        <v>원지동493</v>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v>양재조경 앞 양차선(고속도로방면 침하)_(가로등_청계산로165)</v>
+      </c>
+      <c r="T118" t="str">
+        <v>현장확인필요</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T106"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T118"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-5</v>
+        <v>25-서초구-6</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -530,16 +530,16 @@
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>포장 복구개소</v>
       </c>
       <c r="Q5" t="str">
-        <v>서초동 1328-3</v>
+        <v>서초동 1328-10</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>우리은행 서초금융센터 앞 도로</v>
+        <v>강남역 #5번출구 앞 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-서초구-6</v>
+        <v>25-서초구-7</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -592,16 +592,16 @@
         <v>일반</v>
       </c>
       <c r="P6" t="str">
-        <v>포장 복구개소</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q6" t="str">
-        <v>서초동 1328-10</v>
+        <v>서초동 1328-11</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>강남역 #5번출구 앞 도로</v>
+        <v>도씨의 빛Ⅱ 앞 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="str">
         <v>강남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-서초구-7</v>
+        <v>25-서초구-8</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -654,16 +654,16 @@
         <v>일반</v>
       </c>
       <c r="P7" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q7" t="str">
-        <v>서초동 1328-11</v>
+        <v>서초동 1329</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>도씨의 빛Ⅱ 앞 도로</v>
+        <v>삼성화제 앞 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-서초구-8</v>
+        <v>25-서초구-9</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -716,16 +716,16 @@
         <v>일반</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q8" t="str">
-        <v>서초동 1329</v>
+        <v>서초동 1329-7</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>삼성화제 앞 도로</v>
+        <v>신한투자증권 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-서초구-9</v>
+        <v>25-서초구-10</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -781,13 +781,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q9" t="str">
-        <v>서초동 1329-7</v>
+        <v>서초동 1329-8</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>신한투자증권 앞 도로</v>
+        <v>모닝글로리 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-서초구-10</v>
+        <v>25-서초구-11</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -840,16 +840,16 @@
         <v>일반</v>
       </c>
       <c r="P10" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q10" t="str">
-        <v>서초동 1329-8</v>
+        <v>서초동 1329-10</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>모닝글로리 앞 도로</v>
+        <v>우성아파트 사거리 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-서초구-11</v>
+        <v>25-서초구-12</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -902,16 +902,16 @@
         <v>일반</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q11" t="str">
-        <v>서초동 1329-10</v>
+        <v>서초동 1337-32</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>우성아파트 사거리 도로</v>
+        <v>한국투자증권 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-서초구-12</v>
+        <v>25-서초구-13</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -964,16 +964,16 @@
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q12" t="str">
-        <v>서초동 1337-32</v>
+        <v>서초동 1337-22</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>한국투자증권 앞 도로</v>
+        <v>디오빌프라임 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-서초구-13</v>
+        <v>25-서초구-14</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1029,13 +1029,13 @@
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v>서초동 1337-22</v>
+        <v>서초동 1338-23</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>디오빌프라임 앞 도로</v>
+        <v>투썸플레이스 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-서초구-14</v>
+        <v>25-서초구-15</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1091,13 +1091,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>서초동 1338-23</v>
+        <v>서초동 1338-20</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>투썸플레이스 도로</v>
+        <v>현대렉시온 앞 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-서초구-15</v>
+        <v>25-서초구-16</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1120,7 +1120,7 @@
         <v>거북등</v>
       </c>
       <c r="F15" t="str">
-        <v>양호</v>
+        <v>건조</v>
       </c>
       <c r="G15" t="str">
         <v>13.5</v>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>서초동 1338-20</v>
+        <v>서초동 1339-9</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>현대렉시온 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-서초구-16</v>
+        <v>25-서초구-17</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1215,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>서초동 1339-9</v>
+        <v>서초동 1340-6</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>KIA 서초지점 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1274,7 +1274,7 @@
         <v>일반</v>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q17" t="str">
         <v>서초동 1340-6</v>
@@ -1283,7 +1283,7 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>KIA 서초지점 앞 도로</v>
+        <v>남강매점 앞 횡단보도</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-서초구-18</v>
+        <v>25-서초구-19</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1336,16 +1336,16 @@
         <v>일반</v>
       </c>
       <c r="P18" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q18" t="str">
-        <v>서초동 1340-6</v>
+        <v>서초동 1357-33</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>남강매점 앞 횡단보도</v>
+        <v>한국디지털 평생교육원 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-서초구-19</v>
+        <v>25-서초구-20</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1398,16 +1398,16 @@
         <v>일반</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q19" t="str">
-        <v>서초동 1357-33</v>
+        <v>서초동 1357-35</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>한국디지털 평생교육원 앞 도로</v>
+        <v>부산은행 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-서초구-20</v>
+        <v>25-서초구-21</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1463,13 +1463,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q20" t="str">
-        <v>서초동 1357-35</v>
+        <v>서초동 1358-6</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>부산은행 앞 도로</v>
+        <v>송남빌딩 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,19 +1477,19 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-서초구-21</v>
+        <v>25-서초구-22</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
       </c>
       <c r="E21" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F21" t="str">
         <v>건조</v>
@@ -1504,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1516,22 +1516,22 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O21" t="str">
         <v>일반</v>
       </c>
       <c r="P21" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q21" t="str">
-        <v>서초동 1358-6</v>
+        <v>서초동 1361-1</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>송남빌딩 앞 도로</v>
+        <v>보들설곰탕 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,13 +1539,13 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="str">
         <v>강남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-서초구-22</v>
+        <v>25-서초구-23</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
@@ -1587,13 +1587,13 @@
         <v/>
       </c>
       <c r="Q22" t="str">
-        <v>서초동 1361-1</v>
+        <v>서초동 1361-5</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>보들설곰탕 앞 도로</v>
+        <v>새움빌딩 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="str">
         <v>강남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-서초구-23</v>
+        <v>25-서초구-24</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
       </c>
       <c r="E23" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F23" t="str">
         <v>건조</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O23" t="str">
         <v>일반</v>
@@ -1649,13 +1649,13 @@
         <v/>
       </c>
       <c r="Q23" t="str">
-        <v>서초동 1361-5</v>
+        <v>서초동 1361-10</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>새움빌딩 앞 도로</v>
+        <v>호텔 페이토 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,13 +1663,13 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24" t="str">
         <v>강남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-서초구-24</v>
+        <v>25-서초구-25</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
@@ -1708,16 +1708,16 @@
         <v>일반</v>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q24" t="str">
-        <v>서초동 1361-10</v>
+        <v>서초동 1362</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>호텔 페이토 앞 도로</v>
+        <v>e마트24 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" t="str">
         <v>강남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-서초구-25</v>
+        <v>25-서초구-26</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
@@ -1770,16 +1770,16 @@
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q25" t="str">
-        <v>서초동 1362</v>
+        <v>서초동 1362-26</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>e마트24 앞 도로</v>
+        <v>힐든가든인 서울강남 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" t="str">
         <v>강남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-서초구-26</v>
+        <v>25-서초구-27</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1832,16 +1832,16 @@
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q26" t="str">
-        <v>서초동 1362-26</v>
+        <v>서초동 1362-27</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>힐든가든인 서울강남 앞 도로</v>
+        <v>니드오피스텔 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" t="str">
         <v>강남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-서초구-27</v>
+        <v>25-서초구-28</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1894,16 +1894,16 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q27" t="str">
-        <v>서초동 1362-27</v>
+        <v>서초동 1366-7</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>니드오피스텔 앞 도로</v>
+        <v>깐부치킨 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" t="str">
         <v>강남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-서초구-28</v>
+        <v>25-서초구-29</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q28" t="str">
-        <v>서초동 1366-7</v>
+        <v>서초동 1366-9</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>깐부치킨 앞 도로</v>
+        <v>양재역 교차로 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" t="str">
         <v>강남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-서초구-29</v>
+        <v>25-서초구-30</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2018,16 +2018,16 @@
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q29" t="str">
-        <v>서초동 1366-9</v>
+        <v>양재동 23</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>양재역 교차로 도로</v>
+        <v>바나프레소 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="str">
         <v>강남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-서초구-30</v>
+        <v>25-서초구-31</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2083,13 +2083,13 @@
         <v/>
       </c>
       <c r="Q30" t="str">
-        <v>양재동 23</v>
+        <v>양재동 25</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>바나프레소 앞 도로</v>
+        <v>서초문화 예술회관 앞 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" t="str">
         <v>강남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-서초구-31</v>
+        <v>25-서초구-32</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
@@ -2145,13 +2145,13 @@
         <v/>
       </c>
       <c r="Q31" t="str">
-        <v>양재동 25</v>
+        <v>양재동 14-4</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>서초문화 예술회관 앞 도로</v>
+        <v>모산빌딩 앞 횡단보도</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,19 +2159,19 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-서초구-32</v>
+        <v>25-서초구-33</v>
       </c>
       <c r="D32" t="str">
-        <v>양호</v>
+        <v>50</v>
       </c>
       <c r="E32" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F32" t="str">
         <v>건조</v>
@@ -2182,11 +2182,11 @@
       <c r="H32" t="str">
         <v>-</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="b">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O32" t="str">
         <v>일반</v>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>보도침하5cm</v>
       </c>
       <c r="Q32" t="str">
-        <v>양재동 14-4</v>
+        <v>양재동 67-7</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>모산빌딩 앞 횡단보도</v>
+        <v>바나프레스 앞 보도</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-서초구-33</v>
+        <v>25-서초구-34</v>
       </c>
       <c r="D33" t="str">
-        <v>50</v>
+        <v>양호</v>
       </c>
       <c r="E33" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F33" t="str">
         <v>건조</v>
@@ -2244,11 +2244,11 @@
       <c r="H33" t="str">
         <v>-</v>
       </c>
-      <c r="I33" t="b">
+      <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2260,22 +2260,22 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O33" t="str">
         <v>일반</v>
       </c>
       <c r="P33" t="str">
-        <v>보도침하5cm</v>
+        <v/>
       </c>
       <c r="Q33" t="str">
-        <v>양재동 67-7</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>바나프레스 앞 보도</v>
+        <v>교육개발원 사거리 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,19 +2283,19 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-서초구-34</v>
+        <v>25-서초구-35</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
       </c>
       <c r="E34" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F34" t="str">
         <v>건조</v>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O34" t="str">
         <v>일반</v>
@@ -2331,13 +2331,13 @@
         <v/>
       </c>
       <c r="Q34" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동 109</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>교육개발원 사거리 도로</v>
+        <v>카페 릴리블랑 앞 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,19 +2345,19 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35" t="str">
         <v>강남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-서초구-35</v>
+        <v>25-서초구-36</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
       </c>
       <c r="E35" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F35" t="str">
         <v>건조</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O35" t="str">
         <v>일반</v>
@@ -2393,13 +2393,13 @@
         <v/>
       </c>
       <c r="Q35" t="str">
-        <v>양재동 109</v>
+        <v>양재동 125</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>카페 릴리블랑 앞 도로</v>
+        <v>넥스팜 코리아 앞 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,13 +2407,13 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" t="str">
         <v>강남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-서초구-36</v>
+        <v>25-서초구-37</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2455,13 +2455,13 @@
         <v/>
       </c>
       <c r="Q36" t="str">
-        <v>양재동 125</v>
+        <v>양재동 80-3</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>넥스팜 코리아 앞 도로</v>
+        <v>도야짬뽕 앞 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-서초구-37</v>
+        <v>25-서초구-38</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>양재동 80-3</v>
+        <v>양재동 237-1</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>도야짬뽕 앞 도로</v>
+        <v>공영주차장 앞 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-서초구-38</v>
+        <v>25-서초구-39</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>양재동 237-1</v>
+        <v>신원동 308-1</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>공영주차장 앞 도로</v>
+        <v>가로등(청계산로145) 양차선 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" t="str">
         <v>청계산로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-서초구-39</v>
+        <v>25-서초구-40</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2641,13 +2641,13 @@
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>신원동 308-1</v>
+        <v>원지동 294-3</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>가로등(청계산로145) 양차선 도로</v>
+        <v>전봇대(원지간37H1) 양차선 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" t="str">
         <v>청계산로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-서초구-40</v>
+        <v>25-서초구-41</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2700,16 +2700,16 @@
         <v>일반</v>
       </c>
       <c r="P40" t="str">
-        <v/>
+        <v>거북등 맨홀침하4cm</v>
       </c>
       <c r="Q40" t="str">
-        <v>원지동 294-3</v>
+        <v>원지동 594-1</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>전봇대(원지간37H1) 양차선 도로</v>
+        <v>도로교통표지판 앞 상수도맨홀 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" t="str">
         <v>청계산로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-서초구-41</v>
+        <v>25-서초구-42</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2762,16 +2762,16 @@
         <v>일반</v>
       </c>
       <c r="P41" t="str">
-        <v>거북등 맨홀침하4cm</v>
+        <v/>
       </c>
       <c r="Q41" t="str">
-        <v>원지동 594-1</v>
+        <v>신원동 280</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>도로교통표지판 앞 상수도맨홀 도로</v>
+        <v>공영주차장 앞 T 교차로 양차선 도로</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,13 +2779,13 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" t="str">
         <v>청계산로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-서초구-42</v>
+        <v>25-서초구-43</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
@@ -2827,13 +2827,13 @@
         <v/>
       </c>
       <c r="Q42" t="str">
-        <v>신원동 280</v>
+        <v>신원동 278-6</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>공영주차장 앞 T 교차로 양차선 도로</v>
+        <v>공영주차장 앞 양차선 도로</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" t="str">
         <v>청계산로</v>
       </c>
       <c r="C43" t="str">
-        <v>25-서초구-43</v>
+        <v>25-서초구-44</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
@@ -2886,16 +2886,16 @@
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q43" t="str">
-        <v>신원동 278-6</v>
+        <v>신원동 611</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>공영주차장 앞 양차선 도로</v>
+        <v>투썸플레이스 앞 보도</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,19 +2903,19 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" t="str">
         <v>청계산로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-서초구-44</v>
+        <v>25-서초구-45</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
       <c r="E44" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F44" t="str">
         <v>건조</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -2942,22 +2942,22 @@
         <v>0</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O44" t="str">
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v>보도침하4cm</v>
+        <v/>
       </c>
       <c r="Q44" t="str">
-        <v>신원동 611</v>
+        <v>신원동 612</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>투썸플레이스 앞 보도</v>
+        <v>LAB 앞 도로</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,19 +2965,19 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" t="str">
         <v>청계산로</v>
       </c>
       <c r="C45" t="str">
-        <v>25-서초구-45</v>
+        <v>25-서초구-46</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F45" t="str">
         <v>건조</v>
@@ -2992,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3004,22 +3004,22 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O45" t="str">
         <v>일반</v>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q45" t="str">
-        <v>신원동 612</v>
+        <v>신원동 660</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>LAB 앞 도로</v>
+        <v>심플리시티 앞 보도</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,13 +3027,13 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B46" t="str">
         <v>청계산로</v>
       </c>
       <c r="C46" t="str">
-        <v>25-서초구-46</v>
+        <v>25-서초구-47</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
@@ -3072,16 +3072,16 @@
         <v>일반</v>
       </c>
       <c r="P46" t="str">
-        <v>보도침하4cm</v>
+        <v>보도침하3cm</v>
       </c>
       <c r="Q46" t="str">
-        <v>신원동 660</v>
+        <v>신원동 197-1</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>심플리시티 앞 보도</v>
+        <v>부안애서 맞음편 보도</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,13 +3089,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" t="str">
         <v>청계산로</v>
       </c>
       <c r="C47" t="str">
-        <v>25-서초구-47</v>
+        <v>25-서초구-48</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
@@ -3134,16 +3134,16 @@
         <v>일반</v>
       </c>
       <c r="P47" t="str">
-        <v>보도침하3cm</v>
+        <v/>
       </c>
       <c r="Q47" t="str">
-        <v>신원동 197-1</v>
+        <v>원지동 384-1</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>부안애서 맞음편 보도</v>
+        <v>커피플라워 앞 양차선 도로</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,13 +3151,13 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48" t="str">
         <v>청계산로</v>
       </c>
       <c r="C48" t="str">
-        <v>25-서초구-48</v>
+        <v>25-서초구-49</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
@@ -3199,13 +3199,13 @@
         <v/>
       </c>
       <c r="Q48" t="str">
-        <v>원지동 384-1</v>
+        <v>신원동 192-73</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>커피플라워 앞 양차선 도로</v>
+        <v>봉평막국수 앞 양차선 도로</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,13 +3213,13 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49" t="str">
         <v>청계산로</v>
       </c>
       <c r="C49" t="str">
-        <v>25-서초구-49</v>
+        <v>25-서초구-50</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3261,13 +3261,13 @@
         <v/>
       </c>
       <c r="Q49" t="str">
-        <v>신원동 192-73</v>
+        <v>신원동 172-1</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>봉평막국수 앞 양차선 도로</v>
+        <v>향린조경 앞 양차선 도로</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,13 +3275,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B50" t="str">
         <v>청계산로</v>
       </c>
       <c r="C50" t="str">
-        <v>25-서초구-50</v>
+        <v>25-서초구-51</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3323,13 +3323,13 @@
         <v/>
       </c>
       <c r="Q50" t="str">
-        <v>신원동 172-1</v>
+        <v>신원동 153</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>향린조경 앞 양차선 도로</v>
+        <v>삼석원 앞 양차선 도로</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51" t="str">
         <v>청계산로</v>
       </c>
       <c r="C51" t="str">
-        <v>25-서초구-51</v>
+        <v>25-서초구-52</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3385,13 +3385,13 @@
         <v/>
       </c>
       <c r="Q51" t="str">
-        <v>신원동 153</v>
+        <v>신원동 150-1</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>삼석원 앞 양차선 도로</v>
+        <v>성심조경 앞 양차선 도로</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52" t="str">
         <v>청계산로</v>
       </c>
       <c r="C52" t="str">
-        <v>25-서초구-52</v>
+        <v>25-서초구-53</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3444,16 +3444,16 @@
         <v>일반</v>
       </c>
       <c r="P52" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q52" t="str">
-        <v>신원동 150-1</v>
+        <v>원지동 470-1</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>성심조경 앞 양차선 도로</v>
+        <v>가로등(청계산로154) 앞 보도</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53" t="str">
         <v>청계산로</v>
       </c>
       <c r="C53" t="str">
-        <v>25-서초구-53</v>
+        <v>25-서초구-54</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3506,16 +3506,16 @@
         <v>일반</v>
       </c>
       <c r="P53" t="str">
-        <v>5cm이하 침하</v>
+        <v>보도침하</v>
       </c>
       <c r="Q53" t="str">
-        <v>원지동 470-1</v>
+        <v>원지동 491-6</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>가로등(청계산로154) 앞 보도</v>
+        <v>가로등(청계산로156) 맞음편 보도</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3523,13 +3523,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54" t="str">
         <v>청계산로</v>
       </c>
       <c r="C54" t="str">
-        <v>25-서초구-54</v>
+        <v>25-서초구-55</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3568,16 +3568,16 @@
         <v>일반</v>
       </c>
       <c r="P54" t="str">
-        <v>보도침하</v>
+        <v/>
       </c>
       <c r="Q54" t="str">
-        <v>원지동 491-6</v>
+        <v>원지동 493</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>가로등(청계산로156) 맞음편 보도</v>
+        <v>양재조경 앞 양차선 도로</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B55" t="str">
         <v>청계산로</v>
       </c>
       <c r="C55" t="str">
-        <v>25-서초구-55</v>
+        <v>25-서초구-56</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3633,13 +3633,13 @@
         <v/>
       </c>
       <c r="Q55" t="str">
-        <v>원지동 493</v>
+        <v>원지동 497-3</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>양재조경 앞 양차선 도로</v>
+        <v>가로등(청계산로168) 앞 양차선 도로</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3647,13 +3647,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B56" t="str">
         <v>청계산로</v>
       </c>
       <c r="C56" t="str">
-        <v>25-서초구-56</v>
+        <v>25-서초구-57</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3695,13 +3695,13 @@
         <v/>
       </c>
       <c r="Q56" t="str">
-        <v>원지동 497-3</v>
+        <v>신원동 산 60-2</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>가로등(청계산로168) 앞 양차선 도로</v>
+        <v>대원조경 앞 양차선 도로</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3709,13 +3709,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B57" t="str">
         <v>청계산로</v>
       </c>
       <c r="C57" t="str">
-        <v>25-서초구-57</v>
+        <v>25-서초구-58</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="Q57" t="str">
-        <v>신원동 산 60-2</v>
+        <v>신원동 105-4</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>대원조경 앞 양차선 도로</v>
+        <v>둥지조경 제2농장 앞 양차선 도로</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3771,13 +3771,13 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58" t="str">
         <v>청계산로</v>
       </c>
       <c r="C58" t="str">
-        <v>25-서초구-58</v>
+        <v>25-서초구-59</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3819,13 +3819,13 @@
         <v/>
       </c>
       <c r="Q58" t="str">
-        <v>신원동 105-4</v>
+        <v>신원동 105-33</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>둥지조경 제2농장 앞 양차선 도로</v>
+        <v>한백자생식물원 앞 양차선 도로</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3833,13 +3833,13 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B59" t="str">
         <v>청계산로</v>
       </c>
       <c r="C59" t="str">
-        <v>25-서초구-59</v>
+        <v>25-서초구-60</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3878,16 +3878,16 @@
         <v>일반</v>
       </c>
       <c r="P59" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q59" t="str">
-        <v>신원동 105-33</v>
+        <v>신원동 105-19</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>한백자생식물원 앞 양차선 도로</v>
+        <v>가로등(청계산로190) 앞 양차선 도로</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3895,19 +3895,19 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60" t="str">
         <v>청계산로</v>
       </c>
       <c r="C60" t="str">
-        <v>25-서초구-60</v>
+        <v>25-서초구-61</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
       </c>
       <c r="E60" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F60" t="str">
         <v>건조</v>
@@ -3922,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -3934,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="N60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O60" t="str">
         <v>일반</v>
@@ -3943,13 +3943,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q60" t="str">
-        <v>신원동 105-19</v>
+        <v>신원동 44-1</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>가로등(청계산로190) 앞 양차선 도로</v>
+        <v>새정이마을 입구 교차로</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3957,19 +3957,19 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61" t="str">
         <v>청계산로</v>
       </c>
       <c r="C61" t="str">
-        <v>25-서초구-61</v>
+        <v>25-서초구-62</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
       </c>
       <c r="E61" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F61" t="str">
         <v>건조</v>
@@ -4002,16 +4002,16 @@
         <v>일반</v>
       </c>
       <c r="P61" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q61" t="str">
-        <v>신원동 44-1</v>
+        <v>신원동 44-5</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>새정이마을 입구 교차로</v>
+        <v>은하조경 앞 양차선 도로</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4019,13 +4019,13 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62" t="str">
         <v>청계산로</v>
       </c>
       <c r="C62" t="str">
-        <v>25-서초구-62</v>
+        <v>25-서초구-63</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
@@ -4067,13 +4067,13 @@
         <v/>
       </c>
       <c r="Q62" t="str">
-        <v>신원동 44-5</v>
+        <v>신원동 57</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>은하조경 앞 양차선 도로</v>
+        <v>서림원예종묘 앞 양차선 도로</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4081,19 +4081,19 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63" t="str">
         <v>청계산로</v>
       </c>
       <c r="C63" t="str">
-        <v>25-서초구-63</v>
+        <v>25-서초구-64</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
       </c>
       <c r="E63" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F63" t="str">
         <v>건조</v>
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O63" t="str">
         <v>일반</v>
@@ -4129,27 +4129,27 @@
         <v/>
       </c>
       <c r="Q63" t="str">
-        <v>신원동 57</v>
+        <v>신원동 64-1</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>서림원예종묘 앞 양차선 도로</v>
+        <v>옥천조경 앞 양차선 도로</v>
       </c>
       <c r="T63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64">
-        <v>64</v>
+      <c r="A64" t="str">
+        <v>26-01</v>
       </c>
       <c r="B64" t="str">
-        <v>청계산로</v>
+        <v>강남대로</v>
       </c>
       <c r="C64" t="str">
-        <v>25-서초구-64</v>
+        <v>26-서초구-01</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
@@ -4158,46 +4158,46 @@
         <v>거북등</v>
       </c>
       <c r="F64" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G64" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H64" t="str">
         <v>-</v>
       </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>3</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>1</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
+      <c r="I64" t="str">
+        <v>0</v>
+      </c>
+      <c r="J64" t="str">
+        <v>3</v>
+      </c>
+      <c r="K64" t="str">
+        <v>0</v>
+      </c>
+      <c r="L64" t="str">
+        <v>1</v>
+      </c>
+      <c r="M64" t="str">
+        <v>0</v>
+      </c>
+      <c r="N64" t="str">
         <v>4</v>
       </c>
       <c r="O64" t="str">
         <v>일반</v>
       </c>
       <c r="P64" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q64" t="str">
-        <v>신원동 64-1</v>
+        <v>서초동1318-4</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>옥천조경 앞 양차선 도로</v>
+        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4205,13 +4205,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B65" t="str">
         <v>강남대로</v>
       </c>
       <c r="C65" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
@@ -4253,13 +4253,13 @@
         <v>-</v>
       </c>
       <c r="Q65" t="str">
-        <v>서초동1318-4</v>
+        <v>강남역사거리</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
+        <v>강남역사거리(강남대로396)</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4267,13 +4267,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B66" t="str">
         <v>강남대로</v>
       </c>
       <c r="C66" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4315,13 +4315,13 @@
         <v>-</v>
       </c>
       <c r="Q66" t="str">
-        <v>강남역사거리</v>
+        <v>서초동1319-5</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>강남역사거리(강남대로396)</v>
+        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4329,13 +4329,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B67" t="str">
         <v>강남대로</v>
       </c>
       <c r="C67" t="str">
-        <v>26-서초구-03</v>
+        <v>26-서초구-04</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
@@ -4377,13 +4377,13 @@
         <v>-</v>
       </c>
       <c r="Q67" t="str">
-        <v>서초동1319-5</v>
+        <v>서초동1319-11</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
+        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4391,13 +4391,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B68" t="str">
         <v>강남대로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-서초구-04</v>
+        <v>26-서초구-05</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
@@ -4439,13 +4439,13 @@
         <v>-</v>
       </c>
       <c r="Q68" t="str">
-        <v>서초동1319-11</v>
+        <v>서초동1328-3</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
+        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4453,13 +4453,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B69" t="str">
         <v>강남대로</v>
       </c>
       <c r="C69" t="str">
-        <v>26-서초구-05</v>
+        <v>26-서초구-06</v>
       </c>
       <c r="D69" t="str">
         <v>양호</v>
@@ -4498,16 +4498,16 @@
         <v>일반</v>
       </c>
       <c r="P69" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q69" t="str">
-        <v>서초동1328-3</v>
+        <v>서초동1328-11</v>
       </c>
       <c r="R69" t="str">
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
+        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4515,13 +4515,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B70" t="str">
         <v>강남대로</v>
       </c>
       <c r="C70" t="str">
-        <v>26-서초구-06</v>
+        <v>26-서초구-07</v>
       </c>
       <c r="D70" t="str">
         <v>양호</v>
@@ -4563,13 +4563,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q70" t="str">
-        <v>서초동1328-11</v>
+        <v>서초동1329</v>
       </c>
       <c r="R70" t="str">
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
+        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4577,13 +4577,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B71" t="str">
         <v>강남대로</v>
       </c>
       <c r="C71" t="str">
-        <v>26-서초구-07</v>
+        <v>26-서초구-08</v>
       </c>
       <c r="D71" t="str">
         <v>양호</v>
@@ -4622,16 +4622,16 @@
         <v>일반</v>
       </c>
       <c r="P71" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q71" t="str">
-        <v>서초동1329</v>
+        <v>서초동1329-4</v>
       </c>
       <c r="R71" t="str">
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
+        <v>우남빌딩 앞 도로(강남대로349)</v>
       </c>
       <c r="T71" t="str">
         <v/>
@@ -4639,16 +4639,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B72" t="str">
         <v>강남대로</v>
       </c>
       <c r="C72" t="str">
-        <v>26-서초구-08</v>
+        <v>26-서초구-09</v>
       </c>
       <c r="D72" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E72" t="str">
         <v>거북등</v>
@@ -4663,7 +4663,7 @@
         <v>-</v>
       </c>
       <c r="I72" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J72" t="str">
         <v>3</v>
@@ -4678,22 +4678,22 @@
         <v>0</v>
       </c>
       <c r="N72" t="str">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O72" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P72" t="str">
-        <v>-</v>
+        <v>복구부 밑 빈공간있음(80cm)</v>
       </c>
       <c r="Q72" t="str">
-        <v>서초동1329-4</v>
+        <v>서초동1329-7</v>
       </c>
       <c r="R72" t="str">
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>우남빌딩 앞 도로(강남대로349)</v>
+        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
       </c>
       <c r="T72" t="str">
         <v/>
@@ -4701,16 +4701,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B73" t="str">
         <v>강남대로</v>
       </c>
       <c r="C73" t="str">
-        <v>26-서초구-09</v>
+        <v>26-서초구-10</v>
       </c>
       <c r="D73" t="str">
-        <v>불량</v>
+        <v>양호</v>
       </c>
       <c r="E73" t="str">
         <v>거북등</v>
@@ -4725,7 +4725,7 @@
         <v>-</v>
       </c>
       <c r="I73" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J73" t="str">
         <v>3</v>
@@ -4740,22 +4740,22 @@
         <v>0</v>
       </c>
       <c r="N73" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O73" t="str">
-        <v>긴급</v>
+        <v>일반</v>
       </c>
       <c r="P73" t="str">
-        <v>복구부 밑 빈공간있음(80cm)</v>
+        <v>-</v>
       </c>
       <c r="Q73" t="str">
-        <v>서초동1329-7</v>
+        <v>서초동1329-8</v>
       </c>
       <c r="R73" t="str">
         <v/>
       </c>
       <c r="S73" t="str">
-        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
+        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
       </c>
       <c r="T73" t="str">
         <v/>
@@ -4763,13 +4763,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B74" t="str">
         <v>강남대로</v>
       </c>
       <c r="C74" t="str">
-        <v>26-서초구-10</v>
+        <v>26-서초구-11</v>
       </c>
       <c r="D74" t="str">
         <v>양호</v>
@@ -4808,16 +4808,16 @@
         <v>일반</v>
       </c>
       <c r="P74" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="Q74" t="str">
-        <v>서초동1329-8</v>
+        <v>우성아파트앞 사거리</v>
       </c>
       <c r="R74" t="str">
         <v/>
       </c>
       <c r="S74" t="str">
-        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
+        <v>교차로(강남대로346-2)</v>
       </c>
       <c r="T74" t="str">
         <v/>
@@ -4825,13 +4825,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B75" t="str">
         <v>강남대로</v>
       </c>
       <c r="C75" t="str">
-        <v>26-서초구-11</v>
+        <v>26-서초구-12</v>
       </c>
       <c r="D75" t="str">
         <v>양호</v>
@@ -4870,16 +4870,16 @@
         <v>일반</v>
       </c>
       <c r="P75" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q75" t="str">
-        <v>우성아파트앞 사거리</v>
+        <v>서초동1337-32</v>
       </c>
       <c r="R75" t="str">
         <v/>
       </c>
       <c r="S75" t="str">
-        <v>교차로(강남대로346-2)</v>
+        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
       </c>
       <c r="T75" t="str">
         <v/>
@@ -4887,13 +4887,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B76" t="str">
         <v>강남대로</v>
       </c>
       <c r="C76" t="str">
-        <v>26-서초구-12</v>
+        <v>26-서초구-13</v>
       </c>
       <c r="D76" t="str">
         <v>양호</v>
@@ -4932,16 +4932,16 @@
         <v>일반</v>
       </c>
       <c r="P76" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q76" t="str">
-        <v>서초동1337-32</v>
+        <v>서초동1337-31</v>
       </c>
       <c r="R76" t="str">
         <v/>
       </c>
       <c r="S76" t="str">
-        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
+        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
       </c>
       <c r="T76" t="str">
         <v/>
@@ -4949,13 +4949,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B77" t="str">
         <v>강남대로</v>
       </c>
       <c r="C77" t="str">
-        <v>26-서초구-13</v>
+        <v>26-서초구-14</v>
       </c>
       <c r="D77" t="str">
         <v>양호</v>
@@ -4997,13 +4997,13 @@
         <v>-</v>
       </c>
       <c r="Q77" t="str">
-        <v>서초동1337-31</v>
+        <v>서초동1337-20</v>
       </c>
       <c r="R77" t="str">
         <v/>
       </c>
       <c r="S77" t="str">
-        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
+        <v>대륭서초타워 앞 도로(강남대로327)</v>
       </c>
       <c r="T77" t="str">
         <v/>
@@ -5011,19 +5011,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B78" t="str">
         <v>강남대로</v>
       </c>
       <c r="C78" t="str">
-        <v>26-서초구-14</v>
+        <v>26-서초구-15</v>
       </c>
       <c r="D78" t="str">
         <v>양호</v>
       </c>
       <c r="E78" t="str">
-        <v>거북등</v>
+        <v>거북이</v>
       </c>
       <c r="F78" t="str">
         <v>양호</v>
@@ -5059,13 +5059,13 @@
         <v>-</v>
       </c>
       <c r="Q78" t="str">
-        <v>서초동1337-20</v>
+        <v>서초동1337-22</v>
       </c>
       <c r="R78" t="str">
         <v/>
       </c>
       <c r="S78" t="str">
-        <v>대륭서초타워 앞 도로(강남대로327)</v>
+        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
       </c>
       <c r="T78" t="str">
         <v/>
@@ -5073,19 +5073,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B79" t="str">
         <v>강남대로</v>
       </c>
       <c r="C79" t="str">
-        <v>26-서초구-15</v>
+        <v>26-서초구-16</v>
       </c>
       <c r="D79" t="str">
         <v>양호</v>
       </c>
       <c r="E79" t="str">
-        <v>거북이</v>
+        <v>거북등</v>
       </c>
       <c r="F79" t="str">
         <v>양호</v>
@@ -5121,13 +5121,13 @@
         <v>-</v>
       </c>
       <c r="Q79" t="str">
-        <v>서초동1337-22</v>
+        <v>서초동1338-23</v>
       </c>
       <c r="R79" t="str">
         <v/>
       </c>
       <c r="S79" t="str">
-        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
+        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
       </c>
       <c r="T79" t="str">
         <v/>
@@ -5135,13 +5135,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B80" t="str">
         <v>강남대로</v>
       </c>
       <c r="C80" t="str">
-        <v>26-서초구-16</v>
+        <v>26-서초구-17</v>
       </c>
       <c r="D80" t="str">
         <v>양호</v>
@@ -5183,13 +5183,13 @@
         <v>-</v>
       </c>
       <c r="Q80" t="str">
-        <v>서초동1338-23</v>
+        <v>서초동1338-12</v>
       </c>
       <c r="R80" t="str">
         <v/>
       </c>
       <c r="S80" t="str">
-        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
+        <v>코인노트 앞 도로(강남대로311)</v>
       </c>
       <c r="T80" t="str">
         <v/>
@@ -5197,13 +5197,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B81" t="str">
         <v>강남대로</v>
       </c>
       <c r="C81" t="str">
-        <v>26-서초구-17</v>
+        <v>26-서초구-18</v>
       </c>
       <c r="D81" t="str">
         <v>양호</v>
@@ -5245,13 +5245,13 @@
         <v>-</v>
       </c>
       <c r="Q81" t="str">
-        <v>서초동1338-12</v>
+        <v>서초동1338-21</v>
       </c>
       <c r="R81" t="str">
         <v/>
       </c>
       <c r="S81" t="str">
-        <v>코인노트 앞 도로(강남대로311)</v>
+        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
       </c>
       <c r="T81" t="str">
         <v/>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B82" t="str">
         <v>강남대로</v>
       </c>
       <c r="C82" t="str">
-        <v>26-서초구-18</v>
+        <v>26-서초구-19</v>
       </c>
       <c r="D82" t="str">
         <v>양호</v>
@@ -5307,13 +5307,13 @@
         <v>-</v>
       </c>
       <c r="Q82" t="str">
-        <v>서초동1338-21</v>
+        <v>서초동1338-20</v>
       </c>
       <c r="R82" t="str">
         <v/>
       </c>
       <c r="S82" t="str">
-        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
+        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
       </c>
       <c r="T82" t="str">
         <v/>
@@ -5321,13 +5321,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B83" t="str">
         <v>강남대로</v>
       </c>
       <c r="C83" t="str">
-        <v>26-서초구-19</v>
+        <v>26-서초구-20</v>
       </c>
       <c r="D83" t="str">
         <v>양호</v>
@@ -5369,13 +5369,13 @@
         <v>-</v>
       </c>
       <c r="Q83" t="str">
-        <v>서초동1338-20</v>
+        <v>서초동1339-9</v>
       </c>
       <c r="R83" t="str">
         <v/>
       </c>
       <c r="S83" t="str">
-        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
+        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
       </c>
       <c r="T83" t="str">
         <v/>
@@ -5383,13 +5383,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B84" t="str">
         <v>강남대로</v>
       </c>
       <c r="C84" t="str">
-        <v>26-서초구-20</v>
+        <v>26-서초구-21</v>
       </c>
       <c r="D84" t="str">
         <v>양호</v>
@@ -5431,13 +5431,13 @@
         <v>-</v>
       </c>
       <c r="Q84" t="str">
-        <v>서초동1339-9</v>
+        <v>서초동1340-6</v>
       </c>
       <c r="R84" t="str">
         <v/>
       </c>
       <c r="S84" t="str">
-        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
+        <v>남강빌딩 앞 도로(강남대로291)</v>
       </c>
       <c r="T84" t="str">
         <v/>
@@ -5445,13 +5445,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B85" t="str">
         <v>강남대로</v>
       </c>
       <c r="C85" t="str">
-        <v>26-서초구-21</v>
+        <v>26-서초구-22</v>
       </c>
       <c r="D85" t="str">
         <v>양호</v>
@@ -5493,13 +5493,13 @@
         <v>-</v>
       </c>
       <c r="Q85" t="str">
-        <v>서초동1340-6</v>
+        <v>서초동1357-10</v>
       </c>
       <c r="R85" t="str">
         <v/>
       </c>
       <c r="S85" t="str">
-        <v>남강빌딩 앞 도로(강남대로291)</v>
+        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
       </c>
       <c r="T85" t="str">
         <v/>
@@ -5507,19 +5507,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B86" t="str">
         <v>강남대로</v>
       </c>
       <c r="C86" t="str">
-        <v>26-서초구-22</v>
+        <v>26-서초구-23</v>
       </c>
       <c r="D86" t="str">
         <v>양호</v>
       </c>
       <c r="E86" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F86" t="str">
         <v>양호</v>
@@ -5534,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K86" t="str">
         <v>0</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="N86" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O86" t="str">
         <v>일반</v>
@@ -5555,13 +5555,13 @@
         <v>-</v>
       </c>
       <c r="Q86" t="str">
-        <v>서초동1357-10</v>
+        <v>서초동1357-66</v>
       </c>
       <c r="R86" t="str">
         <v/>
       </c>
       <c r="S86" t="str">
-        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
+        <v>메인타워 CU 앞 도로(강남대로275)</v>
       </c>
       <c r="T86" t="str">
         <v/>
@@ -5569,19 +5569,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B87" t="str">
         <v>강남대로</v>
       </c>
       <c r="C87" t="str">
-        <v>26-서초구-23</v>
+        <v>26-서초구-24</v>
       </c>
       <c r="D87" t="str">
         <v>양호</v>
       </c>
       <c r="E87" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F87" t="str">
         <v>양호</v>
@@ -5617,13 +5617,13 @@
         <v>-</v>
       </c>
       <c r="Q87" t="str">
-        <v>서초동1357-66</v>
+        <v>서초동1358-7</v>
       </c>
       <c r="R87" t="str">
         <v/>
       </c>
       <c r="S87" t="str">
-        <v>메인타워 CU 앞 도로(강남대로275)</v>
+        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
       </c>
       <c r="T87" t="str">
         <v/>
@@ -5631,19 +5631,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>26-24</v>
+        <v>26-25</v>
       </c>
       <c r="B88" t="str">
         <v>강남대로</v>
       </c>
       <c r="C88" t="str">
-        <v>26-서초구-24</v>
+        <v>26-서초구-25</v>
       </c>
       <c r="D88" t="str">
         <v>양호</v>
       </c>
       <c r="E88" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F88" t="str">
         <v>양호</v>
@@ -5658,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K88" t="str">
         <v>0</v>
@@ -5670,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="N88" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O88" t="str">
         <v>일반</v>
@@ -5679,13 +5679,13 @@
         <v>-</v>
       </c>
       <c r="Q88" t="str">
-        <v>서초동1358-7</v>
+        <v>양재역사거리</v>
       </c>
       <c r="R88" t="str">
         <v/>
       </c>
       <c r="S88" t="str">
-        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
+        <v>양재역 교차로(강남대로266-2)</v>
       </c>
       <c r="T88" t="str">
         <v/>
@@ -5693,13 +5693,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>26-25</v>
+        <v>26-26</v>
       </c>
       <c r="B89" t="str">
         <v>강남대로</v>
       </c>
       <c r="C89" t="str">
-        <v>26-서초구-25</v>
+        <v>26-서초구-26</v>
       </c>
       <c r="D89" t="str">
         <v>양호</v>
@@ -5741,13 +5741,13 @@
         <v>-</v>
       </c>
       <c r="Q89" t="str">
-        <v>양재역사거리</v>
+        <v>양재동23</v>
       </c>
       <c r="R89" t="str">
         <v/>
       </c>
       <c r="S89" t="str">
-        <v>양재역 교차로(강남대로266-2)</v>
+        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
       </c>
       <c r="T89" t="str">
         <v/>
@@ -5755,13 +5755,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>26-26</v>
+        <v>26-27</v>
       </c>
       <c r="B90" t="str">
         <v>강남대로</v>
       </c>
       <c r="C90" t="str">
-        <v>26-서초구-26</v>
+        <v>26-서초구-27</v>
       </c>
       <c r="D90" t="str">
         <v>양호</v>
@@ -5803,13 +5803,13 @@
         <v>-</v>
       </c>
       <c r="Q90" t="str">
-        <v>양재동23</v>
+        <v>양재동24</v>
       </c>
       <c r="R90" t="str">
         <v/>
       </c>
       <c r="S90" t="str">
-        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
+        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
       </c>
       <c r="T90" t="str">
         <v/>
@@ -5817,13 +5817,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>26-27</v>
+        <v>26-28</v>
       </c>
       <c r="B91" t="str">
         <v>강남대로</v>
       </c>
       <c r="C91" t="str">
-        <v>26-서초구-27</v>
+        <v>26-서초구-28</v>
       </c>
       <c r="D91" t="str">
         <v>양호</v>
@@ -5871,7 +5871,7 @@
         <v/>
       </c>
       <c r="S91" t="str">
-        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
+        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
       </c>
       <c r="T91" t="str">
         <v/>
@@ -5879,13 +5879,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>26-28</v>
+        <v>26-29</v>
       </c>
       <c r="B92" t="str">
         <v>강남대로</v>
       </c>
       <c r="C92" t="str">
-        <v>26-서초구-28</v>
+        <v>26-서초구-29</v>
       </c>
       <c r="D92" t="str">
         <v>양호</v>
@@ -5927,13 +5927,13 @@
         <v>-</v>
       </c>
       <c r="Q92" t="str">
-        <v>양재동24</v>
+        <v>양재동 산20-2</v>
       </c>
       <c r="R92" t="str">
         <v/>
       </c>
       <c r="S92" t="str">
-        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
+        <v>말죽거리공원 앞 도로(강남대로167)</v>
       </c>
       <c r="T92" t="str">
         <v/>
@@ -5941,19 +5941,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>26-29</v>
+        <v>26-30</v>
       </c>
       <c r="B93" t="str">
         <v>강남대로</v>
       </c>
       <c r="C93" t="str">
-        <v>26-서초구-29</v>
+        <v>26-서초구-30</v>
       </c>
       <c r="D93" t="str">
         <v>양호</v>
       </c>
       <c r="E93" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F93" t="str">
         <v>양호</v>
@@ -5968,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K93" t="str">
         <v>0</v>
@@ -5980,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O93" t="str">
         <v>일반</v>
@@ -5989,13 +5989,13 @@
         <v>-</v>
       </c>
       <c r="Q93" t="str">
-        <v>양재동 산20-2</v>
+        <v>양재동67</v>
       </c>
       <c r="R93" t="str">
         <v/>
       </c>
       <c r="S93" t="str">
-        <v>말죽거리공원 앞 도로(강남대로167)</v>
+        <v>혜인빌딩 앞 도로(163)</v>
       </c>
       <c r="T93" t="str">
         <v/>
@@ -6003,19 +6003,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>26-30</v>
+        <v>26-31</v>
       </c>
       <c r="B94" t="str">
         <v>강남대로</v>
       </c>
       <c r="C94" t="str">
-        <v>26-서초구-30</v>
+        <v>26-서초구-31</v>
       </c>
       <c r="D94" t="str">
         <v>양호</v>
       </c>
       <c r="E94" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F94" t="str">
         <v>양호</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K94" t="str">
         <v>0</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="N94" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O94" t="str">
         <v>일반</v>
@@ -6051,13 +6051,13 @@
         <v>-</v>
       </c>
       <c r="Q94" t="str">
-        <v>양재동67</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R94" t="str">
         <v/>
       </c>
       <c r="S94" t="str">
-        <v>혜인빌딩 앞 도로(163)</v>
+        <v>말죽거리공원 교차로(양재동20-40)</v>
       </c>
       <c r="T94" t="str">
         <v/>
@@ -6065,19 +6065,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>26-31</v>
+        <v>26-32</v>
       </c>
       <c r="B95" t="str">
         <v>강남대로</v>
       </c>
       <c r="C95" t="str">
-        <v>26-서초구-31</v>
+        <v>26-서초구-32</v>
       </c>
       <c r="D95" t="str">
         <v>양호</v>
       </c>
       <c r="E95" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F95" t="str">
         <v>양호</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K95" t="str">
         <v>0</v>
@@ -6104,7 +6104,7 @@
         <v>0</v>
       </c>
       <c r="N95" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O95" t="str">
         <v>일반</v>
@@ -6113,13 +6113,13 @@
         <v>-</v>
       </c>
       <c r="Q95" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동125</v>
       </c>
       <c r="R95" t="str">
         <v/>
       </c>
       <c r="S95" t="str">
-        <v>말죽거리공원 교차로(양재동20-40)</v>
+        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
       </c>
       <c r="T95" t="str">
         <v/>
@@ -6127,19 +6127,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>26-32</v>
+        <v>26-33</v>
       </c>
       <c r="B96" t="str">
         <v>강남대로</v>
       </c>
       <c r="C96" t="str">
-        <v>26-서초구-32</v>
+        <v>26-서초구-33</v>
       </c>
       <c r="D96" t="str">
         <v>양호</v>
       </c>
       <c r="E96" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F96" t="str">
         <v>양호</v>
@@ -6154,7 +6154,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K96" t="str">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="N96" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O96" t="str">
         <v>일반</v>
@@ -6175,13 +6175,13 @@
         <v>-</v>
       </c>
       <c r="Q96" t="str">
-        <v>양재동125</v>
+        <v>양재동80-3</v>
       </c>
       <c r="R96" t="str">
         <v/>
       </c>
       <c r="S96" t="str">
-        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
+        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
       </c>
       <c r="T96" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>26-33</v>
+        <v>26-34</v>
       </c>
       <c r="B97" t="str">
         <v>강남대로</v>
       </c>
       <c r="C97" t="str">
-        <v>26-서초구-33</v>
+        <v>26-서초구-34</v>
       </c>
       <c r="D97" t="str">
         <v>양호</v>
@@ -6237,13 +6237,13 @@
         <v>-</v>
       </c>
       <c r="Q97" t="str">
-        <v>양재동80-3</v>
+        <v>매헌시민의숲사거리</v>
       </c>
       <c r="R97" t="str">
         <v/>
       </c>
       <c r="S97" t="str">
-        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
+        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
       </c>
       <c r="T97" t="str">
         <v/>
@@ -6251,13 +6251,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>26-34</v>
+        <v>26-35</v>
       </c>
       <c r="B98" t="str">
         <v>강남대로</v>
       </c>
       <c r="C98" t="str">
-        <v>26-서초구-34</v>
+        <v>26-서초구-35</v>
       </c>
       <c r="D98" t="str">
         <v>양호</v>
@@ -6299,13 +6299,13 @@
         <v>-</v>
       </c>
       <c r="Q98" t="str">
-        <v>매헌시민의숲사거리</v>
+        <v>양재동237</v>
       </c>
       <c r="R98" t="str">
         <v/>
       </c>
       <c r="S98" t="str">
-        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
+        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
       </c>
       <c r="T98" t="str">
         <v/>
@@ -6313,13 +6313,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>26-35</v>
+        <v>26-36</v>
       </c>
       <c r="B99" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C99" t="str">
-        <v>26-서초구-35</v>
+        <v>26-서초구-36</v>
       </c>
       <c r="D99" t="str">
         <v>양호</v>
@@ -6361,13 +6361,13 @@
         <v>-</v>
       </c>
       <c r="Q99" t="str">
-        <v>양재동237</v>
+        <v>양재동237-2</v>
       </c>
       <c r="R99" t="str">
         <v/>
       </c>
       <c r="S99" t="str">
-        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
+        <v>매헌역 공영주차장 입구 앞 도로</v>
       </c>
       <c r="T99" t="str">
         <v/>
@@ -6375,13 +6375,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>26-36</v>
+        <v>26-37</v>
       </c>
       <c r="B100" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C100" t="str">
-        <v>26-서초구-36</v>
+        <v>26-서초구-37</v>
       </c>
       <c r="D100" t="str">
         <v>양호</v>
@@ -6423,13 +6423,13 @@
         <v>-</v>
       </c>
       <c r="Q100" t="str">
-        <v>양재동237-2</v>
+        <v>신원동308-1</v>
       </c>
       <c r="R100" t="str">
         <v/>
       </c>
       <c r="S100" t="str">
-        <v>매헌역 공영주차장 입구 앞 도로</v>
+        <v>가로등(청계산로69)_양차선</v>
       </c>
       <c r="T100" t="str">
         <v/>
@@ -6437,13 +6437,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>26-37</v>
+        <v>26-38</v>
       </c>
       <c r="B101" t="str">
         <v>청계산로</v>
       </c>
       <c r="C101" t="str">
-        <v>26-서초구-37</v>
+        <v>26-서초구-38</v>
       </c>
       <c r="D101" t="str">
         <v>양호</v>
@@ -6485,13 +6485,13 @@
         <v>-</v>
       </c>
       <c r="Q101" t="str">
-        <v>신원동308-1</v>
+        <v>신원동298-16</v>
       </c>
       <c r="R101" t="str">
         <v/>
       </c>
       <c r="S101" t="str">
-        <v>가로등(청계산로69)_양차선</v>
+        <v>청계산 수변공원 앞 도로_양차선</v>
       </c>
       <c r="T101" t="str">
         <v/>
@@ -6499,13 +6499,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>26-38</v>
+        <v>26-39</v>
       </c>
       <c r="B102" t="str">
         <v>청계산로</v>
       </c>
       <c r="C102" t="str">
-        <v>26-서초구-38</v>
+        <v>26-서초구-39</v>
       </c>
       <c r="D102" t="str">
         <v>양호</v>
@@ -6553,7 +6553,7 @@
         <v/>
       </c>
       <c r="S102" t="str">
-        <v>청계산 수변공원 앞 도로_양차선</v>
+        <v>가로등(청계산로81)앞도로_양차선</v>
       </c>
       <c r="T102" t="str">
         <v/>
@@ -6561,13 +6561,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>26-39</v>
+        <v>26-40</v>
       </c>
       <c r="B103" t="str">
         <v>청계산로</v>
       </c>
       <c r="C103" t="str">
-        <v>26-서초구-39</v>
+        <v>26-서초구-40</v>
       </c>
       <c r="D103" t="str">
         <v>양호</v>
@@ -6606,16 +6606,16 @@
         <v>일반</v>
       </c>
       <c r="P103" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q103" t="str">
-        <v>신원동298-16</v>
+        <v>원지동595</v>
       </c>
       <c r="R103" t="str">
         <v/>
       </c>
       <c r="S103" t="str">
-        <v>가로등(청계산로81)앞도로_양차선</v>
+        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
       </c>
       <c r="T103" t="str">
         <v/>
@@ -6623,13 +6623,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>26-40</v>
+        <v>26-41</v>
       </c>
       <c r="B104" t="str">
         <v>청계산로</v>
       </c>
       <c r="C104" t="str">
-        <v>26-서초구-40</v>
+        <v>26-서초구-41</v>
       </c>
       <c r="D104" t="str">
         <v>양호</v>
@@ -6668,16 +6668,16 @@
         <v>일반</v>
       </c>
       <c r="P104" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q104" t="str">
-        <v>원지동595</v>
+        <v>신원동280-1</v>
       </c>
       <c r="R104" t="str">
         <v/>
       </c>
       <c r="S104" t="str">
-        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
+        <v>교차로(T)_양차선</v>
       </c>
       <c r="T104" t="str">
         <v/>
@@ -6685,13 +6685,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>26-41</v>
+        <v>26-42</v>
       </c>
       <c r="B105" t="str">
         <v>청계산로</v>
       </c>
       <c r="C105" t="str">
-        <v>26-서초구-41</v>
+        <v>26-서초구-42</v>
       </c>
       <c r="D105" t="str">
         <v>양호</v>
@@ -6733,13 +6733,13 @@
         <v>-</v>
       </c>
       <c r="Q105" t="str">
-        <v>신원동280-1</v>
+        <v>신원동278-6</v>
       </c>
       <c r="R105" t="str">
         <v/>
       </c>
       <c r="S105" t="str">
-        <v>교차로(T)_양차선</v>
+        <v>버스정류장 앞 양차선</v>
       </c>
       <c r="T105" t="str">
         <v/>
@@ -6747,13 +6747,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>26-42</v>
+        <v>26-43</v>
       </c>
       <c r="B106" t="str">
         <v>청계산로</v>
       </c>
       <c r="C106" t="str">
-        <v>26-서초구-42</v>
+        <v>26-서초구-43</v>
       </c>
       <c r="D106" t="str">
         <v>양호</v>
@@ -6792,16 +6792,16 @@
         <v>일반</v>
       </c>
       <c r="P106" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q106" t="str">
-        <v>신원동278-6</v>
+        <v>신원동604</v>
       </c>
       <c r="R106" t="str">
         <v/>
       </c>
       <c r="S106" t="str">
-        <v>버스정류장 앞 양차선</v>
+        <v>오라카이 호텔 맞음편 도로 우수,전기맨홀(청계산로9길1-7)</v>
       </c>
       <c r="T106" t="str">
         <v/>
@@ -6809,13 +6809,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>26-43</v>
+        <v>26-44</v>
       </c>
       <c r="B107" t="str">
         <v>청계산로</v>
       </c>
       <c r="C107" t="str">
-        <v>26-서초구-43</v>
+        <v>26-서초구-44</v>
       </c>
       <c r="D107" t="str">
         <v>양호</v>
@@ -6854,16 +6854,16 @@
         <v>일반</v>
       </c>
       <c r="P107" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q107" t="str">
-        <v>신원동604</v>
+        <v>신원동607</v>
       </c>
       <c r="R107" t="str">
         <v/>
       </c>
       <c r="S107" t="str">
-        <v>오라카이 호텔 맞음편 도로 우수,전기맨홀(청계산로9길1-7)</v>
+        <v>내곡드림시티2 펀비어킹 앞 도로(청계산로189)</v>
       </c>
       <c r="T107" t="str">
         <v/>
@@ -6871,13 +6871,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>26-44</v>
+        <v>26-45</v>
       </c>
       <c r="B108" t="str">
         <v>청계산로</v>
       </c>
       <c r="C108" t="str">
-        <v>26-서초구-44</v>
+        <v>26-서초구-45</v>
       </c>
       <c r="D108" t="str">
         <v>양호</v>
@@ -6919,13 +6919,13 @@
         <v>-</v>
       </c>
       <c r="Q108" t="str">
-        <v>신원동607</v>
+        <v>신원동609</v>
       </c>
       <c r="R108" t="str">
         <v/>
       </c>
       <c r="S108" t="str">
-        <v>내곡드림시티2 펀비어킹 앞 도로(청계산로189)</v>
+        <v>내곡프라임시티 앞도로(청계산로195)</v>
       </c>
       <c r="T108" t="str">
         <v/>
@@ -6933,13 +6933,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>26-45</v>
+        <v>26-46</v>
       </c>
       <c r="B109" t="str">
         <v>청계산로</v>
       </c>
       <c r="C109" t="str">
-        <v>26-서초구-45</v>
+        <v>26-서초구-46</v>
       </c>
       <c r="D109" t="str">
         <v>양호</v>
@@ -6981,13 +6981,13 @@
         <v>-</v>
       </c>
       <c r="Q109" t="str">
-        <v>신원동609</v>
+        <v>신원동611</v>
       </c>
       <c r="R109" t="str">
         <v/>
       </c>
       <c r="S109" t="str">
-        <v>내곡프라임시티 앞도로(청계산로195)</v>
+        <v>서초포레지움 투썸플레이스 앞 양차선(청계산로201)</v>
       </c>
       <c r="T109" t="str">
         <v/>
@@ -6995,13 +6995,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>26-46</v>
+        <v>26-47</v>
       </c>
       <c r="B110" t="str">
         <v>청계산로</v>
       </c>
       <c r="C110" t="str">
-        <v>26-서초구-46</v>
+        <v>26-서초구-47</v>
       </c>
       <c r="D110" t="str">
         <v>양호</v>
@@ -7040,16 +7040,16 @@
         <v>일반</v>
       </c>
       <c r="P110" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q110" t="str">
-        <v>신원동611</v>
+        <v>원지동362-1</v>
       </c>
       <c r="R110" t="str">
         <v/>
       </c>
       <c r="S110" t="str">
-        <v>서초포레지움 투썸플레이스 앞 양차선(청계산로201)</v>
+        <v>청계쉼터 앞 도로</v>
       </c>
       <c r="T110" t="str">
         <v/>
@@ -7057,13 +7057,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>26-47</v>
+        <v>26-48</v>
       </c>
       <c r="B111" t="str">
         <v>청계산로</v>
       </c>
       <c r="C111" t="str">
-        <v>26-서초구-47</v>
+        <v>26-서초구-48</v>
       </c>
       <c r="D111" t="str">
         <v>양호</v>
@@ -7102,16 +7102,16 @@
         <v>일반</v>
       </c>
       <c r="P111" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q111" t="str">
-        <v>원지동362-1</v>
+        <v>원지동384-1</v>
       </c>
       <c r="R111" t="str">
         <v/>
       </c>
       <c r="S111" t="str">
-        <v>청계쉼터 앞 도로</v>
+        <v>청계산커피 앞 양차선</v>
       </c>
       <c r="T111" t="str">
         <v/>
@@ -7119,13 +7119,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>26-48</v>
+        <v>26-49</v>
       </c>
       <c r="B112" t="str">
         <v>청계산로</v>
       </c>
       <c r="C112" t="str">
-        <v>26-서초구-48</v>
+        <v>26-서초구-49</v>
       </c>
       <c r="D112" t="str">
         <v>양호</v>
@@ -7167,13 +7167,13 @@
         <v>-</v>
       </c>
       <c r="Q112" t="str">
-        <v>원지동384-1</v>
+        <v>신원동192-75</v>
       </c>
       <c r="R112" t="str">
         <v/>
       </c>
       <c r="S112" t="str">
-        <v>청계산커피 앞 양차선</v>
+        <v>강경불고기_청계 앞 양차선(청계산로245)</v>
       </c>
       <c r="T112" t="str">
         <v/>
@@ -7181,13 +7181,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>26-49</v>
+        <v>26-50</v>
       </c>
       <c r="B113" t="str">
         <v>청계산로</v>
       </c>
       <c r="C113" t="str">
-        <v>26-서초구-49</v>
+        <v>26-서초구-50</v>
       </c>
       <c r="D113" t="str">
         <v>양호</v>
@@ -7226,16 +7226,16 @@
         <v>일반</v>
       </c>
       <c r="P113" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q113" t="str">
-        <v>신원동192-75</v>
+        <v>신원동173-1</v>
       </c>
       <c r="R113" t="str">
         <v/>
       </c>
       <c r="S113" t="str">
-        <v>강경불고기_청계 앞 양차선(청계산로245)</v>
+        <v>향린조경 앞 양차선(고속도로방면침하)</v>
       </c>
       <c r="T113" t="str">
         <v/>
@@ -7243,13 +7243,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>26-50</v>
+        <v>26-51</v>
       </c>
       <c r="B114" t="str">
         <v>청계산로</v>
       </c>
       <c r="C114" t="str">
-        <v>26-서초구-50</v>
+        <v>26-서초구-51</v>
       </c>
       <c r="D114" t="str">
         <v>양호</v>
@@ -7291,13 +7291,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q114" t="str">
-        <v>신원동173-1</v>
+        <v>신원동152-12</v>
       </c>
       <c r="R114" t="str">
         <v/>
       </c>
       <c r="S114" t="str">
-        <v>향린조경 앞 양차선(고속도로방면침하)</v>
+        <v>삼석원 앞 양차선(고속도로방면 침하)</v>
       </c>
       <c r="T114" t="str">
         <v/>
@@ -7305,13 +7305,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>26-51</v>
+        <v>26-52</v>
       </c>
       <c r="B115" t="str">
         <v>청계산로</v>
       </c>
       <c r="C115" t="str">
-        <v>26-서초구-51</v>
+        <v>26-서초구-52</v>
       </c>
       <c r="D115" t="str">
         <v>양호</v>
@@ -7353,13 +7353,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q115" t="str">
-        <v>신원동152-12</v>
+        <v>신원동148-3</v>
       </c>
       <c r="R115" t="str">
         <v/>
       </c>
       <c r="S115" t="str">
-        <v>삼석원 앞 양차선(고속도로방면 침하)</v>
+        <v>은평조경 앞 양차선(고속도로방면 침하)(청계산로283-8)</v>
       </c>
       <c r="T115" t="str">
         <v/>
@@ -7367,13 +7367,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>26-52</v>
+        <v>26-53</v>
       </c>
       <c r="B116" t="str">
         <v>청계산로</v>
       </c>
       <c r="C116" t="str">
-        <v>26-서초구-52</v>
+        <v>26-서초구-53</v>
       </c>
       <c r="D116" t="str">
         <v>양호</v>
@@ -7415,13 +7415,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q116" t="str">
-        <v>신원동148-3</v>
+        <v>원지동490-3</v>
       </c>
       <c r="R116" t="str">
         <v/>
       </c>
       <c r="S116" t="str">
-        <v>은평조경 앞 양차선(고속도로방면 침하)(청계산로283-8)</v>
+        <v>인화원 앞 양차선(고속도로방면 침하)(가로등_청계산로161)</v>
       </c>
       <c r="T116" t="str">
         <v/>
@@ -7429,13 +7429,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>26-53</v>
+        <v>26-54</v>
       </c>
       <c r="B117" t="str">
         <v>청계산로</v>
       </c>
       <c r="C117" t="str">
-        <v>26-서초구-53</v>
+        <v>26-서초구-54</v>
       </c>
       <c r="D117" t="str">
         <v>양호</v>
@@ -7477,27 +7477,27 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q117" t="str">
-        <v>원지동491-2</v>
+        <v>원지동490</v>
       </c>
       <c r="R117" t="str">
         <v/>
       </c>
       <c r="S117" t="str">
-        <v>인화원 앞 양차선(고속도로방면 침하)(가로등_청계산로161)</v>
+        <v>양재조경 앞 양차선(고속도로방면 침하)_(가로등_청계산로165)</v>
       </c>
       <c r="T117" t="str">
-        <v/>
+        <v>현장확인필요</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>26-54</v>
+        <v>26-55</v>
       </c>
       <c r="B118" t="str">
         <v>청계산로</v>
       </c>
       <c r="C118" t="str">
-        <v>26-서초구-54</v>
+        <v>26-서초구-55</v>
       </c>
       <c r="D118" t="str">
         <v>양호</v>
@@ -7539,13 +7539,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q118" t="str">
-        <v>원지동493</v>
+        <v>원지동495-1</v>
       </c>
       <c r="R118" t="str">
         <v/>
       </c>
       <c r="S118" t="str">
-        <v>양재조경 앞 양차선(고속도로방면 침하)_(가로등_청계산로165)</v>
+        <v>화림조경간판 앞 양차선(가로등_청계산로167)</v>
       </c>
       <c r="T118" t="str">
         <v>현장확인필요</v>

--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -7539,7 +7539,7 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q118" t="str">
-        <v>원지동495-1</v>
+        <v>원지동495-5</v>
       </c>
       <c r="R118" t="str">
         <v/>

--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T118"/>
+  <dimension ref="A1:T123"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7486,7 +7486,7 @@
         <v>양재조경 앞 양차선(고속도로방면 침하)_(가로등_청계산로165)</v>
       </c>
       <c r="T117" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -7548,12 +7548,322 @@
         <v>화림조경간판 앞 양차선(가로등_청계산로167)</v>
       </c>
       <c r="T118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>26-56</v>
+      </c>
+      <c r="B119" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C119" t="str">
+        <v>26-서초구-56</v>
+      </c>
+      <c r="D119" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E119" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F119" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G119" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H119" t="str">
+        <v>-</v>
+      </c>
+      <c r="I119" t="str">
+        <v>0</v>
+      </c>
+      <c r="J119" t="str">
+        <v>3</v>
+      </c>
+      <c r="K119" t="str">
+        <v>0</v>
+      </c>
+      <c r="L119" t="str">
+        <v>1</v>
+      </c>
+      <c r="M119" t="str">
+        <v>0</v>
+      </c>
+      <c r="N119" t="str">
+        <v>4</v>
+      </c>
+      <c r="O119" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P119" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q119" t="str">
+        <v>원지동495-6</v>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v>(가로등_청계산로171)</v>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>26-57</v>
+      </c>
+      <c r="B120" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C120" t="str">
+        <v>26-서초구-57</v>
+      </c>
+      <c r="D120" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E120" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F120" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G120" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H120" t="str">
+        <v>-</v>
+      </c>
+      <c r="I120" t="str">
+        <v>0</v>
+      </c>
+      <c r="J120" t="str">
+        <v>1</v>
+      </c>
+      <c r="K120" t="str">
+        <v>0</v>
+      </c>
+      <c r="L120" t="str">
+        <v>1</v>
+      </c>
+      <c r="M120" t="str">
+        <v>0</v>
+      </c>
+      <c r="N120" t="str">
+        <v>2</v>
+      </c>
+      <c r="O120" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P120" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q120" t="str">
+        <v>원지동497-3</v>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+      <c r="S120" t="str">
+        <v>(가로등_청계산로313)</v>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>26-58</v>
+      </c>
+      <c r="B121" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C121" t="str">
+        <v>26-서초구-58</v>
+      </c>
+      <c r="D121" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E121" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F121" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G121" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H121" t="str">
+        <v>-</v>
+      </c>
+      <c r="I121" t="str">
+        <v>0</v>
+      </c>
+      <c r="J121" t="str">
+        <v>3</v>
+      </c>
+      <c r="K121" t="str">
+        <v>0</v>
+      </c>
+      <c r="L121" t="str">
+        <v>1</v>
+      </c>
+      <c r="M121" t="str">
+        <v>0</v>
+      </c>
+      <c r="N121" t="str">
+        <v>4</v>
+      </c>
+      <c r="O121" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P121" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q121" t="str">
+        <v>원지동575-1</v>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+      <c r="S121" t="str">
+        <v>(가로등_청계산로321)</v>
+      </c>
+      <c r="T121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>26-59</v>
+      </c>
+      <c r="B122" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C122" t="str">
+        <v>26-서초구-59</v>
+      </c>
+      <c r="D122" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E122" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F122" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G122" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H122" t="str">
+        <v>-</v>
+      </c>
+      <c r="I122" t="str">
+        <v>0</v>
+      </c>
+      <c r="J122" t="str">
+        <v>1</v>
+      </c>
+      <c r="K122" t="str">
+        <v>0</v>
+      </c>
+      <c r="L122" t="str">
+        <v>1</v>
+      </c>
+      <c r="M122" t="str">
+        <v>0</v>
+      </c>
+      <c r="N122" t="str">
+        <v>2</v>
+      </c>
+      <c r="O122" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P122" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q122" t="str">
+        <v>원지동523-2</v>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
+        <v>둥지조경 앞 도로(가로등_청계산로329)</v>
+      </c>
+      <c r="T122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>26-60</v>
+      </c>
+      <c r="B123" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C123" t="str">
+        <v>26-서초구-60</v>
+      </c>
+      <c r="D123" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E123" t="str">
+        <v>종,횡균열</v>
+      </c>
+      <c r="F123" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G123" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H123" t="str">
+        <v>-</v>
+      </c>
+      <c r="I123" t="str">
+        <v>0</v>
+      </c>
+      <c r="J123" t="str">
+        <v>1</v>
+      </c>
+      <c r="K123" t="str">
+        <v>0</v>
+      </c>
+      <c r="L123" t="str">
+        <v>1</v>
+      </c>
+      <c r="M123" t="str">
+        <v>0</v>
+      </c>
+      <c r="N123" t="str">
+        <v>2</v>
+      </c>
+      <c r="O123" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P123" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q123" t="str">
+        <v>신원동산60-2</v>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+      <c r="S123" t="str">
+        <v>대원조경 앞 양차선(가로등_청계산로181)</v>
+      </c>
+      <c r="T123" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T123"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T123"/>
+  <dimension ref="A1:T125"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7858,12 +7858,136 @@
         <v>대원조경 앞 양차선(가로등_청계산로181)</v>
       </c>
       <c r="T123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>26-61</v>
+      </c>
+      <c r="B124" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C124" t="str">
+        <v>26-서초구-61</v>
+      </c>
+      <c r="D124" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E124" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F124" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G124" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H124" t="str">
+        <v>-</v>
+      </c>
+      <c r="I124" t="str">
+        <v>0</v>
+      </c>
+      <c r="J124" t="str">
+        <v>3</v>
+      </c>
+      <c r="K124" t="str">
+        <v>0</v>
+      </c>
+      <c r="L124" t="str">
+        <v>1</v>
+      </c>
+      <c r="M124" t="str">
+        <v>0</v>
+      </c>
+      <c r="N124" t="str">
+        <v>4</v>
+      </c>
+      <c r="O124" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P124" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q124" t="str">
+        <v>신원동103</v>
+      </c>
+      <c r="R124" t="str">
+        <v/>
+      </c>
+      <c r="S124" t="str">
+        <v>둥지조경제2농장 앞 양차선(고속도로방면 침하)</v>
+      </c>
+      <c r="T124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>26-62</v>
+      </c>
+      <c r="B125" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C125" t="str">
+        <v>26-서초구-62</v>
+      </c>
+      <c r="D125" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E125" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F125" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G125" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H125" t="str">
+        <v>-</v>
+      </c>
+      <c r="I125" t="str">
+        <v>0</v>
+      </c>
+      <c r="J125" t="str">
+        <v>3</v>
+      </c>
+      <c r="K125" t="str">
+        <v>0</v>
+      </c>
+      <c r="L125" t="str">
+        <v>1</v>
+      </c>
+      <c r="M125" t="str">
+        <v>0</v>
+      </c>
+      <c r="N125" t="str">
+        <v>4</v>
+      </c>
+      <c r="O125" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P125" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q125" t="str">
+        <v>신원동105-33</v>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+      <c r="S125" t="str">
+        <v>한백자생식물원 앞 양차선(청계산로353)</v>
+      </c>
+      <c r="T125" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T123"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T125"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T125"/>
+  <dimension ref="A1:T127"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7985,9 +7985,133 @@
         <v>현장확인필요</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>26-63</v>
+      </c>
+      <c r="B126" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C126" t="str">
+        <v>26-서초구-63</v>
+      </c>
+      <c r="D126" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E126" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F126" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G126" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H126" t="str">
+        <v>-</v>
+      </c>
+      <c r="I126" t="str">
+        <v>0</v>
+      </c>
+      <c r="J126" t="str">
+        <v>3</v>
+      </c>
+      <c r="K126" t="str">
+        <v>0</v>
+      </c>
+      <c r="L126" t="str">
+        <v>1</v>
+      </c>
+      <c r="M126" t="str">
+        <v>0</v>
+      </c>
+      <c r="N126" t="str">
+        <v>4</v>
+      </c>
+      <c r="O126" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P126" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q126" t="str">
+        <v>신원동98-3</v>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+      <c r="S126" t="str">
+        <v>양차선(가로둥_청계산로193)</v>
+      </c>
+      <c r="T126" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>26-64</v>
+      </c>
+      <c r="B127" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C127" t="str">
+        <v>26-서초구-64</v>
+      </c>
+      <c r="D127" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E127" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F127" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G127" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H127" t="str">
+        <v>-</v>
+      </c>
+      <c r="I127" t="str">
+        <v>0</v>
+      </c>
+      <c r="J127" t="str">
+        <v>3</v>
+      </c>
+      <c r="K127" t="str">
+        <v>0</v>
+      </c>
+      <c r="L127" t="str">
+        <v>1</v>
+      </c>
+      <c r="M127" t="str">
+        <v>0</v>
+      </c>
+      <c r="N127" t="str">
+        <v>4</v>
+      </c>
+      <c r="O127" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P127" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q127" t="str">
+        <v>신원동44-32</v>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v>직접입력</v>
+      </c>
+      <c r="T127" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T125"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T127"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T127"/>
+  <dimension ref="A1:T133"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-6</v>
+        <v>25-서초구-7</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -530,16 +530,16 @@
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v>포장 복구개소</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q5" t="str">
-        <v>서초동 1328-10</v>
+        <v>서초동 1328-11</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>강남역 #5번출구 앞 도로</v>
+        <v>도씨의 빛Ⅱ 앞 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-서초구-7</v>
+        <v>25-서초구-8</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -592,16 +592,16 @@
         <v>일반</v>
       </c>
       <c r="P6" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
-        <v>서초동 1328-11</v>
+        <v>서초동 1329</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>도씨의 빛Ⅱ 앞 도로</v>
+        <v>삼성화제 앞 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="str">
         <v>강남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-서초구-8</v>
+        <v>25-서초구-9</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -654,16 +654,16 @@
         <v>일반</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q7" t="str">
-        <v>서초동 1329</v>
+        <v>서초동 1329-7</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>삼성화제 앞 도로</v>
+        <v>신한투자증권 앞 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-서초구-9</v>
+        <v>25-서초구-10</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -719,13 +719,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q8" t="str">
-        <v>서초동 1329-7</v>
+        <v>서초동 1329-8</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>신한투자증권 앞 도로</v>
+        <v>모닝글로리 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-서초구-10</v>
+        <v>25-서초구-11</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -778,16 +778,16 @@
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q9" t="str">
-        <v>서초동 1329-8</v>
+        <v>서초동 1329-10</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>모닝글로리 앞 도로</v>
+        <v>우성아파트 사거리 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-서초구-11</v>
+        <v>25-서초구-12</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -840,16 +840,16 @@
         <v>일반</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q10" t="str">
-        <v>서초동 1329-10</v>
+        <v>서초동 1337-32</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>우성아파트 사거리 도로</v>
+        <v>한국투자증권 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-서초구-12</v>
+        <v>25-서초구-13</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -902,16 +902,16 @@
         <v>일반</v>
       </c>
       <c r="P11" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q11" t="str">
-        <v>서초동 1337-32</v>
+        <v>서초동 1337-22</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>한국투자증권 앞 도로</v>
+        <v>디오빌프라임 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-서초구-13</v>
+        <v>25-서초구-14</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -967,13 +967,13 @@
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v>서초동 1337-22</v>
+        <v>서초동 1338-23</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>디오빌프라임 앞 도로</v>
+        <v>투썸플레이스 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-서초구-14</v>
+        <v>25-서초구-15</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1029,13 +1029,13 @@
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v>서초동 1338-23</v>
+        <v>서초동 1338-20</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>투썸플레이스 도로</v>
+        <v>현대렉시온 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-서초구-15</v>
+        <v>25-서초구-16</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1058,7 +1058,7 @@
         <v>거북등</v>
       </c>
       <c r="F14" t="str">
-        <v>양호</v>
+        <v>건조</v>
       </c>
       <c r="G14" t="str">
         <v>13.5</v>
@@ -1091,13 +1091,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>서초동 1338-20</v>
+        <v>서초동 1339-9</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>현대렉시온 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-서초구-16</v>
+        <v>25-서초구-17</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>서초동 1339-9</v>
+        <v>서초동 1340-6</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>KIA 서초지점 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1212,7 +1212,7 @@
         <v>일반</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q16" t="str">
         <v>서초동 1340-6</v>
@@ -1221,7 +1221,7 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>KIA 서초지점 앞 도로</v>
+        <v>남강매점 앞 횡단보도</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-서초구-18</v>
+        <v>25-서초구-19</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1274,16 +1274,16 @@
         <v>일반</v>
       </c>
       <c r="P17" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q17" t="str">
-        <v>서초동 1340-6</v>
+        <v>서초동 1357-33</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>남강매점 앞 횡단보도</v>
+        <v>한국디지털 평생교육원 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-서초구-19</v>
+        <v>25-서초구-20</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1336,16 +1336,16 @@
         <v>일반</v>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q18" t="str">
-        <v>서초동 1357-33</v>
+        <v>서초동 1357-35</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>한국디지털 평생교육원 앞 도로</v>
+        <v>부산은행 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-서초구-20</v>
+        <v>25-서초구-21</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1401,13 +1401,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q19" t="str">
-        <v>서초동 1357-35</v>
+        <v>서초동 1358-6</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>부산은행 앞 도로</v>
+        <v>송남빌딩 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,19 +1415,19 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-서초구-21</v>
+        <v>25-서초구-22</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
       </c>
       <c r="E20" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F20" t="str">
         <v>건조</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1454,22 +1454,22 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O20" t="str">
         <v>일반</v>
       </c>
       <c r="P20" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q20" t="str">
-        <v>서초동 1358-6</v>
+        <v>서초동 1361-1</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>송남빌딩 앞 도로</v>
+        <v>보들설곰탕 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-서초구-22</v>
+        <v>25-서초구-23</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1525,13 +1525,13 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v>서초동 1361-1</v>
+        <v>서초동 1361-5</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>보들설곰탕 앞 도로</v>
+        <v>새움빌딩 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,19 +1539,19 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" t="str">
         <v>강남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-서초구-23</v>
+        <v>25-서초구-24</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
       </c>
       <c r="E22" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F22" t="str">
         <v>건조</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O22" t="str">
         <v>일반</v>
@@ -1587,13 +1587,13 @@
         <v/>
       </c>
       <c r="Q22" t="str">
-        <v>서초동 1361-5</v>
+        <v>서초동 1361-10</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>새움빌딩 앞 도로</v>
+        <v>호텔 페이토 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" t="str">
         <v>강남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-서초구-24</v>
+        <v>25-서초구-25</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
@@ -1646,16 +1646,16 @@
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q23" t="str">
-        <v>서초동 1361-10</v>
+        <v>서초동 1362</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>호텔 페이토 앞 도로</v>
+        <v>e마트24 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,13 +1663,13 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" t="str">
         <v>강남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-서초구-25</v>
+        <v>25-서초구-26</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
@@ -1708,16 +1708,16 @@
         <v>일반</v>
       </c>
       <c r="P24" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q24" t="str">
-        <v>서초동 1362</v>
+        <v>서초동 1362-26</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>e마트24 앞 도로</v>
+        <v>힐든가든인 서울강남 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" t="str">
         <v>강남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-서초구-26</v>
+        <v>25-서초구-27</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
@@ -1770,16 +1770,16 @@
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q25" t="str">
-        <v>서초동 1362-26</v>
+        <v>서초동 1362-27</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>힐든가든인 서울강남 앞 도로</v>
+        <v>니드오피스텔 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" t="str">
         <v>강남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-서초구-27</v>
+        <v>25-서초구-28</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1832,16 +1832,16 @@
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q26" t="str">
-        <v>서초동 1362-27</v>
+        <v>서초동 1366-7</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>니드오피스텔 앞 도로</v>
+        <v>깐부치킨 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" t="str">
         <v>강남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-서초구-28</v>
+        <v>25-서초구-29</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1894,16 +1894,16 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q27" t="str">
-        <v>서초동 1366-7</v>
+        <v>서초동 1366-9</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>깐부치킨 앞 도로</v>
+        <v>양재역 교차로 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" t="str">
         <v>강남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-서초구-29</v>
+        <v>25-서초구-30</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q28" t="str">
-        <v>서초동 1366-9</v>
+        <v>양재동 23</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>양재역 교차로 도로</v>
+        <v>바나프레소 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="str">
         <v>강남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-서초구-30</v>
+        <v>25-서초구-31</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2021,13 +2021,13 @@
         <v/>
       </c>
       <c r="Q29" t="str">
-        <v>양재동 23</v>
+        <v>양재동 25</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>바나프레소 앞 도로</v>
+        <v>서초문화 예술회관 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" t="str">
         <v>강남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-서초구-31</v>
+        <v>25-서초구-32</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2083,13 +2083,13 @@
         <v/>
       </c>
       <c r="Q30" t="str">
-        <v>양재동 25</v>
+        <v>양재동 14-4</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>서초문화 예술회관 앞 도로</v>
+        <v>모산빌딩 앞 횡단보도</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,19 +2097,19 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" t="str">
         <v>강남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-서초구-32</v>
+        <v>25-서초구-33</v>
       </c>
       <c r="D31" t="str">
-        <v>양호</v>
+        <v>50</v>
       </c>
       <c r="E31" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F31" t="str">
         <v>건조</v>
@@ -2120,11 +2120,11 @@
       <c r="H31" t="str">
         <v>-</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2136,22 +2136,22 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O31" t="str">
         <v>일반</v>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>보도침하5cm</v>
       </c>
       <c r="Q31" t="str">
-        <v>양재동 14-4</v>
+        <v>양재동 67-7</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>모산빌딩 앞 횡단보도</v>
+        <v>바나프레스 앞 보도</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,19 +2159,19 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-서초구-33</v>
+        <v>25-서초구-34</v>
       </c>
       <c r="D32" t="str">
-        <v>50</v>
+        <v>양호</v>
       </c>
       <c r="E32" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F32" t="str">
         <v>건조</v>
@@ -2182,11 +2182,11 @@
       <c r="H32" t="str">
         <v>-</v>
       </c>
-      <c r="I32" t="b">
+      <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O32" t="str">
         <v>일반</v>
       </c>
       <c r="P32" t="str">
-        <v>보도침하5cm</v>
+        <v/>
       </c>
       <c r="Q32" t="str">
-        <v>양재동 67-7</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>바나프레스 앞 보도</v>
+        <v>교육개발원 사거리 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-서초구-34</v>
+        <v>25-서초구-35</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
       </c>
       <c r="E33" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F33" t="str">
         <v>건조</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O33" t="str">
         <v>일반</v>
@@ -2269,13 +2269,13 @@
         <v/>
       </c>
       <c r="Q33" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동 109</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>교육개발원 사거리 도로</v>
+        <v>카페 릴리블랑 앞 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,19 +2283,19 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-서초구-35</v>
+        <v>25-서초구-36</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
       </c>
       <c r="E34" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F34" t="str">
         <v>건조</v>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O34" t="str">
         <v>일반</v>
@@ -2331,13 +2331,13 @@
         <v/>
       </c>
       <c r="Q34" t="str">
-        <v>양재동 109</v>
+        <v>양재동 125</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>카페 릴리블랑 앞 도로</v>
+        <v>넥스팜 코리아 앞 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,13 +2345,13 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35" t="str">
         <v>강남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-서초구-36</v>
+        <v>25-서초구-37</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
@@ -2393,13 +2393,13 @@
         <v/>
       </c>
       <c r="Q35" t="str">
-        <v>양재동 125</v>
+        <v>양재동 80-3</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>넥스팜 코리아 앞 도로</v>
+        <v>도야짬뽕 앞 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,13 +2407,13 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-서초구-37</v>
+        <v>25-서초구-38</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2455,13 +2455,13 @@
         <v/>
       </c>
       <c r="Q36" t="str">
-        <v>양재동 80-3</v>
+        <v>양재동 237-1</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>도야짬뽕 앞 도로</v>
+        <v>공영주차장 앞 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-서초구-38</v>
+        <v>25-서초구-39</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>양재동 237-1</v>
+        <v>신원동 308-1</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>공영주차장 앞 도로</v>
+        <v>가로등(청계산로145) 양차선 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" t="str">
         <v>청계산로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-서초구-39</v>
+        <v>25-서초구-40</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>신원동 308-1</v>
+        <v>원지동 294-3</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>가로등(청계산로145) 양차선 도로</v>
+        <v>전봇대(원지간37H1) 양차선 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" t="str">
         <v>청계산로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-서초구-40</v>
+        <v>25-서초구-41</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2638,16 +2638,16 @@
         <v>일반</v>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>거북등 맨홀침하4cm</v>
       </c>
       <c r="Q39" t="str">
-        <v>원지동 294-3</v>
+        <v>원지동 594-1</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>전봇대(원지간37H1) 양차선 도로</v>
+        <v>도로교통표지판 앞 상수도맨홀 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" t="str">
         <v>청계산로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-서초구-41</v>
+        <v>25-서초구-42</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2700,16 +2700,16 @@
         <v>일반</v>
       </c>
       <c r="P40" t="str">
-        <v>거북등 맨홀침하4cm</v>
+        <v/>
       </c>
       <c r="Q40" t="str">
-        <v>원지동 594-1</v>
+        <v>신원동 280</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>도로교통표지판 앞 상수도맨홀 도로</v>
+        <v>공영주차장 앞 T 교차로 양차선 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" t="str">
         <v>청계산로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-서초구-42</v>
+        <v>25-서초구-43</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2765,13 +2765,13 @@
         <v/>
       </c>
       <c r="Q41" t="str">
-        <v>신원동 280</v>
+        <v>신원동 278-6</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>공영주차장 앞 T 교차로 양차선 도로</v>
+        <v>공영주차장 앞 양차선 도로</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,13 +2779,13 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" t="str">
         <v>청계산로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-서초구-43</v>
+        <v>25-서초구-44</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
@@ -2824,16 +2824,16 @@
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q42" t="str">
-        <v>신원동 278-6</v>
+        <v>신원동 611</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>공영주차장 앞 양차선 도로</v>
+        <v>투썸플레이스 앞 보도</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" t="str">
         <v>청계산로</v>
       </c>
       <c r="C43" t="str">
-        <v>25-서초구-44</v>
+        <v>25-서초구-45</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
       </c>
       <c r="E43" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F43" t="str">
         <v>건조</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -2880,22 +2880,22 @@
         <v>0</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O43" t="str">
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v>보도침하4cm</v>
+        <v/>
       </c>
       <c r="Q43" t="str">
-        <v>신원동 611</v>
+        <v>신원동 612</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>투썸플레이스 앞 보도</v>
+        <v>LAB 앞 도로</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,19 +2903,19 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44" t="str">
         <v>청계산로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-서초구-45</v>
+        <v>25-서초구-46</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
       <c r="E44" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F44" t="str">
         <v>건조</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -2942,22 +2942,22 @@
         <v>0</v>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O44" t="str">
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q44" t="str">
-        <v>신원동 612</v>
+        <v>신원동 660</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>LAB 앞 도로</v>
+        <v>심플리시티 앞 보도</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45" t="str">
         <v>청계산로</v>
       </c>
       <c r="C45" t="str">
-        <v>25-서초구-46</v>
+        <v>25-서초구-47</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
@@ -3010,16 +3010,16 @@
         <v>일반</v>
       </c>
       <c r="P45" t="str">
-        <v>보도침하4cm</v>
+        <v>보도침하3cm</v>
       </c>
       <c r="Q45" t="str">
-        <v>신원동 660</v>
+        <v>신원동 197-1</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>심플리시티 앞 보도</v>
+        <v>부안애서 맞음편 보도</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,13 +3027,13 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B46" t="str">
         <v>청계산로</v>
       </c>
       <c r="C46" t="str">
-        <v>25-서초구-47</v>
+        <v>25-서초구-48</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
@@ -3072,16 +3072,16 @@
         <v>일반</v>
       </c>
       <c r="P46" t="str">
-        <v>보도침하3cm</v>
+        <v/>
       </c>
       <c r="Q46" t="str">
-        <v>신원동 197-1</v>
+        <v>원지동 384-1</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>부안애서 맞음편 보도</v>
+        <v>커피플라워 앞 양차선 도로</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,13 +3089,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47" t="str">
         <v>청계산로</v>
       </c>
       <c r="C47" t="str">
-        <v>25-서초구-48</v>
+        <v>25-서초구-49</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
@@ -3137,13 +3137,13 @@
         <v/>
       </c>
       <c r="Q47" t="str">
-        <v>원지동 384-1</v>
+        <v>신원동 192-73</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>커피플라워 앞 양차선 도로</v>
+        <v>봉평막국수 앞 양차선 도로</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,13 +3151,13 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48" t="str">
         <v>청계산로</v>
       </c>
       <c r="C48" t="str">
-        <v>25-서초구-49</v>
+        <v>25-서초구-50</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
@@ -3199,13 +3199,13 @@
         <v/>
       </c>
       <c r="Q48" t="str">
-        <v>신원동 192-73</v>
+        <v>신원동 172-1</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>봉평막국수 앞 양차선 도로</v>
+        <v>향린조경 앞 양차선 도로</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,13 +3213,13 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49" t="str">
         <v>청계산로</v>
       </c>
       <c r="C49" t="str">
-        <v>25-서초구-50</v>
+        <v>25-서초구-51</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3261,13 +3261,13 @@
         <v/>
       </c>
       <c r="Q49" t="str">
-        <v>신원동 172-1</v>
+        <v>신원동 153</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>향린조경 앞 양차선 도로</v>
+        <v>삼석원 앞 양차선 도로</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,13 +3275,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50" t="str">
         <v>청계산로</v>
       </c>
       <c r="C50" t="str">
-        <v>25-서초구-51</v>
+        <v>25-서초구-52</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3323,13 +3323,13 @@
         <v/>
       </c>
       <c r="Q50" t="str">
-        <v>신원동 153</v>
+        <v>신원동 150-1</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>삼석원 앞 양차선 도로</v>
+        <v>성심조경 앞 양차선 도로</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" t="str">
         <v>청계산로</v>
       </c>
       <c r="C51" t="str">
-        <v>25-서초구-52</v>
+        <v>25-서초구-53</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3382,16 +3382,16 @@
         <v>일반</v>
       </c>
       <c r="P51" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q51" t="str">
-        <v>신원동 150-1</v>
+        <v>원지동 470-1</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>성심조경 앞 양차선 도로</v>
+        <v>가로등(청계산로154) 앞 보도</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" t="str">
         <v>청계산로</v>
       </c>
       <c r="C52" t="str">
-        <v>25-서초구-53</v>
+        <v>25-서초구-54</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3444,16 +3444,16 @@
         <v>일반</v>
       </c>
       <c r="P52" t="str">
-        <v>5cm이하 침하</v>
+        <v>보도침하</v>
       </c>
       <c r="Q52" t="str">
-        <v>원지동 470-1</v>
+        <v>원지동 491-6</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>가로등(청계산로154) 앞 보도</v>
+        <v>가로등(청계산로156) 맞음편 보도</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53" t="str">
         <v>청계산로</v>
       </c>
       <c r="C53" t="str">
-        <v>25-서초구-54</v>
+        <v>25-서초구-55</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3506,16 +3506,16 @@
         <v>일반</v>
       </c>
       <c r="P53" t="str">
-        <v>보도침하</v>
+        <v/>
       </c>
       <c r="Q53" t="str">
-        <v>원지동 491-6</v>
+        <v>원지동 493</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>가로등(청계산로156) 맞음편 보도</v>
+        <v>양재조경 앞 양차선 도로</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3523,13 +3523,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54" t="str">
         <v>청계산로</v>
       </c>
       <c r="C54" t="str">
-        <v>25-서초구-55</v>
+        <v>25-서초구-56</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3571,13 +3571,13 @@
         <v/>
       </c>
       <c r="Q54" t="str">
-        <v>원지동 493</v>
+        <v>원지동 497-3</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>양재조경 앞 양차선 도로</v>
+        <v>가로등(청계산로168) 앞 양차선 도로</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55" t="str">
         <v>청계산로</v>
       </c>
       <c r="C55" t="str">
-        <v>25-서초구-56</v>
+        <v>25-서초구-57</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3633,13 +3633,13 @@
         <v/>
       </c>
       <c r="Q55" t="str">
-        <v>원지동 497-3</v>
+        <v>신원동 산 60-2</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>가로등(청계산로168) 앞 양차선 도로</v>
+        <v>대원조경 앞 양차선 도로</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3647,13 +3647,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B56" t="str">
         <v>청계산로</v>
       </c>
       <c r="C56" t="str">
-        <v>25-서초구-57</v>
+        <v>25-서초구-58</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3695,13 +3695,13 @@
         <v/>
       </c>
       <c r="Q56" t="str">
-        <v>신원동 산 60-2</v>
+        <v>신원동 105-4</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>대원조경 앞 양차선 도로</v>
+        <v>둥지조경 제2농장 앞 양차선 도로</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3709,13 +3709,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B57" t="str">
         <v>청계산로</v>
       </c>
       <c r="C57" t="str">
-        <v>25-서초구-58</v>
+        <v>25-서초구-59</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="Q57" t="str">
-        <v>신원동 105-4</v>
+        <v>신원동 105-33</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>둥지조경 제2농장 앞 양차선 도로</v>
+        <v>한백자생식물원 앞 양차선 도로</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3771,13 +3771,13 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58" t="str">
         <v>청계산로</v>
       </c>
       <c r="C58" t="str">
-        <v>25-서초구-59</v>
+        <v>25-서초구-60</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3816,16 +3816,16 @@
         <v>일반</v>
       </c>
       <c r="P58" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q58" t="str">
-        <v>신원동 105-33</v>
+        <v>신원동 105-19</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>한백자생식물원 앞 양차선 도로</v>
+        <v>가로등(청계산로190) 앞 양차선 도로</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3833,19 +3833,19 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B59" t="str">
         <v>청계산로</v>
       </c>
       <c r="C59" t="str">
-        <v>25-서초구-60</v>
+        <v>25-서초구-61</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
       </c>
       <c r="E59" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F59" t="str">
         <v>건조</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O59" t="str">
         <v>일반</v>
@@ -3881,13 +3881,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q59" t="str">
-        <v>신원동 105-19</v>
+        <v>신원동 44-1</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>가로등(청계산로190) 앞 양차선 도로</v>
+        <v>새정이마을 입구 교차로</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3895,19 +3895,19 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60" t="str">
         <v>청계산로</v>
       </c>
       <c r="C60" t="str">
-        <v>25-서초구-61</v>
+        <v>25-서초구-62</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
       </c>
       <c r="E60" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F60" t="str">
         <v>건조</v>
@@ -3940,16 +3940,16 @@
         <v>일반</v>
       </c>
       <c r="P60" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q60" t="str">
-        <v>신원동 44-1</v>
+        <v>신원동 44-5</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>새정이마을 입구 교차로</v>
+        <v>은하조경 앞 양차선 도로</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3957,13 +3957,13 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B61" t="str">
         <v>청계산로</v>
       </c>
       <c r="C61" t="str">
-        <v>25-서초구-62</v>
+        <v>25-서초구-63</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
@@ -4005,13 +4005,13 @@
         <v/>
       </c>
       <c r="Q61" t="str">
-        <v>신원동 44-5</v>
+        <v>신원동 57</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>은하조경 앞 양차선 도로</v>
+        <v>서림원예종묘 앞 양차선 도로</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4019,19 +4019,19 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62" t="str">
         <v>청계산로</v>
       </c>
       <c r="C62" t="str">
-        <v>25-서초구-63</v>
+        <v>25-서초구-64</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
       </c>
       <c r="E62" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F62" t="str">
         <v>건조</v>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O62" t="str">
         <v>일반</v>
@@ -4067,27 +4067,27 @@
         <v/>
       </c>
       <c r="Q62" t="str">
-        <v>신원동 57</v>
+        <v>신원동 64-1</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>서림원예종묘 앞 양차선 도로</v>
+        <v>옥천조경 앞 양차선 도로</v>
       </c>
       <c r="T62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63">
-        <v>64</v>
+      <c r="A63" t="str">
+        <v>26-01</v>
       </c>
       <c r="B63" t="str">
-        <v>청계산로</v>
+        <v>강남대로</v>
       </c>
       <c r="C63" t="str">
-        <v>25-서초구-64</v>
+        <v>26-서초구-01</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
@@ -4096,46 +4096,46 @@
         <v>거북등</v>
       </c>
       <c r="F63" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G63" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H63" t="str">
         <v>-</v>
       </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>3</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>1</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
+      <c r="I63" t="str">
+        <v>0</v>
+      </c>
+      <c r="J63" t="str">
+        <v>3</v>
+      </c>
+      <c r="K63" t="str">
+        <v>0</v>
+      </c>
+      <c r="L63" t="str">
+        <v>1</v>
+      </c>
+      <c r="M63" t="str">
+        <v>0</v>
+      </c>
+      <c r="N63" t="str">
         <v>4</v>
       </c>
       <c r="O63" t="str">
         <v>일반</v>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q63" t="str">
-        <v>신원동 64-1</v>
+        <v>서초동1318-4</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>옥천조경 앞 양차선 도로</v>
+        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4143,13 +4143,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B64" t="str">
         <v>강남대로</v>
       </c>
       <c r="C64" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
@@ -4191,13 +4191,13 @@
         <v>-</v>
       </c>
       <c r="Q64" t="str">
-        <v>서초동1318-4</v>
+        <v>강남역사거리</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
+        <v>강남역사거리(강남대로396)</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4205,13 +4205,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B65" t="str">
         <v>강남대로</v>
       </c>
       <c r="C65" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
@@ -4253,13 +4253,13 @@
         <v>-</v>
       </c>
       <c r="Q65" t="str">
-        <v>강남역사거리</v>
+        <v>서초동1319-5</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>강남역사거리(강남대로396)</v>
+        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4267,13 +4267,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B66" t="str">
         <v>강남대로</v>
       </c>
       <c r="C66" t="str">
-        <v>26-서초구-03</v>
+        <v>26-서초구-04</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4315,13 +4315,13 @@
         <v>-</v>
       </c>
       <c r="Q66" t="str">
-        <v>서초동1319-5</v>
+        <v>서초동1319-11</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
+        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4329,13 +4329,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B67" t="str">
         <v>강남대로</v>
       </c>
       <c r="C67" t="str">
-        <v>26-서초구-04</v>
+        <v>26-서초구-05</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
@@ -4377,13 +4377,13 @@
         <v>-</v>
       </c>
       <c r="Q67" t="str">
-        <v>서초동1319-11</v>
+        <v>서초동1328-3</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
+        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4391,13 +4391,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B68" t="str">
         <v>강남대로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-서초구-05</v>
+        <v>26-서초구-06</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
@@ -4436,16 +4436,16 @@
         <v>일반</v>
       </c>
       <c r="P68" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q68" t="str">
-        <v>서초동1328-3</v>
+        <v>서초동1328-11</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
+        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4453,13 +4453,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B69" t="str">
         <v>강남대로</v>
       </c>
       <c r="C69" t="str">
-        <v>26-서초구-06</v>
+        <v>26-서초구-07</v>
       </c>
       <c r="D69" t="str">
         <v>양호</v>
@@ -4501,13 +4501,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q69" t="str">
-        <v>서초동1328-11</v>
+        <v>서초동1329</v>
       </c>
       <c r="R69" t="str">
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
+        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4515,13 +4515,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B70" t="str">
         <v>강남대로</v>
       </c>
       <c r="C70" t="str">
-        <v>26-서초구-07</v>
+        <v>26-서초구-08</v>
       </c>
       <c r="D70" t="str">
         <v>양호</v>
@@ -4560,16 +4560,16 @@
         <v>일반</v>
       </c>
       <c r="P70" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q70" t="str">
-        <v>서초동1329</v>
+        <v>서초동1329-4</v>
       </c>
       <c r="R70" t="str">
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
+        <v>우남빌딩 앞 도로(강남대로349)</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4577,16 +4577,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B71" t="str">
         <v>강남대로</v>
       </c>
       <c r="C71" t="str">
-        <v>26-서초구-08</v>
+        <v>26-서초구-09</v>
       </c>
       <c r="D71" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E71" t="str">
         <v>거북등</v>
@@ -4601,7 +4601,7 @@
         <v>-</v>
       </c>
       <c r="I71" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J71" t="str">
         <v>3</v>
@@ -4616,22 +4616,22 @@
         <v>0</v>
       </c>
       <c r="N71" t="str">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O71" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P71" t="str">
-        <v>-</v>
+        <v>복구부 밑 빈공간있음(80cm)</v>
       </c>
       <c r="Q71" t="str">
-        <v>서초동1329-4</v>
+        <v>서초동1329-7</v>
       </c>
       <c r="R71" t="str">
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>우남빌딩 앞 도로(강남대로349)</v>
+        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
       </c>
       <c r="T71" t="str">
         <v/>
@@ -4639,16 +4639,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B72" t="str">
         <v>강남대로</v>
       </c>
       <c r="C72" t="str">
-        <v>26-서초구-09</v>
+        <v>26-서초구-10</v>
       </c>
       <c r="D72" t="str">
-        <v>불량</v>
+        <v>양호</v>
       </c>
       <c r="E72" t="str">
         <v>거북등</v>
@@ -4663,7 +4663,7 @@
         <v>-</v>
       </c>
       <c r="I72" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J72" t="str">
         <v>3</v>
@@ -4678,22 +4678,22 @@
         <v>0</v>
       </c>
       <c r="N72" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O72" t="str">
-        <v>긴급</v>
+        <v>일반</v>
       </c>
       <c r="P72" t="str">
-        <v>복구부 밑 빈공간있음(80cm)</v>
+        <v>-</v>
       </c>
       <c r="Q72" t="str">
-        <v>서초동1329-7</v>
+        <v>서초동1329-8</v>
       </c>
       <c r="R72" t="str">
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
+        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
       </c>
       <c r="T72" t="str">
         <v/>
@@ -4701,13 +4701,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B73" t="str">
         <v>강남대로</v>
       </c>
       <c r="C73" t="str">
-        <v>26-서초구-10</v>
+        <v>26-서초구-11</v>
       </c>
       <c r="D73" t="str">
         <v>양호</v>
@@ -4746,16 +4746,16 @@
         <v>일반</v>
       </c>
       <c r="P73" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="Q73" t="str">
-        <v>서초동1329-8</v>
+        <v>우성아파트앞 사거리</v>
       </c>
       <c r="R73" t="str">
         <v/>
       </c>
       <c r="S73" t="str">
-        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
+        <v>교차로(강남대로346-2)</v>
       </c>
       <c r="T73" t="str">
         <v/>
@@ -4763,13 +4763,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B74" t="str">
         <v>강남대로</v>
       </c>
       <c r="C74" t="str">
-        <v>26-서초구-11</v>
+        <v>26-서초구-12</v>
       </c>
       <c r="D74" t="str">
         <v>양호</v>
@@ -4808,16 +4808,16 @@
         <v>일반</v>
       </c>
       <c r="P74" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q74" t="str">
-        <v>우성아파트앞 사거리</v>
+        <v>서초동1337-32</v>
       </c>
       <c r="R74" t="str">
         <v/>
       </c>
       <c r="S74" t="str">
-        <v>교차로(강남대로346-2)</v>
+        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
       </c>
       <c r="T74" t="str">
         <v/>
@@ -4825,13 +4825,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B75" t="str">
         <v>강남대로</v>
       </c>
       <c r="C75" t="str">
-        <v>26-서초구-12</v>
+        <v>26-서초구-13</v>
       </c>
       <c r="D75" t="str">
         <v>양호</v>
@@ -4870,16 +4870,16 @@
         <v>일반</v>
       </c>
       <c r="P75" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q75" t="str">
-        <v>서초동1337-32</v>
+        <v>서초동1337-31</v>
       </c>
       <c r="R75" t="str">
         <v/>
       </c>
       <c r="S75" t="str">
-        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
+        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
       </c>
       <c r="T75" t="str">
         <v/>
@@ -4887,13 +4887,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B76" t="str">
         <v>강남대로</v>
       </c>
       <c r="C76" t="str">
-        <v>26-서초구-13</v>
+        <v>26-서초구-14</v>
       </c>
       <c r="D76" t="str">
         <v>양호</v>
@@ -4935,13 +4935,13 @@
         <v>-</v>
       </c>
       <c r="Q76" t="str">
-        <v>서초동1337-31</v>
+        <v>서초동1337-20</v>
       </c>
       <c r="R76" t="str">
         <v/>
       </c>
       <c r="S76" t="str">
-        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
+        <v>대륭서초타워 앞 도로(강남대로327)</v>
       </c>
       <c r="T76" t="str">
         <v/>
@@ -4949,19 +4949,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B77" t="str">
         <v>강남대로</v>
       </c>
       <c r="C77" t="str">
-        <v>26-서초구-14</v>
+        <v>26-서초구-15</v>
       </c>
       <c r="D77" t="str">
         <v>양호</v>
       </c>
       <c r="E77" t="str">
-        <v>거북등</v>
+        <v>거북이</v>
       </c>
       <c r="F77" t="str">
         <v>양호</v>
@@ -4997,13 +4997,13 @@
         <v>-</v>
       </c>
       <c r="Q77" t="str">
-        <v>서초동1337-20</v>
+        <v>서초동1337-22</v>
       </c>
       <c r="R77" t="str">
         <v/>
       </c>
       <c r="S77" t="str">
-        <v>대륭서초타워 앞 도로(강남대로327)</v>
+        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
       </c>
       <c r="T77" t="str">
         <v/>
@@ -5011,19 +5011,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B78" t="str">
         <v>강남대로</v>
       </c>
       <c r="C78" t="str">
-        <v>26-서초구-15</v>
+        <v>26-서초구-16</v>
       </c>
       <c r="D78" t="str">
         <v>양호</v>
       </c>
       <c r="E78" t="str">
-        <v>거북이</v>
+        <v>거북등</v>
       </c>
       <c r="F78" t="str">
         <v>양호</v>
@@ -5059,13 +5059,13 @@
         <v>-</v>
       </c>
       <c r="Q78" t="str">
-        <v>서초동1337-22</v>
+        <v>서초동1338-23</v>
       </c>
       <c r="R78" t="str">
         <v/>
       </c>
       <c r="S78" t="str">
-        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
+        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
       </c>
       <c r="T78" t="str">
         <v/>
@@ -5073,13 +5073,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B79" t="str">
         <v>강남대로</v>
       </c>
       <c r="C79" t="str">
-        <v>26-서초구-16</v>
+        <v>26-서초구-17</v>
       </c>
       <c r="D79" t="str">
         <v>양호</v>
@@ -5121,13 +5121,13 @@
         <v>-</v>
       </c>
       <c r="Q79" t="str">
-        <v>서초동1338-23</v>
+        <v>서초동1338-12</v>
       </c>
       <c r="R79" t="str">
         <v/>
       </c>
       <c r="S79" t="str">
-        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
+        <v>코인노트 앞 도로(강남대로311)</v>
       </c>
       <c r="T79" t="str">
         <v/>
@@ -5135,13 +5135,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B80" t="str">
         <v>강남대로</v>
       </c>
       <c r="C80" t="str">
-        <v>26-서초구-17</v>
+        <v>26-서초구-18</v>
       </c>
       <c r="D80" t="str">
         <v>양호</v>
@@ -5183,13 +5183,13 @@
         <v>-</v>
       </c>
       <c r="Q80" t="str">
-        <v>서초동1338-12</v>
+        <v>서초동1338-21</v>
       </c>
       <c r="R80" t="str">
         <v/>
       </c>
       <c r="S80" t="str">
-        <v>코인노트 앞 도로(강남대로311)</v>
+        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
       </c>
       <c r="T80" t="str">
         <v/>
@@ -5197,13 +5197,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B81" t="str">
         <v>강남대로</v>
       </c>
       <c r="C81" t="str">
-        <v>26-서초구-18</v>
+        <v>26-서초구-19</v>
       </c>
       <c r="D81" t="str">
         <v>양호</v>
@@ -5245,13 +5245,13 @@
         <v>-</v>
       </c>
       <c r="Q81" t="str">
-        <v>서초동1338-21</v>
+        <v>서초동1338-20</v>
       </c>
       <c r="R81" t="str">
         <v/>
       </c>
       <c r="S81" t="str">
-        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
+        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
       </c>
       <c r="T81" t="str">
         <v/>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B82" t="str">
         <v>강남대로</v>
       </c>
       <c r="C82" t="str">
-        <v>26-서초구-19</v>
+        <v>26-서초구-20</v>
       </c>
       <c r="D82" t="str">
         <v>양호</v>
@@ -5307,13 +5307,13 @@
         <v>-</v>
       </c>
       <c r="Q82" t="str">
-        <v>서초동1338-20</v>
+        <v>서초동1339-9</v>
       </c>
       <c r="R82" t="str">
         <v/>
       </c>
       <c r="S82" t="str">
-        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
+        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
       </c>
       <c r="T82" t="str">
         <v/>
@@ -5321,13 +5321,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B83" t="str">
         <v>강남대로</v>
       </c>
       <c r="C83" t="str">
-        <v>26-서초구-20</v>
+        <v>26-서초구-21</v>
       </c>
       <c r="D83" t="str">
         <v>양호</v>
@@ -5369,13 +5369,13 @@
         <v>-</v>
       </c>
       <c r="Q83" t="str">
-        <v>서초동1339-9</v>
+        <v>서초동1340-6</v>
       </c>
       <c r="R83" t="str">
         <v/>
       </c>
       <c r="S83" t="str">
-        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
+        <v>남강빌딩 앞 도로(강남대로291)</v>
       </c>
       <c r="T83" t="str">
         <v/>
@@ -5383,13 +5383,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B84" t="str">
         <v>강남대로</v>
       </c>
       <c r="C84" t="str">
-        <v>26-서초구-21</v>
+        <v>26-서초구-22</v>
       </c>
       <c r="D84" t="str">
         <v>양호</v>
@@ -5431,13 +5431,13 @@
         <v>-</v>
       </c>
       <c r="Q84" t="str">
-        <v>서초동1340-6</v>
+        <v>서초동1357-10</v>
       </c>
       <c r="R84" t="str">
         <v/>
       </c>
       <c r="S84" t="str">
-        <v>남강빌딩 앞 도로(강남대로291)</v>
+        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
       </c>
       <c r="T84" t="str">
         <v/>
@@ -5445,19 +5445,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B85" t="str">
         <v>강남대로</v>
       </c>
       <c r="C85" t="str">
-        <v>26-서초구-22</v>
+        <v>26-서초구-23</v>
       </c>
       <c r="D85" t="str">
         <v>양호</v>
       </c>
       <c r="E85" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F85" t="str">
         <v>양호</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K85" t="str">
         <v>0</v>
@@ -5484,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="N85" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O85" t="str">
         <v>일반</v>
@@ -5493,13 +5493,13 @@
         <v>-</v>
       </c>
       <c r="Q85" t="str">
-        <v>서초동1357-10</v>
+        <v>서초동1357-66</v>
       </c>
       <c r="R85" t="str">
         <v/>
       </c>
       <c r="S85" t="str">
-        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
+        <v>메인타워 CU 앞 도로(강남대로275)</v>
       </c>
       <c r="T85" t="str">
         <v/>
@@ -5507,19 +5507,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B86" t="str">
         <v>강남대로</v>
       </c>
       <c r="C86" t="str">
-        <v>26-서초구-23</v>
+        <v>26-서초구-24</v>
       </c>
       <c r="D86" t="str">
         <v>양호</v>
       </c>
       <c r="E86" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F86" t="str">
         <v>양호</v>
@@ -5555,13 +5555,13 @@
         <v>-</v>
       </c>
       <c r="Q86" t="str">
-        <v>서초동1357-66</v>
+        <v>서초동1358-7</v>
       </c>
       <c r="R86" t="str">
         <v/>
       </c>
       <c r="S86" t="str">
-        <v>메인타워 CU 앞 도로(강남대로275)</v>
+        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
       </c>
       <c r="T86" t="str">
         <v/>
@@ -5569,19 +5569,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>26-24</v>
+        <v>26-25</v>
       </c>
       <c r="B87" t="str">
         <v>강남대로</v>
       </c>
       <c r="C87" t="str">
-        <v>26-서초구-24</v>
+        <v>26-서초구-25</v>
       </c>
       <c r="D87" t="str">
         <v>양호</v>
       </c>
       <c r="E87" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F87" t="str">
         <v>양호</v>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K87" t="str">
         <v>0</v>
@@ -5608,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="N87" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O87" t="str">
         <v>일반</v>
@@ -5617,13 +5617,13 @@
         <v>-</v>
       </c>
       <c r="Q87" t="str">
-        <v>서초동1358-7</v>
+        <v>양재역사거리</v>
       </c>
       <c r="R87" t="str">
         <v/>
       </c>
       <c r="S87" t="str">
-        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
+        <v>양재역 교차로(강남대로266-2)</v>
       </c>
       <c r="T87" t="str">
         <v/>
@@ -5631,13 +5631,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>26-25</v>
+        <v>26-26</v>
       </c>
       <c r="B88" t="str">
         <v>강남대로</v>
       </c>
       <c r="C88" t="str">
-        <v>26-서초구-25</v>
+        <v>26-서초구-26</v>
       </c>
       <c r="D88" t="str">
         <v>양호</v>
@@ -5679,13 +5679,13 @@
         <v>-</v>
       </c>
       <c r="Q88" t="str">
-        <v>양재역사거리</v>
+        <v>양재동23</v>
       </c>
       <c r="R88" t="str">
         <v/>
       </c>
       <c r="S88" t="str">
-        <v>양재역 교차로(강남대로266-2)</v>
+        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
       </c>
       <c r="T88" t="str">
         <v/>
@@ -5693,13 +5693,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>26-26</v>
+        <v>26-27</v>
       </c>
       <c r="B89" t="str">
         <v>강남대로</v>
       </c>
       <c r="C89" t="str">
-        <v>26-서초구-26</v>
+        <v>26-서초구-27</v>
       </c>
       <c r="D89" t="str">
         <v>양호</v>
@@ -5741,13 +5741,13 @@
         <v>-</v>
       </c>
       <c r="Q89" t="str">
-        <v>양재동23</v>
+        <v>양재동24</v>
       </c>
       <c r="R89" t="str">
         <v/>
       </c>
       <c r="S89" t="str">
-        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
+        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
       </c>
       <c r="T89" t="str">
         <v/>
@@ -5755,13 +5755,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>26-27</v>
+        <v>26-28</v>
       </c>
       <c r="B90" t="str">
         <v>강남대로</v>
       </c>
       <c r="C90" t="str">
-        <v>26-서초구-27</v>
+        <v>26-서초구-28</v>
       </c>
       <c r="D90" t="str">
         <v>양호</v>
@@ -5809,7 +5809,7 @@
         <v/>
       </c>
       <c r="S90" t="str">
-        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
+        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
       </c>
       <c r="T90" t="str">
         <v/>
@@ -5817,13 +5817,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>26-28</v>
+        <v>26-29</v>
       </c>
       <c r="B91" t="str">
         <v>강남대로</v>
       </c>
       <c r="C91" t="str">
-        <v>26-서초구-28</v>
+        <v>26-서초구-29</v>
       </c>
       <c r="D91" t="str">
         <v>양호</v>
@@ -5865,13 +5865,13 @@
         <v>-</v>
       </c>
       <c r="Q91" t="str">
-        <v>양재동24</v>
+        <v>양재동 산20-2</v>
       </c>
       <c r="R91" t="str">
         <v/>
       </c>
       <c r="S91" t="str">
-        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
+        <v>말죽거리공원 앞 도로(강남대로167)</v>
       </c>
       <c r="T91" t="str">
         <v/>
@@ -5879,19 +5879,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>26-29</v>
+        <v>26-30</v>
       </c>
       <c r="B92" t="str">
         <v>강남대로</v>
       </c>
       <c r="C92" t="str">
-        <v>26-서초구-29</v>
+        <v>26-서초구-30</v>
       </c>
       <c r="D92" t="str">
         <v>양호</v>
       </c>
       <c r="E92" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F92" t="str">
         <v>양호</v>
@@ -5906,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K92" t="str">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O92" t="str">
         <v>일반</v>
@@ -5927,13 +5927,13 @@
         <v>-</v>
       </c>
       <c r="Q92" t="str">
-        <v>양재동 산20-2</v>
+        <v>양재동67</v>
       </c>
       <c r="R92" t="str">
         <v/>
       </c>
       <c r="S92" t="str">
-        <v>말죽거리공원 앞 도로(강남대로167)</v>
+        <v>혜인빌딩 앞 도로(163)</v>
       </c>
       <c r="T92" t="str">
         <v/>
@@ -5941,19 +5941,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>26-30</v>
+        <v>26-31</v>
       </c>
       <c r="B93" t="str">
         <v>강남대로</v>
       </c>
       <c r="C93" t="str">
-        <v>26-서초구-30</v>
+        <v>26-서초구-31</v>
       </c>
       <c r="D93" t="str">
         <v>양호</v>
       </c>
       <c r="E93" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F93" t="str">
         <v>양호</v>
@@ -5968,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K93" t="str">
         <v>0</v>
@@ -5980,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O93" t="str">
         <v>일반</v>
@@ -5989,13 +5989,13 @@
         <v>-</v>
       </c>
       <c r="Q93" t="str">
-        <v>양재동67</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R93" t="str">
         <v/>
       </c>
       <c r="S93" t="str">
-        <v>혜인빌딩 앞 도로(163)</v>
+        <v>말죽거리공원 교차로(양재동20-40)</v>
       </c>
       <c r="T93" t="str">
         <v/>
@@ -6003,19 +6003,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>26-31</v>
+        <v>26-32</v>
       </c>
       <c r="B94" t="str">
         <v>강남대로</v>
       </c>
       <c r="C94" t="str">
-        <v>26-서초구-31</v>
+        <v>26-서초구-32</v>
       </c>
       <c r="D94" t="str">
         <v>양호</v>
       </c>
       <c r="E94" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F94" t="str">
         <v>양호</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K94" t="str">
         <v>0</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="N94" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O94" t="str">
         <v>일반</v>
@@ -6051,13 +6051,13 @@
         <v>-</v>
       </c>
       <c r="Q94" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동125</v>
       </c>
       <c r="R94" t="str">
         <v/>
       </c>
       <c r="S94" t="str">
-        <v>말죽거리공원 교차로(양재동20-40)</v>
+        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
       </c>
       <c r="T94" t="str">
         <v/>
@@ -6065,19 +6065,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>26-32</v>
+        <v>26-33</v>
       </c>
       <c r="B95" t="str">
         <v>강남대로</v>
       </c>
       <c r="C95" t="str">
-        <v>26-서초구-32</v>
+        <v>26-서초구-33</v>
       </c>
       <c r="D95" t="str">
         <v>양호</v>
       </c>
       <c r="E95" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F95" t="str">
         <v>양호</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K95" t="str">
         <v>0</v>
@@ -6104,7 +6104,7 @@
         <v>0</v>
       </c>
       <c r="N95" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O95" t="str">
         <v>일반</v>
@@ -6113,13 +6113,13 @@
         <v>-</v>
       </c>
       <c r="Q95" t="str">
-        <v>양재동125</v>
+        <v>양재동80-3</v>
       </c>
       <c r="R95" t="str">
         <v/>
       </c>
       <c r="S95" t="str">
-        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
+        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
       </c>
       <c r="T95" t="str">
         <v/>
@@ -6127,13 +6127,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>26-33</v>
+        <v>26-34</v>
       </c>
       <c r="B96" t="str">
         <v>강남대로</v>
       </c>
       <c r="C96" t="str">
-        <v>26-서초구-33</v>
+        <v>26-서초구-34</v>
       </c>
       <c r="D96" t="str">
         <v>양호</v>
@@ -6175,13 +6175,13 @@
         <v>-</v>
       </c>
       <c r="Q96" t="str">
-        <v>양재동80-3</v>
+        <v>매헌시민의숲사거리</v>
       </c>
       <c r="R96" t="str">
         <v/>
       </c>
       <c r="S96" t="str">
-        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
+        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
       </c>
       <c r="T96" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>26-34</v>
+        <v>26-35</v>
       </c>
       <c r="B97" t="str">
         <v>강남대로</v>
       </c>
       <c r="C97" t="str">
-        <v>26-서초구-34</v>
+        <v>26-서초구-35</v>
       </c>
       <c r="D97" t="str">
         <v>양호</v>
@@ -6237,13 +6237,13 @@
         <v>-</v>
       </c>
       <c r="Q97" t="str">
-        <v>매헌시민의숲사거리</v>
+        <v>양재동237</v>
       </c>
       <c r="R97" t="str">
         <v/>
       </c>
       <c r="S97" t="str">
-        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
+        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
       </c>
       <c r="T97" t="str">
         <v/>
@@ -6251,13 +6251,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>26-35</v>
+        <v>26-36</v>
       </c>
       <c r="B98" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C98" t="str">
-        <v>26-서초구-35</v>
+        <v>26-서초구-36</v>
       </c>
       <c r="D98" t="str">
         <v>양호</v>
@@ -6299,13 +6299,13 @@
         <v>-</v>
       </c>
       <c r="Q98" t="str">
-        <v>양재동237</v>
+        <v>양재동237-2</v>
       </c>
       <c r="R98" t="str">
         <v/>
       </c>
       <c r="S98" t="str">
-        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
+        <v>매헌역 공영주차장 입구 앞 도로</v>
       </c>
       <c r="T98" t="str">
         <v/>
@@ -6313,13 +6313,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>26-36</v>
+        <v>26-37</v>
       </c>
       <c r="B99" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C99" t="str">
-        <v>26-서초구-36</v>
+        <v>26-서초구-37</v>
       </c>
       <c r="D99" t="str">
         <v>양호</v>
@@ -6361,13 +6361,13 @@
         <v>-</v>
       </c>
       <c r="Q99" t="str">
-        <v>양재동237-2</v>
+        <v>신원동308-1</v>
       </c>
       <c r="R99" t="str">
         <v/>
       </c>
       <c r="S99" t="str">
-        <v>매헌역 공영주차장 입구 앞 도로</v>
+        <v>가로등(청계산로69)_양차선</v>
       </c>
       <c r="T99" t="str">
         <v/>
@@ -6375,13 +6375,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>26-37</v>
+        <v>26-38</v>
       </c>
       <c r="B100" t="str">
         <v>청계산로</v>
       </c>
       <c r="C100" t="str">
-        <v>26-서초구-37</v>
+        <v>26-서초구-38</v>
       </c>
       <c r="D100" t="str">
         <v>양호</v>
@@ -6423,13 +6423,13 @@
         <v>-</v>
       </c>
       <c r="Q100" t="str">
-        <v>신원동308-1</v>
+        <v>신원동298-16</v>
       </c>
       <c r="R100" t="str">
         <v/>
       </c>
       <c r="S100" t="str">
-        <v>가로등(청계산로69)_양차선</v>
+        <v>청계산 수변공원 앞 도로_양차선</v>
       </c>
       <c r="T100" t="str">
         <v/>
@@ -6437,13 +6437,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>26-38</v>
+        <v>26-39</v>
       </c>
       <c r="B101" t="str">
         <v>청계산로</v>
       </c>
       <c r="C101" t="str">
-        <v>26-서초구-38</v>
+        <v>26-서초구-39</v>
       </c>
       <c r="D101" t="str">
         <v>양호</v>
@@ -6491,7 +6491,7 @@
         <v/>
       </c>
       <c r="S101" t="str">
-        <v>청계산 수변공원 앞 도로_양차선</v>
+        <v>가로등(청계산로81)앞도로_양차선</v>
       </c>
       <c r="T101" t="str">
         <v/>
@@ -6499,13 +6499,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>26-39</v>
+        <v>26-40</v>
       </c>
       <c r="B102" t="str">
         <v>청계산로</v>
       </c>
       <c r="C102" t="str">
-        <v>26-서초구-39</v>
+        <v>26-서초구-40</v>
       </c>
       <c r="D102" t="str">
         <v>양호</v>
@@ -6544,16 +6544,16 @@
         <v>일반</v>
       </c>
       <c r="P102" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q102" t="str">
-        <v>신원동298-16</v>
+        <v>원지동595</v>
       </c>
       <c r="R102" t="str">
         <v/>
       </c>
       <c r="S102" t="str">
-        <v>가로등(청계산로81)앞도로_양차선</v>
+        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
       </c>
       <c r="T102" t="str">
         <v/>
@@ -6561,13 +6561,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>26-40</v>
+        <v>26-41</v>
       </c>
       <c r="B103" t="str">
         <v>청계산로</v>
       </c>
       <c r="C103" t="str">
-        <v>26-서초구-40</v>
+        <v>26-서초구-41</v>
       </c>
       <c r="D103" t="str">
         <v>양호</v>
@@ -6606,16 +6606,16 @@
         <v>일반</v>
       </c>
       <c r="P103" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q103" t="str">
-        <v>원지동595</v>
+        <v>신원동280-1</v>
       </c>
       <c r="R103" t="str">
         <v/>
       </c>
       <c r="S103" t="str">
-        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
+        <v>교차로(T)_양차선</v>
       </c>
       <c r="T103" t="str">
         <v/>
@@ -6623,13 +6623,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>26-41</v>
+        <v>26-42</v>
       </c>
       <c r="B104" t="str">
         <v>청계산로</v>
       </c>
       <c r="C104" t="str">
-        <v>26-서초구-41</v>
+        <v>26-서초구-42</v>
       </c>
       <c r="D104" t="str">
         <v>양호</v>
@@ -6671,13 +6671,13 @@
         <v>-</v>
       </c>
       <c r="Q104" t="str">
-        <v>신원동280-1</v>
+        <v>신원동278-6</v>
       </c>
       <c r="R104" t="str">
         <v/>
       </c>
       <c r="S104" t="str">
-        <v>교차로(T)_양차선</v>
+        <v>버스정류장 앞 양차선</v>
       </c>
       <c r="T104" t="str">
         <v/>
@@ -6685,13 +6685,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>26-42</v>
+        <v>26-43</v>
       </c>
       <c r="B105" t="str">
         <v>청계산로</v>
       </c>
       <c r="C105" t="str">
-        <v>26-서초구-42</v>
+        <v>26-서초구-43</v>
       </c>
       <c r="D105" t="str">
         <v>양호</v>
@@ -6730,16 +6730,16 @@
         <v>일반</v>
       </c>
       <c r="P105" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q105" t="str">
-        <v>신원동278-6</v>
+        <v>신원동604</v>
       </c>
       <c r="R105" t="str">
         <v/>
       </c>
       <c r="S105" t="str">
-        <v>버스정류장 앞 양차선</v>
+        <v>오라카이 호텔 맞음편 도로 우수,전기맨홀(청계산로9길1-7)</v>
       </c>
       <c r="T105" t="str">
         <v/>
@@ -6747,13 +6747,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>26-43</v>
+        <v>26-44</v>
       </c>
       <c r="B106" t="str">
         <v>청계산로</v>
       </c>
       <c r="C106" t="str">
-        <v>26-서초구-43</v>
+        <v>26-서초구-44</v>
       </c>
       <c r="D106" t="str">
         <v>양호</v>
@@ -6792,16 +6792,16 @@
         <v>일반</v>
       </c>
       <c r="P106" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q106" t="str">
-        <v>신원동604</v>
+        <v>신원동607</v>
       </c>
       <c r="R106" t="str">
         <v/>
       </c>
       <c r="S106" t="str">
-        <v>오라카이 호텔 맞음편 도로 우수,전기맨홀(청계산로9길1-7)</v>
+        <v>내곡드림시티2 펀비어킹 앞 도로(청계산로189)</v>
       </c>
       <c r="T106" t="str">
         <v/>
@@ -6809,13 +6809,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>26-44</v>
+        <v>26-45</v>
       </c>
       <c r="B107" t="str">
         <v>청계산로</v>
       </c>
       <c r="C107" t="str">
-        <v>26-서초구-44</v>
+        <v>26-서초구-45</v>
       </c>
       <c r="D107" t="str">
         <v>양호</v>
@@ -6857,13 +6857,13 @@
         <v>-</v>
       </c>
       <c r="Q107" t="str">
-        <v>신원동607</v>
+        <v>신원동609</v>
       </c>
       <c r="R107" t="str">
         <v/>
       </c>
       <c r="S107" t="str">
-        <v>내곡드림시티2 펀비어킹 앞 도로(청계산로189)</v>
+        <v>내곡프라임시티 앞도로(청계산로195)</v>
       </c>
       <c r="T107" t="str">
         <v/>
@@ -6871,13 +6871,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>26-45</v>
+        <v>26-46</v>
       </c>
       <c r="B108" t="str">
         <v>청계산로</v>
       </c>
       <c r="C108" t="str">
-        <v>26-서초구-45</v>
+        <v>26-서초구-46</v>
       </c>
       <c r="D108" t="str">
         <v>양호</v>
@@ -6919,13 +6919,13 @@
         <v>-</v>
       </c>
       <c r="Q108" t="str">
-        <v>신원동609</v>
+        <v>신원동611</v>
       </c>
       <c r="R108" t="str">
         <v/>
       </c>
       <c r="S108" t="str">
-        <v>내곡프라임시티 앞도로(청계산로195)</v>
+        <v>서초포레지움 투썸플레이스 앞 양차선(청계산로201)</v>
       </c>
       <c r="T108" t="str">
         <v/>
@@ -6933,13 +6933,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>26-46</v>
+        <v>26-47</v>
       </c>
       <c r="B109" t="str">
         <v>청계산로</v>
       </c>
       <c r="C109" t="str">
-        <v>26-서초구-46</v>
+        <v>26-서초구-47</v>
       </c>
       <c r="D109" t="str">
         <v>양호</v>
@@ -6978,16 +6978,16 @@
         <v>일반</v>
       </c>
       <c r="P109" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q109" t="str">
-        <v>신원동611</v>
+        <v>원지동362-1</v>
       </c>
       <c r="R109" t="str">
         <v/>
       </c>
       <c r="S109" t="str">
-        <v>서초포레지움 투썸플레이스 앞 양차선(청계산로201)</v>
+        <v>청계쉼터 앞 도로</v>
       </c>
       <c r="T109" t="str">
         <v/>
@@ -6995,13 +6995,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>26-47</v>
+        <v>26-48</v>
       </c>
       <c r="B110" t="str">
         <v>청계산로</v>
       </c>
       <c r="C110" t="str">
-        <v>26-서초구-47</v>
+        <v>26-서초구-48</v>
       </c>
       <c r="D110" t="str">
         <v>양호</v>
@@ -7040,16 +7040,16 @@
         <v>일반</v>
       </c>
       <c r="P110" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q110" t="str">
-        <v>원지동362-1</v>
+        <v>원지동384-1</v>
       </c>
       <c r="R110" t="str">
         <v/>
       </c>
       <c r="S110" t="str">
-        <v>청계쉼터 앞 도로</v>
+        <v>청계산커피 앞 양차선</v>
       </c>
       <c r="T110" t="str">
         <v/>
@@ -7057,13 +7057,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>26-48</v>
+        <v>26-49</v>
       </c>
       <c r="B111" t="str">
         <v>청계산로</v>
       </c>
       <c r="C111" t="str">
-        <v>26-서초구-48</v>
+        <v>26-서초구-49</v>
       </c>
       <c r="D111" t="str">
         <v>양호</v>
@@ -7105,13 +7105,13 @@
         <v>-</v>
       </c>
       <c r="Q111" t="str">
-        <v>원지동384-1</v>
+        <v>신원동192-75</v>
       </c>
       <c r="R111" t="str">
         <v/>
       </c>
       <c r="S111" t="str">
-        <v>청계산커피 앞 양차선</v>
+        <v>강경불고기_청계 앞 양차선(청계산로245)</v>
       </c>
       <c r="T111" t="str">
         <v/>
@@ -7119,13 +7119,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>26-49</v>
+        <v>26-50</v>
       </c>
       <c r="B112" t="str">
         <v>청계산로</v>
       </c>
       <c r="C112" t="str">
-        <v>26-서초구-49</v>
+        <v>26-서초구-50</v>
       </c>
       <c r="D112" t="str">
         <v>양호</v>
@@ -7164,16 +7164,16 @@
         <v>일반</v>
       </c>
       <c r="P112" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q112" t="str">
-        <v>신원동192-75</v>
+        <v>신원동173-1</v>
       </c>
       <c r="R112" t="str">
         <v/>
       </c>
       <c r="S112" t="str">
-        <v>강경불고기_청계 앞 양차선(청계산로245)</v>
+        <v>향린조경 앞 양차선(고속도로방면침하)</v>
       </c>
       <c r="T112" t="str">
         <v/>
@@ -7181,13 +7181,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>26-50</v>
+        <v>26-51</v>
       </c>
       <c r="B113" t="str">
         <v>청계산로</v>
       </c>
       <c r="C113" t="str">
-        <v>26-서초구-50</v>
+        <v>26-서초구-51</v>
       </c>
       <c r="D113" t="str">
         <v>양호</v>
@@ -7229,13 +7229,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q113" t="str">
-        <v>신원동173-1</v>
+        <v>신원동152-12</v>
       </c>
       <c r="R113" t="str">
         <v/>
       </c>
       <c r="S113" t="str">
-        <v>향린조경 앞 양차선(고속도로방면침하)</v>
+        <v>삼석원 앞 양차선(고속도로방면 침하)</v>
       </c>
       <c r="T113" t="str">
         <v/>
@@ -7243,13 +7243,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>26-51</v>
+        <v>26-52</v>
       </c>
       <c r="B114" t="str">
         <v>청계산로</v>
       </c>
       <c r="C114" t="str">
-        <v>26-서초구-51</v>
+        <v>26-서초구-52</v>
       </c>
       <c r="D114" t="str">
         <v>양호</v>
@@ -7291,13 +7291,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q114" t="str">
-        <v>신원동152-12</v>
+        <v>신원동148-3</v>
       </c>
       <c r="R114" t="str">
         <v/>
       </c>
       <c r="S114" t="str">
-        <v>삼석원 앞 양차선(고속도로방면 침하)</v>
+        <v>은평조경 앞 양차선(고속도로방면 침하)(청계산로283-8)</v>
       </c>
       <c r="T114" t="str">
         <v/>
@@ -7305,13 +7305,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>26-52</v>
+        <v>26-53</v>
       </c>
       <c r="B115" t="str">
         <v>청계산로</v>
       </c>
       <c r="C115" t="str">
-        <v>26-서초구-52</v>
+        <v>26-서초구-53</v>
       </c>
       <c r="D115" t="str">
         <v>양호</v>
@@ -7353,13 +7353,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q115" t="str">
-        <v>신원동148-3</v>
+        <v>원지동490-3</v>
       </c>
       <c r="R115" t="str">
         <v/>
       </c>
       <c r="S115" t="str">
-        <v>은평조경 앞 양차선(고속도로방면 침하)(청계산로283-8)</v>
+        <v>인화원 앞 양차선(고속도로방면 침하)(가로등_청계산로161)</v>
       </c>
       <c r="T115" t="str">
         <v/>
@@ -7367,13 +7367,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>26-53</v>
+        <v>26-54</v>
       </c>
       <c r="B116" t="str">
         <v>청계산로</v>
       </c>
       <c r="C116" t="str">
-        <v>26-서초구-53</v>
+        <v>26-서초구-54</v>
       </c>
       <c r="D116" t="str">
         <v>양호</v>
@@ -7415,13 +7415,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q116" t="str">
-        <v>원지동490-3</v>
+        <v>원지동490</v>
       </c>
       <c r="R116" t="str">
         <v/>
       </c>
       <c r="S116" t="str">
-        <v>인화원 앞 양차선(고속도로방면 침하)(가로등_청계산로161)</v>
+        <v>양재조경 앞 양차선(고속도로방면 침하)_(가로등_청계산로165)</v>
       </c>
       <c r="T116" t="str">
         <v/>
@@ -7429,13 +7429,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>26-54</v>
+        <v>26-55</v>
       </c>
       <c r="B117" t="str">
         <v>청계산로</v>
       </c>
       <c r="C117" t="str">
-        <v>26-서초구-54</v>
+        <v>26-서초구-55</v>
       </c>
       <c r="D117" t="str">
         <v>양호</v>
@@ -7477,13 +7477,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q117" t="str">
-        <v>원지동490</v>
+        <v>원지동495-5</v>
       </c>
       <c r="R117" t="str">
         <v/>
       </c>
       <c r="S117" t="str">
-        <v>양재조경 앞 양차선(고속도로방면 침하)_(가로등_청계산로165)</v>
+        <v>화림조경간판 앞 양차선(가로등_청계산로167)</v>
       </c>
       <c r="T117" t="str">
         <v/>
@@ -7491,13 +7491,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>26-55</v>
+        <v>26-56</v>
       </c>
       <c r="B118" t="str">
         <v>청계산로</v>
       </c>
       <c r="C118" t="str">
-        <v>26-서초구-55</v>
+        <v>26-서초구-56</v>
       </c>
       <c r="D118" t="str">
         <v>양호</v>
@@ -7536,16 +7536,16 @@
         <v>일반</v>
       </c>
       <c r="P118" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q118" t="str">
-        <v>원지동495-5</v>
+        <v>원지동495-6</v>
       </c>
       <c r="R118" t="str">
         <v/>
       </c>
       <c r="S118" t="str">
-        <v>화림조경간판 앞 양차선(가로등_청계산로167)</v>
+        <v>(가로등_청계산로171)</v>
       </c>
       <c r="T118" t="str">
         <v/>
@@ -7553,19 +7553,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>26-56</v>
+        <v>26-57</v>
       </c>
       <c r="B119" t="str">
         <v>청계산로</v>
       </c>
       <c r="C119" t="str">
-        <v>26-서초구-56</v>
+        <v>26-서초구-57</v>
       </c>
       <c r="D119" t="str">
         <v>양호</v>
       </c>
       <c r="E119" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F119" t="str">
         <v>양호</v>
@@ -7580,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K119" t="str">
         <v>0</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="N119" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O119" t="str">
         <v>일반</v>
@@ -7601,13 +7601,13 @@
         <v>-</v>
       </c>
       <c r="Q119" t="str">
-        <v>원지동495-6</v>
+        <v>원지동497-3</v>
       </c>
       <c r="R119" t="str">
         <v/>
       </c>
       <c r="S119" t="str">
-        <v>(가로등_청계산로171)</v>
+        <v>(가로등_청계산로313)</v>
       </c>
       <c r="T119" t="str">
         <v/>
@@ -7615,19 +7615,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>26-57</v>
+        <v>26-58</v>
       </c>
       <c r="B120" t="str">
         <v>청계산로</v>
       </c>
       <c r="C120" t="str">
-        <v>26-서초구-57</v>
+        <v>26-서초구-58</v>
       </c>
       <c r="D120" t="str">
         <v>양호</v>
       </c>
       <c r="E120" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F120" t="str">
         <v>양호</v>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K120" t="str">
         <v>0</v>
@@ -7654,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="N120" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O120" t="str">
         <v>일반</v>
@@ -7663,13 +7663,13 @@
         <v>-</v>
       </c>
       <c r="Q120" t="str">
-        <v>원지동497-3</v>
+        <v>원지동575-1</v>
       </c>
       <c r="R120" t="str">
         <v/>
       </c>
       <c r="S120" t="str">
-        <v>(가로등_청계산로313)</v>
+        <v>(가로등_청계산로321)</v>
       </c>
       <c r="T120" t="str">
         <v/>
@@ -7677,19 +7677,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>26-58</v>
+        <v>26-59</v>
       </c>
       <c r="B121" t="str">
         <v>청계산로</v>
       </c>
       <c r="C121" t="str">
-        <v>26-서초구-58</v>
+        <v>26-서초구-59</v>
       </c>
       <c r="D121" t="str">
         <v>양호</v>
       </c>
       <c r="E121" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F121" t="str">
         <v>양호</v>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="J121" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K121" t="str">
         <v>0</v>
@@ -7716,7 +7716,7 @@
         <v>0</v>
       </c>
       <c r="N121" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O121" t="str">
         <v>일반</v>
@@ -7725,13 +7725,13 @@
         <v>-</v>
       </c>
       <c r="Q121" t="str">
-        <v>원지동575-1</v>
+        <v>원지동523-2</v>
       </c>
       <c r="R121" t="str">
         <v/>
       </c>
       <c r="S121" t="str">
-        <v>(가로등_청계산로321)</v>
+        <v>둥지조경 앞 도로(가로등_청계산로329)</v>
       </c>
       <c r="T121" t="str">
         <v/>
@@ -7739,19 +7739,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>26-59</v>
+        <v>26-60</v>
       </c>
       <c r="B122" t="str">
         <v>청계산로</v>
       </c>
       <c r="C122" t="str">
-        <v>26-서초구-59</v>
+        <v>26-서초구-60</v>
       </c>
       <c r="D122" t="str">
         <v>양호</v>
       </c>
       <c r="E122" t="str">
-        <v>종균열</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F122" t="str">
         <v>양호</v>
@@ -7787,13 +7787,13 @@
         <v>-</v>
       </c>
       <c r="Q122" t="str">
-        <v>원지동523-2</v>
+        <v>신원동산60-2</v>
       </c>
       <c r="R122" t="str">
         <v/>
       </c>
       <c r="S122" t="str">
-        <v>둥지조경 앞 도로(가로등_청계산로329)</v>
+        <v>대원조경 앞 양차선(가로등_청계산로181)</v>
       </c>
       <c r="T122" t="str">
         <v/>
@@ -7801,19 +7801,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>26-60</v>
+        <v>26-61</v>
       </c>
       <c r="B123" t="str">
         <v>청계산로</v>
       </c>
       <c r="C123" t="str">
-        <v>26-서초구-60</v>
+        <v>26-서초구-61</v>
       </c>
       <c r="D123" t="str">
         <v>양호</v>
       </c>
       <c r="E123" t="str">
-        <v>종,횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F123" t="str">
         <v>양호</v>
@@ -7828,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="J123" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K123" t="str">
         <v>0</v>
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="N123" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O123" t="str">
         <v>일반</v>
@@ -7849,13 +7849,13 @@
         <v>-</v>
       </c>
       <c r="Q123" t="str">
-        <v>신원동산60-2</v>
+        <v>신원동103</v>
       </c>
       <c r="R123" t="str">
         <v/>
       </c>
       <c r="S123" t="str">
-        <v>대원조경 앞 양차선(가로등_청계산로181)</v>
+        <v>둥지조경제2농장 앞 양차선(고속도로방면 침하)</v>
       </c>
       <c r="T123" t="str">
         <v/>
@@ -7863,13 +7863,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>26-61</v>
+        <v>26-62</v>
       </c>
       <c r="B124" t="str">
         <v>청계산로</v>
       </c>
       <c r="C124" t="str">
-        <v>26-서초구-61</v>
+        <v>26-서초구-62</v>
       </c>
       <c r="D124" t="str">
         <v>양호</v>
@@ -7911,13 +7911,13 @@
         <v>-</v>
       </c>
       <c r="Q124" t="str">
-        <v>신원동103</v>
+        <v>신원동105-33</v>
       </c>
       <c r="R124" t="str">
         <v/>
       </c>
       <c r="S124" t="str">
-        <v>둥지조경제2농장 앞 양차선(고속도로방면 침하)</v>
+        <v>한백자생식물원 앞 양차선(청계산로353)</v>
       </c>
       <c r="T124" t="str">
         <v/>
@@ -7925,13 +7925,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>26-62</v>
+        <v>26-63</v>
       </c>
       <c r="B125" t="str">
         <v>청계산로</v>
       </c>
       <c r="C125" t="str">
-        <v>26-서초구-62</v>
+        <v>26-서초구-63</v>
       </c>
       <c r="D125" t="str">
         <v>양호</v>
@@ -7970,30 +7970,30 @@
         <v>일반</v>
       </c>
       <c r="P125" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q125" t="str">
-        <v>신원동105-33</v>
+        <v>신원동98-3</v>
       </c>
       <c r="R125" t="str">
         <v/>
       </c>
       <c r="S125" t="str">
-        <v>한백자생식물원 앞 양차선(청계산로353)</v>
+        <v>양차선(가로둥_청계산로193)</v>
       </c>
       <c r="T125" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>26-63</v>
+        <v>26-64</v>
       </c>
       <c r="B126" t="str">
         <v>청계산로</v>
       </c>
       <c r="C126" t="str">
-        <v>26-서초구-63</v>
+        <v>26-서초구-64</v>
       </c>
       <c r="D126" t="str">
         <v>양호</v>
@@ -8035,27 +8035,27 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q126" t="str">
-        <v>신원동98-3</v>
+        <v>신원동44-1</v>
       </c>
       <c r="R126" t="str">
         <v/>
       </c>
       <c r="S126" t="str">
-        <v>양차선(가로둥_청계산로193)</v>
+        <v>새정이마을입구 앞 양차선</v>
       </c>
       <c r="T126" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>26-64</v>
+        <v>26-65</v>
       </c>
       <c r="B127" t="str">
         <v>청계산로</v>
       </c>
       <c r="C127" t="str">
-        <v>26-서초구-64</v>
+        <v>26-서초구-65</v>
       </c>
       <c r="D127" t="str">
         <v>양호</v>
@@ -8094,24 +8094,396 @@
         <v>일반</v>
       </c>
       <c r="P127" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q127" t="str">
+        <v>신원동44-5</v>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v>강남꽃직매장 앞 도로(청계산로377)</v>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>26-66</v>
+      </c>
+      <c r="B128" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C128" t="str">
+        <v>26-서초구-66</v>
+      </c>
+      <c r="D128" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E128" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F128" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G128" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H128" t="str">
+        <v>-</v>
+      </c>
+      <c r="I128" t="str">
+        <v>0</v>
+      </c>
+      <c r="J128" t="str">
+        <v>3</v>
+      </c>
+      <c r="K128" t="str">
+        <v>0</v>
+      </c>
+      <c r="L128" t="str">
+        <v>1</v>
+      </c>
+      <c r="M128" t="str">
+        <v>0</v>
+      </c>
+      <c r="N128" t="str">
+        <v>4</v>
+      </c>
+      <c r="O128" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P128" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q128" t="str">
+        <v>신원동44-6</v>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v>들꽃 입구 앞 도로</v>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>26-67</v>
+      </c>
+      <c r="B129" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C129" t="str">
+        <v>26-서초구-67</v>
+      </c>
+      <c r="D129" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E129" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F129" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G129" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H129" t="str">
+        <v>-</v>
+      </c>
+      <c r="I129" t="str">
+        <v>0</v>
+      </c>
+      <c r="J129" t="str">
+        <v>3</v>
+      </c>
+      <c r="K129" t="str">
+        <v>0</v>
+      </c>
+      <c r="L129" t="str">
+        <v>1</v>
+      </c>
+      <c r="M129" t="str">
+        <v>0</v>
+      </c>
+      <c r="N129" t="str">
+        <v>4</v>
+      </c>
+      <c r="O129" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P129" t="str">
         <v>5cm이하 침하</v>
       </c>
-      <c r="Q127" t="str">
+      <c r="Q129" t="str">
         <v>신원동44-32</v>
       </c>
-      <c r="R127" t="str">
-        <v/>
-      </c>
-      <c r="S127" t="str">
-        <v>직접입력</v>
-      </c>
-      <c r="T127" t="str">
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v>입구 앞 도로(가로등_청계산로385)</v>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>26-68</v>
+      </c>
+      <c r="B130" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C130" t="str">
+        <v>26-서초구-68</v>
+      </c>
+      <c r="D130" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E130" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F130" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G130" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H130" t="str">
+        <v>-</v>
+      </c>
+      <c r="I130" t="str">
+        <v>0</v>
+      </c>
+      <c r="J130" t="str">
+        <v>3</v>
+      </c>
+      <c r="K130" t="str">
+        <v>0</v>
+      </c>
+      <c r="L130" t="str">
+        <v>1</v>
+      </c>
+      <c r="M130" t="str">
+        <v>0</v>
+      </c>
+      <c r="N130" t="str">
+        <v>4</v>
+      </c>
+      <c r="O130" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P130" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q130" t="str">
+        <v>신원동46-3</v>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v>은하조경 앞 양차선</v>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>26-69</v>
+      </c>
+      <c r="B131" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C131" t="str">
+        <v>26-서초구-69</v>
+      </c>
+      <c r="D131" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E131" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F131" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G131" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H131" t="str">
+        <v>-</v>
+      </c>
+      <c r="I131" t="str">
+        <v>0</v>
+      </c>
+      <c r="J131" t="str">
+        <v>3</v>
+      </c>
+      <c r="K131" t="str">
+        <v>0</v>
+      </c>
+      <c r="L131" t="str">
+        <v>1</v>
+      </c>
+      <c r="M131" t="str">
+        <v>0</v>
+      </c>
+      <c r="N131" t="str">
+        <v>4</v>
+      </c>
+      <c r="O131" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P131" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q131" t="str">
+        <v>신원동57</v>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v>서광원예종묘 앞 양차선(청계산로397)</v>
+      </c>
+      <c r="T131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>26-70</v>
+      </c>
+      <c r="B132" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C132" t="str">
+        <v>26-서초구-70</v>
+      </c>
+      <c r="D132" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E132" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F132" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G132" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H132" t="str">
+        <v>-</v>
+      </c>
+      <c r="I132" t="str">
+        <v>0</v>
+      </c>
+      <c r="J132" t="str">
+        <v>3</v>
+      </c>
+      <c r="K132" t="str">
+        <v>0</v>
+      </c>
+      <c r="L132" t="str">
+        <v>1</v>
+      </c>
+      <c r="M132" t="str">
+        <v>0</v>
+      </c>
+      <c r="N132" t="str">
+        <v>4</v>
+      </c>
+      <c r="O132" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P132" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q132" t="str">
+        <v>신원동64-1</v>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v>옥천조경 앞 양차선(청계산로405)</v>
+      </c>
+      <c r="T132" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>26-71</v>
+      </c>
+      <c r="B133" t="str">
+        <v>청계산로</v>
+      </c>
+      <c r="C133" t="str">
+        <v>26-서초구-71</v>
+      </c>
+      <c r="D133" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E133" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F133" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G133" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H133" t="str">
+        <v>-</v>
+      </c>
+      <c r="I133" t="str">
+        <v>0</v>
+      </c>
+      <c r="J133" t="str">
+        <v>3</v>
+      </c>
+      <c r="K133" t="str">
+        <v>0</v>
+      </c>
+      <c r="L133" t="str">
+        <v>1</v>
+      </c>
+      <c r="M133" t="str">
+        <v>0</v>
+      </c>
+      <c r="N133" t="str">
+        <v>4</v>
+      </c>
+      <c r="O133" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P133" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q133" t="str">
+        <v>신원동67-1</v>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v>마당조경 앞 양찬선</v>
+      </c>
+      <c r="T133" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T127"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T133"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-서초구-보고서.xlsx
+++ b/25-신분당-서초구-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T133"/>
+  <dimension ref="A1:T132"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="str">
         <v>강남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-서초구-7</v>
+        <v>25-서초구-8</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -530,16 +530,16 @@
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
-        <v>서초동 1328-11</v>
+        <v>서초동 1329</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>도씨의 빛Ⅱ 앞 도로</v>
+        <v>삼성화제 앞 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="str">
         <v>강남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-서초구-8</v>
+        <v>25-서초구-9</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -592,16 +592,16 @@
         <v>일반</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q6" t="str">
-        <v>서초동 1329</v>
+        <v>서초동 1329-7</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>삼성화제 앞 도로</v>
+        <v>신한투자증권 앞 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="str">
         <v>강남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-서초구-9</v>
+        <v>25-서초구-10</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -657,13 +657,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q7" t="str">
-        <v>서초동 1329-7</v>
+        <v>서초동 1329-8</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>신한투자증권 앞 도로</v>
+        <v>모닝글로리 앞 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="str">
         <v>강남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-서초구-10</v>
+        <v>25-서초구-11</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -716,16 +716,16 @@
         <v>일반</v>
       </c>
       <c r="P8" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q8" t="str">
-        <v>서초동 1329-8</v>
+        <v>서초동 1329-10</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>모닝글로리 앞 도로</v>
+        <v>우성아파트 사거리 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="str">
         <v>강남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-서초구-11</v>
+        <v>25-서초구-12</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -778,16 +778,16 @@
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q9" t="str">
-        <v>서초동 1329-10</v>
+        <v>서초동 1337-32</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>우성아파트 사거리 도로</v>
+        <v>한국투자증권 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="str">
         <v>강남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-서초구-12</v>
+        <v>25-서초구-13</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -840,16 +840,16 @@
         <v>일반</v>
       </c>
       <c r="P10" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q10" t="str">
-        <v>서초동 1337-32</v>
+        <v>서초동 1337-22</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>한국투자증권 앞 도로</v>
+        <v>디오빌프라임 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="str">
         <v>강남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-서초구-13</v>
+        <v>25-서초구-14</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -905,13 +905,13 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>서초동 1337-22</v>
+        <v>서초동 1338-23</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>디오빌프라임 앞 도로</v>
+        <v>투썸플레이스 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="str">
         <v>강남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-서초구-14</v>
+        <v>25-서초구-15</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -967,13 +967,13 @@
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v>서초동 1338-23</v>
+        <v>서초동 1338-20</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>투썸플레이스 도로</v>
+        <v>현대렉시온 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="str">
         <v>강남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-서초구-15</v>
+        <v>25-서초구-16</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -996,7 +996,7 @@
         <v>거북등</v>
       </c>
       <c r="F13" t="str">
-        <v>양호</v>
+        <v>건조</v>
       </c>
       <c r="G13" t="str">
         <v>13.5</v>
@@ -1029,13 +1029,13 @@
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v>서초동 1338-20</v>
+        <v>서초동 1339-9</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>현대렉시온 앞 도로</v>
+        <v>하나은행 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="str">
         <v>강남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-서초구-16</v>
+        <v>25-서초구-17</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1091,13 +1091,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>서초동 1339-9</v>
+        <v>서초동 1340-6</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>하나은행 앞 도로</v>
+        <v>KIA 서초지점 앞 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="str">
         <v>강남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-서초구-17</v>
+        <v>25-서초구-18</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1150,7 +1150,7 @@
         <v>일반</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q15" t="str">
         <v>서초동 1340-6</v>
@@ -1159,7 +1159,7 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>KIA 서초지점 앞 도로</v>
+        <v>남강매점 앞 횡단보도</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="str">
         <v>강남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-서초구-18</v>
+        <v>25-서초구-19</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1212,16 +1212,16 @@
         <v>일반</v>
       </c>
       <c r="P16" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q16" t="str">
-        <v>서초동 1340-6</v>
+        <v>서초동 1357-33</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>남강매점 앞 횡단보도</v>
+        <v>한국디지털 평생교육원 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="str">
         <v>강남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-서초구-19</v>
+        <v>25-서초구-20</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1274,16 +1274,16 @@
         <v>일반</v>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q17" t="str">
-        <v>서초동 1357-33</v>
+        <v>서초동 1357-35</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>한국디지털 평생교육원 앞 도로</v>
+        <v>부산은행 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="str">
         <v>강남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-서초구-20</v>
+        <v>25-서초구-21</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1339,13 +1339,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q18" t="str">
-        <v>서초동 1357-35</v>
+        <v>서초동 1358-6</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>부산은행 앞 도로</v>
+        <v>송남빌딩 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,19 +1353,19 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="str">
         <v>강남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-서초구-21</v>
+        <v>25-서초구-22</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
       </c>
       <c r="E19" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F19" t="str">
         <v>건조</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1392,22 +1392,22 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O19" t="str">
         <v>일반</v>
       </c>
       <c r="P19" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q19" t="str">
-        <v>서초동 1358-6</v>
+        <v>서초동 1361-1</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>송남빌딩 앞 도로</v>
+        <v>보들설곰탕 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="str">
         <v>강남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-서초구-22</v>
+        <v>25-서초구-23</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1463,13 +1463,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>서초동 1361-1</v>
+        <v>서초동 1361-5</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>보들설곰탕 앞 도로</v>
+        <v>새움빌딩 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,19 +1477,19 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="str">
         <v>강남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-서초구-23</v>
+        <v>25-서초구-24</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
       </c>
       <c r="E21" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F21" t="str">
         <v>건조</v>
@@ -1504,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O21" t="str">
         <v>일반</v>
@@ -1525,13 +1525,13 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v>서초동 1361-5</v>
+        <v>서초동 1361-10</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>새움빌딩 앞 도로</v>
+        <v>호텔 페이토 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,13 +1539,13 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="str">
         <v>강남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-서초구-24</v>
+        <v>25-서초구-25</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
@@ -1584,16 +1584,16 @@
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q22" t="str">
-        <v>서초동 1361-10</v>
+        <v>서초동 1362</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>호텔 페이토 앞 도로</v>
+        <v>e마트24 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="str">
         <v>강남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-서초구-25</v>
+        <v>25-서초구-26</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
@@ -1646,16 +1646,16 @@
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q23" t="str">
-        <v>서초동 1362</v>
+        <v>서초동 1362-26</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>e마트24 앞 도로</v>
+        <v>힐든가든인 서울강남 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,13 +1663,13 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="str">
         <v>강남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-서초구-26</v>
+        <v>25-서초구-27</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
@@ -1708,16 +1708,16 @@
         <v>일반</v>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q24" t="str">
-        <v>서초동 1362-26</v>
+        <v>서초동 1362-27</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>힐든가든인 서울강남 앞 도로</v>
+        <v>니드오피스텔 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="str">
         <v>강남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-서초구-27</v>
+        <v>25-서초구-28</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
@@ -1770,16 +1770,16 @@
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q25" t="str">
-        <v>서초동 1362-27</v>
+        <v>서초동 1366-7</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>니드오피스텔 앞 도로</v>
+        <v>깐부치킨 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="str">
         <v>강남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-서초구-28</v>
+        <v>25-서초구-29</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1832,16 +1832,16 @@
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q26" t="str">
-        <v>서초동 1366-7</v>
+        <v>서초동 1366-9</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>깐부치킨 앞 도로</v>
+        <v>양재역 교차로 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="str">
         <v>강남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-서초구-29</v>
+        <v>25-서초구-30</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1894,16 +1894,16 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q27" t="str">
-        <v>서초동 1366-9</v>
+        <v>양재동 23</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>양재역 교차로 도로</v>
+        <v>바나프레소 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="str">
         <v>강남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-서초구-30</v>
+        <v>25-서초구-31</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1959,13 +1959,13 @@
         <v/>
       </c>
       <c r="Q28" t="str">
-        <v>양재동 23</v>
+        <v>양재동 25</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>바나프레소 앞 도로</v>
+        <v>서초문화 예술회관 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="str">
         <v>강남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-서초구-31</v>
+        <v>25-서초구-32</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2021,13 +2021,13 @@
         <v/>
       </c>
       <c r="Q29" t="str">
-        <v>양재동 25</v>
+        <v>양재동 14-4</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>서초문화 예술회관 앞 도로</v>
+        <v>모산빌딩 앞 횡단보도</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="str">
         <v>강남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-서초구-32</v>
+        <v>25-서초구-33</v>
       </c>
       <c r="D30" t="str">
-        <v>양호</v>
+        <v>50</v>
       </c>
       <c r="E30" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F30" t="str">
         <v>건조</v>
@@ -2058,11 +2058,11 @@
       <c r="H30" t="str">
         <v>-</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -2074,22 +2074,22 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O30" t="str">
         <v>일반</v>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>보도침하5cm</v>
       </c>
       <c r="Q30" t="str">
-        <v>양재동 14-4</v>
+        <v>양재동 67-7</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>모산빌딩 앞 횡단보도</v>
+        <v>바나프레스 앞 보도</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,19 +2097,19 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="str">
         <v>강남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-서초구-33</v>
+        <v>25-서초구-34</v>
       </c>
       <c r="D31" t="str">
-        <v>50</v>
+        <v>양호</v>
       </c>
       <c r="E31" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F31" t="str">
         <v>건조</v>
@@ -2120,11 +2120,11 @@
       <c r="H31" t="str">
         <v>-</v>
       </c>
-      <c r="I31" t="b">
+      <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2136,22 +2136,22 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O31" t="str">
         <v>일반</v>
       </c>
       <c r="P31" t="str">
-        <v>보도침하5cm</v>
+        <v/>
       </c>
       <c r="Q31" t="str">
-        <v>양재동 67-7</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>바나프레스 앞 보도</v>
+        <v>교육개발원 사거리 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,19 +2159,19 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="str">
         <v>강남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-서초구-34</v>
+        <v>25-서초구-35</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
       </c>
       <c r="E32" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F32" t="str">
         <v>건조</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O32" t="str">
         <v>일반</v>
@@ -2207,13 +2207,13 @@
         <v/>
       </c>
       <c r="Q32" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동 109</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>교육개발원 사거리 도로</v>
+        <v>카페 릴리블랑 앞 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="str">
         <v>강남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-서초구-35</v>
+        <v>25-서초구-36</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
       </c>
       <c r="E33" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F33" t="str">
         <v>건조</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O33" t="str">
         <v>일반</v>
@@ -2269,13 +2269,13 @@
         <v/>
       </c>
       <c r="Q33" t="str">
-        <v>양재동 109</v>
+        <v>양재동 125</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>카페 릴리블랑 앞 도로</v>
+        <v>넥스팜 코리아 앞 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,13 +2283,13 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="str">
         <v>강남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-서초구-36</v>
+        <v>25-서초구-37</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
@@ -2331,13 +2331,13 @@
         <v/>
       </c>
       <c r="Q34" t="str">
-        <v>양재동 125</v>
+        <v>양재동 80-3</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>넥스팜 코리아 앞 도로</v>
+        <v>도야짬뽕 앞 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,13 +2345,13 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-서초구-37</v>
+        <v>25-서초구-38</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
@@ -2393,13 +2393,13 @@
         <v/>
       </c>
       <c r="Q35" t="str">
-        <v>양재동 80-3</v>
+        <v>양재동 237-1</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>도야짬뽕 앞 도로</v>
+        <v>공영주차장 앞 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,13 +2407,13 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-서초구-38</v>
+        <v>25-서초구-39</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2455,13 +2455,13 @@
         <v/>
       </c>
       <c r="Q36" t="str">
-        <v>양재동 237-1</v>
+        <v>신원동 308-1</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>공영주차장 앞 도로</v>
+        <v>가로등(청계산로145) 양차선 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="str">
         <v>청계산로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-서초구-39</v>
+        <v>25-서초구-40</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>신원동 308-1</v>
+        <v>원지동 294-3</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>가로등(청계산로145) 양차선 도로</v>
+        <v>전봇대(원지간37H1) 양차선 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="str">
         <v>청계산로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-서초구-40</v>
+        <v>25-서초구-41</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2576,16 +2576,16 @@
         <v>일반</v>
       </c>
       <c r="P38" t="str">
-        <v/>
+        <v>거북등 맨홀침하4cm</v>
       </c>
       <c r="Q38" t="str">
-        <v>원지동 294-3</v>
+        <v>원지동 594-1</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>전봇대(원지간37H1) 양차선 도로</v>
+        <v>도로교통표지판 앞 상수도맨홀 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="str">
         <v>청계산로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-서초구-41</v>
+        <v>25-서초구-42</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2638,16 +2638,16 @@
         <v>일반</v>
       </c>
       <c r="P39" t="str">
-        <v>거북등 맨홀침하4cm</v>
+        <v/>
       </c>
       <c r="Q39" t="str">
-        <v>원지동 594-1</v>
+        <v>신원동 280</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>도로교통표지판 앞 상수도맨홀 도로</v>
+        <v>공영주차장 앞 T 교차로 양차선 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="str">
         <v>청계산로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-서초구-42</v>
+        <v>25-서초구-43</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2703,13 +2703,13 @@
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>신원동 280</v>
+        <v>신원동 278-6</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>공영주차장 앞 T 교차로 양차선 도로</v>
+        <v>공영주차장 앞 양차선 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="str">
         <v>청계산로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-서초구-43</v>
+        <v>25-서초구-44</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2762,16 +2762,16 @@
         <v>일반</v>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q41" t="str">
-        <v>신원동 278-6</v>
+        <v>신원동 611</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>공영주차장 앞 양차선 도로</v>
+        <v>투썸플레이스 앞 보도</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,19 +2779,19 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="str">
         <v>청계산로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-서초구-44</v>
+        <v>25-서초구-45</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
       </c>
       <c r="E42" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F42" t="str">
         <v>건조</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -2818,22 +2818,22 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O42" t="str">
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v>보도침하4cm</v>
+        <v/>
       </c>
       <c r="Q42" t="str">
-        <v>신원동 611</v>
+        <v>신원동 612</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>투썸플레이스 앞 보도</v>
+        <v>LAB 앞 도로</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="str">
         <v>청계산로</v>
       </c>
       <c r="C43" t="str">
-        <v>25-서초구-45</v>
+        <v>25-서초구-46</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
       </c>
       <c r="E43" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F43" t="str">
         <v>건조</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -2880,22 +2880,22 @@
         <v>0</v>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O43" t="str">
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v/>
+        <v>보도침하4cm</v>
       </c>
       <c r="Q43" t="str">
-        <v>신원동 612</v>
+        <v>신원동 660</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>LAB 앞 도로</v>
+        <v>심플리시티 앞 보도</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,13 +2903,13 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="str">
         <v>청계산로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-서초구-46</v>
+        <v>25-서초구-47</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
@@ -2948,16 +2948,16 @@
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v>보도침하4cm</v>
+        <v>보도침하3cm</v>
       </c>
       <c r="Q44" t="str">
-        <v>신원동 660</v>
+        <v>신원동 197-1</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>심플리시티 앞 보도</v>
+        <v>부안애서 맞음편 보도</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="str">
         <v>청계산로</v>
       </c>
       <c r="C45" t="str">
-        <v>25-서초구-47</v>
+        <v>25-서초구-48</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
@@ -3010,16 +3010,16 @@
         <v>일반</v>
       </c>
       <c r="P45" t="str">
-        <v>보도침하3cm</v>
+        <v/>
       </c>
       <c r="Q45" t="str">
-        <v>신원동 197-1</v>
+        <v>원지동 384-1</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>부안애서 맞음편 보도</v>
+        <v>커피플라워 앞 양차선 도로</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,13 +3027,13 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="str">
         <v>청계산로</v>
       </c>
       <c r="C46" t="str">
-        <v>25-서초구-48</v>
+        <v>25-서초구-49</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
@@ -3075,13 +3075,13 @@
         <v/>
       </c>
       <c r="Q46" t="str">
-        <v>원지동 384-1</v>
+        <v>신원동 192-73</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>커피플라워 앞 양차선 도로</v>
+        <v>봉평막국수 앞 양차선 도로</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,13 +3089,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="str">
         <v>청계산로</v>
       </c>
       <c r="C47" t="str">
-        <v>25-서초구-49</v>
+        <v>25-서초구-50</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
@@ -3137,13 +3137,13 @@
         <v/>
       </c>
       <c r="Q47" t="str">
-        <v>신원동 192-73</v>
+        <v>신원동 172-1</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>봉평막국수 앞 양차선 도로</v>
+        <v>향린조경 앞 양차선 도로</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,13 +3151,13 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="str">
         <v>청계산로</v>
       </c>
       <c r="C48" t="str">
-        <v>25-서초구-50</v>
+        <v>25-서초구-51</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
@@ -3199,13 +3199,13 @@
         <v/>
       </c>
       <c r="Q48" t="str">
-        <v>신원동 172-1</v>
+        <v>신원동 153</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>향린조경 앞 양차선 도로</v>
+        <v>삼석원 앞 양차선 도로</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,13 +3213,13 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="str">
         <v>청계산로</v>
       </c>
       <c r="C49" t="str">
-        <v>25-서초구-51</v>
+        <v>25-서초구-52</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
@@ -3261,13 +3261,13 @@
         <v/>
       </c>
       <c r="Q49" t="str">
-        <v>신원동 153</v>
+        <v>신원동 150-1</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>삼석원 앞 양차선 도로</v>
+        <v>성심조경 앞 양차선 도로</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,13 +3275,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="str">
         <v>청계산로</v>
       </c>
       <c r="C50" t="str">
-        <v>25-서초구-52</v>
+        <v>25-서초구-53</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
@@ -3320,16 +3320,16 @@
         <v>일반</v>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q50" t="str">
-        <v>신원동 150-1</v>
+        <v>원지동 470-1</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>성심조경 앞 양차선 도로</v>
+        <v>가로등(청계산로154) 앞 보도</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="str">
         <v>청계산로</v>
       </c>
       <c r="C51" t="str">
-        <v>25-서초구-53</v>
+        <v>25-서초구-54</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
@@ -3382,16 +3382,16 @@
         <v>일반</v>
       </c>
       <c r="P51" t="str">
-        <v>5cm이하 침하</v>
+        <v>보도침하</v>
       </c>
       <c r="Q51" t="str">
-        <v>원지동 470-1</v>
+        <v>원지동 491-6</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>가로등(청계산로154) 앞 보도</v>
+        <v>가로등(청계산로156) 맞음편 보도</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="str">
         <v>청계산로</v>
       </c>
       <c r="C52" t="str">
-        <v>25-서초구-54</v>
+        <v>25-서초구-55</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3444,16 +3444,16 @@
         <v>일반</v>
       </c>
       <c r="P52" t="str">
-        <v>보도침하</v>
+        <v/>
       </c>
       <c r="Q52" t="str">
-        <v>원지동 491-6</v>
+        <v>원지동 493</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>가로등(청계산로156) 맞음편 보도</v>
+        <v>양재조경 앞 양차선 도로</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="str">
         <v>청계산로</v>
       </c>
       <c r="C53" t="str">
-        <v>25-서초구-55</v>
+        <v>25-서초구-56</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3509,13 +3509,13 @@
         <v/>
       </c>
       <c r="Q53" t="str">
-        <v>원지동 493</v>
+        <v>원지동 497-3</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>양재조경 앞 양차선 도로</v>
+        <v>가로등(청계산로168) 앞 양차선 도로</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3523,13 +3523,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="str">
         <v>청계산로</v>
       </c>
       <c r="C54" t="str">
-        <v>25-서초구-56</v>
+        <v>25-서초구-57</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3571,13 +3571,13 @@
         <v/>
       </c>
       <c r="Q54" t="str">
-        <v>원지동 497-3</v>
+        <v>신원동 산 60-2</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>가로등(청계산로168) 앞 양차선 도로</v>
+        <v>대원조경 앞 양차선 도로</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="str">
         <v>청계산로</v>
       </c>
       <c r="C55" t="str">
-        <v>25-서초구-57</v>
+        <v>25-서초구-58</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3633,13 +3633,13 @@
         <v/>
       </c>
       <c r="Q55" t="str">
-        <v>신원동 산 60-2</v>
+        <v>신원동 105-4</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>대원조경 앞 양차선 도로</v>
+        <v>둥지조경 제2농장 앞 양차선 도로</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3647,13 +3647,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="str">
         <v>청계산로</v>
       </c>
       <c r="C56" t="str">
-        <v>25-서초구-58</v>
+        <v>25-서초구-59</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
@@ -3695,13 +3695,13 @@
         <v/>
       </c>
       <c r="Q56" t="str">
-        <v>신원동 105-4</v>
+        <v>신원동 105-33</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>둥지조경 제2농장 앞 양차선 도로</v>
+        <v>한백자생식물원 앞 양차선 도로</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3709,13 +3709,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="str">
         <v>청계산로</v>
       </c>
       <c r="C57" t="str">
-        <v>25-서초구-59</v>
+        <v>25-서초구-60</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3754,16 +3754,16 @@
         <v>일반</v>
       </c>
       <c r="P57" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q57" t="str">
-        <v>신원동 105-33</v>
+        <v>신원동 105-19</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>한백자생식물원 앞 양차선 도로</v>
+        <v>가로등(청계산로190) 앞 양차선 도로</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3771,19 +3771,19 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="str">
         <v>청계산로</v>
       </c>
       <c r="C58" t="str">
-        <v>25-서초구-60</v>
+        <v>25-서초구-61</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
       </c>
       <c r="E58" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F58" t="str">
         <v>건조</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O58" t="str">
         <v>일반</v>
@@ -3819,13 +3819,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q58" t="str">
-        <v>신원동 105-19</v>
+        <v>신원동 44-1</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>가로등(청계산로190) 앞 양차선 도로</v>
+        <v>새정이마을 입구 교차로</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3833,19 +3833,19 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="str">
         <v>청계산로</v>
       </c>
       <c r="C59" t="str">
-        <v>25-서초구-61</v>
+        <v>25-서초구-62</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
       </c>
       <c r="E59" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F59" t="str">
         <v>건조</v>
@@ -3878,16 +3878,16 @@
         <v>일반</v>
       </c>
       <c r="P59" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q59" t="str">
-        <v>신원동 44-1</v>
+        <v>신원동 44-5</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>새정이마을 입구 교차로</v>
+        <v>은하조경 앞 양차선 도로</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3895,13 +3895,13 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="str">
         <v>청계산로</v>
       </c>
       <c r="C60" t="str">
-        <v>25-서초구-62</v>
+        <v>25-서초구-63</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
@@ -3943,13 +3943,13 @@
         <v/>
       </c>
       <c r="Q60" t="str">
-        <v>신원동 44-5</v>
+        <v>신원동 57</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>은하조경 앞 양차선 도로</v>
+        <v>서림원예종묘 앞 양차선 도로</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3957,19 +3957,19 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="str">
         <v>청계산로</v>
       </c>
       <c r="C61" t="str">
-        <v>25-서초구-63</v>
+        <v>25-서초구-64</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
       </c>
       <c r="E61" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F61" t="str">
         <v>건조</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="N61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O61" t="str">
         <v>일반</v>
@@ -4005,27 +4005,27 @@
         <v/>
       </c>
       <c r="Q61" t="str">
-        <v>신원동 57</v>
+        <v>신원동 64-1</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>서림원예종묘 앞 양차선 도로</v>
+        <v>옥천조경 앞 양차선 도로</v>
       </c>
       <c r="T61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62">
-        <v>64</v>
+      <c r="A62" t="str">
+        <v>26-01</v>
       </c>
       <c r="B62" t="str">
-        <v>청계산로</v>
+        <v>강남대로</v>
       </c>
       <c r="C62" t="str">
-        <v>25-서초구-64</v>
+        <v>26-서초구-01</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
@@ -4034,46 +4034,46 @@
         <v>거북등</v>
       </c>
       <c r="F62" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G62" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H62" t="str">
         <v>-</v>
       </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>3</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>1</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
+      <c r="I62" t="str">
+        <v>0</v>
+      </c>
+      <c r="J62" t="str">
+        <v>3</v>
+      </c>
+      <c r="K62" t="str">
+        <v>0</v>
+      </c>
+      <c r="L62" t="str">
+        <v>1</v>
+      </c>
+      <c r="M62" t="str">
+        <v>0</v>
+      </c>
+      <c r="N62" t="str">
         <v>4</v>
       </c>
       <c r="O62" t="str">
         <v>일반</v>
       </c>
       <c r="P62" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q62" t="str">
-        <v>신원동 64-1</v>
+        <v>서초동1318-4</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>옥천조경 앞 양차선 도로</v>
+        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4081,13 +4081,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B63" t="str">
         <v>강남대로</v>
       </c>
       <c r="C63" t="str">
-        <v>26-서초구-01</v>
+        <v>26-서초구-02</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
@@ -4129,13 +4129,13 @@
         <v>-</v>
       </c>
       <c r="Q63" t="str">
-        <v>서초동1318-4</v>
+        <v>강남역사거리</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>강남빌딩 올리브영 앞 도로(강남대로403)</v>
+        <v>강남역사거리(강남대로396)</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4143,13 +4143,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B64" t="str">
         <v>강남대로</v>
       </c>
       <c r="C64" t="str">
-        <v>26-서초구-02</v>
+        <v>26-서초구-03</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
@@ -4191,13 +4191,13 @@
         <v>-</v>
       </c>
       <c r="Q64" t="str">
-        <v>강남역사거리</v>
+        <v>서초동1319-5</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>강남역사거리(강남대로396)</v>
+        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4205,13 +4205,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B65" t="str">
         <v>강남대로</v>
       </c>
       <c r="C65" t="str">
-        <v>26-서초구-03</v>
+        <v>26-서초구-04</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
@@ -4253,13 +4253,13 @@
         <v>-</v>
       </c>
       <c r="Q65" t="str">
-        <v>서초동1319-5</v>
+        <v>서초동1319-11</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>대각빌딩 한국산업은행 앞 도로(서초대로78길5)</v>
+        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4267,13 +4267,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B66" t="str">
         <v>강남대로</v>
       </c>
       <c r="C66" t="str">
-        <v>26-서초구-04</v>
+        <v>26-서초구-05</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
@@ -4315,13 +4315,13 @@
         <v>-</v>
       </c>
       <c r="Q66" t="str">
-        <v>서초동1319-11</v>
+        <v>서초동1328-3</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>두산베어스텔 하니은행 앞도로(강남대로381)</v>
+        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4329,13 +4329,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B67" t="str">
         <v>강남대로</v>
       </c>
       <c r="C67" t="str">
-        <v>26-서초구-05</v>
+        <v>26-서초구-06</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
@@ -4374,16 +4374,16 @@
         <v>일반</v>
       </c>
       <c r="P67" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q67" t="str">
-        <v>서초동1328-3</v>
+        <v>서초동1328-11</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>DF타워 우리은행 앞 도로(강남대로369)</v>
+        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4391,13 +4391,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B68" t="str">
         <v>강남대로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-서초구-06</v>
+        <v>26-서초구-07</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
@@ -4439,13 +4439,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q68" t="str">
-        <v>서초동1328-11</v>
+        <v>서초동1329</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>대우도씨에빛2 밀라이스 앞 도로(깅님대로359)</v>
+        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4453,13 +4453,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B69" t="str">
         <v>강남대로</v>
       </c>
       <c r="C69" t="str">
-        <v>26-서초구-07</v>
+        <v>26-서초구-08</v>
       </c>
       <c r="D69" t="str">
         <v>양호</v>
@@ -4498,16 +4498,16 @@
         <v>일반</v>
       </c>
       <c r="P69" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q69" t="str">
-        <v>서초동1329</v>
+        <v>서초동1329-4</v>
       </c>
       <c r="R69" t="str">
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>삼성화재서초사옥 앞 도로(강남대로355)</v>
+        <v>우남빌딩 앞 도로(강남대로349)</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4515,16 +4515,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B70" t="str">
         <v>강남대로</v>
       </c>
       <c r="C70" t="str">
-        <v>26-서초구-08</v>
+        <v>26-서초구-09</v>
       </c>
       <c r="D70" t="str">
-        <v>양호</v>
+        <v>불량</v>
       </c>
       <c r="E70" t="str">
         <v>거북등</v>
@@ -4539,7 +4539,7 @@
         <v>-</v>
       </c>
       <c r="I70" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J70" t="str">
         <v>3</v>
@@ -4554,22 +4554,22 @@
         <v>0</v>
       </c>
       <c r="N70" t="str">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O70" t="str">
-        <v>일반</v>
+        <v>긴급</v>
       </c>
       <c r="P70" t="str">
-        <v>-</v>
+        <v>복구부 밑 빈공간있음(80cm)</v>
       </c>
       <c r="Q70" t="str">
-        <v>서초동1329-4</v>
+        <v>서초동1329-7</v>
       </c>
       <c r="R70" t="str">
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>우남빌딩 앞 도로(강남대로349)</v>
+        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4577,16 +4577,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B71" t="str">
         <v>강남대로</v>
       </c>
       <c r="C71" t="str">
-        <v>26-서초구-09</v>
+        <v>26-서초구-10</v>
       </c>
       <c r="D71" t="str">
-        <v>불량</v>
+        <v>양호</v>
       </c>
       <c r="E71" t="str">
         <v>거북등</v>
@@ -4601,7 +4601,7 @@
         <v>-</v>
       </c>
       <c r="I71" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J71" t="str">
         <v>3</v>
@@ -4616,22 +4616,22 @@
         <v>0</v>
       </c>
       <c r="N71" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O71" t="str">
-        <v>긴급</v>
+        <v>일반</v>
       </c>
       <c r="P71" t="str">
-        <v>복구부 밑 빈공간있음(80cm)</v>
+        <v>-</v>
       </c>
       <c r="Q71" t="str">
-        <v>서초동1329-7</v>
+        <v>서초동1329-8</v>
       </c>
       <c r="R71" t="str">
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>신덕빌딩 버스정류장 앞 도로(강남대로343)</v>
+        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
       </c>
       <c r="T71" t="str">
         <v/>
@@ -4639,13 +4639,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B72" t="str">
         <v>강남대로</v>
       </c>
       <c r="C72" t="str">
-        <v>26-서초구-10</v>
+        <v>26-서초구-11</v>
       </c>
       <c r="D72" t="str">
         <v>양호</v>
@@ -4684,16 +4684,16 @@
         <v>일반</v>
       </c>
       <c r="P72" t="str">
-        <v>-</v>
+        <v/>
       </c>
       <c r="Q72" t="str">
-        <v>서초동1329-8</v>
+        <v>우성아파트앞 사거리</v>
       </c>
       <c r="R72" t="str">
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>삼원빌딩 파파이스 앞 도로(강남대로341)</v>
+        <v>교차로(강남대로346-2)</v>
       </c>
       <c r="T72" t="str">
         <v/>
@@ -4701,13 +4701,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B73" t="str">
         <v>강남대로</v>
       </c>
       <c r="C73" t="str">
-        <v>26-서초구-11</v>
+        <v>26-서초구-12</v>
       </c>
       <c r="D73" t="str">
         <v>양호</v>
@@ -4746,16 +4746,16 @@
         <v>일반</v>
       </c>
       <c r="P73" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q73" t="str">
-        <v>우성아파트앞 사거리</v>
+        <v>서초동1337-32</v>
       </c>
       <c r="R73" t="str">
         <v/>
       </c>
       <c r="S73" t="str">
-        <v>교차로(강남대로346-2)</v>
+        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
       </c>
       <c r="T73" t="str">
         <v/>
@@ -4763,13 +4763,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B74" t="str">
         <v>강남대로</v>
       </c>
       <c r="C74" t="str">
-        <v>26-서초구-12</v>
+        <v>26-서초구-13</v>
       </c>
       <c r="D74" t="str">
         <v>양호</v>
@@ -4808,16 +4808,16 @@
         <v>일반</v>
       </c>
       <c r="P74" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q74" t="str">
-        <v>서초동1337-32</v>
+        <v>서초동1337-31</v>
       </c>
       <c r="R74" t="str">
         <v/>
       </c>
       <c r="S74" t="str">
-        <v>광일프라자 올리브영 앞 도로(강남대로331)</v>
+        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
       </c>
       <c r="T74" t="str">
         <v/>
@@ -4825,13 +4825,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B75" t="str">
         <v>강남대로</v>
       </c>
       <c r="C75" t="str">
-        <v>26-서초구-13</v>
+        <v>26-서초구-14</v>
       </c>
       <c r="D75" t="str">
         <v>양호</v>
@@ -4873,13 +4873,13 @@
         <v>-</v>
       </c>
       <c r="Q75" t="str">
-        <v>서초동1337-31</v>
+        <v>서초동1337-20</v>
       </c>
       <c r="R75" t="str">
         <v/>
       </c>
       <c r="S75" t="str">
-        <v>산학협동재단빌딩 앞 도로(강남대로329)</v>
+        <v>대륭서초타워 앞 도로(강남대로327)</v>
       </c>
       <c r="T75" t="str">
         <v/>
@@ -4887,19 +4887,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B76" t="str">
         <v>강남대로</v>
       </c>
       <c r="C76" t="str">
-        <v>26-서초구-14</v>
+        <v>26-서초구-15</v>
       </c>
       <c r="D76" t="str">
         <v>양호</v>
       </c>
       <c r="E76" t="str">
-        <v>거북등</v>
+        <v>거북이</v>
       </c>
       <c r="F76" t="str">
         <v>양호</v>
@@ -4935,13 +4935,13 @@
         <v>-</v>
       </c>
       <c r="Q76" t="str">
-        <v>서초동1337-20</v>
+        <v>서초동1337-22</v>
       </c>
       <c r="R76" t="str">
         <v/>
       </c>
       <c r="S76" t="str">
-        <v>대륭서초타워 앞 도로(강남대로327)</v>
+        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
       </c>
       <c r="T76" t="str">
         <v/>
@@ -4949,19 +4949,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B77" t="str">
         <v>강남대로</v>
       </c>
       <c r="C77" t="str">
-        <v>26-서초구-15</v>
+        <v>26-서초구-16</v>
       </c>
       <c r="D77" t="str">
         <v>양호</v>
       </c>
       <c r="E77" t="str">
-        <v>거북이</v>
+        <v>거북등</v>
       </c>
       <c r="F77" t="str">
         <v>양호</v>
@@ -4997,13 +4997,13 @@
         <v>-</v>
       </c>
       <c r="Q77" t="str">
-        <v>서초동1337-22</v>
+        <v>서초동1338-23</v>
       </c>
       <c r="R77" t="str">
         <v/>
       </c>
       <c r="S77" t="str">
-        <v>서초동대우디오빌프라임 앞 도로(강남대로321)</v>
+        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
       </c>
       <c r="T77" t="str">
         <v/>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B78" t="str">
         <v>강남대로</v>
       </c>
       <c r="C78" t="str">
-        <v>26-서초구-16</v>
+        <v>26-서초구-17</v>
       </c>
       <c r="D78" t="str">
         <v>양호</v>
@@ -5059,13 +5059,13 @@
         <v>-</v>
       </c>
       <c r="Q78" t="str">
-        <v>서초동1338-23</v>
+        <v>서초동1338-12</v>
       </c>
       <c r="R78" t="str">
         <v/>
       </c>
       <c r="S78" t="str">
-        <v>파이낸셜뉴스빌딩 투썸플레이스 앞 도로(강남도로315)</v>
+        <v>코인노트 앞 도로(강남대로311)</v>
       </c>
       <c r="T78" t="str">
         <v/>
@@ -5073,13 +5073,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B79" t="str">
         <v>강남대로</v>
       </c>
       <c r="C79" t="str">
-        <v>26-서초구-17</v>
+        <v>26-서초구-18</v>
       </c>
       <c r="D79" t="str">
         <v>양호</v>
@@ -5121,13 +5121,13 @@
         <v>-</v>
       </c>
       <c r="Q79" t="str">
-        <v>서초동1338-12</v>
+        <v>서초동1338-21</v>
       </c>
       <c r="R79" t="str">
         <v/>
       </c>
       <c r="S79" t="str">
-        <v>코인노트 앞 도로(강남대로311)</v>
+        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
       </c>
       <c r="T79" t="str">
         <v/>
@@ -5135,13 +5135,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B80" t="str">
         <v>강남대로</v>
       </c>
       <c r="C80" t="str">
-        <v>26-서초구-18</v>
+        <v>26-서초구-19</v>
       </c>
       <c r="D80" t="str">
         <v>양호</v>
@@ -5183,13 +5183,13 @@
         <v>-</v>
       </c>
       <c r="Q80" t="str">
-        <v>서초동1338-21</v>
+        <v>서초동1338-20</v>
       </c>
       <c r="R80" t="str">
         <v/>
       </c>
       <c r="S80" t="str">
-        <v>코리아비즈니스센터빌딩 앞 도로(강남대로309)</v>
+        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
       </c>
       <c r="T80" t="str">
         <v/>
@@ -5197,13 +5197,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B81" t="str">
         <v>강남대로</v>
       </c>
       <c r="C81" t="str">
-        <v>26-서초구-19</v>
+        <v>26-서초구-20</v>
       </c>
       <c r="D81" t="str">
         <v>양호</v>
@@ -5245,13 +5245,13 @@
         <v>-</v>
       </c>
       <c r="Q81" t="str">
-        <v>서초동1338-20</v>
+        <v>서초동1339-9</v>
       </c>
       <c r="R81" t="str">
         <v/>
       </c>
       <c r="S81" t="str">
-        <v>IBK기엄은행_강남대로 앞 도로(강남대로305)</v>
+        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
       </c>
       <c r="T81" t="str">
         <v/>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B82" t="str">
         <v>강남대로</v>
       </c>
       <c r="C82" t="str">
-        <v>26-서초구-20</v>
+        <v>26-서초구-21</v>
       </c>
       <c r="D82" t="str">
         <v>양호</v>
@@ -5307,13 +5307,13 @@
         <v>-</v>
       </c>
       <c r="Q82" t="str">
-        <v>서초동1339-9</v>
+        <v>서초동1340-6</v>
       </c>
       <c r="R82" t="str">
         <v/>
       </c>
       <c r="S82" t="str">
-        <v>하나은행 서초금융센터 앞 도로(강남대로299)</v>
+        <v>남강빌딩 앞 도로(강남대로291)</v>
       </c>
       <c r="T82" t="str">
         <v/>
@@ -5321,13 +5321,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B83" t="str">
         <v>강남대로</v>
       </c>
       <c r="C83" t="str">
-        <v>26-서초구-21</v>
+        <v>26-서초구-22</v>
       </c>
       <c r="D83" t="str">
         <v>양호</v>
@@ -5369,13 +5369,13 @@
         <v>-</v>
       </c>
       <c r="Q83" t="str">
-        <v>서초동1340-6</v>
+        <v>서초동1357-10</v>
       </c>
       <c r="R83" t="str">
         <v/>
       </c>
       <c r="S83" t="str">
-        <v>남강빌딩 앞 도로(강남대로291)</v>
+        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
       </c>
       <c r="T83" t="str">
         <v/>
@@ -5383,19 +5383,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B84" t="str">
         <v>강남대로</v>
       </c>
       <c r="C84" t="str">
-        <v>26-서초구-22</v>
+        <v>26-서초구-23</v>
       </c>
       <c r="D84" t="str">
         <v>양호</v>
       </c>
       <c r="E84" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F84" t="str">
         <v>양호</v>
@@ -5410,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K84" t="str">
         <v>0</v>
@@ -5422,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O84" t="str">
         <v>일반</v>
@@ -5431,13 +5431,13 @@
         <v>-</v>
       </c>
       <c r="Q84" t="str">
-        <v>서초동1357-10</v>
+        <v>서초동1357-66</v>
       </c>
       <c r="R84" t="str">
         <v/>
       </c>
       <c r="S84" t="str">
-        <v>서초태우빌딩 스타벅스 앞 도로(강남대로285)</v>
+        <v>메인타워 CU 앞 도로(강남대로275)</v>
       </c>
       <c r="T84" t="str">
         <v/>
@@ -5445,19 +5445,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B85" t="str">
         <v>강남대로</v>
       </c>
       <c r="C85" t="str">
-        <v>26-서초구-23</v>
+        <v>26-서초구-24</v>
       </c>
       <c r="D85" t="str">
         <v>양호</v>
       </c>
       <c r="E85" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F85" t="str">
         <v>양호</v>
@@ -5493,13 +5493,13 @@
         <v>-</v>
       </c>
       <c r="Q85" t="str">
-        <v>서초동1357-66</v>
+        <v>서초동1358-7</v>
       </c>
       <c r="R85" t="str">
         <v/>
       </c>
       <c r="S85" t="str">
-        <v>메인타워 CU 앞 도로(강남대로275)</v>
+        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
       </c>
       <c r="T85" t="str">
         <v/>
@@ -5507,19 +5507,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>26-24</v>
+        <v>26-25</v>
       </c>
       <c r="B86" t="str">
         <v>강남대로</v>
       </c>
       <c r="C86" t="str">
-        <v>26-서초구-24</v>
+        <v>26-서초구-25</v>
       </c>
       <c r="D86" t="str">
         <v>양호</v>
       </c>
       <c r="E86" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F86" t="str">
         <v>양호</v>
@@ -5534,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K86" t="str">
         <v>0</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="N86" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O86" t="str">
         <v>일반</v>
@@ -5555,13 +5555,13 @@
         <v>-</v>
       </c>
       <c r="Q86" t="str">
-        <v>서초동1358-7</v>
+        <v>양재역사거리</v>
       </c>
       <c r="R86" t="str">
         <v/>
       </c>
       <c r="S86" t="str">
-        <v>송남빌딩 주차장 앞 커피빈방향(강남대로273)</v>
+        <v>양재역 교차로(강남대로266-2)</v>
       </c>
       <c r="T86" t="str">
         <v/>
@@ -5569,13 +5569,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>26-25</v>
+        <v>26-26</v>
       </c>
       <c r="B87" t="str">
         <v>강남대로</v>
       </c>
       <c r="C87" t="str">
-        <v>26-서초구-25</v>
+        <v>26-서초구-26</v>
       </c>
       <c r="D87" t="str">
         <v>양호</v>
@@ -5617,13 +5617,13 @@
         <v>-</v>
       </c>
       <c r="Q87" t="str">
-        <v>양재역사거리</v>
+        <v>양재동23</v>
       </c>
       <c r="R87" t="str">
         <v/>
       </c>
       <c r="S87" t="str">
-        <v>양재역 교차로(강남대로266-2)</v>
+        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
       </c>
       <c r="T87" t="str">
         <v/>
@@ -5631,13 +5631,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>26-26</v>
+        <v>26-27</v>
       </c>
       <c r="B88" t="str">
         <v>강남대로</v>
       </c>
       <c r="C88" t="str">
-        <v>26-서초구-26</v>
+        <v>26-서초구-27</v>
       </c>
       <c r="D88" t="str">
         <v>양호</v>
@@ -5679,13 +5679,13 @@
         <v>-</v>
       </c>
       <c r="Q88" t="str">
-        <v>양재동23</v>
+        <v>양재동24</v>
       </c>
       <c r="R88" t="str">
         <v/>
       </c>
       <c r="S88" t="str">
-        <v>양재역 #10번출구 앞 도로(강남대로221)</v>
+        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
       </c>
       <c r="T88" t="str">
         <v/>
@@ -5693,13 +5693,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>26-27</v>
+        <v>26-28</v>
       </c>
       <c r="B89" t="str">
         <v>강남대로</v>
       </c>
       <c r="C89" t="str">
-        <v>26-서초구-27</v>
+        <v>26-서초구-28</v>
       </c>
       <c r="D89" t="str">
         <v>양호</v>
@@ -5747,7 +5747,7 @@
         <v/>
       </c>
       <c r="S89" t="str">
-        <v>양재스포타임 커피빈 앞 도로(강남대로213)</v>
+        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
       </c>
       <c r="T89" t="str">
         <v/>
@@ -5755,13 +5755,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>26-28</v>
+        <v>26-29</v>
       </c>
       <c r="B90" t="str">
         <v>강남대로</v>
       </c>
       <c r="C90" t="str">
-        <v>26-서초구-28</v>
+        <v>26-서초구-29</v>
       </c>
       <c r="D90" t="str">
         <v>양호</v>
@@ -5803,13 +5803,13 @@
         <v>-</v>
       </c>
       <c r="Q90" t="str">
-        <v>양재동24</v>
+        <v>양재동 산20-2</v>
       </c>
       <c r="R90" t="str">
         <v/>
       </c>
       <c r="S90" t="str">
-        <v>엘타워 국민연금공단 예술회관방향 도로(강남대로213)</v>
+        <v>말죽거리공원 앞 도로(강남대로167)</v>
       </c>
       <c r="T90" t="str">
         <v/>
@@ -5817,19 +5817,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>26-29</v>
+        <v>26-30</v>
       </c>
       <c r="B91" t="str">
         <v>강남대로</v>
       </c>
       <c r="C91" t="str">
-        <v>26-서초구-29</v>
+        <v>26-서초구-30</v>
       </c>
       <c r="D91" t="str">
         <v>양호</v>
       </c>
       <c r="E91" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F91" t="str">
         <v>양호</v>
@@ -5844,7 +5844,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K91" t="str">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="N91" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O91" t="str">
         <v>일반</v>
@@ -5865,13 +5865,13 @@
         <v>-</v>
       </c>
       <c r="Q91" t="str">
-        <v>양재동 산20-2</v>
+        <v>양재동67</v>
       </c>
       <c r="R91" t="str">
         <v/>
       </c>
       <c r="S91" t="str">
-        <v>말죽거리공원 앞 도로(강남대로167)</v>
+        <v>혜인빌딩 앞 도로(163)</v>
       </c>
       <c r="T91" t="str">
         <v/>
@@ -5879,19 +5879,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>26-30</v>
+        <v>26-31</v>
       </c>
       <c r="B92" t="str">
         <v>강남대로</v>
       </c>
       <c r="C92" t="str">
-        <v>26-서초구-30</v>
+        <v>26-서초구-31</v>
       </c>
       <c r="D92" t="str">
         <v>양호</v>
       </c>
       <c r="E92" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F92" t="str">
         <v>양호</v>
@@ -5906,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K92" t="str">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O92" t="str">
         <v>일반</v>
@@ -5927,13 +5927,13 @@
         <v>-</v>
       </c>
       <c r="Q92" t="str">
-        <v>양재동67</v>
+        <v>말죽거리공원사거리</v>
       </c>
       <c r="R92" t="str">
         <v/>
       </c>
       <c r="S92" t="str">
-        <v>혜인빌딩 앞 도로(163)</v>
+        <v>말죽거리공원 교차로(양재동20-40)</v>
       </c>
       <c r="T92" t="str">
         <v/>
@@ -5941,19 +5941,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>26-31</v>
+        <v>26-32</v>
       </c>
       <c r="B93" t="str">
         <v>강남대로</v>
       </c>
       <c r="C93" t="str">
-        <v>26-서초구-31</v>
+        <v>26-서초구-32</v>
       </c>
       <c r="D93" t="str">
         <v>양호</v>
       </c>
       <c r="E93" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F93" t="str">
         <v>양호</v>
@@ -5968,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K93" t="str">
         <v>0</v>
@@ -5980,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O93" t="str">
         <v>일반</v>
@@ -5989,13 +5989,13 @@
         <v>-</v>
       </c>
       <c r="Q93" t="str">
-        <v>말죽거리공원사거리</v>
+        <v>양재동125</v>
       </c>
       <c r="R93" t="str">
         <v/>
       </c>
       <c r="S93" t="str">
-        <v>말죽거리공원 교차로(양재동20-40)</v>
+        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
       </c>
       <c r="T93" t="str">
         <v/>
@@ -6003,19 +6003,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>26-32</v>
+        <v>26-33</v>
       </c>
       <c r="B94" t="str">
         <v>강남대로</v>
       </c>
       <c r="C94" t="str">
-        <v>26-서초구-32</v>
+        <v>26-서초구-33</v>
       </c>
       <c r="D94" t="str">
         <v>양호</v>
       </c>
       <c r="E94" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F94" t="str">
         <v>양호</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K94" t="str">
         <v>0</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="N94" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O94" t="str">
         <v>일반</v>
@@ -6051,13 +6051,13 @@
         <v>-</v>
       </c>
       <c r="Q94" t="str">
-        <v>양재동125</v>
+        <v>양재동80-3</v>
       </c>
       <c r="R94" t="str">
         <v/>
       </c>
       <c r="S94" t="str">
-        <v>케이디빌딩 넥스팜코리아 앞 도로(양재천로19길36)</v>
+        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
       </c>
       <c r="T94" t="str">
         <v/>
@@ -6065,13 +6065,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>26-33</v>
+        <v>26-34</v>
       </c>
       <c r="B95" t="str">
         <v>강남대로</v>
       </c>
       <c r="C95" t="str">
-        <v>26-서초구-33</v>
+        <v>26-서초구-34</v>
       </c>
       <c r="D95" t="str">
         <v>양호</v>
@@ -6113,13 +6113,13 @@
         <v>-</v>
       </c>
       <c r="Q95" t="str">
-        <v>양재동80-3</v>
+        <v>매헌시민의숲사거리</v>
       </c>
       <c r="R95" t="str">
         <v/>
       </c>
       <c r="S95" t="str">
-        <v>동아빌딩 도야짬뽕 앞 도로(양재천로21길39)</v>
+        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
       </c>
       <c r="T95" t="str">
         <v/>
@@ -6127,13 +6127,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>26-34</v>
+        <v>26-35</v>
       </c>
       <c r="B96" t="str">
         <v>강남대로</v>
       </c>
       <c r="C96" t="str">
-        <v>26-서초구-34</v>
+        <v>26-서초구-35</v>
       </c>
       <c r="D96" t="str">
         <v>양호</v>
@@ -6175,13 +6175,13 @@
         <v>-</v>
       </c>
       <c r="Q96" t="str">
-        <v>매헌시민의숲사거리</v>
+        <v>양재동237</v>
       </c>
       <c r="R96" t="str">
         <v/>
       </c>
       <c r="S96" t="str">
-        <v>사거리 테스장 방면 도로(양재천동자전거길484)</v>
+        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
       </c>
       <c r="T96" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>26-35</v>
+        <v>26-36</v>
       </c>
       <c r="B97" t="str">
-        <v>강남대로</v>
+        <v>매헌로</v>
       </c>
       <c r="C97" t="str">
-        <v>26-서초구-35</v>
+        <v>26-서초구-36</v>
       </c>
       <c r="D97" t="str">
         <v>양호</v>
@@ -6237,13 +6237,13 @@
         <v>-</v>
       </c>
       <c r="Q97" t="str">
-        <v>양재동237</v>
+        <v>양재동237-2</v>
       </c>
       <c r="R97" t="str">
         <v/>
       </c>
       <c r="S97" t="str">
-        <v>매헌시민의숲 동측 공영주차장 전기충전소 앞 도로</v>
+        <v>매헌역 공영주차장 입구 앞 도로</v>
       </c>
       <c r="T97" t="str">
         <v/>
@@ -6251,13 +6251,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>26-36</v>
+        <v>26-37</v>
       </c>
       <c r="B98" t="str">
-        <v>매헌로</v>
+        <v>청계산로</v>
       </c>
       <c r="C98" t="str">
-        <v>26-서초구-36</v>
+        <v>26-서초구-37</v>
       </c>
       <c r="D98" t="str">
         <v>양호</v>
@@ -6299,13 +6299,13 @@
         <v>-</v>
       </c>
       <c r="Q98" t="str">
-        <v>양재동237-2</v>
+        <v>신원동308-1</v>
       </c>
       <c r="R98" t="str">
         <v/>
       </c>
       <c r="S98" t="str">
-        <v>매헌역 공영주차장 입구 앞 도로</v>
+        <v>가로등(청계산로69)_양차선</v>
       </c>
       <c r="T98" t="str">
         <v/>
@@ -6313,13 +6313,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>26-37</v>
+        <v>26-38</v>
       </c>
       <c r="B99" t="str">
         <v>청계산로</v>
       </c>
       <c r="C99" t="str">
-        <v>26-서초구-37</v>
+        <v>26-서초구-38</v>
       </c>
       <c r="D99" t="str">
         <v>양호</v>
@@ -6361,13 +6361,13 @@
         <v>-</v>
       </c>
       <c r="Q99" t="str">
-        <v>신원동308-1</v>
+        <v>신원동298-16</v>
       </c>
       <c r="R99" t="str">
         <v/>
       </c>
       <c r="S99" t="str">
-        <v>가로등(청계산로69)_양차선</v>
+        <v>청계산 수변공원 앞 도로_양차선</v>
       </c>
       <c r="T99" t="str">
         <v/>
@@ -6375,13 +6375,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>26-38</v>
+        <v>26-39</v>
       </c>
       <c r="B100" t="str">
         <v>청계산로</v>
       </c>
       <c r="C100" t="str">
-        <v>26-서초구-38</v>
+        <v>26-서초구-39</v>
       </c>
       <c r="D100" t="str">
         <v>양호</v>
@@ -6429,7 +6429,7 @@
         <v/>
       </c>
       <c r="S100" t="str">
-        <v>청계산 수변공원 앞 도로_양차선</v>
+        <v>가로등(청계산로81)앞도로_양차선</v>
       </c>
       <c r="T100" t="str">
         <v/>
@@ -6437,13 +6437,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>26-39</v>
+        <v>26-40</v>
       </c>
       <c r="B101" t="str">
         <v>청계산로</v>
       </c>
       <c r="C101" t="str">
-        <v>26-서초구-39</v>
+        <v>26-서초구-40</v>
       </c>
       <c r="D101" t="str">
         <v>양호</v>
@@ -6482,16 +6482,16 @@
         <v>일반</v>
       </c>
       <c r="P101" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q101" t="str">
-        <v>신원동298-16</v>
+        <v>원지동595</v>
       </c>
       <c r="R101" t="str">
         <v/>
       </c>
       <c r="S101" t="str">
-        <v>가로등(청계산로81)앞도로_양차선</v>
+        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
       </c>
       <c r="T101" t="str">
         <v/>
@@ -6499,13 +6499,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>26-40</v>
+        <v>26-41</v>
       </c>
       <c r="B102" t="str">
         <v>청계산로</v>
       </c>
       <c r="C102" t="str">
-        <v>26-서초구-40</v>
+        <v>26-서초구-41</v>
       </c>
       <c r="D102" t="str">
         <v>양호</v>
@@ -6544,16 +6544,16 @@
         <v>일반</v>
       </c>
       <c r="P102" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q102" t="str">
-        <v>원지동595</v>
+        <v>신원동280-1</v>
       </c>
       <c r="R102" t="str">
         <v/>
       </c>
       <c r="S102" t="str">
-        <v>교통간판 앞 도로(맨홀뚜껑주변)</v>
+        <v>교차로(T)_양차선</v>
       </c>
       <c r="T102" t="str">
         <v/>
@@ -6561,13 +6561,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>26-41</v>
+        <v>26-42</v>
       </c>
       <c r="B103" t="str">
         <v>청계산로</v>
       </c>
       <c r="C103" t="str">
-        <v>26-서초구-41</v>
+        <v>26-서초구-42</v>
       </c>
       <c r="D103" t="str">
         <v>양호</v>
@@ -6609,13 +6609,13 @@
         <v>-</v>
       </c>
       <c r="Q103" t="str">
-        <v>신원동280-1</v>
+        <v>신원동278-6</v>
       </c>
       <c r="R103" t="str">
         <v/>
       </c>
       <c r="S103" t="str">
-        <v>교차로(T)_양차선</v>
+        <v>버스정류장 앞 양차선</v>
       </c>
       <c r="T103" t="str">
         <v/>
@@ -6623,13 +6623,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>26-42</v>
+        <v>26-43</v>
       </c>
       <c r="B104" t="str">
         <v>청계산로</v>
       </c>
       <c r="C104" t="str">
-        <v>26-서초구-42</v>
+        <v>26-서초구-43</v>
       </c>
       <c r="D104" t="str">
         <v>양호</v>
@@ -6668,16 +6668,16 @@
         <v>일반</v>
       </c>
       <c r="P104" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q104" t="str">
-        <v>신원동278-6</v>
+        <v>신원동604</v>
       </c>
       <c r="R104" t="str">
         <v/>
       </c>
       <c r="S104" t="str">
-        <v>버스정류장 앞 양차선</v>
+        <v>오라카이 호텔 맞음편 도로 우수,전기맨홀(청계산로9길1-7)</v>
       </c>
       <c r="T104" t="str">
         <v/>
@@ -6685,13 +6685,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>26-43</v>
+        <v>26-44</v>
       </c>
       <c r="B105" t="str">
         <v>청계산로</v>
       </c>
       <c r="C105" t="str">
-        <v>26-서초구-43</v>
+        <v>26-서초구-44</v>
       </c>
       <c r="D105" t="str">
         <v>양호</v>
@@ -6730,16 +6730,16 @@
         <v>일반</v>
       </c>
       <c r="P105" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q105" t="str">
-        <v>신원동604</v>
+        <v>신원동607</v>
       </c>
       <c r="R105" t="str">
         <v/>
       </c>
       <c r="S105" t="str">
-        <v>오라카이 호텔 맞음편 도로 우수,전기맨홀(청계산로9길1-7)</v>
+        <v>내곡드림시티2 펀비어킹 앞 도로(청계산로189)</v>
       </c>
       <c r="T105" t="str">
         <v/>
@@ -6747,13 +6747,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>26-44</v>
+        <v>26-45</v>
       </c>
       <c r="B106" t="str">
         <v>청계산로</v>
       </c>
       <c r="C106" t="str">
-        <v>26-서초구-44</v>
+        <v>26-서초구-45</v>
       </c>
       <c r="D106" t="str">
         <v>양호</v>
@@ -6795,13 +6795,13 @@
         <v>-</v>
       </c>
       <c r="Q106" t="str">
-        <v>신원동607</v>
+        <v>신원동609</v>
       </c>
       <c r="R106" t="str">
         <v/>
       </c>
       <c r="S106" t="str">
-        <v>내곡드림시티2 펀비어킹 앞 도로(청계산로189)</v>
+        <v>내곡프라임시티 앞도로(청계산로195)</v>
       </c>
       <c r="T106" t="str">
         <v/>
@@ -6809,13 +6809,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>26-45</v>
+        <v>26-46</v>
       </c>
       <c r="B107" t="str">
         <v>청계산로</v>
       </c>
       <c r="C107" t="str">
-        <v>26-서초구-45</v>
+        <v>26-서초구-46</v>
       </c>
       <c r="D107" t="str">
         <v>양호</v>
@@ -6857,13 +6857,13 @@
         <v>-</v>
       </c>
       <c r="Q107" t="str">
-        <v>신원동609</v>
+        <v>신원동611</v>
       </c>
       <c r="R107" t="str">
         <v/>
       </c>
       <c r="S107" t="str">
-        <v>내곡프라임시티 앞도로(청계산로195)</v>
+        <v>서초포레지움 투썸플레이스 앞 양차선(청계산로201)</v>
       </c>
       <c r="T107" t="str">
         <v/>
@@ -6871,13 +6871,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>26-46</v>
+        <v>26-47</v>
       </c>
       <c r="B108" t="str">
         <v>청계산로</v>
       </c>
       <c r="C108" t="str">
-        <v>26-서초구-46</v>
+        <v>26-서초구-47</v>
       </c>
       <c r="D108" t="str">
         <v>양호</v>
@@ -6916,16 +6916,16 @@
         <v>일반</v>
       </c>
       <c r="P108" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q108" t="str">
-        <v>신원동611</v>
+        <v>원지동362-1</v>
       </c>
       <c r="R108" t="str">
         <v/>
       </c>
       <c r="S108" t="str">
-        <v>서초포레지움 투썸플레이스 앞 양차선(청계산로201)</v>
+        <v>청계쉼터 앞 도로</v>
       </c>
       <c r="T108" t="str">
         <v/>
@@ -6933,13 +6933,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>26-47</v>
+        <v>26-48</v>
       </c>
       <c r="B109" t="str">
         <v>청계산로</v>
       </c>
       <c r="C109" t="str">
-        <v>26-서초구-47</v>
+        <v>26-서초구-48</v>
       </c>
       <c r="D109" t="str">
         <v>양호</v>
@@ -6978,16 +6978,16 @@
         <v>일반</v>
       </c>
       <c r="P109" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q109" t="str">
-        <v>원지동362-1</v>
+        <v>원지동384-1</v>
       </c>
       <c r="R109" t="str">
         <v/>
       </c>
       <c r="S109" t="str">
-        <v>청계쉼터 앞 도로</v>
+        <v>청계산커피 앞 양차선</v>
       </c>
       <c r="T109" t="str">
         <v/>
@@ -6995,13 +6995,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>26-48</v>
+        <v>26-49</v>
       </c>
       <c r="B110" t="str">
         <v>청계산로</v>
       </c>
       <c r="C110" t="str">
-        <v>26-서초구-48</v>
+        <v>26-서초구-49</v>
       </c>
       <c r="D110" t="str">
         <v>양호</v>
@@ -7043,13 +7043,13 @@
         <v>-</v>
       </c>
       <c r="Q110" t="str">
-        <v>원지동384-1</v>
+        <v>신원동192-75</v>
       </c>
       <c r="R110" t="str">
         <v/>
       </c>
       <c r="S110" t="str">
-        <v>청계산커피 앞 양차선</v>
+        <v>강경불고기_청계 앞 양차선(청계산로245)</v>
       </c>
       <c r="T110" t="str">
         <v/>
@@ -7057,13 +7057,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>26-49</v>
+        <v>26-50</v>
       </c>
       <c r="B111" t="str">
         <v>청계산로</v>
       </c>
       <c r="C111" t="str">
-        <v>26-서초구-49</v>
+        <v>26-서초구-50</v>
       </c>
       <c r="D111" t="str">
         <v>양호</v>
@@ -7102,16 +7102,16 @@
         <v>일반</v>
       </c>
       <c r="P111" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q111" t="str">
-        <v>신원동192-75</v>
+        <v>신원동173-1</v>
       </c>
       <c r="R111" t="str">
         <v/>
       </c>
       <c r="S111" t="str">
-        <v>강경불고기_청계 앞 양차선(청계산로245)</v>
+        <v>향린조경 앞 양차선(고속도로방면침하)</v>
       </c>
       <c r="T111" t="str">
         <v/>
@@ -7119,13 +7119,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>26-50</v>
+        <v>26-51</v>
       </c>
       <c r="B112" t="str">
         <v>청계산로</v>
       </c>
       <c r="C112" t="str">
-        <v>26-서초구-50</v>
+        <v>26-서초구-51</v>
       </c>
       <c r="D112" t="str">
         <v>양호</v>
@@ -7167,13 +7167,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q112" t="str">
-        <v>신원동173-1</v>
+        <v>신원동152-12</v>
       </c>
       <c r="R112" t="str">
         <v/>
       </c>
       <c r="S112" t="str">
-        <v>향린조경 앞 양차선(고속도로방면침하)</v>
+        <v>삼석원 앞 양차선(고속도로방면 침하)</v>
       </c>
       <c r="T112" t="str">
         <v/>
@@ -7181,13 +7181,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>26-51</v>
+        <v>26-52</v>
       </c>
       <c r="B113" t="str">
         <v>청계산로</v>
       </c>
       <c r="C113" t="str">
-        <v>26-서초구-51</v>
+        <v>26-서초구-52</v>
       </c>
       <c r="D113" t="str">
         <v>양호</v>
@@ -7229,13 +7229,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q113" t="str">
-        <v>신원동152-12</v>
+        <v>신원동148-3</v>
       </c>
       <c r="R113" t="str">
         <v/>
       </c>
       <c r="S113" t="str">
-        <v>삼석원 앞 양차선(고속도로방면 침하)</v>
+        <v>은평조경 앞 양차선(고속도로방면 침하)(청계산로283-8)</v>
       </c>
       <c r="T113" t="str">
         <v/>
@@ -7243,13 +7243,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>26-52</v>
+        <v>26-53</v>
       </c>
       <c r="B114" t="str">
         <v>청계산로</v>
       </c>
       <c r="C114" t="str">
-        <v>26-서초구-52</v>
+        <v>26-서초구-53</v>
       </c>
       <c r="D114" t="str">
         <v>양호</v>
@@ -7291,13 +7291,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q114" t="str">
-        <v>신원동148-3</v>
+        <v>원지동490-3</v>
       </c>
       <c r="R114" t="str">
         <v/>
       </c>
       <c r="S114" t="str">
-        <v>은평조경 앞 양차선(고속도로방면 침하)(청계산로283-8)</v>
+        <v>인화원 앞 양차선(고속도로방면 침하)(가로등_청계산로161)</v>
       </c>
       <c r="T114" t="str">
         <v/>
@@ -7305,13 +7305,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>26-53</v>
+        <v>26-54</v>
       </c>
       <c r="B115" t="str">
         <v>청계산로</v>
       </c>
       <c r="C115" t="str">
-        <v>26-서초구-53</v>
+        <v>26-서초구-54</v>
       </c>
       <c r="D115" t="str">
         <v>양호</v>
@@ -7353,13 +7353,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q115" t="str">
-        <v>원지동490-3</v>
+        <v>원지동490</v>
       </c>
       <c r="R115" t="str">
         <v/>
       </c>
       <c r="S115" t="str">
-        <v>인화원 앞 양차선(고속도로방면 침하)(가로등_청계산로161)</v>
+        <v>양재조경 앞 양차선(고속도로방면 침하)_(가로등_청계산로165)</v>
       </c>
       <c r="T115" t="str">
         <v/>
@@ -7367,13 +7367,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>26-54</v>
+        <v>26-55</v>
       </c>
       <c r="B116" t="str">
         <v>청계산로</v>
       </c>
       <c r="C116" t="str">
-        <v>26-서초구-54</v>
+        <v>26-서초구-55</v>
       </c>
       <c r="D116" t="str">
         <v>양호</v>
@@ -7415,13 +7415,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q116" t="str">
-        <v>원지동490</v>
+        <v>원지동495-5</v>
       </c>
       <c r="R116" t="str">
         <v/>
       </c>
       <c r="S116" t="str">
-        <v>양재조경 앞 양차선(고속도로방면 침하)_(가로등_청계산로165)</v>
+        <v>화림조경간판 앞 양차선(가로등_청계산로167)</v>
       </c>
       <c r="T116" t="str">
         <v/>
@@ -7429,13 +7429,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>26-55</v>
+        <v>26-56</v>
       </c>
       <c r="B117" t="str">
         <v>청계산로</v>
       </c>
       <c r="C117" t="str">
-        <v>26-서초구-55</v>
+        <v>26-서초구-56</v>
       </c>
       <c r="D117" t="str">
         <v>양호</v>
@@ -7474,16 +7474,16 @@
         <v>일반</v>
       </c>
       <c r="P117" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q117" t="str">
-        <v>원지동495-5</v>
+        <v>원지동495-6</v>
       </c>
       <c r="R117" t="str">
         <v/>
       </c>
       <c r="S117" t="str">
-        <v>화림조경간판 앞 양차선(가로등_청계산로167)</v>
+        <v>(가로등_청계산로171)</v>
       </c>
       <c r="T117" t="str">
         <v/>
@@ -7491,19 +7491,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>26-56</v>
+        <v>26-57</v>
       </c>
       <c r="B118" t="str">
         <v>청계산로</v>
       </c>
       <c r="C118" t="str">
-        <v>26-서초구-56</v>
+        <v>26-서초구-57</v>
       </c>
       <c r="D118" t="str">
         <v>양호</v>
       </c>
       <c r="E118" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F118" t="str">
         <v>양호</v>
@@ -7518,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="J118" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K118" t="str">
         <v>0</v>
@@ -7530,7 +7530,7 @@
         <v>0</v>
       </c>
       <c r="N118" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O118" t="str">
         <v>일반</v>
@@ -7539,13 +7539,13 @@
         <v>-</v>
       </c>
       <c r="Q118" t="str">
-        <v>원지동495-6</v>
+        <v>원지동497-3</v>
       </c>
       <c r="R118" t="str">
         <v/>
       </c>
       <c r="S118" t="str">
-        <v>(가로등_청계산로171)</v>
+        <v>(가로등_청계산로313)</v>
       </c>
       <c r="T118" t="str">
         <v/>
@@ -7553,19 +7553,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>26-57</v>
+        <v>26-58</v>
       </c>
       <c r="B119" t="str">
         <v>청계산로</v>
       </c>
       <c r="C119" t="str">
-        <v>26-서초구-57</v>
+        <v>26-서초구-58</v>
       </c>
       <c r="D119" t="str">
         <v>양호</v>
       </c>
       <c r="E119" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F119" t="str">
         <v>양호</v>
@@ -7580,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K119" t="str">
         <v>0</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="N119" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O119" t="str">
         <v>일반</v>
@@ -7601,13 +7601,13 @@
         <v>-</v>
       </c>
       <c r="Q119" t="str">
-        <v>원지동497-3</v>
+        <v>원지동575-1</v>
       </c>
       <c r="R119" t="str">
         <v/>
       </c>
       <c r="S119" t="str">
-        <v>(가로등_청계산로313)</v>
+        <v>(가로등_청계산로321)</v>
       </c>
       <c r="T119" t="str">
         <v/>
@@ -7615,19 +7615,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>26-58</v>
+        <v>26-59</v>
       </c>
       <c r="B120" t="str">
         <v>청계산로</v>
       </c>
       <c r="C120" t="str">
-        <v>26-서초구-58</v>
+        <v>26-서초구-59</v>
       </c>
       <c r="D120" t="str">
         <v>양호</v>
       </c>
       <c r="E120" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F120" t="str">
         <v>양호</v>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K120" t="str">
         <v>0</v>
@@ -7654,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="N120" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O120" t="str">
         <v>일반</v>
@@ -7663,13 +7663,13 @@
         <v>-</v>
       </c>
       <c r="Q120" t="str">
-        <v>원지동575-1</v>
+        <v>원지동523-2</v>
       </c>
       <c r="R120" t="str">
         <v/>
       </c>
       <c r="S120" t="str">
-        <v>(가로등_청계산로321)</v>
+        <v>둥지조경 앞 도로(가로등_청계산로329)</v>
       </c>
       <c r="T120" t="str">
         <v/>
@@ -7677,19 +7677,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>26-59</v>
+        <v>26-60</v>
       </c>
       <c r="B121" t="str">
         <v>청계산로</v>
       </c>
       <c r="C121" t="str">
-        <v>26-서초구-59</v>
+        <v>26-서초구-60</v>
       </c>
       <c r="D121" t="str">
         <v>양호</v>
       </c>
       <c r="E121" t="str">
-        <v>종균열</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F121" t="str">
         <v>양호</v>
@@ -7725,13 +7725,13 @@
         <v>-</v>
       </c>
       <c r="Q121" t="str">
-        <v>원지동523-2</v>
+        <v>신원동산60-2</v>
       </c>
       <c r="R121" t="str">
         <v/>
       </c>
       <c r="S121" t="str">
-        <v>둥지조경 앞 도로(가로등_청계산로329)</v>
+        <v>대원조경 앞 양차선(가로등_청계산로181)</v>
       </c>
       <c r="T121" t="str">
         <v/>
@@ -7739,19 +7739,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>26-60</v>
+        <v>26-61</v>
       </c>
       <c r="B122" t="str">
         <v>청계산로</v>
       </c>
       <c r="C122" t="str">
-        <v>26-서초구-60</v>
+        <v>26-서초구-61</v>
       </c>
       <c r="D122" t="str">
         <v>양호</v>
       </c>
       <c r="E122" t="str">
-        <v>종,횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F122" t="str">
         <v>양호</v>
@@ -7766,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="J122" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K122" t="str">
         <v>0</v>
@@ -7778,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="N122" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O122" t="str">
         <v>일반</v>
@@ -7787,13 +7787,13 @@
         <v>-</v>
       </c>
       <c r="Q122" t="str">
-        <v>신원동산60-2</v>
+        <v>신원동103</v>
       </c>
       <c r="R122" t="str">
         <v/>
       </c>
       <c r="S122" t="str">
-        <v>대원조경 앞 양차선(가로등_청계산로181)</v>
+        <v>둥지조경제2농장 앞 양차선(고속도로방면 침하)</v>
       </c>
       <c r="T122" t="str">
         <v/>
@@ -7801,13 +7801,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>26-61</v>
+        <v>26-62</v>
       </c>
       <c r="B123" t="str">
         <v>청계산로</v>
       </c>
       <c r="C123" t="str">
-        <v>26-서초구-61</v>
+        <v>26-서초구-62</v>
       </c>
       <c r="D123" t="str">
         <v>양호</v>
@@ -7849,13 +7849,13 @@
         <v>-</v>
       </c>
       <c r="Q123" t="str">
-        <v>신원동103</v>
+        <v>신원동105-33</v>
       </c>
       <c r="R123" t="str">
         <v/>
       </c>
       <c r="S123" t="str">
-        <v>둥지조경제2농장 앞 양차선(고속도로방면 침하)</v>
+        <v>한백자생식물원 앞 양차선(청계산로353)</v>
       </c>
       <c r="T123" t="str">
         <v/>
@@ -7863,13 +7863,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>26-62</v>
+        <v>26-63</v>
       </c>
       <c r="B124" t="str">
         <v>청계산로</v>
       </c>
       <c r="C124" t="str">
-        <v>26-서초구-62</v>
+        <v>26-서초구-63</v>
       </c>
       <c r="D124" t="str">
         <v>양호</v>
@@ -7908,16 +7908,16 @@
         <v>일반</v>
       </c>
       <c r="P124" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q124" t="str">
-        <v>신원동105-33</v>
+        <v>신원동98-3</v>
       </c>
       <c r="R124" t="str">
         <v/>
       </c>
       <c r="S124" t="str">
-        <v>한백자생식물원 앞 양차선(청계산로353)</v>
+        <v>양차선(가로둥_청계산로193)</v>
       </c>
       <c r="T124" t="str">
         <v/>
@@ -7925,13 +7925,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>26-63</v>
+        <v>26-64</v>
       </c>
       <c r="B125" t="str">
         <v>청계산로</v>
       </c>
       <c r="C125" t="str">
-        <v>26-서초구-63</v>
+        <v>26-서초구-64</v>
       </c>
       <c r="D125" t="str">
         <v>양호</v>
@@ -7973,13 +7973,13 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q125" t="str">
-        <v>신원동98-3</v>
+        <v>신원동44-1</v>
       </c>
       <c r="R125" t="str">
         <v/>
       </c>
       <c r="S125" t="str">
-        <v>양차선(가로둥_청계산로193)</v>
+        <v>새정이마을입구 앞 양차선</v>
       </c>
       <c r="T125" t="str">
         <v/>
@@ -7987,13 +7987,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>26-64</v>
+        <v>26-65</v>
       </c>
       <c r="B126" t="str">
         <v>청계산로</v>
       </c>
       <c r="C126" t="str">
-        <v>26-서초구-64</v>
+        <v>26-서초구-65</v>
       </c>
       <c r="D126" t="str">
         <v>양호</v>
@@ -8032,16 +8032,16 @@
         <v>일반</v>
       </c>
       <c r="P126" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q126" t="str">
-        <v>신원동44-1</v>
+        <v>신원동44-5</v>
       </c>
       <c r="R126" t="str">
         <v/>
       </c>
       <c r="S126" t="str">
-        <v>새정이마을입구 앞 양차선</v>
+        <v>강남꽃직매장 앞 도로(청계산로377)</v>
       </c>
       <c r="T126" t="str">
         <v/>
@@ -8049,13 +8049,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>26-65</v>
+        <v>26-66</v>
       </c>
       <c r="B127" t="str">
         <v>청계산로</v>
       </c>
       <c r="C127" t="str">
-        <v>26-서초구-65</v>
+        <v>26-서초구-66</v>
       </c>
       <c r="D127" t="str">
         <v>양호</v>
@@ -8097,13 +8097,13 @@
         <v>-</v>
       </c>
       <c r="Q127" t="str">
-        <v>신원동44-5</v>
+        <v>신원동44-6</v>
       </c>
       <c r="R127" t="str">
         <v/>
       </c>
       <c r="S127" t="str">
-        <v>강남꽃직매장 앞 도로(청계산로377)</v>
+        <v>들꽃 입구 앞 도로</v>
       </c>
       <c r="T127" t="str">
         <v/>
@@ -8111,13 +8111,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>26-66</v>
+        <v>26-67</v>
       </c>
       <c r="B128" t="str">
         <v>청계산로</v>
       </c>
       <c r="C128" t="str">
-        <v>26-서초구-66</v>
+        <v>26-서초구-67</v>
       </c>
       <c r="D128" t="str">
         <v>양호</v>
@@ -8156,16 +8156,16 @@
         <v>일반</v>
       </c>
       <c r="P128" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q128" t="str">
-        <v>신원동44-6</v>
+        <v>신원동44-32</v>
       </c>
       <c r="R128" t="str">
         <v/>
       </c>
       <c r="S128" t="str">
-        <v>들꽃 입구 앞 도로</v>
+        <v>입구 앞 도로(가로등_청계산로385)</v>
       </c>
       <c r="T128" t="str">
         <v/>
@@ -8173,13 +8173,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>26-67</v>
+        <v>26-68</v>
       </c>
       <c r="B129" t="str">
         <v>청계산로</v>
       </c>
       <c r="C129" t="str">
-        <v>26-서초구-67</v>
+        <v>26-서초구-68</v>
       </c>
       <c r="D129" t="str">
         <v>양호</v>
@@ -8218,16 +8218,16 @@
         <v>일반</v>
       </c>
       <c r="P129" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q129" t="str">
-        <v>신원동44-32</v>
+        <v>신원동46-3</v>
       </c>
       <c r="R129" t="str">
         <v/>
       </c>
       <c r="S129" t="str">
-        <v>입구 앞 도로(가로등_청계산로385)</v>
+        <v>은하조경 앞 양차선</v>
       </c>
       <c r="T129" t="str">
         <v/>
@@ -8235,13 +8235,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>26-68</v>
+        <v>26-69</v>
       </c>
       <c r="B130" t="str">
         <v>청계산로</v>
       </c>
       <c r="C130" t="str">
-        <v>26-서초구-68</v>
+        <v>26-서초구-69</v>
       </c>
       <c r="D130" t="str">
         <v>양호</v>
@@ -8283,13 +8283,13 @@
         <v>-</v>
       </c>
       <c r="Q130" t="str">
-        <v>신원동46-3</v>
+        <v>신원동57</v>
       </c>
       <c r="R130" t="str">
         <v/>
       </c>
       <c r="S130" t="str">
-        <v>은하조경 앞 양차선</v>
+        <v>서광원예종묘 앞 양차선(청계산로397)</v>
       </c>
       <c r="T130" t="str">
         <v/>
@@ -8297,13 +8297,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>26-69</v>
+        <v>26-70</v>
       </c>
       <c r="B131" t="str">
         <v>청계산로</v>
       </c>
       <c r="C131" t="str">
-        <v>26-서초구-69</v>
+        <v>26-서초구-70</v>
       </c>
       <c r="D131" t="str">
         <v>양호</v>
@@ -8345,13 +8345,13 @@
         <v>-</v>
       </c>
       <c r="Q131" t="str">
-        <v>신원동57</v>
+        <v>신원동64-1</v>
       </c>
       <c r="R131" t="str">
         <v/>
       </c>
       <c r="S131" t="str">
-        <v>서광원예종묘 앞 양차선(청계산로397)</v>
+        <v>옥천조경 앞 양차선(청계산로405)</v>
       </c>
       <c r="T131" t="str">
         <v/>
@@ -8359,13 +8359,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>26-70</v>
+        <v>26-71</v>
       </c>
       <c r="B132" t="str">
         <v>청계산로</v>
       </c>
       <c r="C132" t="str">
-        <v>26-서초구-70</v>
+        <v>26-서초구-71</v>
       </c>
       <c r="D132" t="str">
         <v>양호</v>
@@ -8407,83 +8407,21 @@
         <v>-</v>
       </c>
       <c r="Q132" t="str">
-        <v>신원동64-1</v>
+        <v>신원동67-1</v>
       </c>
       <c r="R132" t="str">
         <v/>
       </c>
       <c r="S132" t="str">
-        <v>옥천조경 앞 양차선(청계산로405)</v>
+        <v>마당조경 앞 양찬선</v>
       </c>
       <c r="T132" t="str">
-        <v>현장확인필요</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>26-71</v>
-      </c>
-      <c r="B133" t="str">
-        <v>청계산로</v>
-      </c>
-      <c r="C133" t="str">
-        <v>26-서초구-71</v>
-      </c>
-      <c r="D133" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E133" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F133" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G133" t="str">
-        <v>14.5</v>
-      </c>
-      <c r="H133" t="str">
-        <v>-</v>
-      </c>
-      <c r="I133" t="str">
-        <v>0</v>
-      </c>
-      <c r="J133" t="str">
-        <v>3</v>
-      </c>
-      <c r="K133" t="str">
-        <v>0</v>
-      </c>
-      <c r="L133" t="str">
-        <v>1</v>
-      </c>
-      <c r="M133" t="str">
-        <v>0</v>
-      </c>
-      <c r="N133" t="str">
-        <v>4</v>
-      </c>
-      <c r="O133" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P133" t="str">
-        <v>-</v>
-      </c>
-      <c r="Q133" t="str">
-        <v>신원동67-1</v>
-      </c>
-      <c r="R133" t="str">
-        <v/>
-      </c>
-      <c r="S133" t="str">
-        <v>마당조경 앞 양찬선</v>
-      </c>
-      <c r="T133" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T132"/>
   </ignoredErrors>
 </worksheet>
 </file>